--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -18958,7 +18958,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>110515817</v>
+        <v>110515862</v>
       </c>
       <c r="B162" t="n">
         <v>57963</v>
@@ -18996,21 +18996,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr"/>
       <c r="M162" t="inlineStr">
         <is>
           <t>spel/sång</t>
         </is>
       </c>
+      <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
           <t>Per Geijerområdet, T lm</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>723754</v>
+        <v>723241</v>
       </c>
       <c r="R162" t="n">
-        <v>7544439</v>
+        <v>7544321</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -19062,14 +19065,14 @@
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Mats Williamson, Nils Ericson, Jan Henriksson, Billy Lindblom, Elias Rankka</t>
+          <t>Nils Ericson, Jan Henriksson, Billy Lindblom, Elias Rankka</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>110515750</v>
+        <v>110515876</v>
       </c>
       <c r="B163" t="n">
         <v>57963</v>
@@ -19107,24 +19110,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
-      <c r="L163" t="inlineStr"/>
       <c r="M163" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N163" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P163" t="inlineStr">
         <is>
           <t>Per Geijerområdet, T lm</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>723784</v>
+        <v>723039</v>
       </c>
       <c r="R163" t="n">
-        <v>7544650</v>
+        <v>7544294</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -19176,14 +19176,14 @@
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Nils Ericson, Jan Henriksson, Billy Lindblom, Elias Rankka</t>
+          <t>Mats Williamson, Nils Ericson, Jan Henriksson, Billy Lindblom, Elias Rankka</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>110515013</v>
+        <v>110515738</v>
       </c>
       <c r="B164" t="n">
         <v>57963</v>
@@ -19218,27 +19218,24 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K164" t="inlineStr"/>
-      <c r="L164" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M164" t="inlineStr">
         <is>
           <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
-      <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
           <t>Per Geijerområdet, T lm</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>722974</v>
+        <v>723431</v>
       </c>
       <c r="R164" t="n">
-        <v>7543813</v>
+        <v>7544751</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -19290,17 +19287,17 @@
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Nils Ericson, Jan Henriksson, Billy Lindblom, Elias Rankka</t>
+          <t>Mats Williamson, Nils Ericson, Jan Henriksson, Billy Lindblom, Elias Rankka</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>110514995</v>
+        <v>110515651</v>
       </c>
       <c r="B165" t="n">
-        <v>57963</v>
+        <v>57656</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -19313,16 +19310,16 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -19335,24 +19332,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
-      <c r="L165" t="inlineStr"/>
       <c r="M165" t="inlineStr">
         <is>
           <t>spel/sång</t>
         </is>
       </c>
-      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Per Geijerområdet, T lm</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>722886</v>
+        <v>723258</v>
       </c>
       <c r="R165" t="n">
-        <v>7543829</v>
+        <v>7545337</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -19404,14 +19398,14 @@
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Nils Ericson, Jan Henriksson, Billy Lindblom, Elias Rankka</t>
+          <t>Mats Williamson, Nils Ericson, Jan Henriksson, Billy Lindblom, Elias Rankka</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>110515768</v>
+        <v>110515013</v>
       </c>
       <c r="B166" t="n">
         <v>57963</v>
@@ -19446,7 +19440,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K166" t="inlineStr"/>
@@ -19463,10 +19457,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>723376</v>
+        <v>722974</v>
       </c>
       <c r="R166" t="n">
-        <v>7544604</v>
+        <v>7543813</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -19525,10 +19519,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>110515651</v>
+        <v>110515879</v>
       </c>
       <c r="B167" t="n">
-        <v>57656</v>
+        <v>57963</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -19541,16 +19535,16 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -19565,7 +19559,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P167" t="inlineStr">
@@ -19574,10 +19568,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>723258</v>
+        <v>723098</v>
       </c>
       <c r="R167" t="n">
-        <v>7545337</v>
+        <v>7544238</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19636,7 +19630,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>110515756</v>
+        <v>110514995</v>
       </c>
       <c r="B168" t="n">
         <v>57963</v>
@@ -19671,14 +19665,14 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K168" t="inlineStr"/>
       <c r="L168" t="inlineStr"/>
       <c r="M168" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N168" t="inlineStr"/>
@@ -19688,10 +19682,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>723307</v>
+        <v>722886</v>
       </c>
       <c r="R168" t="n">
-        <v>7544635</v>
+        <v>7543829</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19750,7 +19744,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>110515876</v>
+        <v>110514959</v>
       </c>
       <c r="B169" t="n">
         <v>57963</v>
@@ -19785,12 +19779,12 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P169" t="inlineStr">
@@ -19799,10 +19793,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>723039</v>
+        <v>722904</v>
       </c>
       <c r="R169" t="n">
-        <v>7544294</v>
+        <v>7543903</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19861,10 +19855,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>110514959</v>
+        <v>110514972</v>
       </c>
       <c r="B170" t="n">
-        <v>57963</v>
+        <v>57656</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -19877,16 +19871,16 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -19896,12 +19890,12 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P170" t="inlineStr">
@@ -19910,10 +19904,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>722904</v>
+        <v>722669</v>
       </c>
       <c r="R170" t="n">
-        <v>7543903</v>
+        <v>7543877</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19972,7 +19966,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>110515679</v>
+        <v>110515817</v>
       </c>
       <c r="B171" t="n">
         <v>57963</v>
@@ -20012,7 +20006,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P171" t="inlineStr">
@@ -20021,10 +20015,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>723479</v>
+        <v>723754</v>
       </c>
       <c r="R171" t="n">
-        <v>7545157</v>
+        <v>7544439</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -20083,7 +20077,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>110515862</v>
+        <v>110515768</v>
       </c>
       <c r="B172" t="n">
         <v>57963</v>
@@ -20125,7 +20119,7 @@
       <c r="L172" t="inlineStr"/>
       <c r="M172" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N172" t="inlineStr"/>
@@ -20135,10 +20129,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>723241</v>
+        <v>723376</v>
       </c>
       <c r="R172" t="n">
-        <v>7544321</v>
+        <v>7544604</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -20197,7 +20191,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>110515879</v>
+        <v>110515679</v>
       </c>
       <c r="B173" t="n">
         <v>57963</v>
@@ -20246,10 +20240,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>723098</v>
+        <v>723479</v>
       </c>
       <c r="R173" t="n">
-        <v>7544238</v>
+        <v>7545157</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -20308,10 +20302,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>110514972</v>
+        <v>110515756</v>
       </c>
       <c r="B174" t="n">
-        <v>57656</v>
+        <v>57963</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -20324,16 +20318,16 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -20343,24 +20337,27 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr"/>
       <c r="M174" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
           <t>Per Geijerområdet, T lm</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>722669</v>
+        <v>723307</v>
       </c>
       <c r="R174" t="n">
-        <v>7543877</v>
+        <v>7544635</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -20412,14 +20409,14 @@
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Mats Williamson, Nils Ericson, Jan Henriksson, Billy Lindblom, Elias Rankka</t>
+          <t>Nils Ericson, Jan Henriksson, Billy Lindblom, Elias Rankka</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>110515738</v>
+        <v>110515750</v>
       </c>
       <c r="B175" t="n">
         <v>57963</v>
@@ -20457,21 +20454,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K175" t="inlineStr"/>
+      <c r="L175" t="inlineStr"/>
       <c r="M175" t="inlineStr">
         <is>
           <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
+      <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
           <t>Per Geijerområdet, T lm</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>723431</v>
+        <v>723784</v>
       </c>
       <c r="R175" t="n">
-        <v>7544751</v>
+        <v>7544650</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -20523,7 +20523,7 @@
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Mats Williamson, Nils Ericson, Jan Henriksson, Billy Lindblom, Elias Rankka</t>
+          <t>Nils Ericson, Jan Henriksson, Billy Lindblom, Elias Rankka</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -18958,10 +18958,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>110515862</v>
+        <v>110515679</v>
       </c>
       <c r="B162" t="n">
-        <v>57963</v>
+        <v>57964</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -18996,24 +18996,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
-      <c r="L162" t="inlineStr"/>
       <c r="M162" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N162" t="inlineStr"/>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P162" t="inlineStr">
         <is>
           <t>Per Geijerområdet, T lm</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>723241</v>
+        <v>723479</v>
       </c>
       <c r="R162" t="n">
-        <v>7544321</v>
+        <v>7545157</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -19065,17 +19062,17 @@
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Nils Ericson, Jan Henriksson, Billy Lindblom, Elias Rankka</t>
+          <t>Mats Williamson, Nils Ericson, Jan Henriksson, Billy Lindblom, Elias Rankka</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>110515876</v>
+        <v>110514959</v>
       </c>
       <c r="B163" t="n">
-        <v>57963</v>
+        <v>57964</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -19107,12 +19104,12 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P163" t="inlineStr">
@@ -19121,10 +19118,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>723039</v>
+        <v>722904</v>
       </c>
       <c r="R163" t="n">
-        <v>7544294</v>
+        <v>7543903</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -19183,10 +19180,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>110515738</v>
+        <v>110515750</v>
       </c>
       <c r="B164" t="n">
-        <v>57963</v>
+        <v>57964</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -19221,21 +19218,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr"/>
       <c r="M164" t="inlineStr">
         <is>
           <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
+      <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
           <t>Per Geijerområdet, T lm</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>723431</v>
+        <v>723784</v>
       </c>
       <c r="R164" t="n">
-        <v>7544751</v>
+        <v>7544650</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -19287,17 +19287,17 @@
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Mats Williamson, Nils Ericson, Jan Henriksson, Billy Lindblom, Elias Rankka</t>
+          <t>Nils Ericson, Jan Henriksson, Billy Lindblom, Elias Rankka</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>110515651</v>
+        <v>110515862</v>
       </c>
       <c r="B165" t="n">
-        <v>57656</v>
+        <v>57964</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -19310,16 +19310,16 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -19332,21 +19332,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr"/>
       <c r="M165" t="inlineStr">
         <is>
           <t>spel/sång</t>
         </is>
       </c>
+      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Per Geijerområdet, T lm</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>723258</v>
+        <v>723241</v>
       </c>
       <c r="R165" t="n">
-        <v>7545337</v>
+        <v>7544321</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -19398,17 +19401,17 @@
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Mats Williamson, Nils Ericson, Jan Henriksson, Billy Lindblom, Elias Rankka</t>
+          <t>Nils Ericson, Jan Henriksson, Billy Lindblom, Elias Rankka</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>110515013</v>
+        <v>110515879</v>
       </c>
       <c r="B166" t="n">
-        <v>57963</v>
+        <v>57964</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -19440,27 +19443,24 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K166" t="inlineStr"/>
-      <c r="L166" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M166" t="inlineStr">
         <is>
           <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
-      <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
           <t>Per Geijerområdet, T lm</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>722974</v>
+        <v>723098</v>
       </c>
       <c r="R166" t="n">
-        <v>7543813</v>
+        <v>7544238</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -19512,17 +19512,17 @@
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Nils Ericson, Jan Henriksson, Billy Lindblom, Elias Rankka</t>
+          <t>Mats Williamson, Nils Ericson, Jan Henriksson, Billy Lindblom, Elias Rankka</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>110515879</v>
+        <v>110515651</v>
       </c>
       <c r="B167" t="n">
-        <v>57963</v>
+        <v>57657</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -19535,16 +19535,16 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -19559,7 +19559,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P167" t="inlineStr">
@@ -19568,10 +19568,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>723098</v>
+        <v>723258</v>
       </c>
       <c r="R167" t="n">
-        <v>7544238</v>
+        <v>7545337</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19630,10 +19630,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>110514995</v>
+        <v>110515876</v>
       </c>
       <c r="B168" t="n">
-        <v>57963</v>
+        <v>57964</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -19668,24 +19668,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
-      <c r="L168" t="inlineStr"/>
       <c r="M168" t="inlineStr">
         <is>
           <t>spel/sång</t>
         </is>
       </c>
-      <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
           <t>Per Geijerområdet, T lm</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>722886</v>
+        <v>723039</v>
       </c>
       <c r="R168" t="n">
-        <v>7543829</v>
+        <v>7544294</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19737,17 +19734,17 @@
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Nils Ericson, Jan Henriksson, Billy Lindblom, Elias Rankka</t>
+          <t>Mats Williamson, Nils Ericson, Jan Henriksson, Billy Lindblom, Elias Rankka</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>110514959</v>
+        <v>110515815</v>
       </c>
       <c r="B169" t="n">
-        <v>57963</v>
+        <v>57964</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -19779,12 +19776,12 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P169" t="inlineStr">
@@ -19793,10 +19790,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>722904</v>
+        <v>723752</v>
       </c>
       <c r="R169" t="n">
-        <v>7543903</v>
+        <v>7544439</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19855,10 +19852,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>110514972</v>
+        <v>110515817</v>
       </c>
       <c r="B170" t="n">
-        <v>57656</v>
+        <v>57964</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -19871,16 +19868,16 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -19904,10 +19901,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>722669</v>
+        <v>723754</v>
       </c>
       <c r="R170" t="n">
-        <v>7543877</v>
+        <v>7544439</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19966,10 +19963,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>110515817</v>
+        <v>110515738</v>
       </c>
       <c r="B171" t="n">
-        <v>57963</v>
+        <v>57964</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -20006,7 +20003,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P171" t="inlineStr">
@@ -20015,10 +20012,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>723754</v>
+        <v>723431</v>
       </c>
       <c r="R171" t="n">
-        <v>7544439</v>
+        <v>7544751</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -20080,7 +20077,7 @@
         <v>110515768</v>
       </c>
       <c r="B172" t="n">
-        <v>57963</v>
+        <v>57964</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -20191,10 +20188,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>110515679</v>
+        <v>110514972</v>
       </c>
       <c r="B173" t="n">
-        <v>57963</v>
+        <v>57657</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -20207,16 +20204,16 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -20231,7 +20228,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P173" t="inlineStr">
@@ -20240,10 +20237,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>723479</v>
+        <v>722669</v>
       </c>
       <c r="R173" t="n">
-        <v>7545157</v>
+        <v>7543877</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -20302,10 +20299,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>110515756</v>
+        <v>110514995</v>
       </c>
       <c r="B174" t="n">
-        <v>57963</v>
+        <v>57964</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -20337,14 +20334,14 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K174" t="inlineStr"/>
       <c r="L174" t="inlineStr"/>
       <c r="M174" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N174" t="inlineStr"/>
@@ -20354,10 +20351,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>723307</v>
+        <v>722886</v>
       </c>
       <c r="R174" t="n">
-        <v>7544635</v>
+        <v>7543829</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -20416,10 +20413,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>110515750</v>
+        <v>110515013</v>
       </c>
       <c r="B175" t="n">
-        <v>57963</v>
+        <v>57964</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -20451,7 +20448,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K175" t="inlineStr"/>
@@ -20468,10 +20465,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>723784</v>
+        <v>722974</v>
       </c>
       <c r="R175" t="n">
-        <v>7544650</v>
+        <v>7543813</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -20530,10 +20527,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>110515815</v>
+        <v>110515756</v>
       </c>
       <c r="B176" t="n">
-        <v>57963</v>
+        <v>57964</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -20565,24 +20562,27 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr"/>
+      <c r="L176" t="inlineStr"/>
       <c r="M176" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
           <t>Per Geijerområdet, T lm</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>723752</v>
+        <v>723307</v>
       </c>
       <c r="R176" t="n">
-        <v>7544439</v>
+        <v>7544635</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -20634,7 +20634,7 @@
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Mats Williamson, Nils Ericson, Jan Henriksson, Billy Lindblom, Elias Rankka</t>
+          <t>Nils Ericson, Jan Henriksson, Billy Lindblom, Elias Rankka</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -805,7 +805,7 @@
         <v>3550638</v>
       </c>
       <c r="B3" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>2556929</v>
       </c>
       <c r="B4" t="n">
-        <v>98074</v>
+        <v>98084</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>2269240</v>
       </c>
       <c r="B5" t="n">
-        <v>98177</v>
+        <v>98187</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>4870391</v>
       </c>
       <c r="B6" t="n">
-        <v>99186</v>
+        <v>99196</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -805,7 +805,7 @@
         <v>3550638</v>
       </c>
       <c r="B3" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>2556929</v>
       </c>
       <c r="B4" t="n">
-        <v>98084</v>
+        <v>98096</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>2269240</v>
       </c>
       <c r="B5" t="n">
-        <v>98187</v>
+        <v>98199</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>4870391</v>
       </c>
       <c r="B6" t="n">
-        <v>99196</v>
+        <v>99208</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -805,7 +805,7 @@
         <v>3550638</v>
       </c>
       <c r="B3" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>2556929</v>
       </c>
       <c r="B4" t="n">
-        <v>98096</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>2269240</v>
       </c>
       <c r="B5" t="n">
-        <v>98199</v>
+        <v>98204</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>4870391</v>
       </c>
       <c r="B6" t="n">
-        <v>99208</v>
+        <v>99213</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -805,7 +805,7 @@
         <v>3550638</v>
       </c>
       <c r="B3" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -819,11 +819,6 @@
       </c>
       <c r="E3" t="n">
         <v>220787</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -907,7 +902,7 @@
         <v>2556929</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>98110</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,11 +916,6 @@
       </c>
       <c r="E4" t="n">
         <v>219795</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Grönkulla</t>
-        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1009,7 +999,7 @@
         <v>2269240</v>
       </c>
       <c r="B5" t="n">
-        <v>98204</v>
+        <v>98213</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,11 +1013,6 @@
       </c>
       <c r="E5" t="n">
         <v>219811</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Brudsporre</t>
-        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1111,7 +1096,7 @@
         <v>4870391</v>
       </c>
       <c r="B6" t="n">
-        <v>99213</v>
+        <v>99222</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1125,11 +1110,6 @@
       </c>
       <c r="E6" t="n">
         <v>222467</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Gräsull</t>
-        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -805,7 +805,7 @@
         <v>3550638</v>
       </c>
       <c r="B3" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -819,6 +819,11 @@
       </c>
       <c r="E3" t="n">
         <v>220787</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -902,7 +907,7 @@
         <v>2556929</v>
       </c>
       <c r="B4" t="n">
-        <v>98110</v>
+        <v>98123</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,6 +921,11 @@
       </c>
       <c r="E4" t="n">
         <v>219795</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Grönkulla</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -999,7 +1009,7 @@
         <v>2269240</v>
       </c>
       <c r="B5" t="n">
-        <v>98213</v>
+        <v>98226</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1013,6 +1023,11 @@
       </c>
       <c r="E5" t="n">
         <v>219811</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1096,7 +1111,7 @@
         <v>4870391</v>
       </c>
       <c r="B6" t="n">
-        <v>99222</v>
+        <v>99235</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1110,6 +1125,11 @@
       </c>
       <c r="E6" t="n">
         <v>222467</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gräsull</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -805,7 +805,7 @@
         <v>3550638</v>
       </c>
       <c r="B3" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>2556929</v>
       </c>
       <c r="B4" t="n">
-        <v>98123</v>
+        <v>98136</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>2269240</v>
       </c>
       <c r="B5" t="n">
-        <v>98226</v>
+        <v>98239</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>4870391</v>
       </c>
       <c r="B6" t="n">
-        <v>99235</v>
+        <v>99248</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -20805,7 +20805,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>124355857</v>
+        <v>124355851</v>
       </c>
       <c r="B179" t="n">
         <v>97128</v>
@@ -20841,14 +20841,14 @@
       <c r="I179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>723343</v>
+        <v>723705</v>
       </c>
       <c r="R179" t="n">
-        <v>7544616</v>
+        <v>7544144</v>
       </c>
       <c r="S179" t="n">
         <v>5</v>
@@ -20875,12 +20875,12 @@
       </c>
       <c r="Y179" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -20907,10 +20907,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>124355592</v>
+        <v>124355857</v>
       </c>
       <c r="B180" t="n">
-        <v>79920</v>
+        <v>97128</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -20923,34 +20923,34 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6462</v>
+        <v>222741</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>723699</v>
+        <v>723343</v>
       </c>
       <c r="R180" t="n">
-        <v>7544155</v>
+        <v>7544616</v>
       </c>
       <c r="S180" t="n">
         <v>5</v>
@@ -20977,12 +20977,12 @@
       </c>
       <c r="Y180" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -21009,10 +21009,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>124355667</v>
+        <v>124355856</v>
       </c>
       <c r="B181" t="n">
-        <v>98101</v>
+        <v>97128</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -21021,38 +21021,38 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>220787</v>
+        <v>222741</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>723695</v>
+        <v>723068</v>
       </c>
       <c r="R181" t="n">
-        <v>7544233</v>
+        <v>7544568</v>
       </c>
       <c r="S181" t="n">
         <v>5</v>
@@ -21079,12 +21079,12 @@
       </c>
       <c r="Y181" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -21111,10 +21111,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>124355570</v>
+        <v>124355877</v>
       </c>
       <c r="B182" t="n">
-        <v>90977</v>
+        <v>74893</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -21123,38 +21123,38 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>5447</v>
+        <v>308</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>723343</v>
+        <v>723696</v>
       </c>
       <c r="R182" t="n">
-        <v>7544616</v>
+        <v>7544172</v>
       </c>
       <c r="S182" t="n">
         <v>5</v>
@@ -21181,12 +21181,12 @@
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -21213,10 +21213,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>124355807</v>
+        <v>124355543</v>
       </c>
       <c r="B183" t="n">
-        <v>98000</v>
+        <v>105102</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -21229,21 +21229,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>219795</v>
+        <v>221725</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -21253,10 +21253,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>723042</v>
+        <v>723227</v>
       </c>
       <c r="R183" t="n">
-        <v>7544553</v>
+        <v>7544640</v>
       </c>
       <c r="S183" t="n">
         <v>5</v>
@@ -21315,10 +21315,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>124355543</v>
+        <v>124355598</v>
       </c>
       <c r="B184" t="n">
-        <v>105102</v>
+        <v>79920</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -21331,21 +21331,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>221725</v>
+        <v>6462</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -21355,10 +21355,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>723227</v>
+        <v>723350</v>
       </c>
       <c r="R184" t="n">
-        <v>7544640</v>
+        <v>7544621</v>
       </c>
       <c r="S184" t="n">
         <v>5</v>
@@ -21417,10 +21417,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>124355609</v>
+        <v>124355667</v>
       </c>
       <c r="B185" t="n">
-        <v>98122</v>
+        <v>98101</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -21429,38 +21429,38 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>723343</v>
+        <v>723695</v>
       </c>
       <c r="R185" t="n">
-        <v>7544612</v>
+        <v>7544233</v>
       </c>
       <c r="S185" t="n">
         <v>5</v>
@@ -21487,12 +21487,12 @@
       </c>
       <c r="Y185" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -21519,10 +21519,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>124355552</v>
+        <v>124355611</v>
       </c>
       <c r="B186" t="n">
-        <v>105102</v>
+        <v>57529</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -21531,38 +21531,38 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>221725</v>
+        <v>100049</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>723608</v>
+        <v>723694</v>
       </c>
       <c r="R186" t="n">
-        <v>7544580</v>
+        <v>7544233</v>
       </c>
       <c r="S186" t="n">
         <v>5</v>
@@ -21589,12 +21589,17 @@
       </c>
       <c r="Y186" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="AC186" t="inlineStr">
+        <is>
+          <t>hackmärken</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -21621,10 +21626,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>124355539</v>
+        <v>124355855</v>
       </c>
       <c r="B187" t="n">
-        <v>105102</v>
+        <v>97128</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -21637,21 +21642,21 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>221725</v>
+        <v>222741</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -21661,10 +21666,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>722977</v>
+        <v>722944</v>
       </c>
       <c r="R187" t="n">
-        <v>7544571</v>
+        <v>7544574</v>
       </c>
       <c r="S187" t="n">
         <v>5</v>
@@ -21723,10 +21728,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>124355806</v>
+        <v>124355551</v>
       </c>
       <c r="B188" t="n">
-        <v>98000</v>
+        <v>105102</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -21739,21 +21744,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>219795</v>
+        <v>221725</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -21763,10 +21768,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>722934</v>
+        <v>723547</v>
       </c>
       <c r="R188" t="n">
-        <v>7544572</v>
+        <v>7544600</v>
       </c>
       <c r="S188" t="n">
         <v>5</v>
@@ -21825,10 +21830,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>124355855</v>
+        <v>124355666</v>
       </c>
       <c r="B189" t="n">
-        <v>97128</v>
+        <v>98101</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -21837,38 +21842,38 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>222741</v>
+        <v>220787</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>722944</v>
+        <v>723699</v>
       </c>
       <c r="R189" t="n">
-        <v>7544574</v>
+        <v>7544235</v>
       </c>
       <c r="S189" t="n">
         <v>5</v>
@@ -21895,12 +21900,12 @@
       </c>
       <c r="Y189" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -21927,7 +21932,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>124355513</v>
+        <v>124355546</v>
       </c>
       <c r="B190" t="n">
         <v>105102</v>
@@ -21963,14 +21968,14 @@
       <c r="I190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>723653</v>
+        <v>723347</v>
       </c>
       <c r="R190" t="n">
-        <v>7544288</v>
+        <v>7544617</v>
       </c>
       <c r="S190" t="n">
         <v>5</v>
@@ -21997,12 +22002,12 @@
       </c>
       <c r="Y190" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -22029,10 +22034,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>124355515</v>
+        <v>124355905</v>
       </c>
       <c r="B191" t="n">
-        <v>105102</v>
+        <v>78194</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -22041,25 +22046,25 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>221725</v>
+        <v>6437</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -22069,10 +22074,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>723720</v>
+        <v>723693</v>
       </c>
       <c r="R191" t="n">
-        <v>7544240</v>
+        <v>7544182</v>
       </c>
       <c r="S191" t="n">
         <v>5</v>
@@ -22131,10 +22136,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>124355877</v>
+        <v>124355592</v>
       </c>
       <c r="B192" t="n">
-        <v>74893</v>
+        <v>79920</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -22143,25 +22148,25 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>308</v>
+        <v>6462</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -22171,10 +22176,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>723696</v>
+        <v>723699</v>
       </c>
       <c r="R192" t="n">
-        <v>7544172</v>
+        <v>7544155</v>
       </c>
       <c r="S192" t="n">
         <v>5</v>
@@ -22233,10 +22238,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>124355668</v>
+        <v>124355552</v>
       </c>
       <c r="B193" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -22245,38 +22250,38 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>723703</v>
+        <v>723608</v>
       </c>
       <c r="R193" t="n">
-        <v>7544180</v>
+        <v>7544580</v>
       </c>
       <c r="S193" t="n">
         <v>5</v>
@@ -22303,12 +22308,12 @@
       </c>
       <c r="Y193" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -22335,7 +22340,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>124355548</v>
+        <v>124355540</v>
       </c>
       <c r="B194" t="n">
         <v>105102</v>
@@ -22375,10 +22380,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>723515</v>
+        <v>723038</v>
       </c>
       <c r="R194" t="n">
-        <v>7544632</v>
+        <v>7544552</v>
       </c>
       <c r="S194" t="n">
         <v>5</v>
@@ -22437,10 +22442,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>124355530</v>
+        <v>124355873</v>
       </c>
       <c r="B195" t="n">
-        <v>105102</v>
+        <v>79926</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -22453,34 +22458,34 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>221725</v>
+        <v>6463</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>723178</v>
+        <v>723684</v>
       </c>
       <c r="R195" t="n">
-        <v>7545219</v>
+        <v>7544232</v>
       </c>
       <c r="S195" t="n">
         <v>5</v>
@@ -22507,12 +22512,12 @@
       </c>
       <c r="Y195" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -22539,10 +22544,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>124355851</v>
+        <v>124355538</v>
       </c>
       <c r="B196" t="n">
-        <v>97128</v>
+        <v>105102</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -22555,34 +22560,34 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>222741</v>
+        <v>221725</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>723705</v>
+        <v>722917</v>
       </c>
       <c r="R196" t="n">
-        <v>7544144</v>
+        <v>7544575</v>
       </c>
       <c r="S196" t="n">
         <v>5</v>
@@ -22609,12 +22614,12 @@
       </c>
       <c r="Y196" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -22641,7 +22646,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>124355551</v>
+        <v>124355548</v>
       </c>
       <c r="B197" t="n">
         <v>105102</v>
@@ -22681,10 +22686,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>723547</v>
+        <v>723515</v>
       </c>
       <c r="R197" t="n">
-        <v>7544600</v>
+        <v>7544632</v>
       </c>
       <c r="S197" t="n">
         <v>5</v>
@@ -22743,10 +22748,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>124355905</v>
+        <v>124355654</v>
       </c>
       <c r="B198" t="n">
-        <v>78194</v>
+        <v>78151</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -22755,25 +22760,25 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>6437</v>
+        <v>498</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -22786,7 +22791,7 @@
         <v>723693</v>
       </c>
       <c r="R198" t="n">
-        <v>7544182</v>
+        <v>7544234</v>
       </c>
       <c r="S198" t="n">
         <v>5</v>
@@ -22845,10 +22850,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>124355654</v>
+        <v>124355826</v>
       </c>
       <c r="B199" t="n">
-        <v>78151</v>
+        <v>91030</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -22857,38 +22862,38 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>498</v>
+        <v>5432</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>723693</v>
+        <v>723345</v>
       </c>
       <c r="R199" t="n">
-        <v>7544234</v>
+        <v>7544616</v>
       </c>
       <c r="S199" t="n">
         <v>5</v>
@@ -22915,12 +22920,12 @@
       </c>
       <c r="Y199" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -22947,10 +22952,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>124355611</v>
+        <v>124355807</v>
       </c>
       <c r="B200" t="n">
-        <v>57529</v>
+        <v>98000</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -22959,38 +22964,38 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>100049</v>
+        <v>219795</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>723694</v>
+        <v>723042</v>
       </c>
       <c r="R200" t="n">
-        <v>7544233</v>
+        <v>7544553</v>
       </c>
       <c r="S200" t="n">
         <v>5</v>
@@ -23017,17 +23022,12 @@
       </c>
       <c r="Y200" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
-        </is>
-      </c>
-      <c r="AC200" t="inlineStr">
-        <is>
-          <t>hackmärken</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -23054,10 +23054,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>124355646</v>
+        <v>124355806</v>
       </c>
       <c r="B201" t="n">
-        <v>79927</v>
+        <v>98000</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -23070,34 +23070,34 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>6464</v>
+        <v>219795</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>723617</v>
+        <v>722934</v>
       </c>
       <c r="R201" t="n">
-        <v>7544144</v>
+        <v>7544572</v>
       </c>
       <c r="S201" t="n">
         <v>5</v>
@@ -23124,12 +23124,12 @@
       </c>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -23156,10 +23156,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>124355856</v>
+        <v>124355632</v>
       </c>
       <c r="B202" t="n">
-        <v>97128</v>
+        <v>96985</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -23172,34 +23172,34 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>222741</v>
+        <v>221941</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>723068</v>
+        <v>723668</v>
       </c>
       <c r="R202" t="n">
-        <v>7544568</v>
+        <v>7544288</v>
       </c>
       <c r="S202" t="n">
         <v>5</v>
@@ -23226,12 +23226,12 @@
       </c>
       <c r="Y202" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -23258,10 +23258,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>124355850</v>
+        <v>124355542</v>
       </c>
       <c r="B203" t="n">
-        <v>97128</v>
+        <v>105102</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -23274,34 +23274,34 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>222741</v>
+        <v>221725</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>723616</v>
+        <v>723159</v>
       </c>
       <c r="R203" t="n">
-        <v>7544154</v>
+        <v>7544605</v>
       </c>
       <c r="S203" t="n">
         <v>5</v>
@@ -23328,12 +23328,12 @@
       </c>
       <c r="Y203" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -23360,10 +23360,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>124355632</v>
+        <v>124355516</v>
       </c>
       <c r="B204" t="n">
-        <v>96985</v>
+        <v>105102</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -23376,21 +23376,21 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>221941</v>
+        <v>221725</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -23400,10 +23400,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>723668</v>
+        <v>723694</v>
       </c>
       <c r="R204" t="n">
-        <v>7544288</v>
+        <v>7544160</v>
       </c>
       <c r="S204" t="n">
         <v>5</v>
@@ -23462,7 +23462,7 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>124355540</v>
+        <v>124355539</v>
       </c>
       <c r="B205" t="n">
         <v>105102</v>
@@ -23502,10 +23502,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>723038</v>
+        <v>722977</v>
       </c>
       <c r="R205" t="n">
-        <v>7544552</v>
+        <v>7544571</v>
       </c>
       <c r="S205" t="n">
         <v>5</v>
@@ -23564,10 +23564,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>124355666</v>
+        <v>124355515</v>
       </c>
       <c r="B206" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -23576,25 +23576,25 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -23604,10 +23604,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>723699</v>
+        <v>723720</v>
       </c>
       <c r="R206" t="n">
-        <v>7544235</v>
+        <v>7544240</v>
       </c>
       <c r="S206" t="n">
         <v>5</v>
@@ -23666,7 +23666,7 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>124355538</v>
+        <v>124355529</v>
       </c>
       <c r="B207" t="n">
         <v>105102</v>
@@ -23706,10 +23706,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>722917</v>
+        <v>723365</v>
       </c>
       <c r="R207" t="n">
-        <v>7544575</v>
+        <v>7545207</v>
       </c>
       <c r="S207" t="n">
         <v>5</v>
@@ -23768,7 +23768,7 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>124355529</v>
+        <v>124355544</v>
       </c>
       <c r="B208" t="n">
         <v>105102</v>
@@ -23808,10 +23808,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>723365</v>
+        <v>723301</v>
       </c>
       <c r="R208" t="n">
-        <v>7545207</v>
+        <v>7544640</v>
       </c>
       <c r="S208" t="n">
         <v>5</v>
@@ -23870,10 +23870,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>124355598</v>
+        <v>124355850</v>
       </c>
       <c r="B209" t="n">
-        <v>79920</v>
+        <v>97128</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -23886,34 +23886,34 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>6462</v>
+        <v>222741</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>723350</v>
+        <v>723616</v>
       </c>
       <c r="R209" t="n">
-        <v>7544621</v>
+        <v>7544154</v>
       </c>
       <c r="S209" t="n">
         <v>5</v>
@@ -23940,12 +23940,12 @@
       </c>
       <c r="Y209" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -23972,10 +23972,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>124355546</v>
+        <v>124355870</v>
       </c>
       <c r="B210" t="n">
-        <v>105102</v>
+        <v>78455</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -23984,38 +23984,38 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>221725</v>
+        <v>353</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>723347</v>
+        <v>723669</v>
       </c>
       <c r="R210" t="n">
-        <v>7544617</v>
+        <v>7544113</v>
       </c>
       <c r="S210" t="n">
         <v>5</v>
@@ -24042,12 +24042,12 @@
       </c>
       <c r="Y210" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -24074,10 +24074,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>124355541</v>
+        <v>124355646</v>
       </c>
       <c r="B211" t="n">
-        <v>105102</v>
+        <v>79927</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -24090,34 +24090,34 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>221725</v>
+        <v>6464</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>723087</v>
+        <v>723617</v>
       </c>
       <c r="R211" t="n">
-        <v>7544566</v>
+        <v>7544144</v>
       </c>
       <c r="S211" t="n">
         <v>5</v>
@@ -24144,12 +24144,12 @@
       </c>
       <c r="Y211" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -24176,10 +24176,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>124355870</v>
+        <v>124355668</v>
       </c>
       <c r="B212" t="n">
-        <v>78455</v>
+        <v>98101</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -24188,25 +24188,25 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -24216,10 +24216,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>723669</v>
+        <v>723703</v>
       </c>
       <c r="R212" t="n">
-        <v>7544113</v>
+        <v>7544180</v>
       </c>
       <c r="S212" t="n">
         <v>5</v>
@@ -24278,10 +24278,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>124355826</v>
+        <v>124355609</v>
       </c>
       <c r="B213" t="n">
-        <v>91030</v>
+        <v>98122</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -24290,25 +24290,25 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -24318,10 +24318,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>723345</v>
+        <v>723343</v>
       </c>
       <c r="R213" t="n">
-        <v>7544616</v>
+        <v>7544612</v>
       </c>
       <c r="S213" t="n">
         <v>5</v>
@@ -24380,10 +24380,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>124355873</v>
+        <v>124355530</v>
       </c>
       <c r="B214" t="n">
-        <v>79926</v>
+        <v>105102</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -24396,34 +24396,34 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>6463</v>
+        <v>221725</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>723684</v>
+        <v>723178</v>
       </c>
       <c r="R214" t="n">
-        <v>7544232</v>
+        <v>7545219</v>
       </c>
       <c r="S214" t="n">
         <v>5</v>
@@ -24450,12 +24450,12 @@
       </c>
       <c r="Y214" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -24482,10 +24482,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>124355802</v>
+        <v>124355513</v>
       </c>
       <c r="B215" t="n">
-        <v>98000</v>
+        <v>105102</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -24498,21 +24498,21 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>219795</v>
+        <v>221725</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
@@ -24522,10 +24522,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>723703</v>
+        <v>723653</v>
       </c>
       <c r="R215" t="n">
-        <v>7544232</v>
+        <v>7544288</v>
       </c>
       <c r="S215" t="n">
         <v>5</v>
@@ -24584,10 +24584,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>124355672</v>
+        <v>124355541</v>
       </c>
       <c r="B216" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -24596,25 +24596,25 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
@@ -24624,10 +24624,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>723359</v>
+        <v>723087</v>
       </c>
       <c r="R216" t="n">
-        <v>7545207</v>
+        <v>7544566</v>
       </c>
       <c r="S216" t="n">
         <v>5</v>
@@ -24686,10 +24686,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>124355516</v>
+        <v>124355802</v>
       </c>
       <c r="B217" t="n">
-        <v>105102</v>
+        <v>98000</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -24702,21 +24702,21 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>221725</v>
+        <v>219795</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -24726,10 +24726,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>723694</v>
+        <v>723703</v>
       </c>
       <c r="R217" t="n">
-        <v>7544160</v>
+        <v>7544232</v>
       </c>
       <c r="S217" t="n">
         <v>5</v>
@@ -24788,10 +24788,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>124355544</v>
+        <v>124355672</v>
       </c>
       <c r="B218" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -24800,25 +24800,25 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -24828,10 +24828,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>723301</v>
+        <v>723359</v>
       </c>
       <c r="R218" t="n">
-        <v>7544640</v>
+        <v>7545207</v>
       </c>
       <c r="S218" t="n">
         <v>5</v>
@@ -24890,10 +24890,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>124355542</v>
+        <v>124355570</v>
       </c>
       <c r="B219" t="n">
-        <v>105102</v>
+        <v>90977</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -24906,21 +24906,21 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>221725</v>
+        <v>5447</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
@@ -24930,10 +24930,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>723159</v>
+        <v>723343</v>
       </c>
       <c r="R219" t="n">
-        <v>7544605</v>
+        <v>7544616</v>
       </c>
       <c r="S219" t="n">
         <v>5</v>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -20805,10 +20805,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>124355851</v>
+        <v>124355552</v>
       </c>
       <c r="B179" t="n">
-        <v>97128</v>
+        <v>105102</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -20821,34 +20821,34 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>222741</v>
+        <v>221725</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>723705</v>
+        <v>723608</v>
       </c>
       <c r="R179" t="n">
-        <v>7544144</v>
+        <v>7544580</v>
       </c>
       <c r="S179" t="n">
         <v>5</v>
@@ -20875,12 +20875,12 @@
       </c>
       <c r="Y179" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -20907,10 +20907,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>124355857</v>
+        <v>124355543</v>
       </c>
       <c r="B180" t="n">
-        <v>97128</v>
+        <v>105102</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -20923,21 +20923,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>222741</v>
+        <v>221725</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -20947,10 +20947,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>723343</v>
+        <v>723227</v>
       </c>
       <c r="R180" t="n">
-        <v>7544616</v>
+        <v>7544640</v>
       </c>
       <c r="S180" t="n">
         <v>5</v>
@@ -21009,10 +21009,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>124355856</v>
+        <v>124355539</v>
       </c>
       <c r="B181" t="n">
-        <v>97128</v>
+        <v>105102</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -21025,21 +21025,21 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>222741</v>
+        <v>221725</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -21049,10 +21049,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>723068</v>
+        <v>722977</v>
       </c>
       <c r="R181" t="n">
-        <v>7544568</v>
+        <v>7544571</v>
       </c>
       <c r="S181" t="n">
         <v>5</v>
@@ -21111,10 +21111,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>124355877</v>
+        <v>124355667</v>
       </c>
       <c r="B182" t="n">
-        <v>74893</v>
+        <v>98101</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -21123,25 +21123,25 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -21151,10 +21151,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>723696</v>
+        <v>723695</v>
       </c>
       <c r="R182" t="n">
-        <v>7544172</v>
+        <v>7544233</v>
       </c>
       <c r="S182" t="n">
         <v>5</v>
@@ -21213,10 +21213,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>124355543</v>
+        <v>124355826</v>
       </c>
       <c r="B183" t="n">
-        <v>105102</v>
+        <v>91030</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -21225,25 +21225,25 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>221725</v>
+        <v>5432</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -21253,10 +21253,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>723227</v>
+        <v>723345</v>
       </c>
       <c r="R183" t="n">
-        <v>7544640</v>
+        <v>7544616</v>
       </c>
       <c r="S183" t="n">
         <v>5</v>
@@ -21315,10 +21315,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>124355598</v>
+        <v>124355551</v>
       </c>
       <c r="B184" t="n">
-        <v>79920</v>
+        <v>105102</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -21331,21 +21331,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6462</v>
+        <v>221725</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -21355,10 +21355,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>723350</v>
+        <v>723547</v>
       </c>
       <c r="R184" t="n">
-        <v>7544621</v>
+        <v>7544600</v>
       </c>
       <c r="S184" t="n">
         <v>5</v>
@@ -21417,7 +21417,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>124355667</v>
+        <v>124355672</v>
       </c>
       <c r="B185" t="n">
         <v>98101</v>
@@ -21453,14 +21453,14 @@
       <c r="I185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>723695</v>
+        <v>723359</v>
       </c>
       <c r="R185" t="n">
-        <v>7544233</v>
+        <v>7545207</v>
       </c>
       <c r="S185" t="n">
         <v>5</v>
@@ -21487,12 +21487,12 @@
       </c>
       <c r="Y185" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -21519,10 +21519,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>124355611</v>
+        <v>124355873</v>
       </c>
       <c r="B186" t="n">
-        <v>57529</v>
+        <v>79926</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -21531,25 +21531,25 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -21559,10 +21559,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>723694</v>
+        <v>723684</v>
       </c>
       <c r="R186" t="n">
-        <v>7544233</v>
+        <v>7544232</v>
       </c>
       <c r="S186" t="n">
         <v>5</v>
@@ -21595,11 +21595,6 @@
       <c r="AA186" t="inlineStr">
         <is>
           <t>2024-08-09</t>
-        </is>
-      </c>
-      <c r="AC186" t="inlineStr">
-        <is>
-          <t>hackmärken</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -21626,10 +21621,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>124355855</v>
+        <v>124355598</v>
       </c>
       <c r="B187" t="n">
-        <v>97128</v>
+        <v>79920</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -21642,21 +21637,21 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>222741</v>
+        <v>6462</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -21666,10 +21661,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>722944</v>
+        <v>723350</v>
       </c>
       <c r="R187" t="n">
-        <v>7544574</v>
+        <v>7544621</v>
       </c>
       <c r="S187" t="n">
         <v>5</v>
@@ -21728,10 +21723,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>124355551</v>
+        <v>124355802</v>
       </c>
       <c r="B188" t="n">
-        <v>105102</v>
+        <v>98000</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -21744,34 +21739,34 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>221725</v>
+        <v>219795</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>723547</v>
+        <v>723703</v>
       </c>
       <c r="R188" t="n">
-        <v>7544600</v>
+        <v>7544232</v>
       </c>
       <c r="S188" t="n">
         <v>5</v>
@@ -21798,12 +21793,12 @@
       </c>
       <c r="Y188" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -21932,10 +21927,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>124355546</v>
+        <v>124355609</v>
       </c>
       <c r="B190" t="n">
-        <v>105102</v>
+        <v>98122</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -21948,21 +21943,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>221725</v>
+        <v>221952</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -21972,10 +21967,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>723347</v>
+        <v>723343</v>
       </c>
       <c r="R190" t="n">
-        <v>7544617</v>
+        <v>7544612</v>
       </c>
       <c r="S190" t="n">
         <v>5</v>
@@ -22034,10 +22029,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>124355905</v>
+        <v>124355851</v>
       </c>
       <c r="B191" t="n">
-        <v>78194</v>
+        <v>97128</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -22046,25 +22041,25 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6437</v>
+        <v>222741</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -22074,10 +22069,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>723693</v>
+        <v>723705</v>
       </c>
       <c r="R191" t="n">
-        <v>7544182</v>
+        <v>7544144</v>
       </c>
       <c r="S191" t="n">
         <v>5</v>
@@ -22136,10 +22131,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>124355592</v>
+        <v>124355850</v>
       </c>
       <c r="B192" t="n">
-        <v>79920</v>
+        <v>97128</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -22152,21 +22147,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6462</v>
+        <v>222741</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -22176,10 +22171,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>723699</v>
+        <v>723616</v>
       </c>
       <c r="R192" t="n">
-        <v>7544155</v>
+        <v>7544154</v>
       </c>
       <c r="S192" t="n">
         <v>5</v>
@@ -22238,10 +22233,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>124355552</v>
+        <v>124355668</v>
       </c>
       <c r="B193" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -22250,38 +22245,38 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>723608</v>
+        <v>723703</v>
       </c>
       <c r="R193" t="n">
-        <v>7544580</v>
+        <v>7544180</v>
       </c>
       <c r="S193" t="n">
         <v>5</v>
@@ -22308,12 +22303,12 @@
       </c>
       <c r="Y193" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -22340,10 +22335,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>124355540</v>
+        <v>124355646</v>
       </c>
       <c r="B194" t="n">
-        <v>105102</v>
+        <v>79927</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -22356,34 +22351,34 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>221725</v>
+        <v>6464</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>723038</v>
+        <v>723617</v>
       </c>
       <c r="R194" t="n">
-        <v>7544552</v>
+        <v>7544144</v>
       </c>
       <c r="S194" t="n">
         <v>5</v>
@@ -22410,12 +22405,12 @@
       </c>
       <c r="Y194" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -22442,10 +22437,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>124355873</v>
+        <v>124355513</v>
       </c>
       <c r="B195" t="n">
-        <v>79926</v>
+        <v>105102</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -22458,21 +22453,21 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6463</v>
+        <v>221725</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -22482,10 +22477,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>723684</v>
+        <v>723653</v>
       </c>
       <c r="R195" t="n">
-        <v>7544232</v>
+        <v>7544288</v>
       </c>
       <c r="S195" t="n">
         <v>5</v>
@@ -22544,7 +22539,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>124355538</v>
+        <v>124355548</v>
       </c>
       <c r="B196" t="n">
         <v>105102</v>
@@ -22584,10 +22579,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>722917</v>
+        <v>723515</v>
       </c>
       <c r="R196" t="n">
-        <v>7544575</v>
+        <v>7544632</v>
       </c>
       <c r="S196" t="n">
         <v>5</v>
@@ -22646,7 +22641,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>124355548</v>
+        <v>124355540</v>
       </c>
       <c r="B197" t="n">
         <v>105102</v>
@@ -22686,10 +22681,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>723515</v>
+        <v>723038</v>
       </c>
       <c r="R197" t="n">
-        <v>7544632</v>
+        <v>7544552</v>
       </c>
       <c r="S197" t="n">
         <v>5</v>
@@ -22748,10 +22743,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>124355654</v>
+        <v>124355529</v>
       </c>
       <c r="B198" t="n">
-        <v>78151</v>
+        <v>105102</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -22760,38 +22755,38 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>498</v>
+        <v>221725</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>723693</v>
+        <v>723365</v>
       </c>
       <c r="R198" t="n">
-        <v>7544234</v>
+        <v>7545207</v>
       </c>
       <c r="S198" t="n">
         <v>5</v>
@@ -22818,12 +22813,12 @@
       </c>
       <c r="Y198" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -22850,10 +22845,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>124355826</v>
+        <v>124355856</v>
       </c>
       <c r="B199" t="n">
-        <v>91030</v>
+        <v>97128</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -22862,25 +22857,25 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>5432</v>
+        <v>222741</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -22890,10 +22885,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>723345</v>
+        <v>723068</v>
       </c>
       <c r="R199" t="n">
-        <v>7544616</v>
+        <v>7544568</v>
       </c>
       <c r="S199" t="n">
         <v>5</v>
@@ -23054,10 +23049,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>124355806</v>
+        <v>124355538</v>
       </c>
       <c r="B201" t="n">
-        <v>98000</v>
+        <v>105102</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -23070,21 +23065,21 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>219795</v>
+        <v>221725</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -23094,10 +23089,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>722934</v>
+        <v>722917</v>
       </c>
       <c r="R201" t="n">
-        <v>7544572</v>
+        <v>7544575</v>
       </c>
       <c r="S201" t="n">
         <v>5</v>
@@ -23156,10 +23151,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>124355632</v>
+        <v>124355905</v>
       </c>
       <c r="B202" t="n">
-        <v>96985</v>
+        <v>78194</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -23168,25 +23163,25 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>221941</v>
+        <v>6437</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -23196,10 +23191,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>723668</v>
+        <v>723693</v>
       </c>
       <c r="R202" t="n">
-        <v>7544288</v>
+        <v>7544182</v>
       </c>
       <c r="S202" t="n">
         <v>5</v>
@@ -23258,10 +23253,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>124355542</v>
+        <v>124355570</v>
       </c>
       <c r="B203" t="n">
-        <v>105102</v>
+        <v>90977</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -23274,21 +23269,21 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>221725</v>
+        <v>5447</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -23298,10 +23293,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>723159</v>
+        <v>723343</v>
       </c>
       <c r="R203" t="n">
-        <v>7544605</v>
+        <v>7544616</v>
       </c>
       <c r="S203" t="n">
         <v>5</v>
@@ -23360,10 +23355,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>124355516</v>
+        <v>124355592</v>
       </c>
       <c r="B204" t="n">
-        <v>105102</v>
+        <v>79920</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -23376,21 +23371,21 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>221725</v>
+        <v>6462</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -23400,10 +23395,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>723694</v>
+        <v>723699</v>
       </c>
       <c r="R204" t="n">
-        <v>7544160</v>
+        <v>7544155</v>
       </c>
       <c r="S204" t="n">
         <v>5</v>
@@ -23462,7 +23457,7 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>124355539</v>
+        <v>124355544</v>
       </c>
       <c r="B205" t="n">
         <v>105102</v>
@@ -23502,10 +23497,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>722977</v>
+        <v>723301</v>
       </c>
       <c r="R205" t="n">
-        <v>7544571</v>
+        <v>7544640</v>
       </c>
       <c r="S205" t="n">
         <v>5</v>
@@ -23564,10 +23559,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>124355515</v>
+        <v>124355855</v>
       </c>
       <c r="B206" t="n">
-        <v>105102</v>
+        <v>97128</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -23580,34 +23575,34 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>221725</v>
+        <v>222741</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>723720</v>
+        <v>722944</v>
       </c>
       <c r="R206" t="n">
-        <v>7544240</v>
+        <v>7544574</v>
       </c>
       <c r="S206" t="n">
         <v>5</v>
@@ -23634,12 +23629,12 @@
       </c>
       <c r="Y206" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -23666,7 +23661,7 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>124355529</v>
+        <v>124355546</v>
       </c>
       <c r="B207" t="n">
         <v>105102</v>
@@ -23706,10 +23701,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>723365</v>
+        <v>723347</v>
       </c>
       <c r="R207" t="n">
-        <v>7545207</v>
+        <v>7544617</v>
       </c>
       <c r="S207" t="n">
         <v>5</v>
@@ -23768,7 +23763,7 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>124355544</v>
+        <v>124355530</v>
       </c>
       <c r="B208" t="n">
         <v>105102</v>
@@ -23808,10 +23803,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>723301</v>
+        <v>723178</v>
       </c>
       <c r="R208" t="n">
-        <v>7544640</v>
+        <v>7545219</v>
       </c>
       <c r="S208" t="n">
         <v>5</v>
@@ -23870,10 +23865,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>124355850</v>
+        <v>124355515</v>
       </c>
       <c r="B209" t="n">
-        <v>97128</v>
+        <v>105102</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -23886,21 +23881,21 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>222741</v>
+        <v>221725</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -23910,10 +23905,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>723616</v>
+        <v>723720</v>
       </c>
       <c r="R209" t="n">
-        <v>7544154</v>
+        <v>7544240</v>
       </c>
       <c r="S209" t="n">
         <v>5</v>
@@ -23972,10 +23967,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>124355870</v>
+        <v>124355857</v>
       </c>
       <c r="B210" t="n">
-        <v>78455</v>
+        <v>97128</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -23984,38 +23979,38 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>353</v>
+        <v>222741</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>723669</v>
+        <v>723343</v>
       </c>
       <c r="R210" t="n">
-        <v>7544113</v>
+        <v>7544616</v>
       </c>
       <c r="S210" t="n">
         <v>5</v>
@@ -24042,12 +24037,12 @@
       </c>
       <c r="Y210" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -24074,10 +24069,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>124355646</v>
+        <v>124355654</v>
       </c>
       <c r="B211" t="n">
-        <v>79927</v>
+        <v>78151</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -24086,25 +24081,25 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>6464</v>
+        <v>498</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -24114,10 +24109,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>723617</v>
+        <v>723693</v>
       </c>
       <c r="R211" t="n">
-        <v>7544144</v>
+        <v>7544234</v>
       </c>
       <c r="S211" t="n">
         <v>5</v>
@@ -24176,10 +24171,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>124355668</v>
+        <v>124355541</v>
       </c>
       <c r="B212" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -24188,38 +24183,38 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>723703</v>
+        <v>723087</v>
       </c>
       <c r="R212" t="n">
-        <v>7544180</v>
+        <v>7544566</v>
       </c>
       <c r="S212" t="n">
         <v>5</v>
@@ -24246,12 +24241,12 @@
       </c>
       <c r="Y212" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -24278,10 +24273,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>124355609</v>
+        <v>124355542</v>
       </c>
       <c r="B213" t="n">
-        <v>98122</v>
+        <v>105102</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -24294,21 +24289,21 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>221952</v>
+        <v>221725</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -24318,10 +24313,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>723343</v>
+        <v>723159</v>
       </c>
       <c r="R213" t="n">
-        <v>7544612</v>
+        <v>7544605</v>
       </c>
       <c r="S213" t="n">
         <v>5</v>
@@ -24380,10 +24375,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>124355530</v>
+        <v>124355877</v>
       </c>
       <c r="B214" t="n">
-        <v>105102</v>
+        <v>74893</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -24392,38 +24387,38 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>221725</v>
+        <v>308</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>723178</v>
+        <v>723696</v>
       </c>
       <c r="R214" t="n">
-        <v>7545219</v>
+        <v>7544172</v>
       </c>
       <c r="S214" t="n">
         <v>5</v>
@@ -24450,12 +24445,12 @@
       </c>
       <c r="Y214" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -24482,10 +24477,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>124355513</v>
+        <v>124355806</v>
       </c>
       <c r="B215" t="n">
-        <v>105102</v>
+        <v>98000</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -24498,34 +24493,34 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>221725</v>
+        <v>219795</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
       <c r="P215" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>723653</v>
+        <v>722934</v>
       </c>
       <c r="R215" t="n">
-        <v>7544288</v>
+        <v>7544572</v>
       </c>
       <c r="S215" t="n">
         <v>5</v>
@@ -24552,12 +24547,12 @@
       </c>
       <c r="Y215" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -24584,10 +24579,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>124355541</v>
+        <v>124355632</v>
       </c>
       <c r="B216" t="n">
-        <v>105102</v>
+        <v>96985</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -24600,34 +24595,34 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>221725</v>
+        <v>221941</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
       <c r="P216" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>723087</v>
+        <v>723668</v>
       </c>
       <c r="R216" t="n">
-        <v>7544566</v>
+        <v>7544288</v>
       </c>
       <c r="S216" t="n">
         <v>5</v>
@@ -24654,12 +24649,12 @@
       </c>
       <c r="Y216" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -24686,10 +24681,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>124355802</v>
+        <v>124355870</v>
       </c>
       <c r="B217" t="n">
-        <v>98000</v>
+        <v>78455</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -24698,25 +24693,25 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>219795</v>
+        <v>353</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -24726,10 +24721,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>723703</v>
+        <v>723669</v>
       </c>
       <c r="R217" t="n">
-        <v>7544232</v>
+        <v>7544113</v>
       </c>
       <c r="S217" t="n">
         <v>5</v>
@@ -24788,10 +24783,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>124355672</v>
+        <v>124355611</v>
       </c>
       <c r="B218" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -24800,38 +24795,38 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
       <c r="P218" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>723359</v>
+        <v>723694</v>
       </c>
       <c r="R218" t="n">
-        <v>7545207</v>
+        <v>7544233</v>
       </c>
       <c r="S218" t="n">
         <v>5</v>
@@ -24858,12 +24853,17 @@
       </c>
       <c r="Y218" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="AC218" t="inlineStr">
+        <is>
+          <t>hackmärken</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -24890,10 +24890,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>124355570</v>
+        <v>124355516</v>
       </c>
       <c r="B219" t="n">
-        <v>90977</v>
+        <v>105102</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -24906,34 +24906,34 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>5447</v>
+        <v>221725</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>723343</v>
+        <v>723694</v>
       </c>
       <c r="R219" t="n">
-        <v>7544616</v>
+        <v>7544160</v>
       </c>
       <c r="S219" t="n">
         <v>5</v>
@@ -24960,12 +24960,12 @@
       </c>
       <c r="Y219" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD219" t="b">

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -20805,10 +20805,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>124355552</v>
+        <v>124355654</v>
       </c>
       <c r="B179" t="n">
-        <v>105102</v>
+        <v>78151</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -20817,38 +20817,38 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>221725</v>
+        <v>498</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>723608</v>
+        <v>723693</v>
       </c>
       <c r="R179" t="n">
-        <v>7544580</v>
+        <v>7544234</v>
       </c>
       <c r="S179" t="n">
         <v>5</v>
@@ -20875,12 +20875,12 @@
       </c>
       <c r="Y179" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -20907,10 +20907,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>124355543</v>
+        <v>124355632</v>
       </c>
       <c r="B180" t="n">
-        <v>105102</v>
+        <v>96985</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -20923,34 +20923,34 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>221725</v>
+        <v>221941</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>723227</v>
+        <v>723668</v>
       </c>
       <c r="R180" t="n">
-        <v>7544640</v>
+        <v>7544288</v>
       </c>
       <c r="S180" t="n">
         <v>5</v>
@@ -20977,12 +20977,12 @@
       </c>
       <c r="Y180" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -21009,7 +21009,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>124355539</v>
+        <v>124355513</v>
       </c>
       <c r="B181" t="n">
         <v>105102</v>
@@ -21045,14 +21045,14 @@
       <c r="I181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>722977</v>
+        <v>723653</v>
       </c>
       <c r="R181" t="n">
-        <v>7544571</v>
+        <v>7544288</v>
       </c>
       <c r="S181" t="n">
         <v>5</v>
@@ -21079,12 +21079,12 @@
       </c>
       <c r="Y181" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -21111,10 +21111,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>124355667</v>
+        <v>124355551</v>
       </c>
       <c r="B182" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -21123,38 +21123,38 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>723695</v>
+        <v>723547</v>
       </c>
       <c r="R182" t="n">
-        <v>7544233</v>
+        <v>7544600</v>
       </c>
       <c r="S182" t="n">
         <v>5</v>
@@ -21181,12 +21181,12 @@
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -21213,10 +21213,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>124355826</v>
+        <v>124355806</v>
       </c>
       <c r="B183" t="n">
-        <v>91030</v>
+        <v>98000</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -21225,25 +21225,25 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>5432</v>
+        <v>219795</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -21253,10 +21253,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>723345</v>
+        <v>722934</v>
       </c>
       <c r="R183" t="n">
-        <v>7544616</v>
+        <v>7544572</v>
       </c>
       <c r="S183" t="n">
         <v>5</v>
@@ -21315,10 +21315,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>124355551</v>
+        <v>124355802</v>
       </c>
       <c r="B184" t="n">
-        <v>105102</v>
+        <v>98000</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -21331,34 +21331,34 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>221725</v>
+        <v>219795</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>723547</v>
+        <v>723703</v>
       </c>
       <c r="R184" t="n">
-        <v>7544600</v>
+        <v>7544232</v>
       </c>
       <c r="S184" t="n">
         <v>5</v>
@@ -21385,12 +21385,12 @@
       </c>
       <c r="Y184" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -21417,10 +21417,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>124355672</v>
+        <v>124355873</v>
       </c>
       <c r="B185" t="n">
-        <v>98101</v>
+        <v>79926</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -21429,38 +21429,38 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>723359</v>
+        <v>723684</v>
       </c>
       <c r="R185" t="n">
-        <v>7545207</v>
+        <v>7544232</v>
       </c>
       <c r="S185" t="n">
         <v>5</v>
@@ -21487,12 +21487,12 @@
       </c>
       <c r="Y185" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -21519,10 +21519,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>124355873</v>
+        <v>124355542</v>
       </c>
       <c r="B186" t="n">
-        <v>79926</v>
+        <v>105102</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -21535,34 +21535,34 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6463</v>
+        <v>221725</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>723684</v>
+        <v>723159</v>
       </c>
       <c r="R186" t="n">
-        <v>7544232</v>
+        <v>7544605</v>
       </c>
       <c r="S186" t="n">
         <v>5</v>
@@ -21589,12 +21589,12 @@
       </c>
       <c r="Y186" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -21621,10 +21621,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>124355598</v>
+        <v>124355667</v>
       </c>
       <c r="B187" t="n">
-        <v>79920</v>
+        <v>98101</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -21633,38 +21633,38 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>723350</v>
+        <v>723695</v>
       </c>
       <c r="R187" t="n">
-        <v>7544621</v>
+        <v>7544233</v>
       </c>
       <c r="S187" t="n">
         <v>5</v>
@@ -21691,12 +21691,12 @@
       </c>
       <c r="Y187" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -21723,10 +21723,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>124355802</v>
+        <v>124355543</v>
       </c>
       <c r="B188" t="n">
-        <v>98000</v>
+        <v>105102</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -21739,34 +21739,34 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>219795</v>
+        <v>221725</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>723703</v>
+        <v>723227</v>
       </c>
       <c r="R188" t="n">
-        <v>7544232</v>
+        <v>7544640</v>
       </c>
       <c r="S188" t="n">
         <v>5</v>
@@ -21793,12 +21793,12 @@
       </c>
       <c r="Y188" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -21825,10 +21825,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>124355666</v>
+        <v>124355529</v>
       </c>
       <c r="B189" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -21837,38 +21837,38 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>723699</v>
+        <v>723365</v>
       </c>
       <c r="R189" t="n">
-        <v>7544235</v>
+        <v>7545207</v>
       </c>
       <c r="S189" t="n">
         <v>5</v>
@@ -21895,12 +21895,12 @@
       </c>
       <c r="Y189" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -21927,10 +21927,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>124355609</v>
+        <v>124355544</v>
       </c>
       <c r="B190" t="n">
-        <v>98122</v>
+        <v>105102</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -21943,21 +21943,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>221952</v>
+        <v>221725</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -21967,10 +21967,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>723343</v>
+        <v>723301</v>
       </c>
       <c r="R190" t="n">
-        <v>7544612</v>
+        <v>7544640</v>
       </c>
       <c r="S190" t="n">
         <v>5</v>
@@ -22029,10 +22029,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>124355851</v>
+        <v>124355541</v>
       </c>
       <c r="B191" t="n">
-        <v>97128</v>
+        <v>105102</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -22045,34 +22045,34 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>222741</v>
+        <v>221725</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>723705</v>
+        <v>723087</v>
       </c>
       <c r="R191" t="n">
-        <v>7544144</v>
+        <v>7544566</v>
       </c>
       <c r="S191" t="n">
         <v>5</v>
@@ -22099,12 +22099,12 @@
       </c>
       <c r="Y191" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -22131,7 +22131,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>124355850</v>
+        <v>124355857</v>
       </c>
       <c r="B192" t="n">
         <v>97128</v>
@@ -22167,14 +22167,14 @@
       <c r="I192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>723616</v>
+        <v>723343</v>
       </c>
       <c r="R192" t="n">
-        <v>7544154</v>
+        <v>7544616</v>
       </c>
       <c r="S192" t="n">
         <v>5</v>
@@ -22201,12 +22201,12 @@
       </c>
       <c r="Y192" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -22233,10 +22233,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>124355668</v>
+        <v>124355646</v>
       </c>
       <c r="B193" t="n">
-        <v>98101</v>
+        <v>79927</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -22245,25 +22245,25 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -22273,10 +22273,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>723703</v>
+        <v>723617</v>
       </c>
       <c r="R193" t="n">
-        <v>7544180</v>
+        <v>7544144</v>
       </c>
       <c r="S193" t="n">
         <v>5</v>
@@ -22335,10 +22335,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>124355646</v>
+        <v>124355666</v>
       </c>
       <c r="B194" t="n">
-        <v>79927</v>
+        <v>98101</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -22347,25 +22347,25 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -22375,10 +22375,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>723617</v>
+        <v>723699</v>
       </c>
       <c r="R194" t="n">
-        <v>7544144</v>
+        <v>7544235</v>
       </c>
       <c r="S194" t="n">
         <v>5</v>
@@ -22437,10 +22437,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>124355513</v>
+        <v>124355905</v>
       </c>
       <c r="B195" t="n">
-        <v>105102</v>
+        <v>78194</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -22449,25 +22449,25 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>221725</v>
+        <v>6437</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -22477,10 +22477,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>723653</v>
+        <v>723693</v>
       </c>
       <c r="R195" t="n">
-        <v>7544288</v>
+        <v>7544182</v>
       </c>
       <c r="S195" t="n">
         <v>5</v>
@@ -22539,7 +22539,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>124355548</v>
+        <v>124355539</v>
       </c>
       <c r="B196" t="n">
         <v>105102</v>
@@ -22579,10 +22579,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>723515</v>
+        <v>722977</v>
       </c>
       <c r="R196" t="n">
-        <v>7544632</v>
+        <v>7544571</v>
       </c>
       <c r="S196" t="n">
         <v>5</v>
@@ -22641,10 +22641,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>124355540</v>
+        <v>124355668</v>
       </c>
       <c r="B197" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -22653,38 +22653,38 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>723038</v>
+        <v>723703</v>
       </c>
       <c r="R197" t="n">
-        <v>7544552</v>
+        <v>7544180</v>
       </c>
       <c r="S197" t="n">
         <v>5</v>
@@ -22711,12 +22711,12 @@
       </c>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -22743,10 +22743,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>124355529</v>
+        <v>124355877</v>
       </c>
       <c r="B198" t="n">
-        <v>105102</v>
+        <v>74893</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -22755,38 +22755,38 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>221725</v>
+        <v>308</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>723365</v>
+        <v>723696</v>
       </c>
       <c r="R198" t="n">
-        <v>7545207</v>
+        <v>7544172</v>
       </c>
       <c r="S198" t="n">
         <v>5</v>
@@ -22813,12 +22813,12 @@
       </c>
       <c r="Y198" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -22845,10 +22845,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>124355856</v>
+        <v>124355611</v>
       </c>
       <c r="B199" t="n">
-        <v>97128</v>
+        <v>57529</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -22857,38 +22857,38 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>222741</v>
+        <v>100049</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>723068</v>
+        <v>723694</v>
       </c>
       <c r="R199" t="n">
-        <v>7544568</v>
+        <v>7544233</v>
       </c>
       <c r="S199" t="n">
         <v>5</v>
@@ -22915,12 +22915,17 @@
       </c>
       <c r="Y199" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="AC199" t="inlineStr">
+        <is>
+          <t>hackmärken</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -22947,10 +22952,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>124355807</v>
+        <v>124355548</v>
       </c>
       <c r="B200" t="n">
-        <v>98000</v>
+        <v>105102</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -22963,21 +22968,21 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>219795</v>
+        <v>221725</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -22987,10 +22992,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>723042</v>
+        <v>723515</v>
       </c>
       <c r="R200" t="n">
-        <v>7544553</v>
+        <v>7544632</v>
       </c>
       <c r="S200" t="n">
         <v>5</v>
@@ -23049,10 +23054,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>124355538</v>
+        <v>124355592</v>
       </c>
       <c r="B201" t="n">
-        <v>105102</v>
+        <v>79920</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -23065,34 +23070,34 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>221725</v>
+        <v>6462</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>722917</v>
+        <v>723699</v>
       </c>
       <c r="R201" t="n">
-        <v>7544575</v>
+        <v>7544155</v>
       </c>
       <c r="S201" t="n">
         <v>5</v>
@@ -23119,12 +23124,12 @@
       </c>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -23151,10 +23156,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>124355905</v>
+        <v>124355807</v>
       </c>
       <c r="B202" t="n">
-        <v>78194</v>
+        <v>98000</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -23163,38 +23168,38 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>6437</v>
+        <v>219795</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>723693</v>
+        <v>723042</v>
       </c>
       <c r="R202" t="n">
-        <v>7544182</v>
+        <v>7544553</v>
       </c>
       <c r="S202" t="n">
         <v>5</v>
@@ -23221,12 +23226,12 @@
       </c>
       <c r="Y202" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -23253,10 +23258,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>124355570</v>
+        <v>124355516</v>
       </c>
       <c r="B203" t="n">
-        <v>90977</v>
+        <v>105102</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -23269,34 +23274,34 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>5447</v>
+        <v>221725</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>723343</v>
+        <v>723694</v>
       </c>
       <c r="R203" t="n">
-        <v>7544616</v>
+        <v>7544160</v>
       </c>
       <c r="S203" t="n">
         <v>5</v>
@@ -23323,12 +23328,12 @@
       </c>
       <c r="Y203" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -23355,10 +23360,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>124355592</v>
+        <v>124355530</v>
       </c>
       <c r="B204" t="n">
-        <v>79920</v>
+        <v>105102</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -23371,34 +23376,34 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>6462</v>
+        <v>221725</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>723699</v>
+        <v>723178</v>
       </c>
       <c r="R204" t="n">
-        <v>7544155</v>
+        <v>7545219</v>
       </c>
       <c r="S204" t="n">
         <v>5</v>
@@ -23425,12 +23430,12 @@
       </c>
       <c r="Y204" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -23457,10 +23462,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>124355544</v>
+        <v>124355856</v>
       </c>
       <c r="B205" t="n">
-        <v>105102</v>
+        <v>97128</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -23473,21 +23478,21 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>221725</v>
+        <v>222741</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -23497,10 +23502,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>723301</v>
+        <v>723068</v>
       </c>
       <c r="R205" t="n">
-        <v>7544640</v>
+        <v>7544568</v>
       </c>
       <c r="S205" t="n">
         <v>5</v>
@@ -23559,10 +23564,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>124355855</v>
+        <v>124355870</v>
       </c>
       <c r="B206" t="n">
-        <v>97128</v>
+        <v>78455</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -23571,38 +23576,38 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>222741</v>
+        <v>353</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>722944</v>
+        <v>723669</v>
       </c>
       <c r="R206" t="n">
-        <v>7544574</v>
+        <v>7544113</v>
       </c>
       <c r="S206" t="n">
         <v>5</v>
@@ -23629,12 +23634,12 @@
       </c>
       <c r="Y206" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -23661,10 +23666,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>124355546</v>
+        <v>124355570</v>
       </c>
       <c r="B207" t="n">
-        <v>105102</v>
+        <v>90977</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -23677,21 +23682,21 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>221725</v>
+        <v>5447</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
@@ -23701,10 +23706,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>723347</v>
+        <v>723343</v>
       </c>
       <c r="R207" t="n">
-        <v>7544617</v>
+        <v>7544616</v>
       </c>
       <c r="S207" t="n">
         <v>5</v>
@@ -23763,10 +23768,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>124355530</v>
+        <v>124355672</v>
       </c>
       <c r="B208" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -23775,25 +23780,25 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
@@ -23803,10 +23808,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>723178</v>
+        <v>723359</v>
       </c>
       <c r="R208" t="n">
-        <v>7545219</v>
+        <v>7545207</v>
       </c>
       <c r="S208" t="n">
         <v>5</v>
@@ -23865,10 +23870,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>124355515</v>
+        <v>124355609</v>
       </c>
       <c r="B209" t="n">
-        <v>105102</v>
+        <v>98122</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -23881,34 +23886,34 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>221725</v>
+        <v>221952</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>723720</v>
+        <v>723343</v>
       </c>
       <c r="R209" t="n">
-        <v>7544240</v>
+        <v>7544612</v>
       </c>
       <c r="S209" t="n">
         <v>5</v>
@@ -23935,12 +23940,12 @@
       </c>
       <c r="Y209" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -23967,10 +23972,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>124355857</v>
+        <v>124355538</v>
       </c>
       <c r="B210" t="n">
-        <v>97128</v>
+        <v>105102</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -23983,21 +23988,21 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>222741</v>
+        <v>221725</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -24007,10 +24012,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>723343</v>
+        <v>722917</v>
       </c>
       <c r="R210" t="n">
-        <v>7544616</v>
+        <v>7544575</v>
       </c>
       <c r="S210" t="n">
         <v>5</v>
@@ -24069,10 +24074,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>124355654</v>
+        <v>124355855</v>
       </c>
       <c r="B211" t="n">
-        <v>78151</v>
+        <v>97128</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -24081,38 +24086,38 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>498</v>
+        <v>222741</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>723693</v>
+        <v>722944</v>
       </c>
       <c r="R211" t="n">
-        <v>7544234</v>
+        <v>7544574</v>
       </c>
       <c r="S211" t="n">
         <v>5</v>
@@ -24139,12 +24144,12 @@
       </c>
       <c r="Y211" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -24171,10 +24176,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>124355541</v>
+        <v>124355851</v>
       </c>
       <c r="B212" t="n">
-        <v>105102</v>
+        <v>97128</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -24187,34 +24192,34 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>221725</v>
+        <v>222741</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>723087</v>
+        <v>723705</v>
       </c>
       <c r="R212" t="n">
-        <v>7544566</v>
+        <v>7544144</v>
       </c>
       <c r="S212" t="n">
         <v>5</v>
@@ -24241,12 +24246,12 @@
       </c>
       <c r="Y212" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -24273,7 +24278,7 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>124355542</v>
+        <v>124355515</v>
       </c>
       <c r="B213" t="n">
         <v>105102</v>
@@ -24309,14 +24314,14 @@
       <c r="I213" t="inlineStr"/>
       <c r="P213" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>723159</v>
+        <v>723720</v>
       </c>
       <c r="R213" t="n">
-        <v>7544605</v>
+        <v>7544240</v>
       </c>
       <c r="S213" t="n">
         <v>5</v>
@@ -24343,12 +24348,12 @@
       </c>
       <c r="Y213" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -24375,10 +24380,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>124355877</v>
+        <v>124355540</v>
       </c>
       <c r="B214" t="n">
-        <v>74893</v>
+        <v>105102</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -24387,38 +24392,38 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>308</v>
+        <v>221725</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>723696</v>
+        <v>723038</v>
       </c>
       <c r="R214" t="n">
-        <v>7544172</v>
+        <v>7544552</v>
       </c>
       <c r="S214" t="n">
         <v>5</v>
@@ -24445,12 +24450,12 @@
       </c>
       <c r="Y214" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -24477,10 +24482,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>124355806</v>
+        <v>124355826</v>
       </c>
       <c r="B215" t="n">
-        <v>98000</v>
+        <v>91030</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -24489,25 +24494,25 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>219795</v>
+        <v>5432</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
@@ -24517,10 +24522,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>722934</v>
+        <v>723345</v>
       </c>
       <c r="R215" t="n">
-        <v>7544572</v>
+        <v>7544616</v>
       </c>
       <c r="S215" t="n">
         <v>5</v>
@@ -24579,10 +24584,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>124355632</v>
+        <v>124355546</v>
       </c>
       <c r="B216" t="n">
-        <v>96985</v>
+        <v>105102</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -24595,34 +24600,34 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>221941</v>
+        <v>221725</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
       <c r="P216" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>723668</v>
+        <v>723347</v>
       </c>
       <c r="R216" t="n">
-        <v>7544288</v>
+        <v>7544617</v>
       </c>
       <c r="S216" t="n">
         <v>5</v>
@@ -24649,12 +24654,12 @@
       </c>
       <c r="Y216" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -24681,10 +24686,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>124355870</v>
+        <v>124355850</v>
       </c>
       <c r="B217" t="n">
-        <v>78455</v>
+        <v>97128</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -24693,25 +24698,25 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>353</v>
+        <v>222741</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -24721,10 +24726,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>723669</v>
+        <v>723616</v>
       </c>
       <c r="R217" t="n">
-        <v>7544113</v>
+        <v>7544154</v>
       </c>
       <c r="S217" t="n">
         <v>5</v>
@@ -24783,10 +24788,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>124355611</v>
+        <v>124355552</v>
       </c>
       <c r="B218" t="n">
-        <v>57529</v>
+        <v>105102</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -24795,38 +24800,38 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>100049</v>
+        <v>221725</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
       <c r="P218" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>723694</v>
+        <v>723608</v>
       </c>
       <c r="R218" t="n">
-        <v>7544233</v>
+        <v>7544580</v>
       </c>
       <c r="S218" t="n">
         <v>5</v>
@@ -24853,17 +24858,12 @@
       </c>
       <c r="Y218" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
-        </is>
-      </c>
-      <c r="AC218" t="inlineStr">
-        <is>
-          <t>hackmärken</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -24890,10 +24890,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>124355516</v>
+        <v>124355598</v>
       </c>
       <c r="B219" t="n">
-        <v>105102</v>
+        <v>79920</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -24906,34 +24906,34 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>221725</v>
+        <v>6462</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>723694</v>
+        <v>723350</v>
       </c>
       <c r="R219" t="n">
-        <v>7544160</v>
+        <v>7544621</v>
       </c>
       <c r="S219" t="n">
         <v>5</v>
@@ -24960,12 +24960,12 @@
       </c>
       <c r="Y219" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD219" t="b">

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -20805,10 +20805,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>124355654</v>
+        <v>124355515</v>
       </c>
       <c r="B179" t="n">
-        <v>78151</v>
+        <v>105102</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -20817,25 +20817,25 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>498</v>
+        <v>221725</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -20845,10 +20845,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>723693</v>
+        <v>723720</v>
       </c>
       <c r="R179" t="n">
-        <v>7544234</v>
+        <v>7544240</v>
       </c>
       <c r="S179" t="n">
         <v>5</v>
@@ -20907,10 +20907,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>124355632</v>
+        <v>124355654</v>
       </c>
       <c r="B180" t="n">
-        <v>96985</v>
+        <v>78151</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -20919,25 +20919,25 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>221941</v>
+        <v>498</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -20947,10 +20947,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>723668</v>
+        <v>723693</v>
       </c>
       <c r="R180" t="n">
-        <v>7544288</v>
+        <v>7544234</v>
       </c>
       <c r="S180" t="n">
         <v>5</v>
@@ -21009,7 +21009,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>124355513</v>
+        <v>124355546</v>
       </c>
       <c r="B181" t="n">
         <v>105102</v>
@@ -21045,14 +21045,14 @@
       <c r="I181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>723653</v>
+        <v>723347</v>
       </c>
       <c r="R181" t="n">
-        <v>7544288</v>
+        <v>7544617</v>
       </c>
       <c r="S181" t="n">
         <v>5</v>
@@ -21079,12 +21079,12 @@
       </c>
       <c r="Y181" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -21111,7 +21111,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>124355551</v>
+        <v>124355543</v>
       </c>
       <c r="B182" t="n">
         <v>105102</v>
@@ -21151,10 +21151,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>723547</v>
+        <v>723227</v>
       </c>
       <c r="R182" t="n">
-        <v>7544600</v>
+        <v>7544640</v>
       </c>
       <c r="S182" t="n">
         <v>5</v>
@@ -21213,10 +21213,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>124355806</v>
+        <v>124355548</v>
       </c>
       <c r="B183" t="n">
-        <v>98000</v>
+        <v>105102</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -21229,21 +21229,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>219795</v>
+        <v>221725</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -21253,10 +21253,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>722934</v>
+        <v>723515</v>
       </c>
       <c r="R183" t="n">
-        <v>7544572</v>
+        <v>7544632</v>
       </c>
       <c r="S183" t="n">
         <v>5</v>
@@ -21315,10 +21315,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>124355802</v>
+        <v>124355542</v>
       </c>
       <c r="B184" t="n">
-        <v>98000</v>
+        <v>105102</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -21331,34 +21331,34 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>219795</v>
+        <v>221725</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>723703</v>
+        <v>723159</v>
       </c>
       <c r="R184" t="n">
-        <v>7544232</v>
+        <v>7544605</v>
       </c>
       <c r="S184" t="n">
         <v>5</v>
@@ -21385,12 +21385,12 @@
       </c>
       <c r="Y184" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -21417,10 +21417,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>124355873</v>
+        <v>124355806</v>
       </c>
       <c r="B185" t="n">
-        <v>79926</v>
+        <v>98000</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -21433,34 +21433,34 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6463</v>
+        <v>219795</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>723684</v>
+        <v>722934</v>
       </c>
       <c r="R185" t="n">
-        <v>7544232</v>
+        <v>7544572</v>
       </c>
       <c r="S185" t="n">
         <v>5</v>
@@ -21487,12 +21487,12 @@
       </c>
       <c r="Y185" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -21519,7 +21519,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>124355542</v>
+        <v>124355530</v>
       </c>
       <c r="B186" t="n">
         <v>105102</v>
@@ -21559,10 +21559,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>723159</v>
+        <v>723178</v>
       </c>
       <c r="R186" t="n">
-        <v>7544605</v>
+        <v>7545219</v>
       </c>
       <c r="S186" t="n">
         <v>5</v>
@@ -21621,10 +21621,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>124355667</v>
+        <v>124355541</v>
       </c>
       <c r="B187" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -21633,38 +21633,38 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>723695</v>
+        <v>723087</v>
       </c>
       <c r="R187" t="n">
-        <v>7544233</v>
+        <v>7544566</v>
       </c>
       <c r="S187" t="n">
         <v>5</v>
@@ -21691,12 +21691,12 @@
       </c>
       <c r="Y187" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -21723,10 +21723,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>124355543</v>
+        <v>124355851</v>
       </c>
       <c r="B188" t="n">
-        <v>105102</v>
+        <v>97128</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -21739,34 +21739,34 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>221725</v>
+        <v>222741</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>723227</v>
+        <v>723705</v>
       </c>
       <c r="R188" t="n">
-        <v>7544640</v>
+        <v>7544144</v>
       </c>
       <c r="S188" t="n">
         <v>5</v>
@@ -21793,12 +21793,12 @@
       </c>
       <c r="Y188" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -21825,10 +21825,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>124355529</v>
+        <v>124355856</v>
       </c>
       <c r="B189" t="n">
-        <v>105102</v>
+        <v>97128</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -21841,21 +21841,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>221725</v>
+        <v>222741</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -21865,10 +21865,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>723365</v>
+        <v>723068</v>
       </c>
       <c r="R189" t="n">
-        <v>7545207</v>
+        <v>7544568</v>
       </c>
       <c r="S189" t="n">
         <v>5</v>
@@ -21927,7 +21927,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>124355544</v>
+        <v>124355516</v>
       </c>
       <c r="B190" t="n">
         <v>105102</v>
@@ -21963,14 +21963,14 @@
       <c r="I190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>723301</v>
+        <v>723694</v>
       </c>
       <c r="R190" t="n">
-        <v>7544640</v>
+        <v>7544160</v>
       </c>
       <c r="S190" t="n">
         <v>5</v>
@@ -21997,12 +21997,12 @@
       </c>
       <c r="Y190" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -22029,7 +22029,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>124355541</v>
+        <v>124355540</v>
       </c>
       <c r="B191" t="n">
         <v>105102</v>
@@ -22069,10 +22069,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>723087</v>
+        <v>723038</v>
       </c>
       <c r="R191" t="n">
-        <v>7544566</v>
+        <v>7544552</v>
       </c>
       <c r="S191" t="n">
         <v>5</v>
@@ -22131,10 +22131,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>124355857</v>
+        <v>124355609</v>
       </c>
       <c r="B192" t="n">
-        <v>97128</v>
+        <v>98122</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -22147,21 +22147,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>222741</v>
+        <v>221952</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -22174,7 +22174,7 @@
         <v>723343</v>
       </c>
       <c r="R192" t="n">
-        <v>7544616</v>
+        <v>7544612</v>
       </c>
       <c r="S192" t="n">
         <v>5</v>
@@ -22233,10 +22233,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>124355646</v>
+        <v>124355668</v>
       </c>
       <c r="B193" t="n">
-        <v>79927</v>
+        <v>98101</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -22245,25 +22245,25 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -22273,10 +22273,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>723617</v>
+        <v>723703</v>
       </c>
       <c r="R193" t="n">
-        <v>7544144</v>
+        <v>7544180</v>
       </c>
       <c r="S193" t="n">
         <v>5</v>
@@ -22335,10 +22335,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>124355666</v>
+        <v>124355870</v>
       </c>
       <c r="B194" t="n">
-        <v>98101</v>
+        <v>78455</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -22347,25 +22347,25 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -22375,10 +22375,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>723699</v>
+        <v>723669</v>
       </c>
       <c r="R194" t="n">
-        <v>7544235</v>
+        <v>7544113</v>
       </c>
       <c r="S194" t="n">
         <v>5</v>
@@ -22437,10 +22437,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>124355905</v>
+        <v>124355592</v>
       </c>
       <c r="B195" t="n">
-        <v>78194</v>
+        <v>79920</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -22449,25 +22449,25 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6437</v>
+        <v>6462</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -22477,10 +22477,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>723693</v>
+        <v>723699</v>
       </c>
       <c r="R195" t="n">
-        <v>7544182</v>
+        <v>7544155</v>
       </c>
       <c r="S195" t="n">
         <v>5</v>
@@ -22539,10 +22539,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>124355539</v>
+        <v>124355611</v>
       </c>
       <c r="B196" t="n">
-        <v>105102</v>
+        <v>57529</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -22551,38 +22551,38 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>221725</v>
+        <v>100049</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>722977</v>
+        <v>723694</v>
       </c>
       <c r="R196" t="n">
-        <v>7544571</v>
+        <v>7544233</v>
       </c>
       <c r="S196" t="n">
         <v>5</v>
@@ -22609,12 +22609,17 @@
       </c>
       <c r="Y196" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="AC196" t="inlineStr">
+        <is>
+          <t>hackmärken</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -22641,10 +22646,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>124355668</v>
+        <v>124355544</v>
       </c>
       <c r="B197" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -22653,38 +22658,38 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>723703</v>
+        <v>723301</v>
       </c>
       <c r="R197" t="n">
-        <v>7544180</v>
+        <v>7544640</v>
       </c>
       <c r="S197" t="n">
         <v>5</v>
@@ -22711,12 +22716,12 @@
       </c>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -22743,10 +22748,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>124355877</v>
+        <v>124355570</v>
       </c>
       <c r="B198" t="n">
-        <v>74893</v>
+        <v>90977</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -22755,38 +22760,38 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>308</v>
+        <v>5447</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>723696</v>
+        <v>723343</v>
       </c>
       <c r="R198" t="n">
-        <v>7544172</v>
+        <v>7544616</v>
       </c>
       <c r="S198" t="n">
         <v>5</v>
@@ -22813,12 +22818,12 @@
       </c>
       <c r="Y198" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -22845,10 +22850,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>124355611</v>
+        <v>124355873</v>
       </c>
       <c r="B199" t="n">
-        <v>57529</v>
+        <v>79926</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -22857,25 +22862,25 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -22885,10 +22890,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>723694</v>
+        <v>723684</v>
       </c>
       <c r="R199" t="n">
-        <v>7544233</v>
+        <v>7544232</v>
       </c>
       <c r="S199" t="n">
         <v>5</v>
@@ -22921,11 +22926,6 @@
       <c r="AA199" t="inlineStr">
         <is>
           <t>2024-08-09</t>
-        </is>
-      </c>
-      <c r="AC199" t="inlineStr">
-        <is>
-          <t>hackmärken</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -22952,7 +22952,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>124355548</v>
+        <v>124355513</v>
       </c>
       <c r="B200" t="n">
         <v>105102</v>
@@ -22988,14 +22988,14 @@
       <c r="I200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>723515</v>
+        <v>723653</v>
       </c>
       <c r="R200" t="n">
-        <v>7544632</v>
+        <v>7544288</v>
       </c>
       <c r="S200" t="n">
         <v>5</v>
@@ -23022,12 +23022,12 @@
       </c>
       <c r="Y200" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -23054,10 +23054,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>124355592</v>
+        <v>124355551</v>
       </c>
       <c r="B201" t="n">
-        <v>79920</v>
+        <v>105102</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -23070,34 +23070,34 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>6462</v>
+        <v>221725</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>723699</v>
+        <v>723547</v>
       </c>
       <c r="R201" t="n">
-        <v>7544155</v>
+        <v>7544600</v>
       </c>
       <c r="S201" t="n">
         <v>5</v>
@@ -23124,12 +23124,12 @@
       </c>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -23156,10 +23156,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>124355807</v>
+        <v>124355672</v>
       </c>
       <c r="B202" t="n">
-        <v>98000</v>
+        <v>98101</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -23168,25 +23168,25 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>219795</v>
+        <v>220787</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -23196,10 +23196,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>723042</v>
+        <v>723359</v>
       </c>
       <c r="R202" t="n">
-        <v>7544553</v>
+        <v>7545207</v>
       </c>
       <c r="S202" t="n">
         <v>5</v>
@@ -23258,10 +23258,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>124355516</v>
+        <v>124355826</v>
       </c>
       <c r="B203" t="n">
-        <v>105102</v>
+        <v>91030</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -23270,38 +23270,38 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>221725</v>
+        <v>5432</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>723694</v>
+        <v>723345</v>
       </c>
       <c r="R203" t="n">
-        <v>7544160</v>
+        <v>7544616</v>
       </c>
       <c r="S203" t="n">
         <v>5</v>
@@ -23328,12 +23328,12 @@
       </c>
       <c r="Y203" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -23360,10 +23360,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>124355530</v>
+        <v>124355807</v>
       </c>
       <c r="B204" t="n">
-        <v>105102</v>
+        <v>98000</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -23376,21 +23376,21 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>221725</v>
+        <v>219795</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -23400,10 +23400,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>723178</v>
+        <v>723042</v>
       </c>
       <c r="R204" t="n">
-        <v>7545219</v>
+        <v>7544553</v>
       </c>
       <c r="S204" t="n">
         <v>5</v>
@@ -23462,10 +23462,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>124355856</v>
+        <v>124355802</v>
       </c>
       <c r="B205" t="n">
-        <v>97128</v>
+        <v>98000</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -23478,34 +23478,34 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>222741</v>
+        <v>219795</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>723068</v>
+        <v>723703</v>
       </c>
       <c r="R205" t="n">
-        <v>7544568</v>
+        <v>7544232</v>
       </c>
       <c r="S205" t="n">
         <v>5</v>
@@ -23532,12 +23532,12 @@
       </c>
       <c r="Y205" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -23564,10 +23564,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>124355870</v>
+        <v>124355529</v>
       </c>
       <c r="B206" t="n">
-        <v>78455</v>
+        <v>105102</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -23576,38 +23576,38 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>353</v>
+        <v>221725</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>723669</v>
+        <v>723365</v>
       </c>
       <c r="R206" t="n">
-        <v>7544113</v>
+        <v>7545207</v>
       </c>
       <c r="S206" t="n">
         <v>5</v>
@@ -23634,12 +23634,12 @@
       </c>
       <c r="Y206" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -23666,10 +23666,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>124355570</v>
+        <v>124355598</v>
       </c>
       <c r="B207" t="n">
-        <v>90977</v>
+        <v>79920</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -23682,21 +23682,21 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
@@ -23706,10 +23706,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>723343</v>
+        <v>723350</v>
       </c>
       <c r="R207" t="n">
-        <v>7544616</v>
+        <v>7544621</v>
       </c>
       <c r="S207" t="n">
         <v>5</v>
@@ -23768,10 +23768,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>124355672</v>
+        <v>124355905</v>
       </c>
       <c r="B208" t="n">
-        <v>98101</v>
+        <v>78194</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -23780,38 +23780,38 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>220787</v>
+        <v>6437</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>723359</v>
+        <v>723693</v>
       </c>
       <c r="R208" t="n">
-        <v>7545207</v>
+        <v>7544182</v>
       </c>
       <c r="S208" t="n">
         <v>5</v>
@@ -23838,12 +23838,12 @@
       </c>
       <c r="Y208" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -23870,10 +23870,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>124355609</v>
+        <v>124355667</v>
       </c>
       <c r="B209" t="n">
-        <v>98122</v>
+        <v>98101</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -23882,38 +23882,38 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>723343</v>
+        <v>723695</v>
       </c>
       <c r="R209" t="n">
-        <v>7544612</v>
+        <v>7544233</v>
       </c>
       <c r="S209" t="n">
         <v>5</v>
@@ -23940,12 +23940,12 @@
       </c>
       <c r="Y209" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -23972,10 +23972,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>124355538</v>
+        <v>124355857</v>
       </c>
       <c r="B210" t="n">
-        <v>105102</v>
+        <v>97128</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -23988,21 +23988,21 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>221725</v>
+        <v>222741</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -24012,10 +24012,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>722917</v>
+        <v>723343</v>
       </c>
       <c r="R210" t="n">
-        <v>7544575</v>
+        <v>7544616</v>
       </c>
       <c r="S210" t="n">
         <v>5</v>
@@ -24074,10 +24074,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>124355855</v>
+        <v>124355632</v>
       </c>
       <c r="B211" t="n">
-        <v>97128</v>
+        <v>96985</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -24090,34 +24090,34 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>222741</v>
+        <v>221941</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>722944</v>
+        <v>723668</v>
       </c>
       <c r="R211" t="n">
-        <v>7544574</v>
+        <v>7544288</v>
       </c>
       <c r="S211" t="n">
         <v>5</v>
@@ -24144,12 +24144,12 @@
       </c>
       <c r="Y211" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -24176,7 +24176,7 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>124355851</v>
+        <v>124355850</v>
       </c>
       <c r="B212" t="n">
         <v>97128</v>
@@ -24216,10 +24216,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>723705</v>
+        <v>723616</v>
       </c>
       <c r="R212" t="n">
-        <v>7544144</v>
+        <v>7544154</v>
       </c>
       <c r="S212" t="n">
         <v>5</v>
@@ -24278,10 +24278,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>124355515</v>
+        <v>124355877</v>
       </c>
       <c r="B213" t="n">
-        <v>105102</v>
+        <v>74893</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -24290,25 +24290,25 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>221725</v>
+        <v>308</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -24318,10 +24318,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>723720</v>
+        <v>723696</v>
       </c>
       <c r="R213" t="n">
-        <v>7544240</v>
+        <v>7544172</v>
       </c>
       <c r="S213" t="n">
         <v>5</v>
@@ -24380,7 +24380,7 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>124355540</v>
+        <v>124355538</v>
       </c>
       <c r="B214" t="n">
         <v>105102</v>
@@ -24420,10 +24420,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>723038</v>
+        <v>722917</v>
       </c>
       <c r="R214" t="n">
-        <v>7544552</v>
+        <v>7544575</v>
       </c>
       <c r="S214" t="n">
         <v>5</v>
@@ -24482,10 +24482,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>124355826</v>
+        <v>124355539</v>
       </c>
       <c r="B215" t="n">
-        <v>91030</v>
+        <v>105102</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -24494,25 +24494,25 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>5432</v>
+        <v>221725</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
@@ -24522,10 +24522,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>723345</v>
+        <v>722977</v>
       </c>
       <c r="R215" t="n">
-        <v>7544616</v>
+        <v>7544571</v>
       </c>
       <c r="S215" t="n">
         <v>5</v>
@@ -24584,10 +24584,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>124355546</v>
+        <v>124355855</v>
       </c>
       <c r="B216" t="n">
-        <v>105102</v>
+        <v>97128</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -24600,21 +24600,21 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>221725</v>
+        <v>222741</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
@@ -24624,10 +24624,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>723347</v>
+        <v>722944</v>
       </c>
       <c r="R216" t="n">
-        <v>7544617</v>
+        <v>7544574</v>
       </c>
       <c r="S216" t="n">
         <v>5</v>
@@ -24686,10 +24686,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>124355850</v>
+        <v>124355646</v>
       </c>
       <c r="B217" t="n">
-        <v>97128</v>
+        <v>79927</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -24702,21 +24702,21 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>222741</v>
+        <v>6464</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -24726,10 +24726,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>723616</v>
+        <v>723617</v>
       </c>
       <c r="R217" t="n">
-        <v>7544154</v>
+        <v>7544144</v>
       </c>
       <c r="S217" t="n">
         <v>5</v>
@@ -24788,10 +24788,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>124355552</v>
+        <v>124355666</v>
       </c>
       <c r="B218" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -24800,38 +24800,38 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
       <c r="P218" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>723608</v>
+        <v>723699</v>
       </c>
       <c r="R218" t="n">
-        <v>7544580</v>
+        <v>7544235</v>
       </c>
       <c r="S218" t="n">
         <v>5</v>
@@ -24858,12 +24858,12 @@
       </c>
       <c r="Y218" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -24890,10 +24890,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>124355598</v>
+        <v>124355552</v>
       </c>
       <c r="B219" t="n">
-        <v>79920</v>
+        <v>105102</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -24906,21 +24906,21 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>6462</v>
+        <v>221725</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
@@ -24930,10 +24930,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>723350</v>
+        <v>723608</v>
       </c>
       <c r="R219" t="n">
-        <v>7544621</v>
+        <v>7544580</v>
       </c>
       <c r="S219" t="n">
         <v>5</v>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -22233,10 +22233,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>124355668</v>
+        <v>124355870</v>
       </c>
       <c r="B193" t="n">
-        <v>98101</v>
+        <v>78455</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -22245,25 +22245,25 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -22273,10 +22273,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>723703</v>
+        <v>723669</v>
       </c>
       <c r="R193" t="n">
-        <v>7544180</v>
+        <v>7544113</v>
       </c>
       <c r="S193" t="n">
         <v>5</v>
@@ -22335,10 +22335,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>124355870</v>
+        <v>124355668</v>
       </c>
       <c r="B194" t="n">
-        <v>78455</v>
+        <v>98101</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -22347,25 +22347,25 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -22375,10 +22375,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>723669</v>
+        <v>723703</v>
       </c>
       <c r="R194" t="n">
-        <v>7544113</v>
+        <v>7544180</v>
       </c>
       <c r="S194" t="n">
         <v>5</v>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -20805,10 +20805,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>124355515</v>
+        <v>124355826</v>
       </c>
       <c r="B179" t="n">
-        <v>105102</v>
+        <v>91030</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -20817,38 +20817,38 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>221725</v>
+        <v>5432</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>723720</v>
+        <v>723345</v>
       </c>
       <c r="R179" t="n">
-        <v>7544240</v>
+        <v>7544616</v>
       </c>
       <c r="S179" t="n">
         <v>5</v>
@@ -20875,12 +20875,12 @@
       </c>
       <c r="Y179" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -21009,10 +21009,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>124355546</v>
+        <v>124355646</v>
       </c>
       <c r="B181" t="n">
-        <v>105102</v>
+        <v>79927</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -21025,34 +21025,34 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>221725</v>
+        <v>6464</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>723347</v>
+        <v>723617</v>
       </c>
       <c r="R181" t="n">
-        <v>7544617</v>
+        <v>7544144</v>
       </c>
       <c r="S181" t="n">
         <v>5</v>
@@ -21079,12 +21079,12 @@
       </c>
       <c r="Y181" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -21111,10 +21111,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>124355543</v>
+        <v>124355806</v>
       </c>
       <c r="B182" t="n">
-        <v>105102</v>
+        <v>98000</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -21127,21 +21127,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>221725</v>
+        <v>219795</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -21151,10 +21151,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>723227</v>
+        <v>722934</v>
       </c>
       <c r="R182" t="n">
-        <v>7544640</v>
+        <v>7544572</v>
       </c>
       <c r="S182" t="n">
         <v>5</v>
@@ -21213,7 +21213,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>124355548</v>
+        <v>124355515</v>
       </c>
       <c r="B183" t="n">
         <v>105102</v>
@@ -21249,14 +21249,14 @@
       <c r="I183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>723515</v>
+        <v>723720</v>
       </c>
       <c r="R183" t="n">
-        <v>7544632</v>
+        <v>7544240</v>
       </c>
       <c r="S183" t="n">
         <v>5</v>
@@ -21283,12 +21283,12 @@
       </c>
       <c r="Y183" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -21315,10 +21315,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>124355542</v>
+        <v>124355850</v>
       </c>
       <c r="B184" t="n">
-        <v>105102</v>
+        <v>97128</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -21331,34 +21331,34 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>221725</v>
+        <v>222741</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>723159</v>
+        <v>723616</v>
       </c>
       <c r="R184" t="n">
-        <v>7544605</v>
+        <v>7544154</v>
       </c>
       <c r="S184" t="n">
         <v>5</v>
@@ -21385,12 +21385,12 @@
       </c>
       <c r="Y184" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -21417,10 +21417,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>124355806</v>
+        <v>124355543</v>
       </c>
       <c r="B185" t="n">
-        <v>98000</v>
+        <v>105102</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -21433,21 +21433,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>219795</v>
+        <v>221725</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -21457,10 +21457,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>722934</v>
+        <v>723227</v>
       </c>
       <c r="R185" t="n">
-        <v>7544572</v>
+        <v>7544640</v>
       </c>
       <c r="S185" t="n">
         <v>5</v>
@@ -21519,7 +21519,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>124355530</v>
+        <v>124355540</v>
       </c>
       <c r="B186" t="n">
         <v>105102</v>
@@ -21559,10 +21559,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>723178</v>
+        <v>723038</v>
       </c>
       <c r="R186" t="n">
-        <v>7545219</v>
+        <v>7544552</v>
       </c>
       <c r="S186" t="n">
         <v>5</v>
@@ -21621,10 +21621,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>124355541</v>
+        <v>124355667</v>
       </c>
       <c r="B187" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -21633,38 +21633,38 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>723087</v>
+        <v>723695</v>
       </c>
       <c r="R187" t="n">
-        <v>7544566</v>
+        <v>7544233</v>
       </c>
       <c r="S187" t="n">
         <v>5</v>
@@ -21691,12 +21691,12 @@
       </c>
       <c r="Y187" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -21723,10 +21723,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>124355851</v>
+        <v>124355873</v>
       </c>
       <c r="B188" t="n">
-        <v>97128</v>
+        <v>79926</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -21739,21 +21739,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>222741</v>
+        <v>6463</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -21763,10 +21763,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>723705</v>
+        <v>723684</v>
       </c>
       <c r="R188" t="n">
-        <v>7544144</v>
+        <v>7544232</v>
       </c>
       <c r="S188" t="n">
         <v>5</v>
@@ -21825,7 +21825,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>124355856</v>
+        <v>124355857</v>
       </c>
       <c r="B189" t="n">
         <v>97128</v>
@@ -21865,10 +21865,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>723068</v>
+        <v>723343</v>
       </c>
       <c r="R189" t="n">
-        <v>7544568</v>
+        <v>7544616</v>
       </c>
       <c r="S189" t="n">
         <v>5</v>
@@ -21927,7 +21927,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>124355516</v>
+        <v>124355530</v>
       </c>
       <c r="B190" t="n">
         <v>105102</v>
@@ -21963,14 +21963,14 @@
       <c r="I190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>723694</v>
+        <v>723178</v>
       </c>
       <c r="R190" t="n">
-        <v>7544160</v>
+        <v>7545219</v>
       </c>
       <c r="S190" t="n">
         <v>5</v>
@@ -21997,12 +21997,12 @@
       </c>
       <c r="Y190" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -22029,10 +22029,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>124355540</v>
+        <v>124355609</v>
       </c>
       <c r="B191" t="n">
-        <v>105102</v>
+        <v>98122</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -22045,21 +22045,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>221725</v>
+        <v>221952</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -22069,10 +22069,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>723038</v>
+        <v>723343</v>
       </c>
       <c r="R191" t="n">
-        <v>7544552</v>
+        <v>7544612</v>
       </c>
       <c r="S191" t="n">
         <v>5</v>
@@ -22131,10 +22131,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>124355609</v>
+        <v>124355672</v>
       </c>
       <c r="B192" t="n">
-        <v>98122</v>
+        <v>98101</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -22143,25 +22143,25 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -22171,10 +22171,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>723343</v>
+        <v>723359</v>
       </c>
       <c r="R192" t="n">
-        <v>7544612</v>
+        <v>7545207</v>
       </c>
       <c r="S192" t="n">
         <v>5</v>
@@ -22233,10 +22233,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>124355870</v>
+        <v>124355548</v>
       </c>
       <c r="B193" t="n">
-        <v>78455</v>
+        <v>105102</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -22245,38 +22245,38 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>353</v>
+        <v>221725</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>723669</v>
+        <v>723515</v>
       </c>
       <c r="R193" t="n">
-        <v>7544113</v>
+        <v>7544632</v>
       </c>
       <c r="S193" t="n">
         <v>5</v>
@@ -22303,12 +22303,12 @@
       </c>
       <c r="Y193" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -22335,10 +22335,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>124355668</v>
+        <v>124355855</v>
       </c>
       <c r="B194" t="n">
-        <v>98101</v>
+        <v>97128</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -22347,38 +22347,38 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>220787</v>
+        <v>222741</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>723703</v>
+        <v>722944</v>
       </c>
       <c r="R194" t="n">
-        <v>7544180</v>
+        <v>7544574</v>
       </c>
       <c r="S194" t="n">
         <v>5</v>
@@ -22405,12 +22405,12 @@
       </c>
       <c r="Y194" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -22437,10 +22437,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>124355592</v>
+        <v>124355542</v>
       </c>
       <c r="B195" t="n">
-        <v>79920</v>
+        <v>105102</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -22453,34 +22453,34 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6462</v>
+        <v>221725</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>723699</v>
+        <v>723159</v>
       </c>
       <c r="R195" t="n">
-        <v>7544155</v>
+        <v>7544605</v>
       </c>
       <c r="S195" t="n">
         <v>5</v>
@@ -22507,12 +22507,12 @@
       </c>
       <c r="Y195" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -22539,10 +22539,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>124355611</v>
+        <v>124355856</v>
       </c>
       <c r="B196" t="n">
-        <v>57529</v>
+        <v>97128</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -22551,38 +22551,38 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>100049</v>
+        <v>222741</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>723694</v>
+        <v>723068</v>
       </c>
       <c r="R196" t="n">
-        <v>7544233</v>
+        <v>7544568</v>
       </c>
       <c r="S196" t="n">
         <v>5</v>
@@ -22609,17 +22609,12 @@
       </c>
       <c r="Y196" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
-        </is>
-      </c>
-      <c r="AC196" t="inlineStr">
-        <is>
-          <t>hackmärken</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -22646,10 +22641,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>124355544</v>
+        <v>124355807</v>
       </c>
       <c r="B197" t="n">
-        <v>105102</v>
+        <v>98000</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -22662,21 +22657,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>221725</v>
+        <v>219795</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -22686,10 +22681,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>723301</v>
+        <v>723042</v>
       </c>
       <c r="R197" t="n">
-        <v>7544640</v>
+        <v>7544553</v>
       </c>
       <c r="S197" t="n">
         <v>5</v>
@@ -22748,10 +22743,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>124355570</v>
+        <v>124355666</v>
       </c>
       <c r="B198" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -22760,38 +22755,38 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>723343</v>
+        <v>723699</v>
       </c>
       <c r="R198" t="n">
-        <v>7544616</v>
+        <v>7544235</v>
       </c>
       <c r="S198" t="n">
         <v>5</v>
@@ -22818,12 +22813,12 @@
       </c>
       <c r="Y198" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -22850,10 +22845,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>124355873</v>
+        <v>124355611</v>
       </c>
       <c r="B199" t="n">
-        <v>79926</v>
+        <v>57529</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -22862,25 +22857,25 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6463</v>
+        <v>100049</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -22890,10 +22885,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>723684</v>
+        <v>723694</v>
       </c>
       <c r="R199" t="n">
-        <v>7544232</v>
+        <v>7544233</v>
       </c>
       <c r="S199" t="n">
         <v>5</v>
@@ -22926,6 +22921,11 @@
       <c r="AA199" t="inlineStr">
         <is>
           <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="AC199" t="inlineStr">
+        <is>
+          <t>hackmärken</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -22952,10 +22952,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>124355513</v>
+        <v>124355870</v>
       </c>
       <c r="B200" t="n">
-        <v>105102</v>
+        <v>78455</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -22964,25 +22964,25 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>221725</v>
+        <v>353</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -22992,10 +22992,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>723653</v>
+        <v>723669</v>
       </c>
       <c r="R200" t="n">
-        <v>7544288</v>
+        <v>7544113</v>
       </c>
       <c r="S200" t="n">
         <v>5</v>
@@ -23156,10 +23156,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>124355672</v>
+        <v>124355592</v>
       </c>
       <c r="B202" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -23168,38 +23168,38 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>723359</v>
+        <v>723699</v>
       </c>
       <c r="R202" t="n">
-        <v>7545207</v>
+        <v>7544155</v>
       </c>
       <c r="S202" t="n">
         <v>5</v>
@@ -23226,12 +23226,12 @@
       </c>
       <c r="Y202" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -23258,10 +23258,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>124355826</v>
+        <v>124355538</v>
       </c>
       <c r="B203" t="n">
-        <v>91030</v>
+        <v>105102</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -23270,25 +23270,25 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>5432</v>
+        <v>221725</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -23298,10 +23298,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>723345</v>
+        <v>722917</v>
       </c>
       <c r="R203" t="n">
-        <v>7544616</v>
+        <v>7544575</v>
       </c>
       <c r="S203" t="n">
         <v>5</v>
@@ -23360,10 +23360,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>124355807</v>
+        <v>124355541</v>
       </c>
       <c r="B204" t="n">
-        <v>98000</v>
+        <v>105102</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -23376,21 +23376,21 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>219795</v>
+        <v>221725</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -23400,10 +23400,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>723042</v>
+        <v>723087</v>
       </c>
       <c r="R204" t="n">
-        <v>7544553</v>
+        <v>7544566</v>
       </c>
       <c r="S204" t="n">
         <v>5</v>
@@ -23462,10 +23462,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>124355802</v>
+        <v>124355851</v>
       </c>
       <c r="B205" t="n">
-        <v>98000</v>
+        <v>97128</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -23478,21 +23478,21 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>219795</v>
+        <v>222741</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -23502,10 +23502,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>723703</v>
+        <v>723705</v>
       </c>
       <c r="R205" t="n">
-        <v>7544232</v>
+        <v>7544144</v>
       </c>
       <c r="S205" t="n">
         <v>5</v>
@@ -23564,10 +23564,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>124355529</v>
+        <v>124355802</v>
       </c>
       <c r="B206" t="n">
-        <v>105102</v>
+        <v>98000</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -23580,34 +23580,34 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>221725</v>
+        <v>219795</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>723365</v>
+        <v>723703</v>
       </c>
       <c r="R206" t="n">
-        <v>7545207</v>
+        <v>7544232</v>
       </c>
       <c r="S206" t="n">
         <v>5</v>
@@ -23634,12 +23634,12 @@
       </c>
       <c r="Y206" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -23666,10 +23666,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>124355598</v>
+        <v>124355632</v>
       </c>
       <c r="B207" t="n">
-        <v>79920</v>
+        <v>96985</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -23682,34 +23682,34 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>6462</v>
+        <v>221941</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>723350</v>
+        <v>723668</v>
       </c>
       <c r="R207" t="n">
-        <v>7544621</v>
+        <v>7544288</v>
       </c>
       <c r="S207" t="n">
         <v>5</v>
@@ -23736,12 +23736,12 @@
       </c>
       <c r="Y207" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -23768,10 +23768,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>124355905</v>
+        <v>124355539</v>
       </c>
       <c r="B208" t="n">
-        <v>78194</v>
+        <v>105102</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -23780,38 +23780,38 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>6437</v>
+        <v>221725</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>723693</v>
+        <v>722977</v>
       </c>
       <c r="R208" t="n">
-        <v>7544182</v>
+        <v>7544571</v>
       </c>
       <c r="S208" t="n">
         <v>5</v>
@@ -23838,12 +23838,12 @@
       </c>
       <c r="Y208" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -23870,10 +23870,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>124355667</v>
+        <v>124355598</v>
       </c>
       <c r="B209" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -23882,38 +23882,38 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>723695</v>
+        <v>723350</v>
       </c>
       <c r="R209" t="n">
-        <v>7544233</v>
+        <v>7544621</v>
       </c>
       <c r="S209" t="n">
         <v>5</v>
@@ -23940,12 +23940,12 @@
       </c>
       <c r="Y209" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -23972,10 +23972,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>124355857</v>
+        <v>124355529</v>
       </c>
       <c r="B210" t="n">
-        <v>97128</v>
+        <v>105102</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -23988,21 +23988,21 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>222741</v>
+        <v>221725</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -24012,10 +24012,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>723343</v>
+        <v>723365</v>
       </c>
       <c r="R210" t="n">
-        <v>7544616</v>
+        <v>7545207</v>
       </c>
       <c r="S210" t="n">
         <v>5</v>
@@ -24074,10 +24074,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>124355632</v>
+        <v>124355570</v>
       </c>
       <c r="B211" t="n">
-        <v>96985</v>
+        <v>90977</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -24090,34 +24090,34 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>221941</v>
+        <v>5447</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>723668</v>
+        <v>723343</v>
       </c>
       <c r="R211" t="n">
-        <v>7544288</v>
+        <v>7544616</v>
       </c>
       <c r="S211" t="n">
         <v>5</v>
@@ -24144,12 +24144,12 @@
       </c>
       <c r="Y211" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -24176,10 +24176,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>124355850</v>
+        <v>124355552</v>
       </c>
       <c r="B212" t="n">
-        <v>97128</v>
+        <v>105102</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -24192,34 +24192,34 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>222741</v>
+        <v>221725</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>723616</v>
+        <v>723608</v>
       </c>
       <c r="R212" t="n">
-        <v>7544154</v>
+        <v>7544580</v>
       </c>
       <c r="S212" t="n">
         <v>5</v>
@@ -24246,12 +24246,12 @@
       </c>
       <c r="Y212" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -24278,10 +24278,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>124355877</v>
+        <v>124355513</v>
       </c>
       <c r="B213" t="n">
-        <v>74893</v>
+        <v>105102</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -24290,25 +24290,25 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>308</v>
+        <v>221725</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -24318,10 +24318,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>723696</v>
+        <v>723653</v>
       </c>
       <c r="R213" t="n">
-        <v>7544172</v>
+        <v>7544288</v>
       </c>
       <c r="S213" t="n">
         <v>5</v>
@@ -24380,7 +24380,7 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>124355538</v>
+        <v>124355546</v>
       </c>
       <c r="B214" t="n">
         <v>105102</v>
@@ -24420,10 +24420,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>722917</v>
+        <v>723347</v>
       </c>
       <c r="R214" t="n">
-        <v>7544575</v>
+        <v>7544617</v>
       </c>
       <c r="S214" t="n">
         <v>5</v>
@@ -24482,10 +24482,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>124355539</v>
+        <v>124355905</v>
       </c>
       <c r="B215" t="n">
-        <v>105102</v>
+        <v>78194</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -24494,38 +24494,38 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>221725</v>
+        <v>6437</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
       <c r="P215" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>722977</v>
+        <v>723693</v>
       </c>
       <c r="R215" t="n">
-        <v>7544571</v>
+        <v>7544182</v>
       </c>
       <c r="S215" t="n">
         <v>5</v>
@@ -24552,12 +24552,12 @@
       </c>
       <c r="Y215" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -24584,10 +24584,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>124355855</v>
+        <v>124355668</v>
       </c>
       <c r="B216" t="n">
-        <v>97128</v>
+        <v>98101</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -24596,38 +24596,38 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>222741</v>
+        <v>220787</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
       <c r="P216" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>722944</v>
+        <v>723703</v>
       </c>
       <c r="R216" t="n">
-        <v>7544574</v>
+        <v>7544180</v>
       </c>
       <c r="S216" t="n">
         <v>5</v>
@@ -24654,12 +24654,12 @@
       </c>
       <c r="Y216" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -24686,10 +24686,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>124355646</v>
+        <v>124355516</v>
       </c>
       <c r="B217" t="n">
-        <v>79927</v>
+        <v>105102</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -24702,21 +24702,21 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>6464</v>
+        <v>221725</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -24726,10 +24726,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>723617</v>
+        <v>723694</v>
       </c>
       <c r="R217" t="n">
-        <v>7544144</v>
+        <v>7544160</v>
       </c>
       <c r="S217" t="n">
         <v>5</v>
@@ -24788,10 +24788,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>124355666</v>
+        <v>124355877</v>
       </c>
       <c r="B218" t="n">
-        <v>98101</v>
+        <v>74893</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -24800,25 +24800,25 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -24828,10 +24828,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>723699</v>
+        <v>723696</v>
       </c>
       <c r="R218" t="n">
-        <v>7544235</v>
+        <v>7544172</v>
       </c>
       <c r="S218" t="n">
         <v>5</v>
@@ -24890,7 +24890,7 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>124355552</v>
+        <v>124355544</v>
       </c>
       <c r="B219" t="n">
         <v>105102</v>
@@ -24930,10 +24930,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>723608</v>
+        <v>723301</v>
       </c>
       <c r="R219" t="n">
-        <v>7544580</v>
+        <v>7544640</v>
       </c>
       <c r="S219" t="n">
         <v>5</v>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -21927,10 +21927,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>124355530</v>
+        <v>124355609</v>
       </c>
       <c r="B190" t="n">
-        <v>105102</v>
+        <v>98122</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -21943,21 +21943,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>221725</v>
+        <v>221952</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -21967,10 +21967,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>723178</v>
+        <v>723343</v>
       </c>
       <c r="R190" t="n">
-        <v>7545219</v>
+        <v>7544612</v>
       </c>
       <c r="S190" t="n">
         <v>5</v>
@@ -22029,10 +22029,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>124355609</v>
+        <v>124355530</v>
       </c>
       <c r="B191" t="n">
-        <v>98122</v>
+        <v>105102</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -22045,21 +22045,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>221952</v>
+        <v>221725</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -22069,10 +22069,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>723343</v>
+        <v>723178</v>
       </c>
       <c r="R191" t="n">
-        <v>7544612</v>
+        <v>7545219</v>
       </c>
       <c r="S191" t="n">
         <v>5</v>
@@ -23156,10 +23156,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>124355592</v>
+        <v>124355802</v>
       </c>
       <c r="B202" t="n">
-        <v>79920</v>
+        <v>98000</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -23172,21 +23172,21 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>6462</v>
+        <v>219795</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -23196,10 +23196,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>723699</v>
+        <v>723703</v>
       </c>
       <c r="R202" t="n">
-        <v>7544155</v>
+        <v>7544232</v>
       </c>
       <c r="S202" t="n">
         <v>5</v>
@@ -23258,10 +23258,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>124355538</v>
+        <v>124355632</v>
       </c>
       <c r="B203" t="n">
-        <v>105102</v>
+        <v>96985</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -23274,34 +23274,34 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>221725</v>
+        <v>221941</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>722917</v>
+        <v>723668</v>
       </c>
       <c r="R203" t="n">
-        <v>7544575</v>
+        <v>7544288</v>
       </c>
       <c r="S203" t="n">
         <v>5</v>
@@ -23328,12 +23328,12 @@
       </c>
       <c r="Y203" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -23360,10 +23360,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>124355541</v>
+        <v>124355851</v>
       </c>
       <c r="B204" t="n">
-        <v>105102</v>
+        <v>97128</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -23376,34 +23376,34 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>221725</v>
+        <v>222741</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>723087</v>
+        <v>723705</v>
       </c>
       <c r="R204" t="n">
-        <v>7544566</v>
+        <v>7544144</v>
       </c>
       <c r="S204" t="n">
         <v>5</v>
@@ -23430,12 +23430,12 @@
       </c>
       <c r="Y204" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -23462,10 +23462,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>124355851</v>
+        <v>124355592</v>
       </c>
       <c r="B205" t="n">
-        <v>97128</v>
+        <v>79920</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -23478,21 +23478,21 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>222741</v>
+        <v>6462</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -23502,10 +23502,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>723705</v>
+        <v>723699</v>
       </c>
       <c r="R205" t="n">
-        <v>7544144</v>
+        <v>7544155</v>
       </c>
       <c r="S205" t="n">
         <v>5</v>
@@ -23564,10 +23564,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>124355802</v>
+        <v>124355538</v>
       </c>
       <c r="B206" t="n">
-        <v>98000</v>
+        <v>105102</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -23580,34 +23580,34 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>219795</v>
+        <v>221725</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>723703</v>
+        <v>722917</v>
       </c>
       <c r="R206" t="n">
-        <v>7544232</v>
+        <v>7544575</v>
       </c>
       <c r="S206" t="n">
         <v>5</v>
@@ -23634,12 +23634,12 @@
       </c>
       <c r="Y206" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -23666,10 +23666,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>124355632</v>
+        <v>124355541</v>
       </c>
       <c r="B207" t="n">
-        <v>96985</v>
+        <v>105102</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -23682,34 +23682,34 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>221941</v>
+        <v>221725</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>723668</v>
+        <v>723087</v>
       </c>
       <c r="R207" t="n">
-        <v>7544288</v>
+        <v>7544566</v>
       </c>
       <c r="S207" t="n">
         <v>5</v>
@@ -23736,12 +23736,12 @@
       </c>
       <c r="Y207" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -23768,10 +23768,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>124355539</v>
+        <v>124355598</v>
       </c>
       <c r="B208" t="n">
-        <v>105102</v>
+        <v>79920</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -23784,21 +23784,21 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>221725</v>
+        <v>6462</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
@@ -23808,10 +23808,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>722977</v>
+        <v>723350</v>
       </c>
       <c r="R208" t="n">
-        <v>7544571</v>
+        <v>7544621</v>
       </c>
       <c r="S208" t="n">
         <v>5</v>
@@ -23870,10 +23870,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>124355598</v>
+        <v>124355529</v>
       </c>
       <c r="B209" t="n">
-        <v>79920</v>
+        <v>105102</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -23886,21 +23886,21 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>6462</v>
+        <v>221725</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -23910,10 +23910,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>723350</v>
+        <v>723365</v>
       </c>
       <c r="R209" t="n">
-        <v>7544621</v>
+        <v>7545207</v>
       </c>
       <c r="S209" t="n">
         <v>5</v>
@@ -23972,7 +23972,7 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>124355529</v>
+        <v>124355539</v>
       </c>
       <c r="B210" t="n">
         <v>105102</v>
@@ -24012,10 +24012,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>723365</v>
+        <v>722977</v>
       </c>
       <c r="R210" t="n">
-        <v>7545207</v>
+        <v>7544571</v>
       </c>
       <c r="S210" t="n">
         <v>5</v>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -20805,10 +20805,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>124355826</v>
+        <v>124355646</v>
       </c>
       <c r="B179" t="n">
-        <v>91030</v>
+        <v>79927</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -20817,38 +20817,38 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>723345</v>
+        <v>723617</v>
       </c>
       <c r="R179" t="n">
-        <v>7544616</v>
+        <v>7544144</v>
       </c>
       <c r="S179" t="n">
         <v>5</v>
@@ -20875,12 +20875,12 @@
       </c>
       <c r="Y179" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -20907,10 +20907,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>124355654</v>
+        <v>124355826</v>
       </c>
       <c r="B180" t="n">
-        <v>78151</v>
+        <v>91030</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -20919,38 +20919,38 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>498</v>
+        <v>5432</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>723693</v>
+        <v>723345</v>
       </c>
       <c r="R180" t="n">
-        <v>7544234</v>
+        <v>7544616</v>
       </c>
       <c r="S180" t="n">
         <v>5</v>
@@ -20977,12 +20977,12 @@
       </c>
       <c r="Y180" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -21009,10 +21009,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>124355646</v>
+        <v>124355654</v>
       </c>
       <c r="B181" t="n">
-        <v>79927</v>
+        <v>78151</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -21021,25 +21021,25 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6464</v>
+        <v>498</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -21049,10 +21049,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>723617</v>
+        <v>723693</v>
       </c>
       <c r="R181" t="n">
-        <v>7544144</v>
+        <v>7544234</v>
       </c>
       <c r="S181" t="n">
         <v>5</v>
@@ -21927,10 +21927,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>124355609</v>
+        <v>124355530</v>
       </c>
       <c r="B190" t="n">
-        <v>98122</v>
+        <v>105102</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -21943,21 +21943,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>221952</v>
+        <v>221725</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -21967,10 +21967,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>723343</v>
+        <v>723178</v>
       </c>
       <c r="R190" t="n">
-        <v>7544612</v>
+        <v>7545219</v>
       </c>
       <c r="S190" t="n">
         <v>5</v>
@@ -22029,10 +22029,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>124355530</v>
+        <v>124355609</v>
       </c>
       <c r="B191" t="n">
-        <v>105102</v>
+        <v>98122</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -22045,21 +22045,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>221725</v>
+        <v>221952</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -22069,10 +22069,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>723178</v>
+        <v>723343</v>
       </c>
       <c r="R191" t="n">
-        <v>7545219</v>
+        <v>7544612</v>
       </c>
       <c r="S191" t="n">
         <v>5</v>
@@ -22641,10 +22641,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>124355807</v>
+        <v>124355666</v>
       </c>
       <c r="B197" t="n">
-        <v>98000</v>
+        <v>98101</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -22653,38 +22653,38 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>219795</v>
+        <v>220787</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>723042</v>
+        <v>723699</v>
       </c>
       <c r="R197" t="n">
-        <v>7544553</v>
+        <v>7544235</v>
       </c>
       <c r="S197" t="n">
         <v>5</v>
@@ -22711,12 +22711,12 @@
       </c>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -22743,10 +22743,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>124355666</v>
+        <v>124355807</v>
       </c>
       <c r="B198" t="n">
-        <v>98101</v>
+        <v>98000</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -22755,38 +22755,38 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>220787</v>
+        <v>219795</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>723699</v>
+        <v>723042</v>
       </c>
       <c r="R198" t="n">
-        <v>7544235</v>
+        <v>7544553</v>
       </c>
       <c r="S198" t="n">
         <v>5</v>
@@ -22813,12 +22813,12 @@
       </c>
       <c r="Y198" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD198" t="b">

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -20805,10 +20805,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>124355646</v>
+        <v>124355611</v>
       </c>
       <c r="B179" t="n">
-        <v>79927</v>
+        <v>57529</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -20817,25 +20817,25 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6464</v>
+        <v>100049</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -20845,10 +20845,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>723617</v>
+        <v>723694</v>
       </c>
       <c r="R179" t="n">
-        <v>7544144</v>
+        <v>7544233</v>
       </c>
       <c r="S179" t="n">
         <v>5</v>
@@ -20881,6 +20881,11 @@
       <c r="AA179" t="inlineStr">
         <is>
           <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="AC179" t="inlineStr">
+        <is>
+          <t>hackmärken</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -20907,10 +20912,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>124355826</v>
+        <v>124355541</v>
       </c>
       <c r="B180" t="n">
-        <v>91030</v>
+        <v>105102</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -20919,25 +20924,25 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>5432</v>
+        <v>221725</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -20947,10 +20952,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>723345</v>
+        <v>723087</v>
       </c>
       <c r="R180" t="n">
-        <v>7544616</v>
+        <v>7544566</v>
       </c>
       <c r="S180" t="n">
         <v>5</v>
@@ -21009,10 +21014,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>124355654</v>
+        <v>124355540</v>
       </c>
       <c r="B181" t="n">
-        <v>78151</v>
+        <v>105102</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -21021,38 +21026,38 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>498</v>
+        <v>221725</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>723693</v>
+        <v>723038</v>
       </c>
       <c r="R181" t="n">
-        <v>7544234</v>
+        <v>7544552</v>
       </c>
       <c r="S181" t="n">
         <v>5</v>
@@ -21079,12 +21084,12 @@
       </c>
       <c r="Y181" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -21111,10 +21116,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>124355806</v>
+        <v>124355515</v>
       </c>
       <c r="B182" t="n">
-        <v>98000</v>
+        <v>105102</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -21127,34 +21132,34 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>219795</v>
+        <v>221725</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>722934</v>
+        <v>723720</v>
       </c>
       <c r="R182" t="n">
-        <v>7544572</v>
+        <v>7544240</v>
       </c>
       <c r="S182" t="n">
         <v>5</v>
@@ -21181,12 +21186,12 @@
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -21213,10 +21218,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>124355515</v>
+        <v>124355855</v>
       </c>
       <c r="B183" t="n">
-        <v>105102</v>
+        <v>97128</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -21229,34 +21234,34 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>221725</v>
+        <v>222741</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>723720</v>
+        <v>722944</v>
       </c>
       <c r="R183" t="n">
-        <v>7544240</v>
+        <v>7544574</v>
       </c>
       <c r="S183" t="n">
         <v>5</v>
@@ -21283,12 +21288,12 @@
       </c>
       <c r="Y183" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -21315,10 +21320,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>124355850</v>
+        <v>124355592</v>
       </c>
       <c r="B184" t="n">
-        <v>97128</v>
+        <v>79920</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -21331,21 +21336,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>222741</v>
+        <v>6462</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -21355,10 +21360,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>723616</v>
+        <v>723699</v>
       </c>
       <c r="R184" t="n">
-        <v>7544154</v>
+        <v>7544155</v>
       </c>
       <c r="S184" t="n">
         <v>5</v>
@@ -21417,7 +21422,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>124355543</v>
+        <v>124355551</v>
       </c>
       <c r="B185" t="n">
         <v>105102</v>
@@ -21457,10 +21462,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>723227</v>
+        <v>723547</v>
       </c>
       <c r="R185" t="n">
-        <v>7544640</v>
+        <v>7544600</v>
       </c>
       <c r="S185" t="n">
         <v>5</v>
@@ -21519,10 +21524,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>124355540</v>
+        <v>124355856</v>
       </c>
       <c r="B186" t="n">
-        <v>105102</v>
+        <v>97128</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -21535,21 +21540,21 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>221725</v>
+        <v>222741</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -21559,10 +21564,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>723038</v>
+        <v>723068</v>
       </c>
       <c r="R186" t="n">
-        <v>7544552</v>
+        <v>7544568</v>
       </c>
       <c r="S186" t="n">
         <v>5</v>
@@ -21621,10 +21626,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>124355667</v>
+        <v>124355850</v>
       </c>
       <c r="B187" t="n">
-        <v>98101</v>
+        <v>97128</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -21633,25 +21638,25 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>220787</v>
+        <v>222741</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -21661,10 +21666,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>723695</v>
+        <v>723616</v>
       </c>
       <c r="R187" t="n">
-        <v>7544233</v>
+        <v>7544154</v>
       </c>
       <c r="S187" t="n">
         <v>5</v>
@@ -21723,10 +21728,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>124355873</v>
+        <v>124355870</v>
       </c>
       <c r="B188" t="n">
-        <v>79926</v>
+        <v>78455</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -21735,25 +21740,25 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6463</v>
+        <v>353</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -21763,10 +21768,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>723684</v>
+        <v>723669</v>
       </c>
       <c r="R188" t="n">
-        <v>7544232</v>
+        <v>7544113</v>
       </c>
       <c r="S188" t="n">
         <v>5</v>
@@ -21825,10 +21830,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>124355857</v>
+        <v>124355598</v>
       </c>
       <c r="B189" t="n">
-        <v>97128</v>
+        <v>79920</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -21841,21 +21846,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>222741</v>
+        <v>6462</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -21865,10 +21870,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>723343</v>
+        <v>723350</v>
       </c>
       <c r="R189" t="n">
-        <v>7544616</v>
+        <v>7544621</v>
       </c>
       <c r="S189" t="n">
         <v>5</v>
@@ -21927,7 +21932,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>124355530</v>
+        <v>124355538</v>
       </c>
       <c r="B190" t="n">
         <v>105102</v>
@@ -21967,10 +21972,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>723178</v>
+        <v>722917</v>
       </c>
       <c r="R190" t="n">
-        <v>7545219</v>
+        <v>7544575</v>
       </c>
       <c r="S190" t="n">
         <v>5</v>
@@ -22029,10 +22034,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>124355609</v>
+        <v>124355548</v>
       </c>
       <c r="B191" t="n">
-        <v>98122</v>
+        <v>105102</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -22045,21 +22050,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>221952</v>
+        <v>221725</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -22069,10 +22074,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>723343</v>
+        <v>723515</v>
       </c>
       <c r="R191" t="n">
-        <v>7544612</v>
+        <v>7544632</v>
       </c>
       <c r="S191" t="n">
         <v>5</v>
@@ -22131,10 +22136,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>124355672</v>
+        <v>124355546</v>
       </c>
       <c r="B192" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -22143,25 +22148,25 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -22171,10 +22176,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>723359</v>
+        <v>723347</v>
       </c>
       <c r="R192" t="n">
-        <v>7545207</v>
+        <v>7544617</v>
       </c>
       <c r="S192" t="n">
         <v>5</v>
@@ -22233,7 +22238,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>124355548</v>
+        <v>124355542</v>
       </c>
       <c r="B193" t="n">
         <v>105102</v>
@@ -22273,10 +22278,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>723515</v>
+        <v>723159</v>
       </c>
       <c r="R193" t="n">
-        <v>7544632</v>
+        <v>7544605</v>
       </c>
       <c r="S193" t="n">
         <v>5</v>
@@ -22335,10 +22340,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>124355855</v>
+        <v>124355529</v>
       </c>
       <c r="B194" t="n">
-        <v>97128</v>
+        <v>105102</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -22351,21 +22356,21 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>222741</v>
+        <v>221725</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -22375,10 +22380,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>722944</v>
+        <v>723365</v>
       </c>
       <c r="R194" t="n">
-        <v>7544574</v>
+        <v>7545207</v>
       </c>
       <c r="S194" t="n">
         <v>5</v>
@@ -22437,10 +22442,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>124355542</v>
+        <v>124355654</v>
       </c>
       <c r="B195" t="n">
-        <v>105102</v>
+        <v>78151</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -22449,38 +22454,38 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>221725</v>
+        <v>498</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>723159</v>
+        <v>723693</v>
       </c>
       <c r="R195" t="n">
-        <v>7544605</v>
+        <v>7544234</v>
       </c>
       <c r="S195" t="n">
         <v>5</v>
@@ -22507,12 +22512,12 @@
       </c>
       <c r="Y195" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -22539,10 +22544,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>124355856</v>
+        <v>124355513</v>
       </c>
       <c r="B196" t="n">
-        <v>97128</v>
+        <v>105102</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -22555,34 +22560,34 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>222741</v>
+        <v>221725</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>723068</v>
+        <v>723653</v>
       </c>
       <c r="R196" t="n">
-        <v>7544568</v>
+        <v>7544288</v>
       </c>
       <c r="S196" t="n">
         <v>5</v>
@@ -22609,12 +22614,12 @@
       </c>
       <c r="Y196" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -22641,10 +22646,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>124355666</v>
+        <v>124355530</v>
       </c>
       <c r="B197" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -22653,38 +22658,38 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>723699</v>
+        <v>723178</v>
       </c>
       <c r="R197" t="n">
-        <v>7544235</v>
+        <v>7545219</v>
       </c>
       <c r="S197" t="n">
         <v>5</v>
@@ -22711,12 +22716,12 @@
       </c>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -22743,10 +22748,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>124355807</v>
+        <v>124355905</v>
       </c>
       <c r="B198" t="n">
-        <v>98000</v>
+        <v>78194</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -22755,38 +22760,38 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>219795</v>
+        <v>6437</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>723042</v>
+        <v>723693</v>
       </c>
       <c r="R198" t="n">
-        <v>7544553</v>
+        <v>7544182</v>
       </c>
       <c r="S198" t="n">
         <v>5</v>
@@ -22813,12 +22818,12 @@
       </c>
       <c r="Y198" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -22845,10 +22850,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>124355611</v>
+        <v>124355851</v>
       </c>
       <c r="B199" t="n">
-        <v>57529</v>
+        <v>97128</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -22857,25 +22862,25 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>100049</v>
+        <v>222741</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -22885,10 +22890,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>723694</v>
+        <v>723705</v>
       </c>
       <c r="R199" t="n">
-        <v>7544233</v>
+        <v>7544144</v>
       </c>
       <c r="S199" t="n">
         <v>5</v>
@@ -22921,11 +22926,6 @@
       <c r="AA199" t="inlineStr">
         <is>
           <t>2024-08-09</t>
-        </is>
-      </c>
-      <c r="AC199" t="inlineStr">
-        <is>
-          <t>hackmärken</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -22952,10 +22952,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>124355870</v>
+        <v>124355802</v>
       </c>
       <c r="B200" t="n">
-        <v>78455</v>
+        <v>98000</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -22964,25 +22964,25 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>353</v>
+        <v>219795</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -22992,10 +22992,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>723669</v>
+        <v>723703</v>
       </c>
       <c r="R200" t="n">
-        <v>7544113</v>
+        <v>7544232</v>
       </c>
       <c r="S200" t="n">
         <v>5</v>
@@ -23054,10 +23054,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>124355551</v>
+        <v>124355667</v>
       </c>
       <c r="B201" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -23066,38 +23066,38 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>723547</v>
+        <v>723695</v>
       </c>
       <c r="R201" t="n">
-        <v>7544600</v>
+        <v>7544233</v>
       </c>
       <c r="S201" t="n">
         <v>5</v>
@@ -23124,12 +23124,12 @@
       </c>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -23156,10 +23156,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>124355802</v>
+        <v>124355544</v>
       </c>
       <c r="B202" t="n">
-        <v>98000</v>
+        <v>105102</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -23172,34 +23172,34 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>219795</v>
+        <v>221725</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>723703</v>
+        <v>723301</v>
       </c>
       <c r="R202" t="n">
-        <v>7544232</v>
+        <v>7544640</v>
       </c>
       <c r="S202" t="n">
         <v>5</v>
@@ -23226,12 +23226,12 @@
       </c>
       <c r="Y202" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -23258,10 +23258,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>124355632</v>
+        <v>124355646</v>
       </c>
       <c r="B203" t="n">
-        <v>96985</v>
+        <v>79927</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -23274,21 +23274,21 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>221941</v>
+        <v>6464</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -23298,10 +23298,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>723668</v>
+        <v>723617</v>
       </c>
       <c r="R203" t="n">
-        <v>7544288</v>
+        <v>7544144</v>
       </c>
       <c r="S203" t="n">
         <v>5</v>
@@ -23360,10 +23360,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>124355851</v>
+        <v>124355516</v>
       </c>
       <c r="B204" t="n">
-        <v>97128</v>
+        <v>105102</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -23376,21 +23376,21 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>222741</v>
+        <v>221725</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -23400,10 +23400,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>723705</v>
+        <v>723694</v>
       </c>
       <c r="R204" t="n">
-        <v>7544144</v>
+        <v>7544160</v>
       </c>
       <c r="S204" t="n">
         <v>5</v>
@@ -23462,10 +23462,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>124355592</v>
+        <v>124355668</v>
       </c>
       <c r="B205" t="n">
-        <v>79920</v>
+        <v>98101</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -23474,25 +23474,25 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -23502,10 +23502,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>723699</v>
+        <v>723703</v>
       </c>
       <c r="R205" t="n">
-        <v>7544155</v>
+        <v>7544180</v>
       </c>
       <c r="S205" t="n">
         <v>5</v>
@@ -23564,10 +23564,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>124355538</v>
+        <v>124355806</v>
       </c>
       <c r="B206" t="n">
-        <v>105102</v>
+        <v>98000</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -23580,21 +23580,21 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>221725</v>
+        <v>219795</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -23604,10 +23604,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>722917</v>
+        <v>722934</v>
       </c>
       <c r="R206" t="n">
-        <v>7544575</v>
+        <v>7544572</v>
       </c>
       <c r="S206" t="n">
         <v>5</v>
@@ -23666,10 +23666,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>124355541</v>
+        <v>124355609</v>
       </c>
       <c r="B207" t="n">
-        <v>105102</v>
+        <v>98122</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -23682,21 +23682,21 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>221725</v>
+        <v>221952</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
@@ -23706,10 +23706,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>723087</v>
+        <v>723343</v>
       </c>
       <c r="R207" t="n">
-        <v>7544566</v>
+        <v>7544612</v>
       </c>
       <c r="S207" t="n">
         <v>5</v>
@@ -23768,10 +23768,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>124355598</v>
+        <v>124355570</v>
       </c>
       <c r="B208" t="n">
-        <v>79920</v>
+        <v>90977</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -23784,21 +23784,21 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
@@ -23808,10 +23808,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>723350</v>
+        <v>723343</v>
       </c>
       <c r="R208" t="n">
-        <v>7544621</v>
+        <v>7544616</v>
       </c>
       <c r="S208" t="n">
         <v>5</v>
@@ -23870,7 +23870,7 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>124355529</v>
+        <v>124355543</v>
       </c>
       <c r="B209" t="n">
         <v>105102</v>
@@ -23910,10 +23910,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>723365</v>
+        <v>723227</v>
       </c>
       <c r="R209" t="n">
-        <v>7545207</v>
+        <v>7544640</v>
       </c>
       <c r="S209" t="n">
         <v>5</v>
@@ -23972,10 +23972,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>124355539</v>
+        <v>124355877</v>
       </c>
       <c r="B210" t="n">
-        <v>105102</v>
+        <v>74893</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -23984,38 +23984,38 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>221725</v>
+        <v>308</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>722977</v>
+        <v>723696</v>
       </c>
       <c r="R210" t="n">
-        <v>7544571</v>
+        <v>7544172</v>
       </c>
       <c r="S210" t="n">
         <v>5</v>
@@ -24042,12 +24042,12 @@
       </c>
       <c r="Y210" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -24074,10 +24074,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>124355570</v>
+        <v>124355672</v>
       </c>
       <c r="B211" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -24086,25 +24086,25 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -24114,10 +24114,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>723343</v>
+        <v>723359</v>
       </c>
       <c r="R211" t="n">
-        <v>7544616</v>
+        <v>7545207</v>
       </c>
       <c r="S211" t="n">
         <v>5</v>
@@ -24176,10 +24176,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>124355552</v>
+        <v>124355807</v>
       </c>
       <c r="B212" t="n">
-        <v>105102</v>
+        <v>98000</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -24192,21 +24192,21 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>221725</v>
+        <v>219795</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -24216,10 +24216,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>723608</v>
+        <v>723042</v>
       </c>
       <c r="R212" t="n">
-        <v>7544580</v>
+        <v>7544553</v>
       </c>
       <c r="S212" t="n">
         <v>5</v>
@@ -24278,10 +24278,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>124355513</v>
+        <v>124355666</v>
       </c>
       <c r="B213" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -24290,25 +24290,25 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -24318,10 +24318,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>723653</v>
+        <v>723699</v>
       </c>
       <c r="R213" t="n">
-        <v>7544288</v>
+        <v>7544235</v>
       </c>
       <c r="S213" t="n">
         <v>5</v>
@@ -24380,10 +24380,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>124355546</v>
+        <v>124355632</v>
       </c>
       <c r="B214" t="n">
-        <v>105102</v>
+        <v>96985</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -24396,34 +24396,34 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>221725</v>
+        <v>221941</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>723347</v>
+        <v>723668</v>
       </c>
       <c r="R214" t="n">
-        <v>7544617</v>
+        <v>7544288</v>
       </c>
       <c r="S214" t="n">
         <v>5</v>
@@ -24450,12 +24450,12 @@
       </c>
       <c r="Y214" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -24482,10 +24482,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>124355905</v>
+        <v>124355552</v>
       </c>
       <c r="B215" t="n">
-        <v>78194</v>
+        <v>105102</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -24494,38 +24494,38 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>6437</v>
+        <v>221725</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
       <c r="P215" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>723693</v>
+        <v>723608</v>
       </c>
       <c r="R215" t="n">
-        <v>7544182</v>
+        <v>7544580</v>
       </c>
       <c r="S215" t="n">
         <v>5</v>
@@ -24552,12 +24552,12 @@
       </c>
       <c r="Y215" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -24584,10 +24584,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>124355668</v>
+        <v>124355857</v>
       </c>
       <c r="B216" t="n">
-        <v>98101</v>
+        <v>97128</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -24596,38 +24596,38 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>220787</v>
+        <v>222741</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
       <c r="P216" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>723703</v>
+        <v>723343</v>
       </c>
       <c r="R216" t="n">
-        <v>7544180</v>
+        <v>7544616</v>
       </c>
       <c r="S216" t="n">
         <v>5</v>
@@ -24654,12 +24654,12 @@
       </c>
       <c r="Y216" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -24686,7 +24686,7 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>124355516</v>
+        <v>124355539</v>
       </c>
       <c r="B217" t="n">
         <v>105102</v>
@@ -24722,14 +24722,14 @@
       <c r="I217" t="inlineStr"/>
       <c r="P217" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>723694</v>
+        <v>722977</v>
       </c>
       <c r="R217" t="n">
-        <v>7544160</v>
+        <v>7544571</v>
       </c>
       <c r="S217" t="n">
         <v>5</v>
@@ -24756,12 +24756,12 @@
       </c>
       <c r="Y217" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -24788,10 +24788,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>124355877</v>
+        <v>124355873</v>
       </c>
       <c r="B218" t="n">
-        <v>74893</v>
+        <v>79926</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -24800,25 +24800,25 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>308</v>
+        <v>6463</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -24828,10 +24828,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>723696</v>
+        <v>723684</v>
       </c>
       <c r="R218" t="n">
-        <v>7544172</v>
+        <v>7544232</v>
       </c>
       <c r="S218" t="n">
         <v>5</v>
@@ -24890,10 +24890,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>124355544</v>
+        <v>124355826</v>
       </c>
       <c r="B219" t="n">
-        <v>105102</v>
+        <v>91030</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -24902,25 +24902,25 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>221725</v>
+        <v>5432</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
@@ -24930,10 +24930,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>723301</v>
+        <v>723345</v>
       </c>
       <c r="R219" t="n">
-        <v>7544640</v>
+        <v>7544616</v>
       </c>
       <c r="S219" t="n">
         <v>5</v>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -20805,10 +20805,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>124355611</v>
+        <v>124355826</v>
       </c>
       <c r="B179" t="n">
-        <v>57529</v>
+        <v>91030</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -20821,34 +20821,34 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>723694</v>
+        <v>723345</v>
       </c>
       <c r="R179" t="n">
-        <v>7544233</v>
+        <v>7544616</v>
       </c>
       <c r="S179" t="n">
         <v>5</v>
@@ -20875,17 +20875,12 @@
       </c>
       <c r="Y179" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
-        </is>
-      </c>
-      <c r="AC179" t="inlineStr">
-        <is>
-          <t>hackmärken</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -20912,7 +20907,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>124355541</v>
+        <v>124355552</v>
       </c>
       <c r="B180" t="n">
         <v>105102</v>
@@ -20952,10 +20947,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>723087</v>
+        <v>723608</v>
       </c>
       <c r="R180" t="n">
-        <v>7544566</v>
+        <v>7544580</v>
       </c>
       <c r="S180" t="n">
         <v>5</v>
@@ -21014,10 +21009,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>124355540</v>
+        <v>124355807</v>
       </c>
       <c r="B181" t="n">
-        <v>105102</v>
+        <v>98000</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -21030,21 +21025,21 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>221725</v>
+        <v>219795</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -21054,10 +21049,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>723038</v>
+        <v>723042</v>
       </c>
       <c r="R181" t="n">
-        <v>7544552</v>
+        <v>7544553</v>
       </c>
       <c r="S181" t="n">
         <v>5</v>
@@ -21116,10 +21111,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>124355515</v>
+        <v>124355851</v>
       </c>
       <c r="B182" t="n">
-        <v>105102</v>
+        <v>97128</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -21132,21 +21127,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>221725</v>
+        <v>222741</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -21156,10 +21151,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>723720</v>
+        <v>723705</v>
       </c>
       <c r="R182" t="n">
-        <v>7544240</v>
+        <v>7544144</v>
       </c>
       <c r="S182" t="n">
         <v>5</v>
@@ -21218,10 +21213,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>124355855</v>
+        <v>124355668</v>
       </c>
       <c r="B183" t="n">
-        <v>97128</v>
+        <v>98101</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -21230,38 +21225,38 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>222741</v>
+        <v>220787</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>722944</v>
+        <v>723703</v>
       </c>
       <c r="R183" t="n">
-        <v>7544574</v>
+        <v>7544180</v>
       </c>
       <c r="S183" t="n">
         <v>5</v>
@@ -21288,12 +21283,12 @@
       </c>
       <c r="Y183" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -21320,10 +21315,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>124355592</v>
+        <v>124355806</v>
       </c>
       <c r="B184" t="n">
-        <v>79920</v>
+        <v>98000</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -21336,34 +21331,34 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6462</v>
+        <v>219795</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>723699</v>
+        <v>722934</v>
       </c>
       <c r="R184" t="n">
-        <v>7544155</v>
+        <v>7544572</v>
       </c>
       <c r="S184" t="n">
         <v>5</v>
@@ -21390,12 +21385,12 @@
       </c>
       <c r="Y184" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -21422,10 +21417,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>124355551</v>
+        <v>124355802</v>
       </c>
       <c r="B185" t="n">
-        <v>105102</v>
+        <v>98000</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -21438,34 +21433,34 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>221725</v>
+        <v>219795</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>723547</v>
+        <v>723703</v>
       </c>
       <c r="R185" t="n">
-        <v>7544600</v>
+        <v>7544232</v>
       </c>
       <c r="S185" t="n">
         <v>5</v>
@@ -21492,12 +21487,12 @@
       </c>
       <c r="Y185" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -21524,10 +21519,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>124355856</v>
+        <v>124355540</v>
       </c>
       <c r="B186" t="n">
-        <v>97128</v>
+        <v>105102</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -21540,21 +21535,21 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>222741</v>
+        <v>221725</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -21564,10 +21559,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>723068</v>
+        <v>723038</v>
       </c>
       <c r="R186" t="n">
-        <v>7544568</v>
+        <v>7544552</v>
       </c>
       <c r="S186" t="n">
         <v>5</v>
@@ -21626,10 +21621,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>124355850</v>
+        <v>124355873</v>
       </c>
       <c r="B187" t="n">
-        <v>97128</v>
+        <v>79926</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -21642,21 +21637,21 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>222741</v>
+        <v>6463</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -21666,10 +21661,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>723616</v>
+        <v>723684</v>
       </c>
       <c r="R187" t="n">
-        <v>7544154</v>
+        <v>7544232</v>
       </c>
       <c r="S187" t="n">
         <v>5</v>
@@ -21728,10 +21723,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>124355870</v>
+        <v>124355850</v>
       </c>
       <c r="B188" t="n">
-        <v>78455</v>
+        <v>97128</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -21740,25 +21735,25 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>353</v>
+        <v>222741</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -21768,10 +21763,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>723669</v>
+        <v>723616</v>
       </c>
       <c r="R188" t="n">
-        <v>7544113</v>
+        <v>7544154</v>
       </c>
       <c r="S188" t="n">
         <v>5</v>
@@ -21932,7 +21927,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>124355538</v>
+        <v>124355513</v>
       </c>
       <c r="B190" t="n">
         <v>105102</v>
@@ -21968,14 +21963,14 @@
       <c r="I190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>722917</v>
+        <v>723653</v>
       </c>
       <c r="R190" t="n">
-        <v>7544575</v>
+        <v>7544288</v>
       </c>
       <c r="S190" t="n">
         <v>5</v>
@@ -22002,12 +21997,12 @@
       </c>
       <c r="Y190" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -22034,7 +22029,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>124355548</v>
+        <v>124355515</v>
       </c>
       <c r="B191" t="n">
         <v>105102</v>
@@ -22070,14 +22065,14 @@
       <c r="I191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>723515</v>
+        <v>723720</v>
       </c>
       <c r="R191" t="n">
-        <v>7544632</v>
+        <v>7544240</v>
       </c>
       <c r="S191" t="n">
         <v>5</v>
@@ -22104,12 +22099,12 @@
       </c>
       <c r="Y191" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -22136,10 +22131,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>124355546</v>
+        <v>124355857</v>
       </c>
       <c r="B192" t="n">
-        <v>105102</v>
+        <v>97128</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -22152,21 +22147,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>221725</v>
+        <v>222741</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -22176,10 +22171,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>723347</v>
+        <v>723343</v>
       </c>
       <c r="R192" t="n">
-        <v>7544617</v>
+        <v>7544616</v>
       </c>
       <c r="S192" t="n">
         <v>5</v>
@@ -22238,7 +22233,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>124355542</v>
+        <v>124355548</v>
       </c>
       <c r="B193" t="n">
         <v>105102</v>
@@ -22278,10 +22273,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>723159</v>
+        <v>723515</v>
       </c>
       <c r="R193" t="n">
-        <v>7544605</v>
+        <v>7544632</v>
       </c>
       <c r="S193" t="n">
         <v>5</v>
@@ -22340,7 +22335,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>124355529</v>
+        <v>124355543</v>
       </c>
       <c r="B194" t="n">
         <v>105102</v>
@@ -22380,10 +22375,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>723365</v>
+        <v>723227</v>
       </c>
       <c r="R194" t="n">
-        <v>7545207</v>
+        <v>7544640</v>
       </c>
       <c r="S194" t="n">
         <v>5</v>
@@ -22442,10 +22437,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>124355654</v>
+        <v>124355541</v>
       </c>
       <c r="B195" t="n">
-        <v>78151</v>
+        <v>105102</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -22454,38 +22449,38 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>498</v>
+        <v>221725</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>723693</v>
+        <v>723087</v>
       </c>
       <c r="R195" t="n">
-        <v>7544234</v>
+        <v>7544566</v>
       </c>
       <c r="S195" t="n">
         <v>5</v>
@@ -22512,12 +22507,12 @@
       </c>
       <c r="Y195" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -22544,10 +22539,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>124355513</v>
+        <v>124355654</v>
       </c>
       <c r="B196" t="n">
-        <v>105102</v>
+        <v>78151</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -22556,25 +22551,25 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>221725</v>
+        <v>498</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -22584,10 +22579,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>723653</v>
+        <v>723693</v>
       </c>
       <c r="R196" t="n">
-        <v>7544288</v>
+        <v>7544234</v>
       </c>
       <c r="S196" t="n">
         <v>5</v>
@@ -22646,10 +22641,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>124355530</v>
+        <v>124355632</v>
       </c>
       <c r="B197" t="n">
-        <v>105102</v>
+        <v>96985</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -22662,34 +22657,34 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>221725</v>
+        <v>221941</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>723178</v>
+        <v>723668</v>
       </c>
       <c r="R197" t="n">
-        <v>7545219</v>
+        <v>7544288</v>
       </c>
       <c r="S197" t="n">
         <v>5</v>
@@ -22716,12 +22711,12 @@
       </c>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -22748,10 +22743,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>124355905</v>
+        <v>124355667</v>
       </c>
       <c r="B198" t="n">
-        <v>78194</v>
+        <v>98101</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -22760,25 +22755,25 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>6437</v>
+        <v>220787</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -22788,10 +22783,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>723693</v>
+        <v>723695</v>
       </c>
       <c r="R198" t="n">
-        <v>7544182</v>
+        <v>7544233</v>
       </c>
       <c r="S198" t="n">
         <v>5</v>
@@ -22850,10 +22845,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>124355851</v>
+        <v>124355551</v>
       </c>
       <c r="B199" t="n">
-        <v>97128</v>
+        <v>105102</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -22866,34 +22861,34 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>222741</v>
+        <v>221725</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>723705</v>
+        <v>723547</v>
       </c>
       <c r="R199" t="n">
-        <v>7544144</v>
+        <v>7544600</v>
       </c>
       <c r="S199" t="n">
         <v>5</v>
@@ -22920,12 +22915,12 @@
       </c>
       <c r="Y199" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -22952,10 +22947,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>124355802</v>
+        <v>124355855</v>
       </c>
       <c r="B200" t="n">
-        <v>98000</v>
+        <v>97128</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -22968,34 +22963,34 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>219795</v>
+        <v>222741</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>723703</v>
+        <v>722944</v>
       </c>
       <c r="R200" t="n">
-        <v>7544232</v>
+        <v>7544574</v>
       </c>
       <c r="S200" t="n">
         <v>5</v>
@@ -23022,12 +23017,12 @@
       </c>
       <c r="Y200" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -23054,10 +23049,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>124355667</v>
+        <v>124355905</v>
       </c>
       <c r="B201" t="n">
-        <v>98101</v>
+        <v>78194</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -23066,25 +23061,25 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>220787</v>
+        <v>6437</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -23094,10 +23089,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>723695</v>
+        <v>723693</v>
       </c>
       <c r="R201" t="n">
-        <v>7544233</v>
+        <v>7544182</v>
       </c>
       <c r="S201" t="n">
         <v>5</v>
@@ -23156,7 +23151,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>124355544</v>
+        <v>124355538</v>
       </c>
       <c r="B202" t="n">
         <v>105102</v>
@@ -23196,10 +23191,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>723301</v>
+        <v>722917</v>
       </c>
       <c r="R202" t="n">
-        <v>7544640</v>
+        <v>7544575</v>
       </c>
       <c r="S202" t="n">
         <v>5</v>
@@ -23258,10 +23253,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>124355646</v>
+        <v>124355672</v>
       </c>
       <c r="B203" t="n">
-        <v>79927</v>
+        <v>98101</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -23270,38 +23265,38 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>723617</v>
+        <v>723359</v>
       </c>
       <c r="R203" t="n">
-        <v>7544144</v>
+        <v>7545207</v>
       </c>
       <c r="S203" t="n">
         <v>5</v>
@@ -23328,12 +23323,12 @@
       </c>
       <c r="Y203" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -23360,10 +23355,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>124355516</v>
+        <v>124355592</v>
       </c>
       <c r="B204" t="n">
-        <v>105102</v>
+        <v>79920</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -23376,21 +23371,21 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>221725</v>
+        <v>6462</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -23400,10 +23395,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>723694</v>
+        <v>723699</v>
       </c>
       <c r="R204" t="n">
-        <v>7544160</v>
+        <v>7544155</v>
       </c>
       <c r="S204" t="n">
         <v>5</v>
@@ -23462,10 +23457,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>124355668</v>
+        <v>124355856</v>
       </c>
       <c r="B205" t="n">
-        <v>98101</v>
+        <v>97128</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -23474,38 +23469,38 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>220787</v>
+        <v>222741</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>723703</v>
+        <v>723068</v>
       </c>
       <c r="R205" t="n">
-        <v>7544180</v>
+        <v>7544568</v>
       </c>
       <c r="S205" t="n">
         <v>5</v>
@@ -23532,12 +23527,12 @@
       </c>
       <c r="Y205" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -23564,10 +23559,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>124355806</v>
+        <v>124355570</v>
       </c>
       <c r="B206" t="n">
-        <v>98000</v>
+        <v>90977</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -23580,21 +23575,21 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>219795</v>
+        <v>5447</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -23604,10 +23599,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>722934</v>
+        <v>723343</v>
       </c>
       <c r="R206" t="n">
-        <v>7544572</v>
+        <v>7544616</v>
       </c>
       <c r="S206" t="n">
         <v>5</v>
@@ -23666,10 +23661,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>124355609</v>
+        <v>124355546</v>
       </c>
       <c r="B207" t="n">
-        <v>98122</v>
+        <v>105102</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -23682,21 +23677,21 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>221952</v>
+        <v>221725</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
@@ -23706,10 +23701,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>723343</v>
+        <v>723347</v>
       </c>
       <c r="R207" t="n">
-        <v>7544612</v>
+        <v>7544617</v>
       </c>
       <c r="S207" t="n">
         <v>5</v>
@@ -23768,10 +23763,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>124355570</v>
+        <v>124355539</v>
       </c>
       <c r="B208" t="n">
-        <v>90977</v>
+        <v>105102</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -23784,21 +23779,21 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>5447</v>
+        <v>221725</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
@@ -23808,10 +23803,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>723343</v>
+        <v>722977</v>
       </c>
       <c r="R208" t="n">
-        <v>7544616</v>
+        <v>7544571</v>
       </c>
       <c r="S208" t="n">
         <v>5</v>
@@ -23870,7 +23865,7 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>124355543</v>
+        <v>124355529</v>
       </c>
       <c r="B209" t="n">
         <v>105102</v>
@@ -23910,10 +23905,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>723227</v>
+        <v>723365</v>
       </c>
       <c r="R209" t="n">
-        <v>7544640</v>
+        <v>7545207</v>
       </c>
       <c r="S209" t="n">
         <v>5</v>
@@ -23972,10 +23967,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>124355877</v>
+        <v>124355516</v>
       </c>
       <c r="B210" t="n">
-        <v>74893</v>
+        <v>105102</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -23984,25 +23979,25 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>308</v>
+        <v>221725</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -24012,10 +24007,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>723696</v>
+        <v>723694</v>
       </c>
       <c r="R210" t="n">
-        <v>7544172</v>
+        <v>7544160</v>
       </c>
       <c r="S210" t="n">
         <v>5</v>
@@ -24074,10 +24069,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>124355672</v>
+        <v>124355542</v>
       </c>
       <c r="B211" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -24086,25 +24081,25 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -24114,10 +24109,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>723359</v>
+        <v>723159</v>
       </c>
       <c r="R211" t="n">
-        <v>7545207</v>
+        <v>7544605</v>
       </c>
       <c r="S211" t="n">
         <v>5</v>
@@ -24176,10 +24171,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>124355807</v>
+        <v>124355544</v>
       </c>
       <c r="B212" t="n">
-        <v>98000</v>
+        <v>105102</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -24192,21 +24187,21 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>219795</v>
+        <v>221725</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -24216,10 +24211,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>723042</v>
+        <v>723301</v>
       </c>
       <c r="R212" t="n">
-        <v>7544553</v>
+        <v>7544640</v>
       </c>
       <c r="S212" t="n">
         <v>5</v>
@@ -24278,10 +24273,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>124355666</v>
+        <v>124355609</v>
       </c>
       <c r="B213" t="n">
-        <v>98101</v>
+        <v>98122</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -24290,38 +24285,38 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
       <c r="P213" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>723699</v>
+        <v>723343</v>
       </c>
       <c r="R213" t="n">
-        <v>7544235</v>
+        <v>7544612</v>
       </c>
       <c r="S213" t="n">
         <v>5</v>
@@ -24348,12 +24343,12 @@
       </c>
       <c r="Y213" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -24380,10 +24375,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>124355632</v>
+        <v>124355611</v>
       </c>
       <c r="B214" t="n">
-        <v>96985</v>
+        <v>57529</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -24392,25 +24387,25 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>221941</v>
+        <v>100049</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
@@ -24420,10 +24415,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>723668</v>
+        <v>723694</v>
       </c>
       <c r="R214" t="n">
-        <v>7544288</v>
+        <v>7544233</v>
       </c>
       <c r="S214" t="n">
         <v>5</v>
@@ -24456,6 +24451,11 @@
       <c r="AA214" t="inlineStr">
         <is>
           <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="AC214" t="inlineStr">
+        <is>
+          <t>hackmärken</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -24482,10 +24482,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>124355552</v>
+        <v>124355666</v>
       </c>
       <c r="B215" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -24494,38 +24494,38 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
       <c r="P215" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>723608</v>
+        <v>723699</v>
       </c>
       <c r="R215" t="n">
-        <v>7544580</v>
+        <v>7544235</v>
       </c>
       <c r="S215" t="n">
         <v>5</v>
@@ -24552,12 +24552,12 @@
       </c>
       <c r="Y215" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -24584,10 +24584,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>124355857</v>
+        <v>124355646</v>
       </c>
       <c r="B216" t="n">
-        <v>97128</v>
+        <v>79927</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -24600,34 +24600,34 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>222741</v>
+        <v>6464</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
       <c r="P216" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>723343</v>
+        <v>723617</v>
       </c>
       <c r="R216" t="n">
-        <v>7544616</v>
+        <v>7544144</v>
       </c>
       <c r="S216" t="n">
         <v>5</v>
@@ -24654,12 +24654,12 @@
       </c>
       <c r="Y216" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -24686,10 +24686,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>124355539</v>
+        <v>124355870</v>
       </c>
       <c r="B217" t="n">
-        <v>105102</v>
+        <v>78455</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -24698,38 +24698,38 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>221725</v>
+        <v>353</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
       <c r="P217" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>722977</v>
+        <v>723669</v>
       </c>
       <c r="R217" t="n">
-        <v>7544571</v>
+        <v>7544113</v>
       </c>
       <c r="S217" t="n">
         <v>5</v>
@@ -24756,12 +24756,12 @@
       </c>
       <c r="Y217" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -24788,10 +24788,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>124355873</v>
+        <v>124355530</v>
       </c>
       <c r="B218" t="n">
-        <v>79926</v>
+        <v>105102</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -24804,34 +24804,34 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>6463</v>
+        <v>221725</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
       <c r="P218" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>723684</v>
+        <v>723178</v>
       </c>
       <c r="R218" t="n">
-        <v>7544232</v>
+        <v>7545219</v>
       </c>
       <c r="S218" t="n">
         <v>5</v>
@@ -24858,12 +24858,12 @@
       </c>
       <c r="Y218" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -24890,10 +24890,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>124355826</v>
+        <v>124355877</v>
       </c>
       <c r="B219" t="n">
-        <v>91030</v>
+        <v>74893</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -24906,34 +24906,34 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>5432</v>
+        <v>308</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>723345</v>
+        <v>723696</v>
       </c>
       <c r="R219" t="n">
-        <v>7544616</v>
+        <v>7544172</v>
       </c>
       <c r="S219" t="n">
         <v>5</v>
@@ -24960,12 +24960,12 @@
       </c>
       <c r="Y219" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD219" t="b">

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -21519,10 +21519,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>124355540</v>
+        <v>124355873</v>
       </c>
       <c r="B186" t="n">
-        <v>105102</v>
+        <v>79926</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -21535,34 +21535,34 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>221725</v>
+        <v>6463</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>723038</v>
+        <v>723684</v>
       </c>
       <c r="R186" t="n">
-        <v>7544552</v>
+        <v>7544232</v>
       </c>
       <c r="S186" t="n">
         <v>5</v>
@@ -21589,12 +21589,12 @@
       </c>
       <c r="Y186" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -21621,10 +21621,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>124355873</v>
+        <v>124355540</v>
       </c>
       <c r="B187" t="n">
-        <v>79926</v>
+        <v>105102</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -21637,34 +21637,34 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6463</v>
+        <v>221725</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>723684</v>
+        <v>723038</v>
       </c>
       <c r="R187" t="n">
-        <v>7544232</v>
+        <v>7544552</v>
       </c>
       <c r="S187" t="n">
         <v>5</v>
@@ -21691,12 +21691,12 @@
       </c>
       <c r="Y187" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -21723,10 +21723,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>124355850</v>
+        <v>124355598</v>
       </c>
       <c r="B188" t="n">
-        <v>97128</v>
+        <v>79920</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -21739,34 +21739,34 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>222741</v>
+        <v>6462</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>723616</v>
+        <v>723350</v>
       </c>
       <c r="R188" t="n">
-        <v>7544154</v>
+        <v>7544621</v>
       </c>
       <c r="S188" t="n">
         <v>5</v>
@@ -21793,12 +21793,12 @@
       </c>
       <c r="Y188" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -21825,10 +21825,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>124355598</v>
+        <v>124355850</v>
       </c>
       <c r="B189" t="n">
-        <v>79920</v>
+        <v>97128</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -21841,34 +21841,34 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6462</v>
+        <v>222741</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>723350</v>
+        <v>723616</v>
       </c>
       <c r="R189" t="n">
-        <v>7544621</v>
+        <v>7544154</v>
       </c>
       <c r="S189" t="n">
         <v>5</v>
@@ -21895,12 +21895,12 @@
       </c>
       <c r="Y189" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -23457,10 +23457,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>124355856</v>
+        <v>124355570</v>
       </c>
       <c r="B205" t="n">
-        <v>97128</v>
+        <v>90977</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -23473,21 +23473,21 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>222741</v>
+        <v>5447</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -23497,10 +23497,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>723068</v>
+        <v>723343</v>
       </c>
       <c r="R205" t="n">
-        <v>7544568</v>
+        <v>7544616</v>
       </c>
       <c r="S205" t="n">
         <v>5</v>
@@ -23559,10 +23559,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>124355570</v>
+        <v>124355856</v>
       </c>
       <c r="B206" t="n">
-        <v>90977</v>
+        <v>97128</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -23575,21 +23575,21 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>5447</v>
+        <v>222741</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -23599,10 +23599,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>723343</v>
+        <v>723068</v>
       </c>
       <c r="R206" t="n">
-        <v>7544616</v>
+        <v>7544568</v>
       </c>
       <c r="S206" t="n">
         <v>5</v>
@@ -23967,7 +23967,7 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>124355516</v>
+        <v>124355542</v>
       </c>
       <c r="B210" t="n">
         <v>105102</v>
@@ -24003,14 +24003,14 @@
       <c r="I210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>723694</v>
+        <v>723159</v>
       </c>
       <c r="R210" t="n">
-        <v>7544160</v>
+        <v>7544605</v>
       </c>
       <c r="S210" t="n">
         <v>5</v>
@@ -24037,12 +24037,12 @@
       </c>
       <c r="Y210" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -24069,7 +24069,7 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>124355542</v>
+        <v>124355516</v>
       </c>
       <c r="B211" t="n">
         <v>105102</v>
@@ -24105,14 +24105,14 @@
       <c r="I211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>723159</v>
+        <v>723694</v>
       </c>
       <c r="R211" t="n">
-        <v>7544605</v>
+        <v>7544160</v>
       </c>
       <c r="S211" t="n">
         <v>5</v>
@@ -24139,12 +24139,12 @@
       </c>
       <c r="Y211" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD211" t="b">

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -20805,10 +20805,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>124355826</v>
+        <v>124355802</v>
       </c>
       <c r="B179" t="n">
-        <v>91030</v>
+        <v>98000</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -20817,38 +20817,38 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>5432</v>
+        <v>219795</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>723345</v>
+        <v>723703</v>
       </c>
       <c r="R179" t="n">
-        <v>7544616</v>
+        <v>7544232</v>
       </c>
       <c r="S179" t="n">
         <v>5</v>
@@ -20875,12 +20875,12 @@
       </c>
       <c r="Y179" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -20907,10 +20907,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>124355552</v>
+        <v>124355851</v>
       </c>
       <c r="B180" t="n">
-        <v>105102</v>
+        <v>97128</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -20923,34 +20923,34 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>221725</v>
+        <v>222741</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>723608</v>
+        <v>723705</v>
       </c>
       <c r="R180" t="n">
-        <v>7544580</v>
+        <v>7544144</v>
       </c>
       <c r="S180" t="n">
         <v>5</v>
@@ -20977,12 +20977,12 @@
       </c>
       <c r="Y180" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -21009,10 +21009,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>124355807</v>
+        <v>124355592</v>
       </c>
       <c r="B181" t="n">
-        <v>98000</v>
+        <v>79920</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -21025,34 +21025,34 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>219795</v>
+        <v>6462</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>723042</v>
+        <v>723699</v>
       </c>
       <c r="R181" t="n">
-        <v>7544553</v>
+        <v>7544155</v>
       </c>
       <c r="S181" t="n">
         <v>5</v>
@@ -21079,12 +21079,12 @@
       </c>
       <c r="Y181" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -21111,10 +21111,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>124355851</v>
+        <v>124355877</v>
       </c>
       <c r="B182" t="n">
-        <v>97128</v>
+        <v>74893</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -21123,25 +21123,25 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>222741</v>
+        <v>308</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -21151,10 +21151,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>723705</v>
+        <v>723696</v>
       </c>
       <c r="R182" t="n">
-        <v>7544144</v>
+        <v>7544172</v>
       </c>
       <c r="S182" t="n">
         <v>5</v>
@@ -21213,10 +21213,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>124355668</v>
+        <v>124355826</v>
       </c>
       <c r="B183" t="n">
-        <v>98101</v>
+        <v>91030</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -21225,38 +21225,38 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>723703</v>
+        <v>723345</v>
       </c>
       <c r="R183" t="n">
-        <v>7544180</v>
+        <v>7544616</v>
       </c>
       <c r="S183" t="n">
         <v>5</v>
@@ -21283,12 +21283,12 @@
       </c>
       <c r="Y183" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -21315,10 +21315,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>124355806</v>
+        <v>124355544</v>
       </c>
       <c r="B184" t="n">
-        <v>98000</v>
+        <v>105102</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -21331,21 +21331,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>219795</v>
+        <v>221725</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -21355,10 +21355,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>722934</v>
+        <v>723301</v>
       </c>
       <c r="R184" t="n">
-        <v>7544572</v>
+        <v>7544640</v>
       </c>
       <c r="S184" t="n">
         <v>5</v>
@@ -21417,10 +21417,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>124355802</v>
+        <v>124355515</v>
       </c>
       <c r="B185" t="n">
-        <v>98000</v>
+        <v>105102</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -21433,21 +21433,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>219795</v>
+        <v>221725</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -21457,10 +21457,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>723703</v>
+        <v>723720</v>
       </c>
       <c r="R185" t="n">
-        <v>7544232</v>
+        <v>7544240</v>
       </c>
       <c r="S185" t="n">
         <v>5</v>
@@ -21519,10 +21519,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>124355873</v>
+        <v>124355538</v>
       </c>
       <c r="B186" t="n">
-        <v>79926</v>
+        <v>105102</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -21535,34 +21535,34 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6463</v>
+        <v>221725</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>723684</v>
+        <v>722917</v>
       </c>
       <c r="R186" t="n">
-        <v>7544232</v>
+        <v>7544575</v>
       </c>
       <c r="S186" t="n">
         <v>5</v>
@@ -21589,12 +21589,12 @@
       </c>
       <c r="Y186" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -21621,10 +21621,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>124355540</v>
+        <v>124355570</v>
       </c>
       <c r="B187" t="n">
-        <v>105102</v>
+        <v>90977</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -21637,21 +21637,21 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>221725</v>
+        <v>5447</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -21661,10 +21661,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>723038</v>
+        <v>723343</v>
       </c>
       <c r="R187" t="n">
-        <v>7544552</v>
+        <v>7544616</v>
       </c>
       <c r="S187" t="n">
         <v>5</v>
@@ -21723,10 +21723,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>124355598</v>
+        <v>124355632</v>
       </c>
       <c r="B188" t="n">
-        <v>79920</v>
+        <v>96985</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -21739,34 +21739,34 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6462</v>
+        <v>221941</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>723350</v>
+        <v>723668</v>
       </c>
       <c r="R188" t="n">
-        <v>7544621</v>
+        <v>7544288</v>
       </c>
       <c r="S188" t="n">
         <v>5</v>
@@ -21793,12 +21793,12 @@
       </c>
       <c r="Y188" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -21825,10 +21825,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>124355850</v>
+        <v>124355546</v>
       </c>
       <c r="B189" t="n">
-        <v>97128</v>
+        <v>105102</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -21841,34 +21841,34 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>222741</v>
+        <v>221725</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>723616</v>
+        <v>723347</v>
       </c>
       <c r="R189" t="n">
-        <v>7544154</v>
+        <v>7544617</v>
       </c>
       <c r="S189" t="n">
         <v>5</v>
@@ -21895,12 +21895,12 @@
       </c>
       <c r="Y189" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -21927,10 +21927,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>124355513</v>
+        <v>124355856</v>
       </c>
       <c r="B190" t="n">
-        <v>105102</v>
+        <v>97128</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -21943,34 +21943,34 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>221725</v>
+        <v>222741</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>723653</v>
+        <v>723068</v>
       </c>
       <c r="R190" t="n">
-        <v>7544288</v>
+        <v>7544568</v>
       </c>
       <c r="S190" t="n">
         <v>5</v>
@@ -21997,12 +21997,12 @@
       </c>
       <c r="Y190" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -22029,7 +22029,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>124355515</v>
+        <v>124355542</v>
       </c>
       <c r="B191" t="n">
         <v>105102</v>
@@ -22065,14 +22065,14 @@
       <c r="I191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>723720</v>
+        <v>723159</v>
       </c>
       <c r="R191" t="n">
-        <v>7544240</v>
+        <v>7544605</v>
       </c>
       <c r="S191" t="n">
         <v>5</v>
@@ -22099,12 +22099,12 @@
       </c>
       <c r="Y191" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -22131,10 +22131,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>124355857</v>
+        <v>124355870</v>
       </c>
       <c r="B192" t="n">
-        <v>97128</v>
+        <v>78455</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -22143,38 +22143,38 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>222741</v>
+        <v>353</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>723343</v>
+        <v>723669</v>
       </c>
       <c r="R192" t="n">
-        <v>7544616</v>
+        <v>7544113</v>
       </c>
       <c r="S192" t="n">
         <v>5</v>
@@ -22201,12 +22201,12 @@
       </c>
       <c r="Y192" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -22233,10 +22233,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>124355548</v>
+        <v>124355807</v>
       </c>
       <c r="B193" t="n">
-        <v>105102</v>
+        <v>98000</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -22249,21 +22249,21 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>221725</v>
+        <v>219795</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -22273,10 +22273,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>723515</v>
+        <v>723042</v>
       </c>
       <c r="R193" t="n">
-        <v>7544632</v>
+        <v>7544553</v>
       </c>
       <c r="S193" t="n">
         <v>5</v>
@@ -22335,7 +22335,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>124355543</v>
+        <v>124355552</v>
       </c>
       <c r="B194" t="n">
         <v>105102</v>
@@ -22375,10 +22375,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>723227</v>
+        <v>723608</v>
       </c>
       <c r="R194" t="n">
-        <v>7544640</v>
+        <v>7544580</v>
       </c>
       <c r="S194" t="n">
         <v>5</v>
@@ -22437,10 +22437,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>124355541</v>
+        <v>124355905</v>
       </c>
       <c r="B195" t="n">
-        <v>105102</v>
+        <v>78194</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -22449,38 +22449,38 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>221725</v>
+        <v>6437</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>723087</v>
+        <v>723693</v>
       </c>
       <c r="R195" t="n">
-        <v>7544566</v>
+        <v>7544182</v>
       </c>
       <c r="S195" t="n">
         <v>5</v>
@@ -22507,12 +22507,12 @@
       </c>
       <c r="Y195" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -22539,10 +22539,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>124355654</v>
+        <v>124355598</v>
       </c>
       <c r="B196" t="n">
-        <v>78151</v>
+        <v>79920</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -22551,38 +22551,38 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>498</v>
+        <v>6462</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>723693</v>
+        <v>723350</v>
       </c>
       <c r="R196" t="n">
-        <v>7544234</v>
+        <v>7544621</v>
       </c>
       <c r="S196" t="n">
         <v>5</v>
@@ -22609,12 +22609,12 @@
       </c>
       <c r="Y196" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -22641,10 +22641,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>124355632</v>
+        <v>124355672</v>
       </c>
       <c r="B197" t="n">
-        <v>96985</v>
+        <v>98101</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -22653,38 +22653,38 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>723668</v>
+        <v>723359</v>
       </c>
       <c r="R197" t="n">
-        <v>7544288</v>
+        <v>7545207</v>
       </c>
       <c r="S197" t="n">
         <v>5</v>
@@ -22711,12 +22711,12 @@
       </c>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -22743,7 +22743,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>124355667</v>
+        <v>124355666</v>
       </c>
       <c r="B198" t="n">
         <v>98101</v>
@@ -22783,10 +22783,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>723695</v>
+        <v>723699</v>
       </c>
       <c r="R198" t="n">
-        <v>7544233</v>
+        <v>7544235</v>
       </c>
       <c r="S198" t="n">
         <v>5</v>
@@ -22845,10 +22845,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>124355551</v>
+        <v>124355850</v>
       </c>
       <c r="B199" t="n">
-        <v>105102</v>
+        <v>97128</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -22861,34 +22861,34 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>221725</v>
+        <v>222741</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>723547</v>
+        <v>723616</v>
       </c>
       <c r="R199" t="n">
-        <v>7544600</v>
+        <v>7544154</v>
       </c>
       <c r="S199" t="n">
         <v>5</v>
@@ -22915,12 +22915,12 @@
       </c>
       <c r="Y199" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -22947,7 +22947,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>124355855</v>
+        <v>124355857</v>
       </c>
       <c r="B200" t="n">
         <v>97128</v>
@@ -22987,10 +22987,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>722944</v>
+        <v>723343</v>
       </c>
       <c r="R200" t="n">
-        <v>7544574</v>
+        <v>7544616</v>
       </c>
       <c r="S200" t="n">
         <v>5</v>
@@ -23049,10 +23049,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>124355905</v>
+        <v>124355513</v>
       </c>
       <c r="B201" t="n">
-        <v>78194</v>
+        <v>105102</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -23061,25 +23061,25 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>6437</v>
+        <v>221725</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -23089,10 +23089,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>723693</v>
+        <v>723653</v>
       </c>
       <c r="R201" t="n">
-        <v>7544182</v>
+        <v>7544288</v>
       </c>
       <c r="S201" t="n">
         <v>5</v>
@@ -23151,7 +23151,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>124355538</v>
+        <v>124355516</v>
       </c>
       <c r="B202" t="n">
         <v>105102</v>
@@ -23187,14 +23187,14 @@
       <c r="I202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>722917</v>
+        <v>723694</v>
       </c>
       <c r="R202" t="n">
-        <v>7544575</v>
+        <v>7544160</v>
       </c>
       <c r="S202" t="n">
         <v>5</v>
@@ -23221,12 +23221,12 @@
       </c>
       <c r="Y202" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -23253,10 +23253,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>124355672</v>
+        <v>124355529</v>
       </c>
       <c r="B203" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -23265,25 +23265,25 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -23293,7 +23293,7 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>723359</v>
+        <v>723365</v>
       </c>
       <c r="R203" t="n">
         <v>7545207</v>
@@ -23355,10 +23355,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>124355592</v>
+        <v>124355539</v>
       </c>
       <c r="B204" t="n">
-        <v>79920</v>
+        <v>105102</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -23371,34 +23371,34 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>6462</v>
+        <v>221725</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>723699</v>
+        <v>722977</v>
       </c>
       <c r="R204" t="n">
-        <v>7544155</v>
+        <v>7544571</v>
       </c>
       <c r="S204" t="n">
         <v>5</v>
@@ -23425,12 +23425,12 @@
       </c>
       <c r="Y204" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -23457,10 +23457,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>124355570</v>
+        <v>124355548</v>
       </c>
       <c r="B205" t="n">
-        <v>90977</v>
+        <v>105102</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -23473,21 +23473,21 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>5447</v>
+        <v>221725</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -23497,10 +23497,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>723343</v>
+        <v>723515</v>
       </c>
       <c r="R205" t="n">
-        <v>7544616</v>
+        <v>7544632</v>
       </c>
       <c r="S205" t="n">
         <v>5</v>
@@ -23559,10 +23559,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>124355856</v>
+        <v>124355551</v>
       </c>
       <c r="B206" t="n">
-        <v>97128</v>
+        <v>105102</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -23575,21 +23575,21 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>222741</v>
+        <v>221725</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -23599,10 +23599,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>723068</v>
+        <v>723547</v>
       </c>
       <c r="R206" t="n">
-        <v>7544568</v>
+        <v>7544600</v>
       </c>
       <c r="S206" t="n">
         <v>5</v>
@@ -23661,10 +23661,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>124355546</v>
+        <v>124355667</v>
       </c>
       <c r="B207" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -23673,38 +23673,38 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>723347</v>
+        <v>723695</v>
       </c>
       <c r="R207" t="n">
-        <v>7544617</v>
+        <v>7544233</v>
       </c>
       <c r="S207" t="n">
         <v>5</v>
@@ -23731,12 +23731,12 @@
       </c>
       <c r="Y207" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -23763,10 +23763,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>124355539</v>
+        <v>124355646</v>
       </c>
       <c r="B208" t="n">
-        <v>105102</v>
+        <v>79927</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -23779,34 +23779,34 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>221725</v>
+        <v>6464</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>722977</v>
+        <v>723617</v>
       </c>
       <c r="R208" t="n">
-        <v>7544571</v>
+        <v>7544144</v>
       </c>
       <c r="S208" t="n">
         <v>5</v>
@@ -23833,12 +23833,12 @@
       </c>
       <c r="Y208" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -23865,10 +23865,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>124355529</v>
+        <v>124355873</v>
       </c>
       <c r="B209" t="n">
-        <v>105102</v>
+        <v>79926</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -23881,34 +23881,34 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>221725</v>
+        <v>6463</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>723365</v>
+        <v>723684</v>
       </c>
       <c r="R209" t="n">
-        <v>7545207</v>
+        <v>7544232</v>
       </c>
       <c r="S209" t="n">
         <v>5</v>
@@ -23935,12 +23935,12 @@
       </c>
       <c r="Y209" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -23967,10 +23967,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>124355542</v>
+        <v>124355611</v>
       </c>
       <c r="B210" t="n">
-        <v>105102</v>
+        <v>57529</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -23979,38 +23979,38 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>221725</v>
+        <v>100049</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>723159</v>
+        <v>723694</v>
       </c>
       <c r="R210" t="n">
-        <v>7544605</v>
+        <v>7544233</v>
       </c>
       <c r="S210" t="n">
         <v>5</v>
@@ -24037,12 +24037,17 @@
       </c>
       <c r="Y210" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="AC210" t="inlineStr">
+        <is>
+          <t>hackmärken</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -24069,10 +24074,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>124355516</v>
+        <v>124355609</v>
       </c>
       <c r="B211" t="n">
-        <v>105102</v>
+        <v>98122</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -24085,34 +24090,34 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>221725</v>
+        <v>221952</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>723694</v>
+        <v>723343</v>
       </c>
       <c r="R211" t="n">
-        <v>7544160</v>
+        <v>7544612</v>
       </c>
       <c r="S211" t="n">
         <v>5</v>
@@ -24139,12 +24144,12 @@
       </c>
       <c r="Y211" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -24171,10 +24176,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>124355544</v>
+        <v>124355855</v>
       </c>
       <c r="B212" t="n">
-        <v>105102</v>
+        <v>97128</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -24187,21 +24192,21 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>221725</v>
+        <v>222741</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -24211,10 +24216,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>723301</v>
+        <v>722944</v>
       </c>
       <c r="R212" t="n">
-        <v>7544640</v>
+        <v>7544574</v>
       </c>
       <c r="S212" t="n">
         <v>5</v>
@@ -24273,10 +24278,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>124355609</v>
+        <v>124355530</v>
       </c>
       <c r="B213" t="n">
-        <v>98122</v>
+        <v>105102</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -24289,21 +24294,21 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>221952</v>
+        <v>221725</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -24313,10 +24318,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>723343</v>
+        <v>723178</v>
       </c>
       <c r="R213" t="n">
-        <v>7544612</v>
+        <v>7545219</v>
       </c>
       <c r="S213" t="n">
         <v>5</v>
@@ -24375,10 +24380,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>124355611</v>
+        <v>124355541</v>
       </c>
       <c r="B214" t="n">
-        <v>57529</v>
+        <v>105102</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -24387,38 +24392,38 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>100049</v>
+        <v>221725</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>723694</v>
+        <v>723087</v>
       </c>
       <c r="R214" t="n">
-        <v>7544233</v>
+        <v>7544566</v>
       </c>
       <c r="S214" t="n">
         <v>5</v>
@@ -24445,17 +24450,12 @@
       </c>
       <c r="Y214" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
-        </is>
-      </c>
-      <c r="AC214" t="inlineStr">
-        <is>
-          <t>hackmärken</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -24482,7 +24482,7 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>124355666</v>
+        <v>124355668</v>
       </c>
       <c r="B215" t="n">
         <v>98101</v>
@@ -24522,10 +24522,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>723699</v>
+        <v>723703</v>
       </c>
       <c r="R215" t="n">
-        <v>7544235</v>
+        <v>7544180</v>
       </c>
       <c r="S215" t="n">
         <v>5</v>
@@ -24584,10 +24584,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>124355646</v>
+        <v>124355654</v>
       </c>
       <c r="B216" t="n">
-        <v>79927</v>
+        <v>78151</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -24596,25 +24596,25 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>6464</v>
+        <v>498</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
@@ -24624,10 +24624,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>723617</v>
+        <v>723693</v>
       </c>
       <c r="R216" t="n">
-        <v>7544144</v>
+        <v>7544234</v>
       </c>
       <c r="S216" t="n">
         <v>5</v>
@@ -24686,10 +24686,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>124355870</v>
+        <v>124355543</v>
       </c>
       <c r="B217" t="n">
-        <v>78455</v>
+        <v>105102</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -24698,38 +24698,38 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>353</v>
+        <v>221725</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
       <c r="P217" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>723669</v>
+        <v>723227</v>
       </c>
       <c r="R217" t="n">
-        <v>7544113</v>
+        <v>7544640</v>
       </c>
       <c r="S217" t="n">
         <v>5</v>
@@ -24756,12 +24756,12 @@
       </c>
       <c r="Y217" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -24788,10 +24788,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>124355530</v>
+        <v>124355806</v>
       </c>
       <c r="B218" t="n">
-        <v>105102</v>
+        <v>98000</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -24804,21 +24804,21 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>221725</v>
+        <v>219795</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -24828,10 +24828,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>723178</v>
+        <v>722934</v>
       </c>
       <c r="R218" t="n">
-        <v>7545219</v>
+        <v>7544572</v>
       </c>
       <c r="S218" t="n">
         <v>5</v>
@@ -24890,10 +24890,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>124355877</v>
+        <v>124355540</v>
       </c>
       <c r="B219" t="n">
-        <v>74893</v>
+        <v>105102</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -24902,38 +24902,38 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>308</v>
+        <v>221725</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>723696</v>
+        <v>723038</v>
       </c>
       <c r="R219" t="n">
-        <v>7544172</v>
+        <v>7544552</v>
       </c>
       <c r="S219" t="n">
         <v>5</v>
@@ -24960,12 +24960,12 @@
       </c>
       <c r="Y219" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD219" t="b">

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -21621,10 +21621,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>124355570</v>
+        <v>124355632</v>
       </c>
       <c r="B187" t="n">
-        <v>90977</v>
+        <v>96985</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -21637,34 +21637,34 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>5447</v>
+        <v>221941</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>723343</v>
+        <v>723668</v>
       </c>
       <c r="R187" t="n">
-        <v>7544616</v>
+        <v>7544288</v>
       </c>
       <c r="S187" t="n">
         <v>5</v>
@@ -21691,12 +21691,12 @@
       </c>
       <c r="Y187" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -21723,10 +21723,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>124355632</v>
+        <v>124355546</v>
       </c>
       <c r="B188" t="n">
-        <v>96985</v>
+        <v>105102</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -21739,34 +21739,34 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>221941</v>
+        <v>221725</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>723668</v>
+        <v>723347</v>
       </c>
       <c r="R188" t="n">
-        <v>7544288</v>
+        <v>7544617</v>
       </c>
       <c r="S188" t="n">
         <v>5</v>
@@ -21793,12 +21793,12 @@
       </c>
       <c r="Y188" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -21825,10 +21825,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>124355546</v>
+        <v>124355570</v>
       </c>
       <c r="B189" t="n">
-        <v>105102</v>
+        <v>90977</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -21841,21 +21841,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>221725</v>
+        <v>5447</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -21865,10 +21865,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>723347</v>
+        <v>723343</v>
       </c>
       <c r="R189" t="n">
-        <v>7544617</v>
+        <v>7544616</v>
       </c>
       <c r="S189" t="n">
         <v>5</v>
@@ -22131,10 +22131,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>124355870</v>
+        <v>124355807</v>
       </c>
       <c r="B192" t="n">
-        <v>78455</v>
+        <v>98000</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -22143,38 +22143,38 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>353</v>
+        <v>219795</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>723669</v>
+        <v>723042</v>
       </c>
       <c r="R192" t="n">
-        <v>7544113</v>
+        <v>7544553</v>
       </c>
       <c r="S192" t="n">
         <v>5</v>
@@ -22201,12 +22201,12 @@
       </c>
       <c r="Y192" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -22233,10 +22233,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>124355807</v>
+        <v>124355870</v>
       </c>
       <c r="B193" t="n">
-        <v>98000</v>
+        <v>78455</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -22245,38 +22245,38 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>219795</v>
+        <v>353</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>723042</v>
+        <v>723669</v>
       </c>
       <c r="R193" t="n">
-        <v>7544553</v>
+        <v>7544113</v>
       </c>
       <c r="S193" t="n">
         <v>5</v>
@@ -22303,12 +22303,12 @@
       </c>
       <c r="Y193" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD193" t="b">

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -20805,10 +20805,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>124355802</v>
+        <v>124355529</v>
       </c>
       <c r="B179" t="n">
-        <v>98000</v>
+        <v>105102</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -20821,34 +20821,34 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>219795</v>
+        <v>221725</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>723703</v>
+        <v>723365</v>
       </c>
       <c r="R179" t="n">
-        <v>7544232</v>
+        <v>7545207</v>
       </c>
       <c r="S179" t="n">
         <v>5</v>
@@ -20875,12 +20875,12 @@
       </c>
       <c r="Y179" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -20907,10 +20907,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>124355851</v>
+        <v>124355552</v>
       </c>
       <c r="B180" t="n">
-        <v>97128</v>
+        <v>105102</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -20923,34 +20923,34 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>222741</v>
+        <v>221725</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>723705</v>
+        <v>723608</v>
       </c>
       <c r="R180" t="n">
-        <v>7544144</v>
+        <v>7544580</v>
       </c>
       <c r="S180" t="n">
         <v>5</v>
@@ -20977,12 +20977,12 @@
       </c>
       <c r="Y180" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -21009,10 +21009,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>124355592</v>
+        <v>124355551</v>
       </c>
       <c r="B181" t="n">
-        <v>79920</v>
+        <v>105102</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -21025,34 +21025,34 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6462</v>
+        <v>221725</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>723699</v>
+        <v>723547</v>
       </c>
       <c r="R181" t="n">
-        <v>7544155</v>
+        <v>7544600</v>
       </c>
       <c r="S181" t="n">
         <v>5</v>
@@ -21079,12 +21079,12 @@
       </c>
       <c r="Y181" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -21111,10 +21111,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>124355877</v>
+        <v>124355851</v>
       </c>
       <c r="B182" t="n">
-        <v>74893</v>
+        <v>97128</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -21123,25 +21123,25 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>308</v>
+        <v>222741</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -21151,10 +21151,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>723696</v>
+        <v>723705</v>
       </c>
       <c r="R182" t="n">
-        <v>7544172</v>
+        <v>7544144</v>
       </c>
       <c r="S182" t="n">
         <v>5</v>
@@ -21213,10 +21213,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>124355826</v>
+        <v>124355530</v>
       </c>
       <c r="B183" t="n">
-        <v>91030</v>
+        <v>105102</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -21225,25 +21225,25 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>5432</v>
+        <v>221725</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -21253,10 +21253,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>723345</v>
+        <v>723178</v>
       </c>
       <c r="R183" t="n">
-        <v>7544616</v>
+        <v>7545219</v>
       </c>
       <c r="S183" t="n">
         <v>5</v>
@@ -21315,7 +21315,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>124355544</v>
+        <v>124355542</v>
       </c>
       <c r="B184" t="n">
         <v>105102</v>
@@ -21355,10 +21355,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>723301</v>
+        <v>723159</v>
       </c>
       <c r="R184" t="n">
-        <v>7544640</v>
+        <v>7544605</v>
       </c>
       <c r="S184" t="n">
         <v>5</v>
@@ -21417,10 +21417,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>124355515</v>
+        <v>124355570</v>
       </c>
       <c r="B185" t="n">
-        <v>105102</v>
+        <v>90977</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -21433,34 +21433,34 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>221725</v>
+        <v>5447</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>723720</v>
+        <v>723343</v>
       </c>
       <c r="R185" t="n">
-        <v>7544240</v>
+        <v>7544616</v>
       </c>
       <c r="S185" t="n">
         <v>5</v>
@@ -21487,12 +21487,12 @@
       </c>
       <c r="Y185" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -21519,10 +21519,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>124355538</v>
+        <v>124355870</v>
       </c>
       <c r="B186" t="n">
-        <v>105102</v>
+        <v>78455</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -21531,38 +21531,38 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>221725</v>
+        <v>353</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>722917</v>
+        <v>723669</v>
       </c>
       <c r="R186" t="n">
-        <v>7544575</v>
+        <v>7544113</v>
       </c>
       <c r="S186" t="n">
         <v>5</v>
@@ -21589,12 +21589,12 @@
       </c>
       <c r="Y186" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -21621,10 +21621,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>124355632</v>
+        <v>124355598</v>
       </c>
       <c r="B187" t="n">
-        <v>96985</v>
+        <v>79920</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -21637,34 +21637,34 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>221941</v>
+        <v>6462</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>723668</v>
+        <v>723350</v>
       </c>
       <c r="R187" t="n">
-        <v>7544288</v>
+        <v>7544621</v>
       </c>
       <c r="S187" t="n">
         <v>5</v>
@@ -21691,12 +21691,12 @@
       </c>
       <c r="Y187" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -21723,10 +21723,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>124355546</v>
+        <v>124355855</v>
       </c>
       <c r="B188" t="n">
-        <v>105102</v>
+        <v>97128</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -21739,21 +21739,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>221725</v>
+        <v>222741</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -21763,10 +21763,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>723347</v>
+        <v>722944</v>
       </c>
       <c r="R188" t="n">
-        <v>7544617</v>
+        <v>7544574</v>
       </c>
       <c r="S188" t="n">
         <v>5</v>
@@ -21825,10 +21825,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>124355570</v>
+        <v>124355857</v>
       </c>
       <c r="B189" t="n">
-        <v>90977</v>
+        <v>97128</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -21841,21 +21841,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>5447</v>
+        <v>222741</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -21927,10 +21927,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>124355856</v>
+        <v>124355672</v>
       </c>
       <c r="B190" t="n">
-        <v>97128</v>
+        <v>98101</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -21939,25 +21939,25 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>222741</v>
+        <v>220787</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -21967,10 +21967,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>723068</v>
+        <v>723359</v>
       </c>
       <c r="R190" t="n">
-        <v>7544568</v>
+        <v>7545207</v>
       </c>
       <c r="S190" t="n">
         <v>5</v>
@@ -22029,7 +22029,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>124355542</v>
+        <v>124355540</v>
       </c>
       <c r="B191" t="n">
         <v>105102</v>
@@ -22069,10 +22069,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>723159</v>
+        <v>723038</v>
       </c>
       <c r="R191" t="n">
-        <v>7544605</v>
+        <v>7544552</v>
       </c>
       <c r="S191" t="n">
         <v>5</v>
@@ -22131,10 +22131,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>124355807</v>
+        <v>124355611</v>
       </c>
       <c r="B192" t="n">
-        <v>98000</v>
+        <v>57529</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -22143,38 +22143,38 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>219795</v>
+        <v>100049</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>723042</v>
+        <v>723694</v>
       </c>
       <c r="R192" t="n">
-        <v>7544553</v>
+        <v>7544233</v>
       </c>
       <c r="S192" t="n">
         <v>5</v>
@@ -22201,12 +22201,17 @@
       </c>
       <c r="Y192" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="AC192" t="inlineStr">
+        <is>
+          <t>hackmärken</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -22233,10 +22238,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>124355870</v>
+        <v>124355806</v>
       </c>
       <c r="B193" t="n">
-        <v>78455</v>
+        <v>98000</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -22245,38 +22250,38 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>353</v>
+        <v>219795</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>723669</v>
+        <v>722934</v>
       </c>
       <c r="R193" t="n">
-        <v>7544113</v>
+        <v>7544572</v>
       </c>
       <c r="S193" t="n">
         <v>5</v>
@@ -22303,12 +22308,12 @@
       </c>
       <c r="Y193" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -22335,7 +22340,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>124355552</v>
+        <v>124355516</v>
       </c>
       <c r="B194" t="n">
         <v>105102</v>
@@ -22371,14 +22376,14 @@
       <c r="I194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>723608</v>
+        <v>723694</v>
       </c>
       <c r="R194" t="n">
-        <v>7544580</v>
+        <v>7544160</v>
       </c>
       <c r="S194" t="n">
         <v>5</v>
@@ -22405,12 +22410,12 @@
       </c>
       <c r="Y194" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -22437,10 +22442,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>124355905</v>
+        <v>124355632</v>
       </c>
       <c r="B195" t="n">
-        <v>78194</v>
+        <v>96985</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -22449,25 +22454,25 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6437</v>
+        <v>221941</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -22477,10 +22482,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>723693</v>
+        <v>723668</v>
       </c>
       <c r="R195" t="n">
-        <v>7544182</v>
+        <v>7544288</v>
       </c>
       <c r="S195" t="n">
         <v>5</v>
@@ -22539,10 +22544,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>124355598</v>
+        <v>124355543</v>
       </c>
       <c r="B196" t="n">
-        <v>79920</v>
+        <v>105102</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -22555,21 +22560,21 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6462</v>
+        <v>221725</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -22579,10 +22584,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>723350</v>
+        <v>723227</v>
       </c>
       <c r="R196" t="n">
-        <v>7544621</v>
+        <v>7544640</v>
       </c>
       <c r="S196" t="n">
         <v>5</v>
@@ -22641,10 +22646,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>124355672</v>
+        <v>124355873</v>
       </c>
       <c r="B197" t="n">
-        <v>98101</v>
+        <v>79926</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -22653,38 +22658,38 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>723359</v>
+        <v>723684</v>
       </c>
       <c r="R197" t="n">
-        <v>7545207</v>
+        <v>7544232</v>
       </c>
       <c r="S197" t="n">
         <v>5</v>
@@ -22711,12 +22716,12 @@
       </c>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -22743,7 +22748,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>124355666</v>
+        <v>124355667</v>
       </c>
       <c r="B198" t="n">
         <v>98101</v>
@@ -22783,10 +22788,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>723699</v>
+        <v>723695</v>
       </c>
       <c r="R198" t="n">
-        <v>7544235</v>
+        <v>7544233</v>
       </c>
       <c r="S198" t="n">
         <v>5</v>
@@ -22845,10 +22850,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>124355850</v>
+        <v>124355666</v>
       </c>
       <c r="B199" t="n">
-        <v>97128</v>
+        <v>98101</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -22857,25 +22862,25 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>222741</v>
+        <v>220787</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -22885,10 +22890,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>723616</v>
+        <v>723699</v>
       </c>
       <c r="R199" t="n">
-        <v>7544154</v>
+        <v>7544235</v>
       </c>
       <c r="S199" t="n">
         <v>5</v>
@@ -22947,10 +22952,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>124355857</v>
+        <v>124355807</v>
       </c>
       <c r="B200" t="n">
-        <v>97128</v>
+        <v>98000</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -22963,21 +22968,21 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>222741</v>
+        <v>219795</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -22987,10 +22992,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>723343</v>
+        <v>723042</v>
       </c>
       <c r="R200" t="n">
-        <v>7544616</v>
+        <v>7544553</v>
       </c>
       <c r="S200" t="n">
         <v>5</v>
@@ -23049,7 +23054,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>124355513</v>
+        <v>124355541</v>
       </c>
       <c r="B201" t="n">
         <v>105102</v>
@@ -23085,14 +23090,14 @@
       <c r="I201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>723653</v>
+        <v>723087</v>
       </c>
       <c r="R201" t="n">
-        <v>7544288</v>
+        <v>7544566</v>
       </c>
       <c r="S201" t="n">
         <v>5</v>
@@ -23119,12 +23124,12 @@
       </c>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -23151,10 +23156,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>124355516</v>
+        <v>124355850</v>
       </c>
       <c r="B202" t="n">
-        <v>105102</v>
+        <v>97128</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -23167,21 +23172,21 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>221725</v>
+        <v>222741</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -23191,10 +23196,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>723694</v>
+        <v>723616</v>
       </c>
       <c r="R202" t="n">
-        <v>7544160</v>
+        <v>7544154</v>
       </c>
       <c r="S202" t="n">
         <v>5</v>
@@ -23253,10 +23258,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>124355529</v>
+        <v>124355826</v>
       </c>
       <c r="B203" t="n">
-        <v>105102</v>
+        <v>91030</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -23265,25 +23270,25 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>221725</v>
+        <v>5432</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -23293,10 +23298,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>723365</v>
+        <v>723345</v>
       </c>
       <c r="R203" t="n">
-        <v>7545207</v>
+        <v>7544616</v>
       </c>
       <c r="S203" t="n">
         <v>5</v>
@@ -23355,10 +23360,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>124355539</v>
+        <v>124355646</v>
       </c>
       <c r="B204" t="n">
-        <v>105102</v>
+        <v>79927</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -23371,34 +23376,34 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>221725</v>
+        <v>6464</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>722977</v>
+        <v>723617</v>
       </c>
       <c r="R204" t="n">
-        <v>7544571</v>
+        <v>7544144</v>
       </c>
       <c r="S204" t="n">
         <v>5</v>
@@ -23425,12 +23430,12 @@
       </c>
       <c r="Y204" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -23457,7 +23462,7 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>124355548</v>
+        <v>124355538</v>
       </c>
       <c r="B205" t="n">
         <v>105102</v>
@@ -23497,10 +23502,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>723515</v>
+        <v>722917</v>
       </c>
       <c r="R205" t="n">
-        <v>7544632</v>
+        <v>7544575</v>
       </c>
       <c r="S205" t="n">
         <v>5</v>
@@ -23559,10 +23564,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>124355551</v>
+        <v>124355592</v>
       </c>
       <c r="B206" t="n">
-        <v>105102</v>
+        <v>79920</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -23575,34 +23580,34 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>221725</v>
+        <v>6462</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>723547</v>
+        <v>723699</v>
       </c>
       <c r="R206" t="n">
-        <v>7544600</v>
+        <v>7544155</v>
       </c>
       <c r="S206" t="n">
         <v>5</v>
@@ -23629,12 +23634,12 @@
       </c>
       <c r="Y206" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -23661,10 +23666,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>124355667</v>
+        <v>124355546</v>
       </c>
       <c r="B207" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -23673,38 +23678,38 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>723695</v>
+        <v>723347</v>
       </c>
       <c r="R207" t="n">
-        <v>7544233</v>
+        <v>7544617</v>
       </c>
       <c r="S207" t="n">
         <v>5</v>
@@ -23731,12 +23736,12 @@
       </c>
       <c r="Y207" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -23763,10 +23768,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>124355646</v>
+        <v>124355548</v>
       </c>
       <c r="B208" t="n">
-        <v>79927</v>
+        <v>105102</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -23779,34 +23784,34 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>6464</v>
+        <v>221725</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>723617</v>
+        <v>723515</v>
       </c>
       <c r="R208" t="n">
-        <v>7544144</v>
+        <v>7544632</v>
       </c>
       <c r="S208" t="n">
         <v>5</v>
@@ -23833,12 +23838,12 @@
       </c>
       <c r="Y208" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -23865,10 +23870,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>124355873</v>
+        <v>124355515</v>
       </c>
       <c r="B209" t="n">
-        <v>79926</v>
+        <v>105102</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -23881,21 +23886,21 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>6463</v>
+        <v>221725</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -23905,10 +23910,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>723684</v>
+        <v>723720</v>
       </c>
       <c r="R209" t="n">
-        <v>7544232</v>
+        <v>7544240</v>
       </c>
       <c r="S209" t="n">
         <v>5</v>
@@ -23967,10 +23972,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>124355611</v>
+        <v>124355539</v>
       </c>
       <c r="B210" t="n">
-        <v>57529</v>
+        <v>105102</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -23979,38 +23984,38 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>100049</v>
+        <v>221725</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>723694</v>
+        <v>722977</v>
       </c>
       <c r="R210" t="n">
-        <v>7544233</v>
+        <v>7544571</v>
       </c>
       <c r="S210" t="n">
         <v>5</v>
@@ -24037,17 +24042,12 @@
       </c>
       <c r="Y210" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
-        </is>
-      </c>
-      <c r="AC210" t="inlineStr">
-        <is>
-          <t>hackmärken</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -24074,10 +24074,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>124355609</v>
+        <v>124355877</v>
       </c>
       <c r="B211" t="n">
-        <v>98122</v>
+        <v>74893</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -24086,38 +24086,38 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>221952</v>
+        <v>308</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>723343</v>
+        <v>723696</v>
       </c>
       <c r="R211" t="n">
-        <v>7544612</v>
+        <v>7544172</v>
       </c>
       <c r="S211" t="n">
         <v>5</v>
@@ -24144,12 +24144,12 @@
       </c>
       <c r="Y211" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -24176,10 +24176,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>124355855</v>
+        <v>124355802</v>
       </c>
       <c r="B212" t="n">
-        <v>97128</v>
+        <v>98000</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -24192,34 +24192,34 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>222741</v>
+        <v>219795</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>722944</v>
+        <v>723703</v>
       </c>
       <c r="R212" t="n">
-        <v>7544574</v>
+        <v>7544232</v>
       </c>
       <c r="S212" t="n">
         <v>5</v>
@@ -24246,12 +24246,12 @@
       </c>
       <c r="Y212" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -24278,10 +24278,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>124355530</v>
+        <v>124355609</v>
       </c>
       <c r="B213" t="n">
-        <v>105102</v>
+        <v>98122</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -24294,21 +24294,21 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>221725</v>
+        <v>221952</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -24318,10 +24318,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>723178</v>
+        <v>723343</v>
       </c>
       <c r="R213" t="n">
-        <v>7545219</v>
+        <v>7544612</v>
       </c>
       <c r="S213" t="n">
         <v>5</v>
@@ -24380,10 +24380,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>124355541</v>
+        <v>124355668</v>
       </c>
       <c r="B214" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -24392,38 +24392,38 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>723087</v>
+        <v>723703</v>
       </c>
       <c r="R214" t="n">
-        <v>7544566</v>
+        <v>7544180</v>
       </c>
       <c r="S214" t="n">
         <v>5</v>
@@ -24450,12 +24450,12 @@
       </c>
       <c r="Y214" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -24482,10 +24482,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>124355668</v>
+        <v>124355513</v>
       </c>
       <c r="B215" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -24494,25 +24494,25 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
@@ -24522,10 +24522,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>723703</v>
+        <v>723653</v>
       </c>
       <c r="R215" t="n">
-        <v>7544180</v>
+        <v>7544288</v>
       </c>
       <c r="S215" t="n">
         <v>5</v>
@@ -24584,10 +24584,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>124355654</v>
+        <v>124355905</v>
       </c>
       <c r="B216" t="n">
-        <v>78151</v>
+        <v>78194</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -24596,25 +24596,25 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>498</v>
+        <v>6437</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
@@ -24627,7 +24627,7 @@
         <v>723693</v>
       </c>
       <c r="R216" t="n">
-        <v>7544234</v>
+        <v>7544182</v>
       </c>
       <c r="S216" t="n">
         <v>5</v>
@@ -24686,10 +24686,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>124355543</v>
+        <v>124355654</v>
       </c>
       <c r="B217" t="n">
-        <v>105102</v>
+        <v>78151</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -24698,38 +24698,38 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>221725</v>
+        <v>498</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
       <c r="P217" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>723227</v>
+        <v>723693</v>
       </c>
       <c r="R217" t="n">
-        <v>7544640</v>
+        <v>7544234</v>
       </c>
       <c r="S217" t="n">
         <v>5</v>
@@ -24756,12 +24756,12 @@
       </c>
       <c r="Y217" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -24788,10 +24788,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>124355806</v>
+        <v>124355856</v>
       </c>
       <c r="B218" t="n">
-        <v>98000</v>
+        <v>97128</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -24804,21 +24804,21 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>219795</v>
+        <v>222741</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -24828,10 +24828,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>722934</v>
+        <v>723068</v>
       </c>
       <c r="R218" t="n">
-        <v>7544572</v>
+        <v>7544568</v>
       </c>
       <c r="S218" t="n">
         <v>5</v>
@@ -24890,7 +24890,7 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>124355540</v>
+        <v>124355544</v>
       </c>
       <c r="B219" t="n">
         <v>105102</v>
@@ -24930,10 +24930,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>723038</v>
+        <v>723301</v>
       </c>
       <c r="R219" t="n">
-        <v>7544552</v>
+        <v>7544640</v>
       </c>
       <c r="S219" t="n">
         <v>5</v>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -20805,10 +20805,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>124355529</v>
+        <v>124355667</v>
       </c>
       <c r="B179" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -20817,38 +20817,38 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>723365</v>
+        <v>723695</v>
       </c>
       <c r="R179" t="n">
-        <v>7545207</v>
+        <v>7544233</v>
       </c>
       <c r="S179" t="n">
         <v>5</v>
@@ -20875,12 +20875,12 @@
       </c>
       <c r="Y179" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -20907,10 +20907,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>124355552</v>
+        <v>124355807</v>
       </c>
       <c r="B180" t="n">
-        <v>105102</v>
+        <v>98000</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -20923,21 +20923,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>221725</v>
+        <v>219795</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -20947,10 +20947,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>723608</v>
+        <v>723042</v>
       </c>
       <c r="R180" t="n">
-        <v>7544580</v>
+        <v>7544553</v>
       </c>
       <c r="S180" t="n">
         <v>5</v>
@@ -21009,7 +21009,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>124355551</v>
+        <v>124355529</v>
       </c>
       <c r="B181" t="n">
         <v>105102</v>
@@ -21049,10 +21049,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>723547</v>
+        <v>723365</v>
       </c>
       <c r="R181" t="n">
-        <v>7544600</v>
+        <v>7545207</v>
       </c>
       <c r="S181" t="n">
         <v>5</v>
@@ -21111,10 +21111,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>124355851</v>
+        <v>124355544</v>
       </c>
       <c r="B182" t="n">
-        <v>97128</v>
+        <v>105102</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -21127,34 +21127,34 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>222741</v>
+        <v>221725</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>723705</v>
+        <v>723301</v>
       </c>
       <c r="R182" t="n">
-        <v>7544144</v>
+        <v>7544640</v>
       </c>
       <c r="S182" t="n">
         <v>5</v>
@@ -21181,12 +21181,12 @@
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -21213,10 +21213,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>124355530</v>
+        <v>124355592</v>
       </c>
       <c r="B183" t="n">
-        <v>105102</v>
+        <v>79920</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -21229,34 +21229,34 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>221725</v>
+        <v>6462</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>723178</v>
+        <v>723699</v>
       </c>
       <c r="R183" t="n">
-        <v>7545219</v>
+        <v>7544155</v>
       </c>
       <c r="S183" t="n">
         <v>5</v>
@@ -21283,12 +21283,12 @@
       </c>
       <c r="Y183" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -21315,10 +21315,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>124355542</v>
+        <v>124355806</v>
       </c>
       <c r="B184" t="n">
-        <v>105102</v>
+        <v>98000</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -21331,21 +21331,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>221725</v>
+        <v>219795</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -21355,10 +21355,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>723159</v>
+        <v>722934</v>
       </c>
       <c r="R184" t="n">
-        <v>7544605</v>
+        <v>7544572</v>
       </c>
       <c r="S184" t="n">
         <v>5</v>
@@ -21417,10 +21417,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>124355570</v>
+        <v>124355543</v>
       </c>
       <c r="B185" t="n">
-        <v>90977</v>
+        <v>105102</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -21433,21 +21433,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>5447</v>
+        <v>221725</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -21457,10 +21457,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>723343</v>
+        <v>723227</v>
       </c>
       <c r="R185" t="n">
-        <v>7544616</v>
+        <v>7544640</v>
       </c>
       <c r="S185" t="n">
         <v>5</v>
@@ -21519,10 +21519,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>124355870</v>
+        <v>124355540</v>
       </c>
       <c r="B186" t="n">
-        <v>78455</v>
+        <v>105102</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -21531,38 +21531,38 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>353</v>
+        <v>221725</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>723669</v>
+        <v>723038</v>
       </c>
       <c r="R186" t="n">
-        <v>7544113</v>
+        <v>7544552</v>
       </c>
       <c r="S186" t="n">
         <v>5</v>
@@ -21589,12 +21589,12 @@
       </c>
       <c r="Y186" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -21621,10 +21621,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>124355598</v>
+        <v>124355552</v>
       </c>
       <c r="B187" t="n">
-        <v>79920</v>
+        <v>105102</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -21637,21 +21637,21 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6462</v>
+        <v>221725</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -21661,10 +21661,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>723350</v>
+        <v>723608</v>
       </c>
       <c r="R187" t="n">
-        <v>7544621</v>
+        <v>7544580</v>
       </c>
       <c r="S187" t="n">
         <v>5</v>
@@ -21723,10 +21723,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>124355855</v>
+        <v>124355870</v>
       </c>
       <c r="B188" t="n">
-        <v>97128</v>
+        <v>78455</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -21735,38 +21735,38 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>222741</v>
+        <v>353</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>722944</v>
+        <v>723669</v>
       </c>
       <c r="R188" t="n">
-        <v>7544574</v>
+        <v>7544113</v>
       </c>
       <c r="S188" t="n">
         <v>5</v>
@@ -21793,12 +21793,12 @@
       </c>
       <c r="Y188" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -21825,10 +21825,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>124355857</v>
+        <v>124355598</v>
       </c>
       <c r="B189" t="n">
-        <v>97128</v>
+        <v>79920</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -21841,21 +21841,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>222741</v>
+        <v>6462</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -21865,10 +21865,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>723343</v>
+        <v>723350</v>
       </c>
       <c r="R189" t="n">
-        <v>7544616</v>
+        <v>7544621</v>
       </c>
       <c r="S189" t="n">
         <v>5</v>
@@ -21927,10 +21927,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>124355672</v>
+        <v>124355873</v>
       </c>
       <c r="B190" t="n">
-        <v>98101</v>
+        <v>79926</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -21939,38 +21939,38 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>723359</v>
+        <v>723684</v>
       </c>
       <c r="R190" t="n">
-        <v>7545207</v>
+        <v>7544232</v>
       </c>
       <c r="S190" t="n">
         <v>5</v>
@@ -21997,12 +21997,12 @@
       </c>
       <c r="Y190" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -22029,7 +22029,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>124355540</v>
+        <v>124355516</v>
       </c>
       <c r="B191" t="n">
         <v>105102</v>
@@ -22065,14 +22065,14 @@
       <c r="I191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>723038</v>
+        <v>723694</v>
       </c>
       <c r="R191" t="n">
-        <v>7544552</v>
+        <v>7544160</v>
       </c>
       <c r="S191" t="n">
         <v>5</v>
@@ -22099,12 +22099,12 @@
       </c>
       <c r="Y191" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -22131,10 +22131,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>124355611</v>
+        <v>124355548</v>
       </c>
       <c r="B192" t="n">
-        <v>57529</v>
+        <v>105102</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -22143,38 +22143,38 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>100049</v>
+        <v>221725</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>723694</v>
+        <v>723515</v>
       </c>
       <c r="R192" t="n">
-        <v>7544233</v>
+        <v>7544632</v>
       </c>
       <c r="S192" t="n">
         <v>5</v>
@@ -22201,17 +22201,12 @@
       </c>
       <c r="Y192" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
-        </is>
-      </c>
-      <c r="AC192" t="inlineStr">
-        <is>
-          <t>hackmärken</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -22238,10 +22233,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>124355806</v>
+        <v>124355542</v>
       </c>
       <c r="B193" t="n">
-        <v>98000</v>
+        <v>105102</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -22254,21 +22249,21 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>219795</v>
+        <v>221725</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -22278,10 +22273,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>722934</v>
+        <v>723159</v>
       </c>
       <c r="R193" t="n">
-        <v>7544572</v>
+        <v>7544605</v>
       </c>
       <c r="S193" t="n">
         <v>5</v>
@@ -22340,10 +22335,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>124355516</v>
+        <v>124355851</v>
       </c>
       <c r="B194" t="n">
-        <v>105102</v>
+        <v>97128</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -22356,21 +22351,21 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>221725</v>
+        <v>222741</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -22380,10 +22375,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>723694</v>
+        <v>723705</v>
       </c>
       <c r="R194" t="n">
-        <v>7544160</v>
+        <v>7544144</v>
       </c>
       <c r="S194" t="n">
         <v>5</v>
@@ -22442,10 +22437,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>124355632</v>
+        <v>124355857</v>
       </c>
       <c r="B195" t="n">
-        <v>96985</v>
+        <v>97128</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -22458,34 +22453,34 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>221941</v>
+        <v>222741</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>723668</v>
+        <v>723343</v>
       </c>
       <c r="R195" t="n">
-        <v>7544288</v>
+        <v>7544616</v>
       </c>
       <c r="S195" t="n">
         <v>5</v>
@@ -22512,12 +22507,12 @@
       </c>
       <c r="Y195" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -22544,10 +22539,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>124355543</v>
+        <v>124355802</v>
       </c>
       <c r="B196" t="n">
-        <v>105102</v>
+        <v>98000</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -22560,34 +22555,34 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>221725</v>
+        <v>219795</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>723227</v>
+        <v>723703</v>
       </c>
       <c r="R196" t="n">
-        <v>7544640</v>
+        <v>7544232</v>
       </c>
       <c r="S196" t="n">
         <v>5</v>
@@ -22614,12 +22609,12 @@
       </c>
       <c r="Y196" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -22646,10 +22641,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>124355873</v>
+        <v>124355826</v>
       </c>
       <c r="B197" t="n">
-        <v>79926</v>
+        <v>91030</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -22658,38 +22653,38 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>723684</v>
+        <v>723345</v>
       </c>
       <c r="R197" t="n">
-        <v>7544232</v>
+        <v>7544616</v>
       </c>
       <c r="S197" t="n">
         <v>5</v>
@@ -22716,12 +22711,12 @@
       </c>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -22748,7 +22743,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>124355667</v>
+        <v>124355672</v>
       </c>
       <c r="B198" t="n">
         <v>98101</v>
@@ -22784,14 +22779,14 @@
       <c r="I198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>723695</v>
+        <v>723359</v>
       </c>
       <c r="R198" t="n">
-        <v>7544233</v>
+        <v>7545207</v>
       </c>
       <c r="S198" t="n">
         <v>5</v>
@@ -22818,12 +22813,12 @@
       </c>
       <c r="Y198" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -22850,10 +22845,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>124355666</v>
+        <v>124355850</v>
       </c>
       <c r="B199" t="n">
-        <v>98101</v>
+        <v>97128</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -22862,25 +22857,25 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>220787</v>
+        <v>222741</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -22890,10 +22885,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>723699</v>
+        <v>723616</v>
       </c>
       <c r="R199" t="n">
-        <v>7544235</v>
+        <v>7544154</v>
       </c>
       <c r="S199" t="n">
         <v>5</v>
@@ -22952,10 +22947,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>124355807</v>
+        <v>124355570</v>
       </c>
       <c r="B200" t="n">
-        <v>98000</v>
+        <v>90977</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -22968,21 +22963,21 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>219795</v>
+        <v>5447</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -22992,10 +22987,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>723042</v>
+        <v>723343</v>
       </c>
       <c r="R200" t="n">
-        <v>7544553</v>
+        <v>7544616</v>
       </c>
       <c r="S200" t="n">
         <v>5</v>
@@ -23054,7 +23049,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>124355541</v>
+        <v>124355551</v>
       </c>
       <c r="B201" t="n">
         <v>105102</v>
@@ -23094,10 +23089,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>723087</v>
+        <v>723547</v>
       </c>
       <c r="R201" t="n">
-        <v>7544566</v>
+        <v>7544600</v>
       </c>
       <c r="S201" t="n">
         <v>5</v>
@@ -23156,7 +23151,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>124355850</v>
+        <v>124355856</v>
       </c>
       <c r="B202" t="n">
         <v>97128</v>
@@ -23192,14 +23187,14 @@
       <c r="I202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>723616</v>
+        <v>723068</v>
       </c>
       <c r="R202" t="n">
-        <v>7544154</v>
+        <v>7544568</v>
       </c>
       <c r="S202" t="n">
         <v>5</v>
@@ -23226,12 +23221,12 @@
       </c>
       <c r="Y202" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -23258,10 +23253,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>124355826</v>
+        <v>124355632</v>
       </c>
       <c r="B203" t="n">
-        <v>91030</v>
+        <v>96985</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -23270,38 +23265,38 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>5432</v>
+        <v>221941</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>723345</v>
+        <v>723668</v>
       </c>
       <c r="R203" t="n">
-        <v>7544616</v>
+        <v>7544288</v>
       </c>
       <c r="S203" t="n">
         <v>5</v>
@@ -23328,12 +23323,12 @@
       </c>
       <c r="Y203" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -23360,10 +23355,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>124355646</v>
+        <v>124355530</v>
       </c>
       <c r="B204" t="n">
-        <v>79927</v>
+        <v>105102</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -23376,34 +23371,34 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>6464</v>
+        <v>221725</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>723617</v>
+        <v>723178</v>
       </c>
       <c r="R204" t="n">
-        <v>7544144</v>
+        <v>7545219</v>
       </c>
       <c r="S204" t="n">
         <v>5</v>
@@ -23430,12 +23425,12 @@
       </c>
       <c r="Y204" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -23462,10 +23457,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>124355538</v>
+        <v>124355611</v>
       </c>
       <c r="B205" t="n">
-        <v>105102</v>
+        <v>57529</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -23474,38 +23469,38 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>221725</v>
+        <v>100049</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>722917</v>
+        <v>723694</v>
       </c>
       <c r="R205" t="n">
-        <v>7544575</v>
+        <v>7544233</v>
       </c>
       <c r="S205" t="n">
         <v>5</v>
@@ -23532,12 +23527,17 @@
       </c>
       <c r="Y205" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="AC205" t="inlineStr">
+        <is>
+          <t>hackmärken</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -23564,10 +23564,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>124355592</v>
+        <v>124355855</v>
       </c>
       <c r="B206" t="n">
-        <v>79920</v>
+        <v>97128</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -23580,34 +23580,34 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>6462</v>
+        <v>222741</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>723699</v>
+        <v>722944</v>
       </c>
       <c r="R206" t="n">
-        <v>7544155</v>
+        <v>7544574</v>
       </c>
       <c r="S206" t="n">
         <v>5</v>
@@ -23634,12 +23634,12 @@
       </c>
       <c r="Y206" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -23666,7 +23666,7 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>124355546</v>
+        <v>124355538</v>
       </c>
       <c r="B207" t="n">
         <v>105102</v>
@@ -23706,10 +23706,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>723347</v>
+        <v>722917</v>
       </c>
       <c r="R207" t="n">
-        <v>7544617</v>
+        <v>7544575</v>
       </c>
       <c r="S207" t="n">
         <v>5</v>
@@ -23768,10 +23768,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>124355548</v>
+        <v>124355668</v>
       </c>
       <c r="B208" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -23780,38 +23780,38 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>723515</v>
+        <v>723703</v>
       </c>
       <c r="R208" t="n">
-        <v>7544632</v>
+        <v>7544180</v>
       </c>
       <c r="S208" t="n">
         <v>5</v>
@@ -23838,12 +23838,12 @@
       </c>
       <c r="Y208" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -23870,7 +23870,7 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>124355515</v>
+        <v>124355541</v>
       </c>
       <c r="B209" t="n">
         <v>105102</v>
@@ -23906,14 +23906,14 @@
       <c r="I209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>723720</v>
+        <v>723087</v>
       </c>
       <c r="R209" t="n">
-        <v>7544240</v>
+        <v>7544566</v>
       </c>
       <c r="S209" t="n">
         <v>5</v>
@@ -23940,12 +23940,12 @@
       </c>
       <c r="Y209" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -23972,10 +23972,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>124355539</v>
+        <v>124355654</v>
       </c>
       <c r="B210" t="n">
-        <v>105102</v>
+        <v>78151</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -23984,38 +23984,38 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>221725</v>
+        <v>498</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>722977</v>
+        <v>723693</v>
       </c>
       <c r="R210" t="n">
-        <v>7544571</v>
+        <v>7544234</v>
       </c>
       <c r="S210" t="n">
         <v>5</v>
@@ -24042,12 +24042,12 @@
       </c>
       <c r="Y210" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -24074,10 +24074,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>124355877</v>
+        <v>124355646</v>
       </c>
       <c r="B211" t="n">
-        <v>74893</v>
+        <v>79927</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -24086,25 +24086,25 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>308</v>
+        <v>6464</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -24114,10 +24114,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>723696</v>
+        <v>723617</v>
       </c>
       <c r="R211" t="n">
-        <v>7544172</v>
+        <v>7544144</v>
       </c>
       <c r="S211" t="n">
         <v>5</v>
@@ -24176,10 +24176,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>124355802</v>
+        <v>124355515</v>
       </c>
       <c r="B212" t="n">
-        <v>98000</v>
+        <v>105102</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -24192,21 +24192,21 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>219795</v>
+        <v>221725</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -24216,10 +24216,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>723703</v>
+        <v>723720</v>
       </c>
       <c r="R212" t="n">
-        <v>7544232</v>
+        <v>7544240</v>
       </c>
       <c r="S212" t="n">
         <v>5</v>
@@ -24278,10 +24278,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>124355609</v>
+        <v>124355666</v>
       </c>
       <c r="B213" t="n">
-        <v>98122</v>
+        <v>98101</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -24290,38 +24290,38 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
       <c r="P213" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>723343</v>
+        <v>723699</v>
       </c>
       <c r="R213" t="n">
-        <v>7544612</v>
+        <v>7544235</v>
       </c>
       <c r="S213" t="n">
         <v>5</v>
@@ -24348,12 +24348,12 @@
       </c>
       <c r="Y213" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -24380,10 +24380,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>124355668</v>
+        <v>124355609</v>
       </c>
       <c r="B214" t="n">
-        <v>98101</v>
+        <v>98122</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -24392,38 +24392,38 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>723703</v>
+        <v>723343</v>
       </c>
       <c r="R214" t="n">
-        <v>7544180</v>
+        <v>7544612</v>
       </c>
       <c r="S214" t="n">
         <v>5</v>
@@ -24450,12 +24450,12 @@
       </c>
       <c r="Y214" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -24482,10 +24482,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>124355513</v>
+        <v>124355877</v>
       </c>
       <c r="B215" t="n">
-        <v>105102</v>
+        <v>74893</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -24494,25 +24494,25 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>221725</v>
+        <v>308</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
@@ -24522,10 +24522,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>723653</v>
+        <v>723696</v>
       </c>
       <c r="R215" t="n">
-        <v>7544288</v>
+        <v>7544172</v>
       </c>
       <c r="S215" t="n">
         <v>5</v>
@@ -24686,10 +24686,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>124355654</v>
+        <v>124355546</v>
       </c>
       <c r="B217" t="n">
-        <v>78151</v>
+        <v>105102</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -24698,38 +24698,38 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>498</v>
+        <v>221725</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
       <c r="P217" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>723693</v>
+        <v>723347</v>
       </c>
       <c r="R217" t="n">
-        <v>7544234</v>
+        <v>7544617</v>
       </c>
       <c r="S217" t="n">
         <v>5</v>
@@ -24756,12 +24756,12 @@
       </c>
       <c r="Y217" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -24788,10 +24788,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>124355856</v>
+        <v>124355513</v>
       </c>
       <c r="B218" t="n">
-        <v>97128</v>
+        <v>105102</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -24804,34 +24804,34 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>222741</v>
+        <v>221725</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
       <c r="P218" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>723068</v>
+        <v>723653</v>
       </c>
       <c r="R218" t="n">
-        <v>7544568</v>
+        <v>7544288</v>
       </c>
       <c r="S218" t="n">
         <v>5</v>
@@ -24858,12 +24858,12 @@
       </c>
       <c r="Y218" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -24890,7 +24890,7 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>124355544</v>
+        <v>124355539</v>
       </c>
       <c r="B219" t="n">
         <v>105102</v>
@@ -24930,10 +24930,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>723301</v>
+        <v>722977</v>
       </c>
       <c r="R219" t="n">
-        <v>7544640</v>
+        <v>7544571</v>
       </c>
       <c r="S219" t="n">
         <v>5</v>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -20805,10 +20805,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>124355667</v>
+        <v>124355654</v>
       </c>
       <c r="B179" t="n">
-        <v>98101</v>
+        <v>78151</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -20821,21 +20821,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>220787</v>
+        <v>498</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -20845,10 +20845,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>723695</v>
+        <v>723693</v>
       </c>
       <c r="R179" t="n">
-        <v>7544233</v>
+        <v>7544234</v>
       </c>
       <c r="S179" t="n">
         <v>5</v>
@@ -20907,10 +20907,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>124355807</v>
+        <v>124355530</v>
       </c>
       <c r="B180" t="n">
-        <v>98000</v>
+        <v>105102</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -20923,21 +20923,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>219795</v>
+        <v>221725</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -20947,10 +20947,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>723042</v>
+        <v>723178</v>
       </c>
       <c r="R180" t="n">
-        <v>7544553</v>
+        <v>7545219</v>
       </c>
       <c r="S180" t="n">
         <v>5</v>
@@ -21009,10 +21009,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>124355529</v>
+        <v>124355855</v>
       </c>
       <c r="B181" t="n">
-        <v>105102</v>
+        <v>97128</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -21025,21 +21025,21 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>221725</v>
+        <v>222741</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -21049,10 +21049,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>723365</v>
+        <v>722944</v>
       </c>
       <c r="R181" t="n">
-        <v>7545207</v>
+        <v>7544574</v>
       </c>
       <c r="S181" t="n">
         <v>5</v>
@@ -21111,7 +21111,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>124355544</v>
+        <v>124355551</v>
       </c>
       <c r="B182" t="n">
         <v>105102</v>
@@ -21151,10 +21151,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>723301</v>
+        <v>723547</v>
       </c>
       <c r="R182" t="n">
-        <v>7544640</v>
+        <v>7544600</v>
       </c>
       <c r="S182" t="n">
         <v>5</v>
@@ -21213,10 +21213,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>124355592</v>
+        <v>124355802</v>
       </c>
       <c r="B183" t="n">
-        <v>79920</v>
+        <v>98000</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -21229,21 +21229,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6462</v>
+        <v>219795</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -21253,10 +21253,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>723699</v>
+        <v>723703</v>
       </c>
       <c r="R183" t="n">
-        <v>7544155</v>
+        <v>7544232</v>
       </c>
       <c r="S183" t="n">
         <v>5</v>
@@ -21315,10 +21315,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>124355806</v>
+        <v>124355667</v>
       </c>
       <c r="B184" t="n">
-        <v>98000</v>
+        <v>98101</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -21327,38 +21327,38 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>219795</v>
+        <v>220787</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>722934</v>
+        <v>723695</v>
       </c>
       <c r="R184" t="n">
-        <v>7544572</v>
+        <v>7544233</v>
       </c>
       <c r="S184" t="n">
         <v>5</v>
@@ -21385,12 +21385,12 @@
       </c>
       <c r="Y184" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -21519,7 +21519,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>124355540</v>
+        <v>124355513</v>
       </c>
       <c r="B186" t="n">
         <v>105102</v>
@@ -21555,14 +21555,14 @@
       <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>723038</v>
+        <v>723653</v>
       </c>
       <c r="R186" t="n">
-        <v>7544552</v>
+        <v>7544288</v>
       </c>
       <c r="S186" t="n">
         <v>5</v>
@@ -21589,12 +21589,12 @@
       </c>
       <c r="Y186" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -21621,10 +21621,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>124355552</v>
+        <v>124355666</v>
       </c>
       <c r="B187" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -21633,38 +21633,38 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>723608</v>
+        <v>723699</v>
       </c>
       <c r="R187" t="n">
-        <v>7544580</v>
+        <v>7544235</v>
       </c>
       <c r="S187" t="n">
         <v>5</v>
@@ -21691,12 +21691,12 @@
       </c>
       <c r="Y187" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -21723,10 +21723,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>124355870</v>
+        <v>124355538</v>
       </c>
       <c r="B188" t="n">
-        <v>78455</v>
+        <v>105102</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -21735,38 +21735,38 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>353</v>
+        <v>221725</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>723669</v>
+        <v>722917</v>
       </c>
       <c r="R188" t="n">
-        <v>7544113</v>
+        <v>7544575</v>
       </c>
       <c r="S188" t="n">
         <v>5</v>
@@ -21793,12 +21793,12 @@
       </c>
       <c r="Y188" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -21825,10 +21825,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>124355598</v>
+        <v>124355516</v>
       </c>
       <c r="B189" t="n">
-        <v>79920</v>
+        <v>105102</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -21841,34 +21841,34 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6462</v>
+        <v>221725</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>723350</v>
+        <v>723694</v>
       </c>
       <c r="R189" t="n">
-        <v>7544621</v>
+        <v>7544160</v>
       </c>
       <c r="S189" t="n">
         <v>5</v>
@@ -21895,12 +21895,12 @@
       </c>
       <c r="Y189" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -21927,10 +21927,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>124355873</v>
+        <v>124355826</v>
       </c>
       <c r="B190" t="n">
-        <v>79926</v>
+        <v>91030</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -21939,38 +21939,38 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>723684</v>
+        <v>723345</v>
       </c>
       <c r="R190" t="n">
-        <v>7544232</v>
+        <v>7544616</v>
       </c>
       <c r="S190" t="n">
         <v>5</v>
@@ -21997,12 +21997,12 @@
       </c>
       <c r="Y190" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -22029,10 +22029,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>124355516</v>
+        <v>124355850</v>
       </c>
       <c r="B191" t="n">
-        <v>105102</v>
+        <v>97128</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -22045,21 +22045,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>221725</v>
+        <v>222741</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -22069,10 +22069,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>723694</v>
+        <v>723616</v>
       </c>
       <c r="R191" t="n">
-        <v>7544160</v>
+        <v>7544154</v>
       </c>
       <c r="S191" t="n">
         <v>5</v>
@@ -22131,10 +22131,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>124355548</v>
+        <v>124355806</v>
       </c>
       <c r="B192" t="n">
-        <v>105102</v>
+        <v>98000</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -22147,21 +22147,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>221725</v>
+        <v>219795</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -22171,10 +22171,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>723515</v>
+        <v>722934</v>
       </c>
       <c r="R192" t="n">
-        <v>7544632</v>
+        <v>7544572</v>
       </c>
       <c r="S192" t="n">
         <v>5</v>
@@ -22233,7 +22233,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>124355542</v>
+        <v>124355548</v>
       </c>
       <c r="B193" t="n">
         <v>105102</v>
@@ -22273,10 +22273,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>723159</v>
+        <v>723515</v>
       </c>
       <c r="R193" t="n">
-        <v>7544605</v>
+        <v>7544632</v>
       </c>
       <c r="S193" t="n">
         <v>5</v>
@@ -22335,10 +22335,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>124355851</v>
+        <v>124355529</v>
       </c>
       <c r="B194" t="n">
-        <v>97128</v>
+        <v>105102</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -22351,34 +22351,34 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>222741</v>
+        <v>221725</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>723705</v>
+        <v>723365</v>
       </c>
       <c r="R194" t="n">
-        <v>7544144</v>
+        <v>7545207</v>
       </c>
       <c r="S194" t="n">
         <v>5</v>
@@ -22405,12 +22405,12 @@
       </c>
       <c r="Y194" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -22437,10 +22437,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>124355857</v>
+        <v>124355542</v>
       </c>
       <c r="B195" t="n">
-        <v>97128</v>
+        <v>105102</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -22453,21 +22453,21 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>222741</v>
+        <v>221725</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -22477,10 +22477,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>723343</v>
+        <v>723159</v>
       </c>
       <c r="R195" t="n">
-        <v>7544616</v>
+        <v>7544605</v>
       </c>
       <c r="S195" t="n">
         <v>5</v>
@@ -22539,10 +22539,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>124355802</v>
+        <v>124355609</v>
       </c>
       <c r="B196" t="n">
-        <v>98000</v>
+        <v>98122</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -22555,34 +22555,34 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>219795</v>
+        <v>221952</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>723703</v>
+        <v>723343</v>
       </c>
       <c r="R196" t="n">
-        <v>7544232</v>
+        <v>7544612</v>
       </c>
       <c r="S196" t="n">
         <v>5</v>
@@ -22609,12 +22609,12 @@
       </c>
       <c r="Y196" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -22641,10 +22641,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>124355826</v>
+        <v>124355546</v>
       </c>
       <c r="B197" t="n">
-        <v>91030</v>
+        <v>105102</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -22653,25 +22653,25 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>5432</v>
+        <v>221725</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -22681,10 +22681,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>723345</v>
+        <v>723347</v>
       </c>
       <c r="R197" t="n">
-        <v>7544616</v>
+        <v>7544617</v>
       </c>
       <c r="S197" t="n">
         <v>5</v>
@@ -22743,10 +22743,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>124355672</v>
+        <v>124355541</v>
       </c>
       <c r="B198" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -22755,25 +22755,25 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -22783,10 +22783,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>723359</v>
+        <v>723087</v>
       </c>
       <c r="R198" t="n">
-        <v>7545207</v>
+        <v>7544566</v>
       </c>
       <c r="S198" t="n">
         <v>5</v>
@@ -22845,10 +22845,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>124355850</v>
+        <v>124355672</v>
       </c>
       <c r="B199" t="n">
-        <v>97128</v>
+        <v>98101</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -22857,38 +22857,38 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>222741</v>
+        <v>220787</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>723616</v>
+        <v>723359</v>
       </c>
       <c r="R199" t="n">
-        <v>7544154</v>
+        <v>7545207</v>
       </c>
       <c r="S199" t="n">
         <v>5</v>
@@ -22915,12 +22915,12 @@
       </c>
       <c r="Y199" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -22947,10 +22947,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>124355570</v>
+        <v>124355807</v>
       </c>
       <c r="B200" t="n">
-        <v>90977</v>
+        <v>98000</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -22963,21 +22963,21 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>5447</v>
+        <v>219795</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -22987,10 +22987,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>723343</v>
+        <v>723042</v>
       </c>
       <c r="R200" t="n">
-        <v>7544616</v>
+        <v>7544553</v>
       </c>
       <c r="S200" t="n">
         <v>5</v>
@@ -23049,7 +23049,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>124355551</v>
+        <v>124355515</v>
       </c>
       <c r="B201" t="n">
         <v>105102</v>
@@ -23085,14 +23085,14 @@
       <c r="I201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>723547</v>
+        <v>723720</v>
       </c>
       <c r="R201" t="n">
-        <v>7544600</v>
+        <v>7544240</v>
       </c>
       <c r="S201" t="n">
         <v>5</v>
@@ -23119,12 +23119,12 @@
       </c>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -23151,10 +23151,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>124355856</v>
+        <v>124355873</v>
       </c>
       <c r="B202" t="n">
-        <v>97128</v>
+        <v>79926</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -23167,34 +23167,34 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>222741</v>
+        <v>6463</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>723068</v>
+        <v>723684</v>
       </c>
       <c r="R202" t="n">
-        <v>7544568</v>
+        <v>7544232</v>
       </c>
       <c r="S202" t="n">
         <v>5</v>
@@ -23221,12 +23221,12 @@
       </c>
       <c r="Y202" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -23253,10 +23253,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>124355632</v>
+        <v>124355540</v>
       </c>
       <c r="B203" t="n">
-        <v>96985</v>
+        <v>105102</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -23269,34 +23269,34 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>221941</v>
+        <v>221725</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>723668</v>
+        <v>723038</v>
       </c>
       <c r="R203" t="n">
-        <v>7544288</v>
+        <v>7544552</v>
       </c>
       <c r="S203" t="n">
         <v>5</v>
@@ -23323,12 +23323,12 @@
       </c>
       <c r="Y203" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -23355,10 +23355,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>124355530</v>
+        <v>124355598</v>
       </c>
       <c r="B204" t="n">
-        <v>105102</v>
+        <v>79920</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -23371,21 +23371,21 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>221725</v>
+        <v>6462</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -23395,10 +23395,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>723178</v>
+        <v>723350</v>
       </c>
       <c r="R204" t="n">
-        <v>7545219</v>
+        <v>7544621</v>
       </c>
       <c r="S204" t="n">
         <v>5</v>
@@ -23564,10 +23564,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>124355855</v>
+        <v>124355668</v>
       </c>
       <c r="B206" t="n">
-        <v>97128</v>
+        <v>98101</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -23576,38 +23576,38 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>222741</v>
+        <v>220787</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>722944</v>
+        <v>723703</v>
       </c>
       <c r="R206" t="n">
-        <v>7544574</v>
+        <v>7544180</v>
       </c>
       <c r="S206" t="n">
         <v>5</v>
@@ -23634,12 +23634,12 @@
       </c>
       <c r="Y206" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -23666,10 +23666,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>124355538</v>
+        <v>124355877</v>
       </c>
       <c r="B207" t="n">
-        <v>105102</v>
+        <v>74893</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -23678,38 +23678,38 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>221725</v>
+        <v>308</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>722917</v>
+        <v>723696</v>
       </c>
       <c r="R207" t="n">
-        <v>7544575</v>
+        <v>7544172</v>
       </c>
       <c r="S207" t="n">
         <v>5</v>
@@ -23736,12 +23736,12 @@
       </c>
       <c r="Y207" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -23768,10 +23768,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>124355668</v>
+        <v>124355646</v>
       </c>
       <c r="B208" t="n">
-        <v>98101</v>
+        <v>79927</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -23780,25 +23780,25 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
@@ -23808,10 +23808,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>723703</v>
+        <v>723617</v>
       </c>
       <c r="R208" t="n">
-        <v>7544180</v>
+        <v>7544144</v>
       </c>
       <c r="S208" t="n">
         <v>5</v>
@@ -23870,7 +23870,7 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>124355541</v>
+        <v>124355552</v>
       </c>
       <c r="B209" t="n">
         <v>105102</v>
@@ -23910,10 +23910,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>723087</v>
+        <v>723608</v>
       </c>
       <c r="R209" t="n">
-        <v>7544566</v>
+        <v>7544580</v>
       </c>
       <c r="S209" t="n">
         <v>5</v>
@@ -23972,10 +23972,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>124355654</v>
+        <v>124355905</v>
       </c>
       <c r="B210" t="n">
-        <v>78151</v>
+        <v>78194</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -23984,25 +23984,25 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>498</v>
+        <v>6437</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -24015,7 +24015,7 @@
         <v>723693</v>
       </c>
       <c r="R210" t="n">
-        <v>7544234</v>
+        <v>7544182</v>
       </c>
       <c r="S210" t="n">
         <v>5</v>
@@ -24074,10 +24074,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>124355646</v>
+        <v>124355870</v>
       </c>
       <c r="B211" t="n">
-        <v>79927</v>
+        <v>78455</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -24086,25 +24086,25 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>6464</v>
+        <v>353</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -24114,10 +24114,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>723617</v>
+        <v>723669</v>
       </c>
       <c r="R211" t="n">
-        <v>7544144</v>
+        <v>7544113</v>
       </c>
       <c r="S211" t="n">
         <v>5</v>
@@ -24176,10 +24176,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>124355515</v>
+        <v>124355857</v>
       </c>
       <c r="B212" t="n">
-        <v>105102</v>
+        <v>97128</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -24192,34 +24192,34 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>221725</v>
+        <v>222741</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>723720</v>
+        <v>723343</v>
       </c>
       <c r="R212" t="n">
-        <v>7544240</v>
+        <v>7544616</v>
       </c>
       <c r="S212" t="n">
         <v>5</v>
@@ -24246,12 +24246,12 @@
       </c>
       <c r="Y212" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -24278,10 +24278,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>124355666</v>
+        <v>124355856</v>
       </c>
       <c r="B213" t="n">
-        <v>98101</v>
+        <v>97128</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -24290,38 +24290,38 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>220787</v>
+        <v>222741</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
       <c r="P213" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>723699</v>
+        <v>723068</v>
       </c>
       <c r="R213" t="n">
-        <v>7544235</v>
+        <v>7544568</v>
       </c>
       <c r="S213" t="n">
         <v>5</v>
@@ -24348,12 +24348,12 @@
       </c>
       <c r="Y213" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -24380,10 +24380,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>124355609</v>
+        <v>124355632</v>
       </c>
       <c r="B214" t="n">
-        <v>98122</v>
+        <v>96985</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -24396,34 +24396,34 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>221952</v>
+        <v>221941</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>723343</v>
+        <v>723668</v>
       </c>
       <c r="R214" t="n">
-        <v>7544612</v>
+        <v>7544288</v>
       </c>
       <c r="S214" t="n">
         <v>5</v>
@@ -24450,12 +24450,12 @@
       </c>
       <c r="Y214" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -24482,10 +24482,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>124355877</v>
+        <v>124355544</v>
       </c>
       <c r="B215" t="n">
-        <v>74893</v>
+        <v>105102</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -24494,38 +24494,38 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>308</v>
+        <v>221725</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
       <c r="P215" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>723696</v>
+        <v>723301</v>
       </c>
       <c r="R215" t="n">
-        <v>7544172</v>
+        <v>7544640</v>
       </c>
       <c r="S215" t="n">
         <v>5</v>
@@ -24552,12 +24552,12 @@
       </c>
       <c r="Y215" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -24584,10 +24584,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>124355905</v>
+        <v>124355851</v>
       </c>
       <c r="B216" t="n">
-        <v>78194</v>
+        <v>97128</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -24596,25 +24596,25 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>6437</v>
+        <v>222741</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
@@ -24624,10 +24624,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>723693</v>
+        <v>723705</v>
       </c>
       <c r="R216" t="n">
-        <v>7544182</v>
+        <v>7544144</v>
       </c>
       <c r="S216" t="n">
         <v>5</v>
@@ -24686,7 +24686,7 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>124355546</v>
+        <v>124355539</v>
       </c>
       <c r="B217" t="n">
         <v>105102</v>
@@ -24726,10 +24726,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>723347</v>
+        <v>722977</v>
       </c>
       <c r="R217" t="n">
-        <v>7544617</v>
+        <v>7544571</v>
       </c>
       <c r="S217" t="n">
         <v>5</v>
@@ -24788,10 +24788,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>124355513</v>
+        <v>124355570</v>
       </c>
       <c r="B218" t="n">
-        <v>105102</v>
+        <v>90977</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -24804,34 +24804,34 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>221725</v>
+        <v>5447</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
       <c r="P218" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>723653</v>
+        <v>723343</v>
       </c>
       <c r="R218" t="n">
-        <v>7544288</v>
+        <v>7544616</v>
       </c>
       <c r="S218" t="n">
         <v>5</v>
@@ -24858,12 +24858,12 @@
       </c>
       <c r="Y218" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -24890,10 +24890,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>124355539</v>
+        <v>124355592</v>
       </c>
       <c r="B219" t="n">
-        <v>105102</v>
+        <v>79920</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -24906,34 +24906,34 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>221725</v>
+        <v>6462</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>722977</v>
+        <v>723699</v>
       </c>
       <c r="R219" t="n">
-        <v>7544571</v>
+        <v>7544155</v>
       </c>
       <c r="S219" t="n">
         <v>5</v>
@@ -24960,12 +24960,12 @@
       </c>
       <c r="Y219" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD219" t="b">

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -21315,10 +21315,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>124355667</v>
+        <v>124355543</v>
       </c>
       <c r="B184" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -21327,38 +21327,38 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>723695</v>
+        <v>723227</v>
       </c>
       <c r="R184" t="n">
-        <v>7544233</v>
+        <v>7544640</v>
       </c>
       <c r="S184" t="n">
         <v>5</v>
@@ -21385,12 +21385,12 @@
       </c>
       <c r="Y184" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -21417,10 +21417,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>124355543</v>
+        <v>124355667</v>
       </c>
       <c r="B185" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -21429,38 +21429,38 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>723227</v>
+        <v>723695</v>
       </c>
       <c r="R185" t="n">
-        <v>7544640</v>
+        <v>7544233</v>
       </c>
       <c r="S185" t="n">
         <v>5</v>
@@ -21487,12 +21487,12 @@
       </c>
       <c r="Y185" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -22845,10 +22845,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>124355672</v>
+        <v>124355515</v>
       </c>
       <c r="B199" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -22857,38 +22857,38 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>723359</v>
+        <v>723720</v>
       </c>
       <c r="R199" t="n">
-        <v>7545207</v>
+        <v>7544240</v>
       </c>
       <c r="S199" t="n">
         <v>5</v>
@@ -22915,12 +22915,12 @@
       </c>
       <c r="Y199" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -23049,10 +23049,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>124355515</v>
+        <v>124355672</v>
       </c>
       <c r="B201" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -23061,38 +23061,38 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>723720</v>
+        <v>723359</v>
       </c>
       <c r="R201" t="n">
-        <v>7544240</v>
+        <v>7545207</v>
       </c>
       <c r="S201" t="n">
         <v>5</v>
@@ -23119,12 +23119,12 @@
       </c>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -23355,10 +23355,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>124355598</v>
+        <v>124355668</v>
       </c>
       <c r="B204" t="n">
-        <v>79920</v>
+        <v>98101</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -23367,38 +23367,38 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>723350</v>
+        <v>723703</v>
       </c>
       <c r="R204" t="n">
-        <v>7544621</v>
+        <v>7544180</v>
       </c>
       <c r="S204" t="n">
         <v>5</v>
@@ -23425,12 +23425,12 @@
       </c>
       <c r="Y204" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -23457,10 +23457,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>124355611</v>
+        <v>124355877</v>
       </c>
       <c r="B205" t="n">
-        <v>57529</v>
+        <v>74893</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -23473,21 +23473,21 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>100049</v>
+        <v>308</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -23497,10 +23497,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>723694</v>
+        <v>723696</v>
       </c>
       <c r="R205" t="n">
-        <v>7544233</v>
+        <v>7544172</v>
       </c>
       <c r="S205" t="n">
         <v>5</v>
@@ -23533,11 +23533,6 @@
       <c r="AA205" t="inlineStr">
         <is>
           <t>2024-08-09</t>
-        </is>
-      </c>
-      <c r="AC205" t="inlineStr">
-        <is>
-          <t>hackmärken</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -23564,10 +23559,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>124355668</v>
+        <v>124355598</v>
       </c>
       <c r="B206" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -23576,38 +23571,38 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>723703</v>
+        <v>723350</v>
       </c>
       <c r="R206" t="n">
-        <v>7544180</v>
+        <v>7544621</v>
       </c>
       <c r="S206" t="n">
         <v>5</v>
@@ -23634,12 +23629,12 @@
       </c>
       <c r="Y206" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -23666,10 +23661,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>124355877</v>
+        <v>124355611</v>
       </c>
       <c r="B207" t="n">
-        <v>74893</v>
+        <v>57529</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -23682,21 +23677,21 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>308</v>
+        <v>100049</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
@@ -23706,10 +23701,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>723696</v>
+        <v>723694</v>
       </c>
       <c r="R207" t="n">
-        <v>7544172</v>
+        <v>7544233</v>
       </c>
       <c r="S207" t="n">
         <v>5</v>
@@ -23742,6 +23737,11 @@
       <c r="AA207" t="inlineStr">
         <is>
           <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="AC207" t="inlineStr">
+        <is>
+          <t>hackmärken</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -23768,10 +23768,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>124355646</v>
+        <v>124355552</v>
       </c>
       <c r="B208" t="n">
-        <v>79927</v>
+        <v>105102</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -23784,34 +23784,34 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>6464</v>
+        <v>221725</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>723617</v>
+        <v>723608</v>
       </c>
       <c r="R208" t="n">
-        <v>7544144</v>
+        <v>7544580</v>
       </c>
       <c r="S208" t="n">
         <v>5</v>
@@ -23838,12 +23838,12 @@
       </c>
       <c r="Y208" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -23870,10 +23870,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>124355552</v>
+        <v>124355646</v>
       </c>
       <c r="B209" t="n">
-        <v>105102</v>
+        <v>79927</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -23886,34 +23886,34 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>221725</v>
+        <v>6464</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>723608</v>
+        <v>723617</v>
       </c>
       <c r="R209" t="n">
-        <v>7544580</v>
+        <v>7544144</v>
       </c>
       <c r="S209" t="n">
         <v>5</v>
@@ -23940,12 +23940,12 @@
       </c>
       <c r="Y209" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD209" t="b">

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -20805,10 +20805,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>124355654</v>
+        <v>124355855</v>
       </c>
       <c r="B179" t="n">
-        <v>78151</v>
+        <v>97128</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -20817,38 +20817,38 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>498</v>
+        <v>222741</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>723693</v>
+        <v>722944</v>
       </c>
       <c r="R179" t="n">
-        <v>7544234</v>
+        <v>7544574</v>
       </c>
       <c r="S179" t="n">
         <v>5</v>
@@ -20875,12 +20875,12 @@
       </c>
       <c r="Y179" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -20907,10 +20907,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>124355530</v>
+        <v>124355856</v>
       </c>
       <c r="B180" t="n">
-        <v>105102</v>
+        <v>97128</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -20923,21 +20923,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>221725</v>
+        <v>222741</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -20947,10 +20947,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>723178</v>
+        <v>723068</v>
       </c>
       <c r="R180" t="n">
-        <v>7545219</v>
+        <v>7544568</v>
       </c>
       <c r="S180" t="n">
         <v>5</v>
@@ -21009,10 +21009,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>124355855</v>
+        <v>124355654</v>
       </c>
       <c r="B181" t="n">
-        <v>97128</v>
+        <v>78151</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -21021,38 +21021,38 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>222741</v>
+        <v>498</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>722944</v>
+        <v>723693</v>
       </c>
       <c r="R181" t="n">
-        <v>7544574</v>
+        <v>7544234</v>
       </c>
       <c r="S181" t="n">
         <v>5</v>
@@ -21079,12 +21079,12 @@
       </c>
       <c r="Y181" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -21111,10 +21111,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>124355551</v>
+        <v>124355592</v>
       </c>
       <c r="B182" t="n">
-        <v>105102</v>
+        <v>79920</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -21127,34 +21127,34 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>221725</v>
+        <v>6462</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>723547</v>
+        <v>723699</v>
       </c>
       <c r="R182" t="n">
-        <v>7544600</v>
+        <v>7544155</v>
       </c>
       <c r="S182" t="n">
         <v>5</v>
@@ -21181,12 +21181,12 @@
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -21213,10 +21213,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>124355802</v>
+        <v>124355850</v>
       </c>
       <c r="B183" t="n">
-        <v>98000</v>
+        <v>97128</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -21229,21 +21229,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>219795</v>
+        <v>222741</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -21253,10 +21253,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>723703</v>
+        <v>723616</v>
       </c>
       <c r="R183" t="n">
-        <v>7544232</v>
+        <v>7544154</v>
       </c>
       <c r="S183" t="n">
         <v>5</v>
@@ -21315,10 +21315,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>124355543</v>
+        <v>124355611</v>
       </c>
       <c r="B184" t="n">
-        <v>105102</v>
+        <v>57529</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -21327,38 +21327,38 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>221725</v>
+        <v>100049</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>723227</v>
+        <v>723694</v>
       </c>
       <c r="R184" t="n">
-        <v>7544640</v>
+        <v>7544233</v>
       </c>
       <c r="S184" t="n">
         <v>5</v>
@@ -21385,12 +21385,17 @@
       </c>
       <c r="Y184" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="AC184" t="inlineStr">
+        <is>
+          <t>hackmärken</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -21417,7 +21422,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>124355667</v>
+        <v>124355666</v>
       </c>
       <c r="B185" t="n">
         <v>98101</v>
@@ -21457,10 +21462,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>723695</v>
+        <v>723699</v>
       </c>
       <c r="R185" t="n">
-        <v>7544233</v>
+        <v>7544235</v>
       </c>
       <c r="S185" t="n">
         <v>5</v>
@@ -21519,7 +21524,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>124355513</v>
+        <v>124355516</v>
       </c>
       <c r="B186" t="n">
         <v>105102</v>
@@ -21559,10 +21564,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>723653</v>
+        <v>723694</v>
       </c>
       <c r="R186" t="n">
-        <v>7544288</v>
+        <v>7544160</v>
       </c>
       <c r="S186" t="n">
         <v>5</v>
@@ -21621,10 +21626,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>124355666</v>
+        <v>124355806</v>
       </c>
       <c r="B187" t="n">
-        <v>98101</v>
+        <v>98000</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -21633,38 +21638,38 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>220787</v>
+        <v>219795</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>723699</v>
+        <v>722934</v>
       </c>
       <c r="R187" t="n">
-        <v>7544235</v>
+        <v>7544572</v>
       </c>
       <c r="S187" t="n">
         <v>5</v>
@@ -21691,12 +21696,12 @@
       </c>
       <c r="Y187" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -21723,7 +21728,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>124355538</v>
+        <v>124355529</v>
       </c>
       <c r="B188" t="n">
         <v>105102</v>
@@ -21763,10 +21768,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>722917</v>
+        <v>723365</v>
       </c>
       <c r="R188" t="n">
-        <v>7544575</v>
+        <v>7545207</v>
       </c>
       <c r="S188" t="n">
         <v>5</v>
@@ -21825,10 +21830,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>124355516</v>
+        <v>124355667</v>
       </c>
       <c r="B189" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -21837,25 +21842,25 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -21865,10 +21870,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>723694</v>
+        <v>723695</v>
       </c>
       <c r="R189" t="n">
-        <v>7544160</v>
+        <v>7544233</v>
       </c>
       <c r="S189" t="n">
         <v>5</v>
@@ -21927,10 +21932,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>124355826</v>
+        <v>124355548</v>
       </c>
       <c r="B190" t="n">
-        <v>91030</v>
+        <v>105102</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -21939,25 +21944,25 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>5432</v>
+        <v>221725</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -21967,10 +21972,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>723345</v>
+        <v>723515</v>
       </c>
       <c r="R190" t="n">
-        <v>7544616</v>
+        <v>7544632</v>
       </c>
       <c r="S190" t="n">
         <v>5</v>
@@ -22029,10 +22034,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>124355850</v>
+        <v>124355541</v>
       </c>
       <c r="B191" t="n">
-        <v>97128</v>
+        <v>105102</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -22045,34 +22050,34 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>222741</v>
+        <v>221725</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>723616</v>
+        <v>723087</v>
       </c>
       <c r="R191" t="n">
-        <v>7544154</v>
+        <v>7544566</v>
       </c>
       <c r="S191" t="n">
         <v>5</v>
@@ -22099,12 +22104,12 @@
       </c>
       <c r="Y191" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -22131,10 +22136,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>124355806</v>
+        <v>124355544</v>
       </c>
       <c r="B192" t="n">
-        <v>98000</v>
+        <v>105102</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -22147,21 +22152,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>219795</v>
+        <v>221725</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -22171,10 +22176,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>722934</v>
+        <v>723301</v>
       </c>
       <c r="R192" t="n">
-        <v>7544572</v>
+        <v>7544640</v>
       </c>
       <c r="S192" t="n">
         <v>5</v>
@@ -22233,10 +22238,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>124355548</v>
+        <v>124355802</v>
       </c>
       <c r="B193" t="n">
-        <v>105102</v>
+        <v>98000</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -22249,34 +22254,34 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>221725</v>
+        <v>219795</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>723515</v>
+        <v>723703</v>
       </c>
       <c r="R193" t="n">
-        <v>7544632</v>
+        <v>7544232</v>
       </c>
       <c r="S193" t="n">
         <v>5</v>
@@ -22303,12 +22308,12 @@
       </c>
       <c r="Y193" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -22335,10 +22340,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>124355529</v>
+        <v>124355870</v>
       </c>
       <c r="B194" t="n">
-        <v>105102</v>
+        <v>78455</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -22347,38 +22352,38 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>221725</v>
+        <v>353</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>723365</v>
+        <v>723669</v>
       </c>
       <c r="R194" t="n">
-        <v>7545207</v>
+        <v>7544113</v>
       </c>
       <c r="S194" t="n">
         <v>5</v>
@@ -22405,12 +22410,12 @@
       </c>
       <c r="Y194" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -22437,7 +22442,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>124355542</v>
+        <v>124355546</v>
       </c>
       <c r="B195" t="n">
         <v>105102</v>
@@ -22477,10 +22482,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>723159</v>
+        <v>723347</v>
       </c>
       <c r="R195" t="n">
-        <v>7544605</v>
+        <v>7544617</v>
       </c>
       <c r="S195" t="n">
         <v>5</v>
@@ -22539,10 +22544,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>124355609</v>
+        <v>124355668</v>
       </c>
       <c r="B196" t="n">
-        <v>98122</v>
+        <v>98101</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -22551,38 +22556,38 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>723343</v>
+        <v>723703</v>
       </c>
       <c r="R196" t="n">
-        <v>7544612</v>
+        <v>7544180</v>
       </c>
       <c r="S196" t="n">
         <v>5</v>
@@ -22609,12 +22614,12 @@
       </c>
       <c r="Y196" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -22641,7 +22646,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>124355546</v>
+        <v>124355530</v>
       </c>
       <c r="B197" t="n">
         <v>105102</v>
@@ -22681,10 +22686,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>723347</v>
+        <v>723178</v>
       </c>
       <c r="R197" t="n">
-        <v>7544617</v>
+        <v>7545219</v>
       </c>
       <c r="S197" t="n">
         <v>5</v>
@@ -22743,7 +22748,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>124355541</v>
+        <v>124355538</v>
       </c>
       <c r="B198" t="n">
         <v>105102</v>
@@ -22783,10 +22788,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>723087</v>
+        <v>722917</v>
       </c>
       <c r="R198" t="n">
-        <v>7544566</v>
+        <v>7544575</v>
       </c>
       <c r="S198" t="n">
         <v>5</v>
@@ -22845,7 +22850,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>124355515</v>
+        <v>124355543</v>
       </c>
       <c r="B199" t="n">
         <v>105102</v>
@@ -22881,14 +22886,14 @@
       <c r="I199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>723720</v>
+        <v>723227</v>
       </c>
       <c r="R199" t="n">
-        <v>7544240</v>
+        <v>7544640</v>
       </c>
       <c r="S199" t="n">
         <v>5</v>
@@ -22915,12 +22920,12 @@
       </c>
       <c r="Y199" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -22947,10 +22952,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>124355807</v>
+        <v>124355646</v>
       </c>
       <c r="B200" t="n">
-        <v>98000</v>
+        <v>79927</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -22963,34 +22968,34 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>219795</v>
+        <v>6464</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>723042</v>
+        <v>723617</v>
       </c>
       <c r="R200" t="n">
-        <v>7544553</v>
+        <v>7544144</v>
       </c>
       <c r="S200" t="n">
         <v>5</v>
@@ -23017,12 +23022,12 @@
       </c>
       <c r="Y200" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -23049,10 +23054,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>124355672</v>
+        <v>124355873</v>
       </c>
       <c r="B201" t="n">
-        <v>98101</v>
+        <v>79926</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -23061,38 +23066,38 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>723359</v>
+        <v>723684</v>
       </c>
       <c r="R201" t="n">
-        <v>7545207</v>
+        <v>7544232</v>
       </c>
       <c r="S201" t="n">
         <v>5</v>
@@ -23119,12 +23124,12 @@
       </c>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -23151,10 +23156,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>124355873</v>
+        <v>124355515</v>
       </c>
       <c r="B202" t="n">
-        <v>79926</v>
+        <v>105102</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -23167,21 +23172,21 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>6463</v>
+        <v>221725</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -23191,10 +23196,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>723684</v>
+        <v>723720</v>
       </c>
       <c r="R202" t="n">
-        <v>7544232</v>
+        <v>7544240</v>
       </c>
       <c r="S202" t="n">
         <v>5</v>
@@ -23253,10 +23258,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>124355540</v>
+        <v>124355905</v>
       </c>
       <c r="B203" t="n">
-        <v>105102</v>
+        <v>78194</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -23265,38 +23270,38 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>221725</v>
+        <v>6437</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>723038</v>
+        <v>723693</v>
       </c>
       <c r="R203" t="n">
-        <v>7544552</v>
+        <v>7544182</v>
       </c>
       <c r="S203" t="n">
         <v>5</v>
@@ -23323,12 +23328,12 @@
       </c>
       <c r="Y203" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -23355,10 +23360,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>124355668</v>
+        <v>124355807</v>
       </c>
       <c r="B204" t="n">
-        <v>98101</v>
+        <v>98000</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -23367,38 +23372,38 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>220787</v>
+        <v>219795</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>723703</v>
+        <v>723042</v>
       </c>
       <c r="R204" t="n">
-        <v>7544180</v>
+        <v>7544553</v>
       </c>
       <c r="S204" t="n">
         <v>5</v>
@@ -23425,12 +23430,12 @@
       </c>
       <c r="Y204" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -23457,10 +23462,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>124355877</v>
+        <v>124355513</v>
       </c>
       <c r="B205" t="n">
-        <v>74893</v>
+        <v>105102</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -23469,25 +23474,25 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>308</v>
+        <v>221725</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -23497,10 +23502,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>723696</v>
+        <v>723653</v>
       </c>
       <c r="R205" t="n">
-        <v>7544172</v>
+        <v>7544288</v>
       </c>
       <c r="S205" t="n">
         <v>5</v>
@@ -23559,10 +23564,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>124355598</v>
+        <v>124355632</v>
       </c>
       <c r="B206" t="n">
-        <v>79920</v>
+        <v>96985</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -23575,34 +23580,34 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>6462</v>
+        <v>221941</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>723350</v>
+        <v>723668</v>
       </c>
       <c r="R206" t="n">
-        <v>7544621</v>
+        <v>7544288</v>
       </c>
       <c r="S206" t="n">
         <v>5</v>
@@ -23629,12 +23634,12 @@
       </c>
       <c r="Y206" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -23661,10 +23666,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>124355611</v>
+        <v>124355598</v>
       </c>
       <c r="B207" t="n">
-        <v>57529</v>
+        <v>79920</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -23673,38 +23678,38 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>723694</v>
+        <v>723350</v>
       </c>
       <c r="R207" t="n">
-        <v>7544233</v>
+        <v>7544621</v>
       </c>
       <c r="S207" t="n">
         <v>5</v>
@@ -23731,17 +23736,12 @@
       </c>
       <c r="Y207" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
-        </is>
-      </c>
-      <c r="AC207" t="inlineStr">
-        <is>
-          <t>hackmärken</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -23768,10 +23768,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>124355552</v>
+        <v>124355826</v>
       </c>
       <c r="B208" t="n">
-        <v>105102</v>
+        <v>91030</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -23780,25 +23780,25 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>221725</v>
+        <v>5432</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
@@ -23808,10 +23808,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>723608</v>
+        <v>723345</v>
       </c>
       <c r="R208" t="n">
-        <v>7544580</v>
+        <v>7544616</v>
       </c>
       <c r="S208" t="n">
         <v>5</v>
@@ -23870,10 +23870,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>124355646</v>
+        <v>124355539</v>
       </c>
       <c r="B209" t="n">
-        <v>79927</v>
+        <v>105102</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -23886,34 +23886,34 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>6464</v>
+        <v>221725</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>723617</v>
+        <v>722977</v>
       </c>
       <c r="R209" t="n">
-        <v>7544144</v>
+        <v>7544571</v>
       </c>
       <c r="S209" t="n">
         <v>5</v>
@@ -23940,12 +23940,12 @@
       </c>
       <c r="Y209" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -23972,10 +23972,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>124355905</v>
+        <v>124355851</v>
       </c>
       <c r="B210" t="n">
-        <v>78194</v>
+        <v>97128</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -23984,25 +23984,25 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>6437</v>
+        <v>222741</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -24012,10 +24012,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>723693</v>
+        <v>723705</v>
       </c>
       <c r="R210" t="n">
-        <v>7544182</v>
+        <v>7544144</v>
       </c>
       <c r="S210" t="n">
         <v>5</v>
@@ -24074,10 +24074,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>124355870</v>
+        <v>124355877</v>
       </c>
       <c r="B211" t="n">
-        <v>78455</v>
+        <v>74893</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -24090,21 +24090,21 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>353</v>
+        <v>308</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -24114,10 +24114,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>723669</v>
+        <v>723696</v>
       </c>
       <c r="R211" t="n">
-        <v>7544113</v>
+        <v>7544172</v>
       </c>
       <c r="S211" t="n">
         <v>5</v>
@@ -24176,10 +24176,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>124355857</v>
+        <v>124355609</v>
       </c>
       <c r="B212" t="n">
-        <v>97128</v>
+        <v>98122</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -24192,21 +24192,21 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>222741</v>
+        <v>221952</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -24219,7 +24219,7 @@
         <v>723343</v>
       </c>
       <c r="R212" t="n">
-        <v>7544616</v>
+        <v>7544612</v>
       </c>
       <c r="S212" t="n">
         <v>5</v>
@@ -24278,7 +24278,7 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>124355856</v>
+        <v>124355857</v>
       </c>
       <c r="B213" t="n">
         <v>97128</v>
@@ -24318,10 +24318,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>723068</v>
+        <v>723343</v>
       </c>
       <c r="R213" t="n">
-        <v>7544568</v>
+        <v>7544616</v>
       </c>
       <c r="S213" t="n">
         <v>5</v>
@@ -24380,10 +24380,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>124355632</v>
+        <v>124355551</v>
       </c>
       <c r="B214" t="n">
-        <v>96985</v>
+        <v>105102</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -24396,34 +24396,34 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>221941</v>
+        <v>221725</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>723668</v>
+        <v>723547</v>
       </c>
       <c r="R214" t="n">
-        <v>7544288</v>
+        <v>7544600</v>
       </c>
       <c r="S214" t="n">
         <v>5</v>
@@ -24450,12 +24450,12 @@
       </c>
       <c r="Y214" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -24482,7 +24482,7 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>124355544</v>
+        <v>124355542</v>
       </c>
       <c r="B215" t="n">
         <v>105102</v>
@@ -24522,10 +24522,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>723301</v>
+        <v>723159</v>
       </c>
       <c r="R215" t="n">
-        <v>7544640</v>
+        <v>7544605</v>
       </c>
       <c r="S215" t="n">
         <v>5</v>
@@ -24584,10 +24584,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>124355851</v>
+        <v>124355552</v>
       </c>
       <c r="B216" t="n">
-        <v>97128</v>
+        <v>105102</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -24600,34 +24600,34 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>222741</v>
+        <v>221725</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
       <c r="P216" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>723705</v>
+        <v>723608</v>
       </c>
       <c r="R216" t="n">
-        <v>7544144</v>
+        <v>7544580</v>
       </c>
       <c r="S216" t="n">
         <v>5</v>
@@ -24654,12 +24654,12 @@
       </c>
       <c r="Y216" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -24686,10 +24686,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>124355539</v>
+        <v>124355570</v>
       </c>
       <c r="B217" t="n">
-        <v>105102</v>
+        <v>90977</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -24702,21 +24702,21 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>221725</v>
+        <v>5447</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -24726,10 +24726,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>722977</v>
+        <v>723343</v>
       </c>
       <c r="R217" t="n">
-        <v>7544571</v>
+        <v>7544616</v>
       </c>
       <c r="S217" t="n">
         <v>5</v>
@@ -24788,10 +24788,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>124355570</v>
+        <v>124355672</v>
       </c>
       <c r="B218" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -24800,25 +24800,25 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -24828,10 +24828,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>723343</v>
+        <v>723359</v>
       </c>
       <c r="R218" t="n">
-        <v>7544616</v>
+        <v>7545207</v>
       </c>
       <c r="S218" t="n">
         <v>5</v>
@@ -24890,10 +24890,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>124355592</v>
+        <v>124355540</v>
       </c>
       <c r="B219" t="n">
-        <v>79920</v>
+        <v>105102</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -24906,34 +24906,34 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>6462</v>
+        <v>221725</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>723699</v>
+        <v>723038</v>
       </c>
       <c r="R219" t="n">
-        <v>7544155</v>
+        <v>7544552</v>
       </c>
       <c r="S219" t="n">
         <v>5</v>
@@ -24960,12 +24960,12 @@
       </c>
       <c r="Y219" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD219" t="b">

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -20805,7 +20805,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>124355855</v>
+        <v>124355857</v>
       </c>
       <c r="B179" t="n">
         <v>97128</v>
@@ -20845,10 +20845,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>722944</v>
+        <v>723343</v>
       </c>
       <c r="R179" t="n">
-        <v>7544574</v>
+        <v>7544616</v>
       </c>
       <c r="S179" t="n">
         <v>5</v>
@@ -20907,10 +20907,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>124355856</v>
+        <v>124355541</v>
       </c>
       <c r="B180" t="n">
-        <v>97128</v>
+        <v>105102</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -20923,21 +20923,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>222741</v>
+        <v>221725</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -20947,10 +20947,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>723068</v>
+        <v>723087</v>
       </c>
       <c r="R180" t="n">
-        <v>7544568</v>
+        <v>7544566</v>
       </c>
       <c r="S180" t="n">
         <v>5</v>
@@ -21009,10 +21009,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>124355654</v>
+        <v>124355806</v>
       </c>
       <c r="B181" t="n">
-        <v>78151</v>
+        <v>98000</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -21021,38 +21021,38 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>498</v>
+        <v>219795</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>723693</v>
+        <v>722934</v>
       </c>
       <c r="R181" t="n">
-        <v>7544234</v>
+        <v>7544572</v>
       </c>
       <c r="S181" t="n">
         <v>5</v>
@@ -21079,12 +21079,12 @@
       </c>
       <c r="Y181" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -21111,10 +21111,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>124355592</v>
+        <v>124355542</v>
       </c>
       <c r="B182" t="n">
-        <v>79920</v>
+        <v>105102</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -21127,34 +21127,34 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6462</v>
+        <v>221725</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>723699</v>
+        <v>723159</v>
       </c>
       <c r="R182" t="n">
-        <v>7544155</v>
+        <v>7544605</v>
       </c>
       <c r="S182" t="n">
         <v>5</v>
@@ -21181,12 +21181,12 @@
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -21213,10 +21213,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>124355850</v>
+        <v>124355544</v>
       </c>
       <c r="B183" t="n">
-        <v>97128</v>
+        <v>105102</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -21229,34 +21229,34 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>222741</v>
+        <v>221725</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>723616</v>
+        <v>723301</v>
       </c>
       <c r="R183" t="n">
-        <v>7544154</v>
+        <v>7544640</v>
       </c>
       <c r="S183" t="n">
         <v>5</v>
@@ -21283,12 +21283,12 @@
       </c>
       <c r="Y183" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -21315,10 +21315,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>124355611</v>
+        <v>124355515</v>
       </c>
       <c r="B184" t="n">
-        <v>57529</v>
+        <v>105102</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -21327,25 +21327,25 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>100049</v>
+        <v>221725</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -21355,10 +21355,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>723694</v>
+        <v>723720</v>
       </c>
       <c r="R184" t="n">
-        <v>7544233</v>
+        <v>7544240</v>
       </c>
       <c r="S184" t="n">
         <v>5</v>
@@ -21391,11 +21391,6 @@
       <c r="AA184" t="inlineStr">
         <is>
           <t>2024-08-09</t>
-        </is>
-      </c>
-      <c r="AC184" t="inlineStr">
-        <is>
-          <t>hackmärken</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -21422,10 +21417,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>124355666</v>
+        <v>124355870</v>
       </c>
       <c r="B185" t="n">
-        <v>98101</v>
+        <v>78455</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -21434,25 +21429,25 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -21462,10 +21457,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>723699</v>
+        <v>723669</v>
       </c>
       <c r="R185" t="n">
-        <v>7544235</v>
+        <v>7544113</v>
       </c>
       <c r="S185" t="n">
         <v>5</v>
@@ -21524,10 +21519,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>124355516</v>
+        <v>124355598</v>
       </c>
       <c r="B186" t="n">
-        <v>105102</v>
+        <v>79920</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -21540,34 +21535,34 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>221725</v>
+        <v>6462</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>723694</v>
+        <v>723350</v>
       </c>
       <c r="R186" t="n">
-        <v>7544160</v>
+        <v>7544621</v>
       </c>
       <c r="S186" t="n">
         <v>5</v>
@@ -21594,12 +21589,12 @@
       </c>
       <c r="Y186" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -21626,10 +21621,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>124355806</v>
+        <v>124355856</v>
       </c>
       <c r="B187" t="n">
-        <v>98000</v>
+        <v>97128</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -21642,21 +21637,21 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>219795</v>
+        <v>222741</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -21666,10 +21661,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>722934</v>
+        <v>723068</v>
       </c>
       <c r="R187" t="n">
-        <v>7544572</v>
+        <v>7544568</v>
       </c>
       <c r="S187" t="n">
         <v>5</v>
@@ -21728,7 +21723,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>124355529</v>
+        <v>124355546</v>
       </c>
       <c r="B188" t="n">
         <v>105102</v>
@@ -21768,10 +21763,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>723365</v>
+        <v>723347</v>
       </c>
       <c r="R188" t="n">
-        <v>7545207</v>
+        <v>7544617</v>
       </c>
       <c r="S188" t="n">
         <v>5</v>
@@ -21830,10 +21825,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>124355667</v>
+        <v>124355807</v>
       </c>
       <c r="B189" t="n">
-        <v>98101</v>
+        <v>98000</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -21842,38 +21837,38 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>220787</v>
+        <v>219795</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>723695</v>
+        <v>723042</v>
       </c>
       <c r="R189" t="n">
-        <v>7544233</v>
+        <v>7544553</v>
       </c>
       <c r="S189" t="n">
         <v>5</v>
@@ -21900,12 +21895,12 @@
       </c>
       <c r="Y189" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -21932,10 +21927,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>124355548</v>
+        <v>124355905</v>
       </c>
       <c r="B190" t="n">
-        <v>105102</v>
+        <v>78194</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -21944,38 +21939,38 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>221725</v>
+        <v>6437</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>723515</v>
+        <v>723693</v>
       </c>
       <c r="R190" t="n">
-        <v>7544632</v>
+        <v>7544182</v>
       </c>
       <c r="S190" t="n">
         <v>5</v>
@@ -22002,12 +21997,12 @@
       </c>
       <c r="Y190" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -22034,10 +22029,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>124355541</v>
+        <v>124355873</v>
       </c>
       <c r="B191" t="n">
-        <v>105102</v>
+        <v>79926</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -22050,34 +22045,34 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>221725</v>
+        <v>6463</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>723087</v>
+        <v>723684</v>
       </c>
       <c r="R191" t="n">
-        <v>7544566</v>
+        <v>7544232</v>
       </c>
       <c r="S191" t="n">
         <v>5</v>
@@ -22104,12 +22099,12 @@
       </c>
       <c r="Y191" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -22136,7 +22131,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>124355544</v>
+        <v>124355539</v>
       </c>
       <c r="B192" t="n">
         <v>105102</v>
@@ -22176,10 +22171,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>723301</v>
+        <v>722977</v>
       </c>
       <c r="R192" t="n">
-        <v>7544640</v>
+        <v>7544571</v>
       </c>
       <c r="S192" t="n">
         <v>5</v>
@@ -22238,10 +22233,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>124355802</v>
+        <v>124355877</v>
       </c>
       <c r="B193" t="n">
-        <v>98000</v>
+        <v>74893</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -22250,25 +22245,25 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>219795</v>
+        <v>308</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -22278,10 +22273,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>723703</v>
+        <v>723696</v>
       </c>
       <c r="R193" t="n">
-        <v>7544232</v>
+        <v>7544172</v>
       </c>
       <c r="S193" t="n">
         <v>5</v>
@@ -22340,10 +22335,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>124355870</v>
+        <v>124355850</v>
       </c>
       <c r="B194" t="n">
-        <v>78455</v>
+        <v>97128</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -22352,25 +22347,25 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>353</v>
+        <v>222741</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -22380,10 +22375,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>723669</v>
+        <v>723616</v>
       </c>
       <c r="R194" t="n">
-        <v>7544113</v>
+        <v>7544154</v>
       </c>
       <c r="S194" t="n">
         <v>5</v>
@@ -22442,10 +22437,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>124355546</v>
+        <v>124355570</v>
       </c>
       <c r="B195" t="n">
-        <v>105102</v>
+        <v>90977</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -22458,21 +22453,21 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>221725</v>
+        <v>5447</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -22482,10 +22477,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>723347</v>
+        <v>723343</v>
       </c>
       <c r="R195" t="n">
-        <v>7544617</v>
+        <v>7544616</v>
       </c>
       <c r="S195" t="n">
         <v>5</v>
@@ -22544,10 +22539,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>124355668</v>
+        <v>124355632</v>
       </c>
       <c r="B196" t="n">
-        <v>98101</v>
+        <v>96985</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -22556,25 +22551,25 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -22584,10 +22579,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>723703</v>
+        <v>723668</v>
       </c>
       <c r="R196" t="n">
-        <v>7544180</v>
+        <v>7544288</v>
       </c>
       <c r="S196" t="n">
         <v>5</v>
@@ -22646,7 +22641,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>124355530</v>
+        <v>124355529</v>
       </c>
       <c r="B197" t="n">
         <v>105102</v>
@@ -22686,10 +22681,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>723178</v>
+        <v>723365</v>
       </c>
       <c r="R197" t="n">
-        <v>7545219</v>
+        <v>7545207</v>
       </c>
       <c r="S197" t="n">
         <v>5</v>
@@ -22748,7 +22743,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>124355538</v>
+        <v>124355540</v>
       </c>
       <c r="B198" t="n">
         <v>105102</v>
@@ -22788,10 +22783,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>722917</v>
+        <v>723038</v>
       </c>
       <c r="R198" t="n">
-        <v>7544575</v>
+        <v>7544552</v>
       </c>
       <c r="S198" t="n">
         <v>5</v>
@@ -22850,10 +22845,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>124355543</v>
+        <v>124355666</v>
       </c>
       <c r="B199" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -22862,38 +22857,38 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>723227</v>
+        <v>723699</v>
       </c>
       <c r="R199" t="n">
-        <v>7544640</v>
+        <v>7544235</v>
       </c>
       <c r="S199" t="n">
         <v>5</v>
@@ -22920,12 +22915,12 @@
       </c>
       <c r="Y199" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -22952,10 +22947,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>124355646</v>
+        <v>124355609</v>
       </c>
       <c r="B200" t="n">
-        <v>79927</v>
+        <v>98122</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -22968,34 +22963,34 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>6464</v>
+        <v>221952</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>723617</v>
+        <v>723343</v>
       </c>
       <c r="R200" t="n">
-        <v>7544144</v>
+        <v>7544612</v>
       </c>
       <c r="S200" t="n">
         <v>5</v>
@@ -23022,12 +23017,12 @@
       </c>
       <c r="Y200" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -23054,10 +23049,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>124355873</v>
+        <v>124355551</v>
       </c>
       <c r="B201" t="n">
-        <v>79926</v>
+        <v>105102</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -23070,34 +23065,34 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>6463</v>
+        <v>221725</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>723684</v>
+        <v>723547</v>
       </c>
       <c r="R201" t="n">
-        <v>7544232</v>
+        <v>7544600</v>
       </c>
       <c r="S201" t="n">
         <v>5</v>
@@ -23124,12 +23119,12 @@
       </c>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -23156,10 +23151,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>124355515</v>
+        <v>124355668</v>
       </c>
       <c r="B202" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -23168,25 +23163,25 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -23196,10 +23191,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>723720</v>
+        <v>723703</v>
       </c>
       <c r="R202" t="n">
-        <v>7544240</v>
+        <v>7544180</v>
       </c>
       <c r="S202" t="n">
         <v>5</v>
@@ -23258,10 +23253,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>124355905</v>
+        <v>124355513</v>
       </c>
       <c r="B203" t="n">
-        <v>78194</v>
+        <v>105102</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -23270,25 +23265,25 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>6437</v>
+        <v>221725</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -23298,10 +23293,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>723693</v>
+        <v>723653</v>
       </c>
       <c r="R203" t="n">
-        <v>7544182</v>
+        <v>7544288</v>
       </c>
       <c r="S203" t="n">
         <v>5</v>
@@ -23360,10 +23355,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>124355807</v>
+        <v>124355611</v>
       </c>
       <c r="B204" t="n">
-        <v>98000</v>
+        <v>57529</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -23372,38 +23367,38 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>219795</v>
+        <v>100049</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>723042</v>
+        <v>723694</v>
       </c>
       <c r="R204" t="n">
-        <v>7544553</v>
+        <v>7544233</v>
       </c>
       <c r="S204" t="n">
         <v>5</v>
@@ -23430,12 +23425,17 @@
       </c>
       <c r="Y204" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="AC204" t="inlineStr">
+        <is>
+          <t>hackmärken</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -23462,7 +23462,7 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>124355513</v>
+        <v>124355543</v>
       </c>
       <c r="B205" t="n">
         <v>105102</v>
@@ -23498,14 +23498,14 @@
       <c r="I205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>723653</v>
+        <v>723227</v>
       </c>
       <c r="R205" t="n">
-        <v>7544288</v>
+        <v>7544640</v>
       </c>
       <c r="S205" t="n">
         <v>5</v>
@@ -23532,12 +23532,12 @@
       </c>
       <c r="Y205" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -23564,10 +23564,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>124355632</v>
+        <v>124355654</v>
       </c>
       <c r="B206" t="n">
-        <v>96985</v>
+        <v>78151</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -23576,25 +23576,25 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>221941</v>
+        <v>498</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -23604,10 +23604,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>723668</v>
+        <v>723693</v>
       </c>
       <c r="R206" t="n">
-        <v>7544288</v>
+        <v>7544234</v>
       </c>
       <c r="S206" t="n">
         <v>5</v>
@@ -23666,10 +23666,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>124355598</v>
+        <v>124355530</v>
       </c>
       <c r="B207" t="n">
-        <v>79920</v>
+        <v>105102</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -23682,21 +23682,21 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>6462</v>
+        <v>221725</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
@@ -23706,10 +23706,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>723350</v>
+        <v>723178</v>
       </c>
       <c r="R207" t="n">
-        <v>7544621</v>
+        <v>7545219</v>
       </c>
       <c r="S207" t="n">
         <v>5</v>
@@ -23768,10 +23768,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>124355826</v>
+        <v>124355667</v>
       </c>
       <c r="B208" t="n">
-        <v>91030</v>
+        <v>98101</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -23780,38 +23780,38 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>723345</v>
+        <v>723695</v>
       </c>
       <c r="R208" t="n">
-        <v>7544616</v>
+        <v>7544233</v>
       </c>
       <c r="S208" t="n">
         <v>5</v>
@@ -23838,12 +23838,12 @@
       </c>
       <c r="Y208" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -23870,10 +23870,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>124355539</v>
+        <v>124355802</v>
       </c>
       <c r="B209" t="n">
-        <v>105102</v>
+        <v>98000</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -23886,34 +23886,34 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>221725</v>
+        <v>219795</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>722977</v>
+        <v>723703</v>
       </c>
       <c r="R209" t="n">
-        <v>7544571</v>
+        <v>7544232</v>
       </c>
       <c r="S209" t="n">
         <v>5</v>
@@ -23940,12 +23940,12 @@
       </c>
       <c r="Y209" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -23972,10 +23972,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>124355851</v>
+        <v>124355826</v>
       </c>
       <c r="B210" t="n">
-        <v>97128</v>
+        <v>91030</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -23984,38 +23984,38 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>222741</v>
+        <v>5432</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>723705</v>
+        <v>723345</v>
       </c>
       <c r="R210" t="n">
-        <v>7544144</v>
+        <v>7544616</v>
       </c>
       <c r="S210" t="n">
         <v>5</v>
@@ -24042,12 +24042,12 @@
       </c>
       <c r="Y210" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -24074,10 +24074,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>124355877</v>
+        <v>124355851</v>
       </c>
       <c r="B211" t="n">
-        <v>74893</v>
+        <v>97128</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -24086,25 +24086,25 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>308</v>
+        <v>222741</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -24114,10 +24114,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>723696</v>
+        <v>723705</v>
       </c>
       <c r="R211" t="n">
-        <v>7544172</v>
+        <v>7544144</v>
       </c>
       <c r="S211" t="n">
         <v>5</v>
@@ -24176,10 +24176,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>124355609</v>
+        <v>124355592</v>
       </c>
       <c r="B212" t="n">
-        <v>98122</v>
+        <v>79920</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -24192,34 +24192,34 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>723343</v>
+        <v>723699</v>
       </c>
       <c r="R212" t="n">
-        <v>7544612</v>
+        <v>7544155</v>
       </c>
       <c r="S212" t="n">
         <v>5</v>
@@ -24246,12 +24246,12 @@
       </c>
       <c r="Y212" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -24278,10 +24278,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>124355857</v>
+        <v>124355538</v>
       </c>
       <c r="B213" t="n">
-        <v>97128</v>
+        <v>105102</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -24294,21 +24294,21 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>222741</v>
+        <v>221725</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -24318,10 +24318,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>723343</v>
+        <v>722917</v>
       </c>
       <c r="R213" t="n">
-        <v>7544616</v>
+        <v>7544575</v>
       </c>
       <c r="S213" t="n">
         <v>5</v>
@@ -24380,7 +24380,7 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>124355551</v>
+        <v>124355548</v>
       </c>
       <c r="B214" t="n">
         <v>105102</v>
@@ -24420,10 +24420,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>723547</v>
+        <v>723515</v>
       </c>
       <c r="R214" t="n">
-        <v>7544600</v>
+        <v>7544632</v>
       </c>
       <c r="S214" t="n">
         <v>5</v>
@@ -24482,7 +24482,7 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>124355542</v>
+        <v>124355516</v>
       </c>
       <c r="B215" t="n">
         <v>105102</v>
@@ -24518,14 +24518,14 @@
       <c r="I215" t="inlineStr"/>
       <c r="P215" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>723159</v>
+        <v>723694</v>
       </c>
       <c r="R215" t="n">
-        <v>7544605</v>
+        <v>7544160</v>
       </c>
       <c r="S215" t="n">
         <v>5</v>
@@ -24552,12 +24552,12 @@
       </c>
       <c r="Y215" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -24584,10 +24584,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>124355552</v>
+        <v>124355672</v>
       </c>
       <c r="B216" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -24596,25 +24596,25 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
@@ -24624,10 +24624,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>723608</v>
+        <v>723359</v>
       </c>
       <c r="R216" t="n">
-        <v>7544580</v>
+        <v>7545207</v>
       </c>
       <c r="S216" t="n">
         <v>5</v>
@@ -24686,10 +24686,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>124355570</v>
+        <v>124355646</v>
       </c>
       <c r="B217" t="n">
-        <v>90977</v>
+        <v>79927</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -24702,34 +24702,34 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>5447</v>
+        <v>6464</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
       <c r="P217" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>723343</v>
+        <v>723617</v>
       </c>
       <c r="R217" t="n">
-        <v>7544616</v>
+        <v>7544144</v>
       </c>
       <c r="S217" t="n">
         <v>5</v>
@@ -24756,12 +24756,12 @@
       </c>
       <c r="Y217" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -24788,10 +24788,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>124355672</v>
+        <v>124355855</v>
       </c>
       <c r="B218" t="n">
-        <v>98101</v>
+        <v>97128</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -24800,25 +24800,25 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>220787</v>
+        <v>222741</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -24828,10 +24828,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>723359</v>
+        <v>722944</v>
       </c>
       <c r="R218" t="n">
-        <v>7545207</v>
+        <v>7544574</v>
       </c>
       <c r="S218" t="n">
         <v>5</v>
@@ -24890,7 +24890,7 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>124355540</v>
+        <v>124355552</v>
       </c>
       <c r="B219" t="n">
         <v>105102</v>
@@ -24930,10 +24930,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>723038</v>
+        <v>723608</v>
       </c>
       <c r="R219" t="n">
-        <v>7544552</v>
+        <v>7544580</v>
       </c>
       <c r="S219" t="n">
         <v>5</v>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY219"/>
+  <dimension ref="A1:AY222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24990,6 +24990,297 @@
       </c>
       <c r="AY219" t="inlineStr"/>
     </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>128391652</v>
+      </c>
+      <c r="B220" t="n">
+        <v>92642</v>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E220" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr"/>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>Gruvberget, Gruvberget, T lm</t>
+        </is>
+      </c>
+      <c r="Q220" t="n">
+        <v>723366</v>
+      </c>
+      <c r="R220" t="n">
+        <v>7544960</v>
+      </c>
+      <c r="S220" t="n">
+        <v>10</v>
+      </c>
+      <c r="T220" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V220" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W220" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y220" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD220" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE220" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG220" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT220" t="inlineStr"/>
+      <c r="AW220" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX220" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>128391313</v>
+      </c>
+      <c r="B221" t="n">
+        <v>91354</v>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E221" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr"/>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>Gruvberget, Gruvberget, T lm</t>
+        </is>
+      </c>
+      <c r="Q221" t="n">
+        <v>723317</v>
+      </c>
+      <c r="R221" t="n">
+        <v>7544967</v>
+      </c>
+      <c r="S221" t="n">
+        <v>10</v>
+      </c>
+      <c r="T221" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V221" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W221" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y221" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD221" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE221" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG221" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT221" t="inlineStr"/>
+      <c r="AW221" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX221" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY221" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>128391239</v>
+      </c>
+      <c r="B222" t="n">
+        <v>91812</v>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E222" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr"/>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>Gruvberget, Gruvberget, T lm</t>
+        </is>
+      </c>
+      <c r="Q222" t="n">
+        <v>723330</v>
+      </c>
+      <c r="R222" t="n">
+        <v>7544944</v>
+      </c>
+      <c r="S222" t="n">
+        <v>10</v>
+      </c>
+      <c r="T222" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U222" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V222" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W222" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y222" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD222" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE222" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG222" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT222" t="inlineStr"/>
+      <c r="AW222" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX222" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY222" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -24995,7 +24995,7 @@
         <v>128391652</v>
       </c>
       <c r="B220" t="n">
-        <v>92642</v>
+        <v>92644</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -25092,7 +25092,7 @@
         <v>128391313</v>
       </c>
       <c r="B221" t="n">
-        <v>91354</v>
+        <v>91356</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -25189,7 +25189,7 @@
         <v>128391239</v>
       </c>
       <c r="B222" t="n">
-        <v>91812</v>
+        <v>91814</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -24995,7 +24995,7 @@
         <v>128391652</v>
       </c>
       <c r="B220" t="n">
-        <v>92644</v>
+        <v>92736</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -25092,7 +25092,7 @@
         <v>128391313</v>
       </c>
       <c r="B221" t="n">
-        <v>91356</v>
+        <v>91448</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -25189,7 +25189,7 @@
         <v>128391239</v>
       </c>
       <c r="B222" t="n">
-        <v>91814</v>
+        <v>91906</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -24995,7 +24995,7 @@
         <v>128391652</v>
       </c>
       <c r="B220" t="n">
-        <v>92736</v>
+        <v>92748</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -25092,7 +25092,7 @@
         <v>128391313</v>
       </c>
       <c r="B221" t="n">
-        <v>91448</v>
+        <v>91460</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -25189,7 +25189,7 @@
         <v>128391239</v>
       </c>
       <c r="B222" t="n">
-        <v>91906</v>
+        <v>91918</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -24995,7 +24995,7 @@
         <v>128391652</v>
       </c>
       <c r="B220" t="n">
-        <v>92748</v>
+        <v>92750</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -25092,7 +25092,7 @@
         <v>128391313</v>
       </c>
       <c r="B221" t="n">
-        <v>91460</v>
+        <v>91462</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -25189,7 +25189,7 @@
         <v>128391239</v>
       </c>
       <c r="B222" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -24995,7 +24995,7 @@
         <v>128391652</v>
       </c>
       <c r="B220" t="n">
-        <v>92750</v>
+        <v>92751</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -25092,7 +25092,7 @@
         <v>128391313</v>
       </c>
       <c r="B221" t="n">
-        <v>91462</v>
+        <v>91463</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -25189,7 +25189,7 @@
         <v>128391239</v>
       </c>
       <c r="B222" t="n">
-        <v>91920</v>
+        <v>91921</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -24995,7 +24995,7 @@
         <v>128391652</v>
       </c>
       <c r="B220" t="n">
-        <v>92751</v>
+        <v>92778</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -25092,7 +25092,7 @@
         <v>128391313</v>
       </c>
       <c r="B221" t="n">
-        <v>91463</v>
+        <v>91490</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -25189,7 +25189,7 @@
         <v>128391239</v>
       </c>
       <c r="B222" t="n">
-        <v>91921</v>
+        <v>91948</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY222"/>
+  <dimension ref="A1:AY230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25281,6 +25281,807 @@
       </c>
       <c r="AY222" t="inlineStr"/>
     </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>128880600</v>
+      </c>
+      <c r="B223" t="n">
+        <v>92141</v>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E223" t="n">
+        <v>106596</v>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>Nordlig parasitporing</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>Antrodiella pallasii</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>Renvall &amp; al.</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr"/>
+      <c r="J223" t="inlineStr"/>
+      <c r="K223" t="inlineStr"/>
+      <c r="N223" t="inlineStr"/>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>Kurravaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q223" t="n">
+        <v>723104</v>
+      </c>
+      <c r="R223" t="n">
+        <v>7544625</v>
+      </c>
+      <c r="S223" t="n">
+        <v>10</v>
+      </c>
+      <c r="T223" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U223" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V223" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W223" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y223" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD223" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE223" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF223" t="inlineStr"/>
+      <c r="AG223" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT223" t="inlineStr"/>
+      <c r="AW223" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX223" t="inlineStr">
+        <is>
+          <t>per-erik mukka, Anna Öhlund</t>
+        </is>
+      </c>
+      <c r="AY223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>128880607</v>
+      </c>
+      <c r="B224" t="n">
+        <v>91495</v>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E224" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr"/>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>Kurravaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q224" t="n">
+        <v>723171</v>
+      </c>
+      <c r="R224" t="n">
+        <v>7544634</v>
+      </c>
+      <c r="S224" t="n">
+        <v>10</v>
+      </c>
+      <c r="T224" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U224" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V224" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W224" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y224" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA224" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD224" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE224" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG224" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT224" t="inlineStr"/>
+      <c r="AW224" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX224" t="inlineStr">
+        <is>
+          <t>per-erik mukka, Anna Öhlund</t>
+        </is>
+      </c>
+      <c r="AY224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>128880616</v>
+      </c>
+      <c r="B225" t="n">
+        <v>91760</v>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E225" t="n">
+        <v>65</v>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Fläckporing</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>Anthoporia albobrunnea</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr"/>
+      <c r="J225" t="inlineStr"/>
+      <c r="K225" t="inlineStr"/>
+      <c r="N225" t="inlineStr"/>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>Kurravaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q225" t="n">
+        <v>723036</v>
+      </c>
+      <c r="R225" t="n">
+        <v>7544611</v>
+      </c>
+      <c r="S225" t="n">
+        <v>10</v>
+      </c>
+      <c r="T225" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V225" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W225" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y225" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD225" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE225" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF225" t="inlineStr"/>
+      <c r="AG225" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT225" t="inlineStr"/>
+      <c r="AW225" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX225" t="inlineStr">
+        <is>
+          <t>per-erik mukka, Anna Öhlund</t>
+        </is>
+      </c>
+      <c r="AY225" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>128880594</v>
+      </c>
+      <c r="B226" t="n">
+        <v>91953</v>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E226" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr"/>
+      <c r="J226" t="inlineStr"/>
+      <c r="K226" t="inlineStr"/>
+      <c r="N226" t="inlineStr"/>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>Kurravaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q226" t="n">
+        <v>723169</v>
+      </c>
+      <c r="R226" t="n">
+        <v>7544641</v>
+      </c>
+      <c r="S226" t="n">
+        <v>10</v>
+      </c>
+      <c r="T226" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V226" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W226" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y226" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD226" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE226" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF226" t="inlineStr"/>
+      <c r="AG226" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT226" t="inlineStr"/>
+      <c r="AW226" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX226" t="inlineStr">
+        <is>
+          <t>per-erik mukka, Anna Öhlund</t>
+        </is>
+      </c>
+      <c r="AY226" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>128880583</v>
+      </c>
+      <c r="B227" t="n">
+        <v>92196</v>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E227" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr"/>
+      <c r="J227" t="inlineStr"/>
+      <c r="K227" t="inlineStr"/>
+      <c r="N227" t="inlineStr"/>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>Kurravaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q227" t="n">
+        <v>722997</v>
+      </c>
+      <c r="R227" t="n">
+        <v>7544482</v>
+      </c>
+      <c r="S227" t="n">
+        <v>10</v>
+      </c>
+      <c r="T227" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U227" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V227" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W227" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y227" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA227" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD227" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE227" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF227" t="inlineStr"/>
+      <c r="AG227" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT227" t="inlineStr"/>
+      <c r="AW227" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX227" t="inlineStr">
+        <is>
+          <t>per-erik mukka, Anna Öhlund</t>
+        </is>
+      </c>
+      <c r="AY227" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>128880613</v>
+      </c>
+      <c r="B228" t="n">
+        <v>91517</v>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E228" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr"/>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>Kurravaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q228" t="n">
+        <v>722995</v>
+      </c>
+      <c r="R228" t="n">
+        <v>7544630</v>
+      </c>
+      <c r="S228" t="n">
+        <v>10</v>
+      </c>
+      <c r="T228" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V228" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W228" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y228" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD228" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE228" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG228" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT228" t="inlineStr"/>
+      <c r="AW228" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX228" t="inlineStr">
+        <is>
+          <t>per-erik mukka, Anna Öhlund</t>
+        </is>
+      </c>
+      <c r="AY228" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>128880596</v>
+      </c>
+      <c r="B229" t="n">
+        <v>91795</v>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E229" t="n">
+        <v>658</v>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr"/>
+      <c r="J229" t="inlineStr"/>
+      <c r="K229" t="inlineStr"/>
+      <c r="N229" t="inlineStr"/>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>Kurravaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q229" t="n">
+        <v>723169</v>
+      </c>
+      <c r="R229" t="n">
+        <v>7544641</v>
+      </c>
+      <c r="S229" t="n">
+        <v>10</v>
+      </c>
+      <c r="T229" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U229" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V229" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W229" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y229" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA229" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD229" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE229" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF229" t="inlineStr"/>
+      <c r="AG229" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT229" t="inlineStr"/>
+      <c r="AW229" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX229" t="inlineStr">
+        <is>
+          <t>per-erik mukka, Anna Öhlund</t>
+        </is>
+      </c>
+      <c r="AY229" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>128880601</v>
+      </c>
+      <c r="B230" t="n">
+        <v>80225</v>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E230" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr"/>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>Kurravaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q230" t="n">
+        <v>722951</v>
+      </c>
+      <c r="R230" t="n">
+        <v>7544425</v>
+      </c>
+      <c r="S230" t="n">
+        <v>10</v>
+      </c>
+      <c r="T230" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U230" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V230" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W230" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y230" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AC230" t="inlineStr">
+        <is>
+          <t>på klippa</t>
+        </is>
+      </c>
+      <c r="AD230" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE230" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG230" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT230" t="inlineStr"/>
+      <c r="AW230" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX230" t="inlineStr">
+        <is>
+          <t>per-erik mukka, Anna Öhlund</t>
+        </is>
+      </c>
+      <c r="AY230" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -24995,7 +24995,7 @@
         <v>128391652</v>
       </c>
       <c r="B220" t="n">
-        <v>92778</v>
+        <v>92788</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -25092,7 +25092,7 @@
         <v>128391313</v>
       </c>
       <c r="B221" t="n">
-        <v>91490</v>
+        <v>91500</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -25189,7 +25189,7 @@
         <v>128391239</v>
       </c>
       <c r="B222" t="n">
-        <v>91948</v>
+        <v>91958</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -25286,7 +25286,7 @@
         <v>128880600</v>
       </c>
       <c r="B223" t="n">
-        <v>92141</v>
+        <v>92146</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -25387,7 +25387,7 @@
         <v>128880607</v>
       </c>
       <c r="B224" t="n">
-        <v>91495</v>
+        <v>91500</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -25484,7 +25484,7 @@
         <v>128880616</v>
       </c>
       <c r="B225" t="n">
-        <v>91760</v>
+        <v>91765</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -25585,7 +25585,7 @@
         <v>128880594</v>
       </c>
       <c r="B226" t="n">
-        <v>91953</v>
+        <v>91958</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -25683,48 +25683,45 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>128880583</v>
+        <v>128880613</v>
       </c>
       <c r="B227" t="n">
-        <v>92196</v>
+        <v>91522</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
-      <c r="J227" t="inlineStr"/>
-      <c r="K227" t="inlineStr"/>
-      <c r="N227" t="inlineStr"/>
       <c r="P227" t="inlineStr">
         <is>
           <t>Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>722997</v>
+        <v>722995</v>
       </c>
       <c r="R227" t="n">
-        <v>7544482</v>
+        <v>7544630</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25765,7 +25762,6 @@
       <c r="AE227" t="b">
         <v>0</v>
       </c>
-      <c r="AF227" t="inlineStr"/>
       <c r="AG227" t="b">
         <v>0</v>
       </c>
@@ -25784,45 +25780,48 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>128880613</v>
+        <v>128880583</v>
       </c>
       <c r="B228" t="n">
-        <v>91517</v>
+        <v>92201</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
+      <c r="J228" t="inlineStr"/>
+      <c r="K228" t="inlineStr"/>
+      <c r="N228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
           <t>Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>722995</v>
+        <v>722997</v>
       </c>
       <c r="R228" t="n">
-        <v>7544630</v>
+        <v>7544482</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25863,6 +25862,7 @@
       <c r="AE228" t="b">
         <v>0</v>
       </c>
+      <c r="AF228" t="inlineStr"/>
       <c r="AG228" t="b">
         <v>0</v>
       </c>
@@ -25884,7 +25884,7 @@
         <v>128880596</v>
       </c>
       <c r="B229" t="n">
-        <v>91795</v>
+        <v>91800</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -25683,45 +25683,48 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>128880613</v>
+        <v>128880583</v>
       </c>
       <c r="B227" t="n">
-        <v>91522</v>
+        <v>92201</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
+      <c r="J227" t="inlineStr"/>
+      <c r="K227" t="inlineStr"/>
+      <c r="N227" t="inlineStr"/>
       <c r="P227" t="inlineStr">
         <is>
           <t>Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>722995</v>
+        <v>722997</v>
       </c>
       <c r="R227" t="n">
-        <v>7544630</v>
+        <v>7544482</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25762,6 +25765,7 @@
       <c r="AE227" t="b">
         <v>0</v>
       </c>
+      <c r="AF227" t="inlineStr"/>
       <c r="AG227" t="b">
         <v>0</v>
       </c>
@@ -25780,48 +25784,45 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>128880583</v>
+        <v>128880613</v>
       </c>
       <c r="B228" t="n">
-        <v>92201</v>
+        <v>91522</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
-      <c r="J228" t="inlineStr"/>
-      <c r="K228" t="inlineStr"/>
-      <c r="N228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
           <t>Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>722997</v>
+        <v>722995</v>
       </c>
       <c r="R228" t="n">
-        <v>7544482</v>
+        <v>7544630</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25862,7 +25863,6 @@
       <c r="AE228" t="b">
         <v>0</v>
       </c>
-      <c r="AF228" t="inlineStr"/>
       <c r="AG228" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -25683,48 +25683,45 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>128880583</v>
+        <v>128880613</v>
       </c>
       <c r="B227" t="n">
-        <v>92201</v>
+        <v>91522</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
-      <c r="J227" t="inlineStr"/>
-      <c r="K227" t="inlineStr"/>
-      <c r="N227" t="inlineStr"/>
       <c r="P227" t="inlineStr">
         <is>
           <t>Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>722997</v>
+        <v>722995</v>
       </c>
       <c r="R227" t="n">
-        <v>7544482</v>
+        <v>7544630</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25765,7 +25762,6 @@
       <c r="AE227" t="b">
         <v>0</v>
       </c>
-      <c r="AF227" t="inlineStr"/>
       <c r="AG227" t="b">
         <v>0</v>
       </c>
@@ -25784,45 +25780,48 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>128880613</v>
+        <v>128880583</v>
       </c>
       <c r="B228" t="n">
-        <v>91522</v>
+        <v>92201</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
+      <c r="J228" t="inlineStr"/>
+      <c r="K228" t="inlineStr"/>
+      <c r="N228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
           <t>Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>722995</v>
+        <v>722997</v>
       </c>
       <c r="R228" t="n">
-        <v>7544630</v>
+        <v>7544482</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25863,6 +25862,7 @@
       <c r="AE228" t="b">
         <v>0</v>
       </c>
+      <c r="AF228" t="inlineStr"/>
       <c r="AG228" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -25286,7 +25286,7 @@
         <v>128880600</v>
       </c>
       <c r="B223" t="n">
-        <v>92146</v>
+        <v>92150</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -25387,7 +25387,7 @@
         <v>128880607</v>
       </c>
       <c r="B224" t="n">
-        <v>91500</v>
+        <v>91504</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -25484,7 +25484,7 @@
         <v>128880616</v>
       </c>
       <c r="B225" t="n">
-        <v>91765</v>
+        <v>91769</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -25585,7 +25585,7 @@
         <v>128880594</v>
       </c>
       <c r="B226" t="n">
-        <v>91958</v>
+        <v>91962</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -25683,45 +25683,48 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>128880613</v>
+        <v>128880583</v>
       </c>
       <c r="B227" t="n">
-        <v>91522</v>
+        <v>92205</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
+      <c r="J227" t="inlineStr"/>
+      <c r="K227" t="inlineStr"/>
+      <c r="N227" t="inlineStr"/>
       <c r="P227" t="inlineStr">
         <is>
           <t>Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>722995</v>
+        <v>722997</v>
       </c>
       <c r="R227" t="n">
-        <v>7544630</v>
+        <v>7544482</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25762,6 +25765,7 @@
       <c r="AE227" t="b">
         <v>0</v>
       </c>
+      <c r="AF227" t="inlineStr"/>
       <c r="AG227" t="b">
         <v>0</v>
       </c>
@@ -25780,48 +25784,45 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>128880583</v>
+        <v>128880613</v>
       </c>
       <c r="B228" t="n">
-        <v>92201</v>
+        <v>91526</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
-      <c r="J228" t="inlineStr"/>
-      <c r="K228" t="inlineStr"/>
-      <c r="N228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
           <t>Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>722997</v>
+        <v>722995</v>
       </c>
       <c r="R228" t="n">
-        <v>7544482</v>
+        <v>7544630</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25862,7 +25863,6 @@
       <c r="AE228" t="b">
         <v>0</v>
       </c>
-      <c r="AF228" t="inlineStr"/>
       <c r="AG228" t="b">
         <v>0</v>
       </c>
@@ -25884,7 +25884,7 @@
         <v>128880596</v>
       </c>
       <c r="B229" t="n">
-        <v>91800</v>
+        <v>91804</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -25985,7 +25985,7 @@
         <v>128880601</v>
       </c>
       <c r="B230" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY230"/>
+  <dimension ref="A1:AY235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24995,7 +24995,7 @@
         <v>128391652</v>
       </c>
       <c r="B220" t="n">
-        <v>92788</v>
+        <v>92792</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -25092,7 +25092,7 @@
         <v>128391313</v>
       </c>
       <c r="B221" t="n">
-        <v>91500</v>
+        <v>91504</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -25189,7 +25189,7 @@
         <v>128391239</v>
       </c>
       <c r="B222" t="n">
-        <v>91958</v>
+        <v>91962</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -25683,48 +25683,45 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>128880583</v>
+        <v>128880613</v>
       </c>
       <c r="B227" t="n">
-        <v>92205</v>
+        <v>91526</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
-      <c r="J227" t="inlineStr"/>
-      <c r="K227" t="inlineStr"/>
-      <c r="N227" t="inlineStr"/>
       <c r="P227" t="inlineStr">
         <is>
           <t>Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>722997</v>
+        <v>722995</v>
       </c>
       <c r="R227" t="n">
-        <v>7544482</v>
+        <v>7544630</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25765,7 +25762,6 @@
       <c r="AE227" t="b">
         <v>0</v>
       </c>
-      <c r="AF227" t="inlineStr"/>
       <c r="AG227" t="b">
         <v>0</v>
       </c>
@@ -25784,45 +25780,48 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>128880613</v>
+        <v>128880583</v>
       </c>
       <c r="B228" t="n">
-        <v>91526</v>
+        <v>92205</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
+      <c r="J228" t="inlineStr"/>
+      <c r="K228" t="inlineStr"/>
+      <c r="N228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
           <t>Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>722995</v>
+        <v>722997</v>
       </c>
       <c r="R228" t="n">
-        <v>7544630</v>
+        <v>7544482</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25863,6 +25862,7 @@
       <c r="AE228" t="b">
         <v>0</v>
       </c>
+      <c r="AF228" t="inlineStr"/>
       <c r="AG228" t="b">
         <v>0</v>
       </c>
@@ -26082,6 +26082,491 @@
       </c>
       <c r="AY230" t="inlineStr"/>
     </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>128981901</v>
+      </c>
+      <c r="B231" t="n">
+        <v>91522</v>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E231" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr"/>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>Kurravaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q231" t="n">
+        <v>723261</v>
+      </c>
+      <c r="R231" t="n">
+        <v>7544311</v>
+      </c>
+      <c r="S231" t="n">
+        <v>10</v>
+      </c>
+      <c r="T231" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U231" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V231" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W231" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y231" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD231" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE231" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG231" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT231" t="inlineStr"/>
+      <c r="AW231" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX231" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY231" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>128981896</v>
+      </c>
+      <c r="B232" t="n">
+        <v>91804</v>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E232" t="n">
+        <v>658</v>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr"/>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>Kurravaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q232" t="n">
+        <v>723262</v>
+      </c>
+      <c r="R232" t="n">
+        <v>7544293</v>
+      </c>
+      <c r="S232" t="n">
+        <v>10</v>
+      </c>
+      <c r="T232" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V232" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W232" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y232" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD232" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE232" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG232" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT232" t="inlineStr"/>
+      <c r="AW232" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX232" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY232" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>128981895</v>
+      </c>
+      <c r="B233" t="n">
+        <v>91962</v>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E233" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr"/>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>Kurravaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q233" t="n">
+        <v>723259</v>
+      </c>
+      <c r="R233" t="n">
+        <v>7544292</v>
+      </c>
+      <c r="S233" t="n">
+        <v>10</v>
+      </c>
+      <c r="T233" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V233" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W233" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y233" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD233" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE233" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG233" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT233" t="inlineStr"/>
+      <c r="AW233" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX233" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>128981900</v>
+      </c>
+      <c r="B234" t="n">
+        <v>91504</v>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E234" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr"/>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>Kurravaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q234" t="n">
+        <v>723242</v>
+      </c>
+      <c r="R234" t="n">
+        <v>7544301</v>
+      </c>
+      <c r="S234" t="n">
+        <v>10</v>
+      </c>
+      <c r="T234" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U234" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V234" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W234" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y234" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD234" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE234" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG234" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT234" t="inlineStr"/>
+      <c r="AW234" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX234" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY234" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>128981894</v>
+      </c>
+      <c r="B235" t="n">
+        <v>92205</v>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E235" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr"/>
+      <c r="P235" t="inlineStr">
+        <is>
+          <t>Kurravaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q235" t="n">
+        <v>723197</v>
+      </c>
+      <c r="R235" t="n">
+        <v>7544189</v>
+      </c>
+      <c r="S235" t="n">
+        <v>10</v>
+      </c>
+      <c r="T235" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U235" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V235" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W235" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y235" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD235" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE235" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG235" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT235" t="inlineStr"/>
+      <c r="AW235" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX235" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY235" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY235"/>
+  <dimension ref="A1:AY241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25683,45 +25683,48 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>128880613</v>
+        <v>128880583</v>
       </c>
       <c r="B227" t="n">
-        <v>91526</v>
+        <v>92205</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
+      <c r="J227" t="inlineStr"/>
+      <c r="K227" t="inlineStr"/>
+      <c r="N227" t="inlineStr"/>
       <c r="P227" t="inlineStr">
         <is>
           <t>Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>722995</v>
+        <v>722997</v>
       </c>
       <c r="R227" t="n">
-        <v>7544630</v>
+        <v>7544482</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25762,6 +25765,7 @@
       <c r="AE227" t="b">
         <v>0</v>
       </c>
+      <c r="AF227" t="inlineStr"/>
       <c r="AG227" t="b">
         <v>0</v>
       </c>
@@ -25780,48 +25784,45 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>128880583</v>
+        <v>128880613</v>
       </c>
       <c r="B228" t="n">
-        <v>92205</v>
+        <v>91526</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
-      <c r="J228" t="inlineStr"/>
-      <c r="K228" t="inlineStr"/>
-      <c r="N228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
           <t>Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>722997</v>
+        <v>722995</v>
       </c>
       <c r="R228" t="n">
-        <v>7544482</v>
+        <v>7544630</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25862,7 +25863,6 @@
       <c r="AE228" t="b">
         <v>0</v>
       </c>
-      <c r="AF228" t="inlineStr"/>
       <c r="AG228" t="b">
         <v>0</v>
       </c>
@@ -26567,6 +26567,588 @@
       </c>
       <c r="AY235" t="inlineStr"/>
     </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>129004994</v>
+      </c>
+      <c r="B236" t="n">
+        <v>57880</v>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E236" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr"/>
+      <c r="P236" t="inlineStr">
+        <is>
+          <t>Kurravaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q236" t="n">
+        <v>723510</v>
+      </c>
+      <c r="R236" t="n">
+        <v>7544754</v>
+      </c>
+      <c r="S236" t="n">
+        <v>10</v>
+      </c>
+      <c r="T236" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U236" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V236" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W236" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y236" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD236" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE236" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG236" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT236" t="inlineStr"/>
+      <c r="AW236" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX236" t="inlineStr">
+        <is>
+          <t>per-erik mukka, Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY236" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>129004991</v>
+      </c>
+      <c r="B237" t="n">
+        <v>91430</v>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E237" t="n">
+        <v>3242</v>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Vitplätt</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>Chaetodermella luna</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr"/>
+      <c r="P237" t="inlineStr">
+        <is>
+          <t>Kurravaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q237" t="n">
+        <v>723044</v>
+      </c>
+      <c r="R237" t="n">
+        <v>7544626</v>
+      </c>
+      <c r="S237" t="n">
+        <v>10</v>
+      </c>
+      <c r="T237" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U237" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V237" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W237" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y237" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD237" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE237" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG237" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT237" t="inlineStr"/>
+      <c r="AW237" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX237" t="inlineStr">
+        <is>
+          <t>per-erik mukka, Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY237" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>129005002</v>
+      </c>
+      <c r="B238" t="n">
+        <v>80230</v>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E238" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr"/>
+      <c r="P238" t="inlineStr">
+        <is>
+          <t>Kurravaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q238" t="n">
+        <v>722882</v>
+      </c>
+      <c r="R238" t="n">
+        <v>7544421</v>
+      </c>
+      <c r="S238" t="n">
+        <v>10</v>
+      </c>
+      <c r="T238" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U238" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V238" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W238" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y238" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA238" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD238" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE238" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG238" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT238" t="inlineStr"/>
+      <c r="AW238" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX238" t="inlineStr">
+        <is>
+          <t>per-erik mukka, Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY238" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>129005011</v>
+      </c>
+      <c r="B239" t="n">
+        <v>56901</v>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E239" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr"/>
+      <c r="P239" t="inlineStr">
+        <is>
+          <t>Kurravaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q239" t="n">
+        <v>723208</v>
+      </c>
+      <c r="R239" t="n">
+        <v>7544649</v>
+      </c>
+      <c r="S239" t="n">
+        <v>10</v>
+      </c>
+      <c r="T239" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U239" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V239" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W239" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y239" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA239" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD239" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE239" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG239" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT239" t="inlineStr"/>
+      <c r="AW239" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX239" t="inlineStr">
+        <is>
+          <t>per-erik mukka, Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY239" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>129005003</v>
+      </c>
+      <c r="B240" t="n">
+        <v>80230</v>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E240" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr"/>
+      <c r="P240" t="inlineStr">
+        <is>
+          <t>Kurravaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q240" t="n">
+        <v>722853</v>
+      </c>
+      <c r="R240" t="n">
+        <v>7544438</v>
+      </c>
+      <c r="S240" t="n">
+        <v>10</v>
+      </c>
+      <c r="T240" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U240" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V240" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W240" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y240" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA240" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD240" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE240" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG240" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT240" t="inlineStr"/>
+      <c r="AW240" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX240" t="inlineStr">
+        <is>
+          <t>per-erik mukka, Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY240" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>129005009</v>
+      </c>
+      <c r="B241" t="n">
+        <v>91880</v>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E241" t="n">
+        <v>1505</v>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>Kristallticka</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>Skeletocutis stellae</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>(Pilát) Jean Keller</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr"/>
+      <c r="P241" t="inlineStr">
+        <is>
+          <t>Kurravaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q241" t="n">
+        <v>723109</v>
+      </c>
+      <c r="R241" t="n">
+        <v>7544621</v>
+      </c>
+      <c r="S241" t="n">
+        <v>10</v>
+      </c>
+      <c r="T241" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U241" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V241" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W241" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y241" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA241" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD241" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE241" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG241" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT241" t="inlineStr"/>
+      <c r="AW241" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX241" t="inlineStr">
+        <is>
+          <t>per-erik mukka, Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY241" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY241"/>
+  <dimension ref="A1:AY248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24995,7 +24995,7 @@
         <v>128391652</v>
       </c>
       <c r="B220" t="n">
-        <v>92792</v>
+        <v>92797</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -25092,7 +25092,7 @@
         <v>128391313</v>
       </c>
       <c r="B221" t="n">
-        <v>91504</v>
+        <v>91509</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -25189,7 +25189,7 @@
         <v>128391239</v>
       </c>
       <c r="B222" t="n">
-        <v>91962</v>
+        <v>91967</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -25286,7 +25286,7 @@
         <v>128880600</v>
       </c>
       <c r="B223" t="n">
-        <v>92150</v>
+        <v>92155</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -25387,7 +25387,7 @@
         <v>128880607</v>
       </c>
       <c r="B224" t="n">
-        <v>91504</v>
+        <v>91509</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -25484,7 +25484,7 @@
         <v>128880616</v>
       </c>
       <c r="B225" t="n">
-        <v>91769</v>
+        <v>91774</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -25585,7 +25585,7 @@
         <v>128880594</v>
       </c>
       <c r="B226" t="n">
-        <v>91962</v>
+        <v>91967</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -25686,7 +25686,7 @@
         <v>128880583</v>
       </c>
       <c r="B227" t="n">
-        <v>92205</v>
+        <v>92210</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -25787,7 +25787,7 @@
         <v>128880613</v>
       </c>
       <c r="B228" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -25884,7 +25884,7 @@
         <v>128880596</v>
       </c>
       <c r="B229" t="n">
-        <v>91804</v>
+        <v>91809</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -25985,7 +25985,7 @@
         <v>128880601</v>
       </c>
       <c r="B230" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -26087,7 +26087,7 @@
         <v>128981901</v>
       </c>
       <c r="B231" t="n">
-        <v>91522</v>
+        <v>91527</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -26184,7 +26184,7 @@
         <v>128981896</v>
       </c>
       <c r="B232" t="n">
-        <v>91804</v>
+        <v>91809</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -26281,7 +26281,7 @@
         <v>128981895</v>
       </c>
       <c r="B233" t="n">
-        <v>91962</v>
+        <v>91967</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -26378,7 +26378,7 @@
         <v>128981900</v>
       </c>
       <c r="B234" t="n">
-        <v>91504</v>
+        <v>91509</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -26475,7 +26475,7 @@
         <v>128981894</v>
       </c>
       <c r="B235" t="n">
-        <v>92205</v>
+        <v>92210</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -26572,7 +26572,7 @@
         <v>129004994</v>
       </c>
       <c r="B236" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -26669,7 +26669,7 @@
         <v>129004991</v>
       </c>
       <c r="B237" t="n">
-        <v>91430</v>
+        <v>91435</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -26766,7 +26766,7 @@
         <v>129005002</v>
       </c>
       <c r="B238" t="n">
-        <v>80230</v>
+        <v>80135</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -26860,10 +26860,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>129005011</v>
+        <v>129005003</v>
       </c>
       <c r="B239" t="n">
-        <v>56901</v>
+        <v>80135</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -26871,21 +26871,21 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>102612</v>
+        <v>2081</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
@@ -26895,10 +26895,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>723208</v>
+        <v>722853</v>
       </c>
       <c r="R239" t="n">
-        <v>7544649</v>
+        <v>7544438</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -26957,32 +26957,32 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>129005003</v>
+        <v>129005009</v>
       </c>
       <c r="B240" t="n">
-        <v>80230</v>
+        <v>91885</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>2081</v>
+        <v>1505</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kristallticka</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Skeletocutis stellae</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Pilát) Jean Keller</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
@@ -26992,10 +26992,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>722853</v>
+        <v>723109</v>
       </c>
       <c r="R240" t="n">
-        <v>7544438</v>
+        <v>7544621</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -27054,32 +27054,32 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>129005009</v>
+        <v>129005011</v>
       </c>
       <c r="B241" t="n">
-        <v>91880</v>
+        <v>56904</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>1505</v>
+        <v>102612</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Kristallticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Skeletocutis stellae</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Pilát) Jean Keller</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
@@ -27089,10 +27089,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>723109</v>
+        <v>723208</v>
       </c>
       <c r="R241" t="n">
-        <v>7544621</v>
+        <v>7544649</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -27148,6 +27148,686 @@
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>129015603</v>
+      </c>
+      <c r="B242" t="n">
+        <v>80163</v>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E242" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr"/>
+      <c r="P242" t="inlineStr">
+        <is>
+          <t>Kurravaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q242" t="n">
+        <v>722995</v>
+      </c>
+      <c r="R242" t="n">
+        <v>7544632</v>
+      </c>
+      <c r="S242" t="n">
+        <v>10</v>
+      </c>
+      <c r="T242" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U242" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V242" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W242" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y242" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA242" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD242" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE242" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG242" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT242" t="inlineStr"/>
+      <c r="AW242" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX242" t="inlineStr">
+        <is>
+          <t>Christina Boyd, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY242" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>129015628</v>
+      </c>
+      <c r="B243" t="n">
+        <v>91531</v>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E243" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr"/>
+      <c r="P243" t="inlineStr">
+        <is>
+          <t>Kurravaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q243" t="n">
+        <v>723040</v>
+      </c>
+      <c r="R243" t="n">
+        <v>7544636</v>
+      </c>
+      <c r="S243" t="n">
+        <v>10</v>
+      </c>
+      <c r="T243" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U243" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V243" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W243" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y243" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA243" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD243" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE243" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG243" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT243" t="inlineStr"/>
+      <c r="AW243" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX243" t="inlineStr">
+        <is>
+          <t>Christina Boyd, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY243" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>129015623</v>
+      </c>
+      <c r="B244" t="n">
+        <v>79108</v>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E244" t="n">
+        <v>864</v>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr"/>
+      <c r="P244" t="inlineStr">
+        <is>
+          <t>Kurravaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q244" t="n">
+        <v>722827</v>
+      </c>
+      <c r="R244" t="n">
+        <v>7544403</v>
+      </c>
+      <c r="S244" t="n">
+        <v>10</v>
+      </c>
+      <c r="T244" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U244" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V244" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W244" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y244" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA244" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD244" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE244" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG244" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT244" t="inlineStr"/>
+      <c r="AW244" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX244" t="inlineStr">
+        <is>
+          <t>Christina Boyd, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY244" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>129016111</v>
+      </c>
+      <c r="B245" t="n">
+        <v>88598</v>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E245" t="n">
+        <v>3294</v>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>Ängsfingersvamp</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>Clavulinopsis corniculata</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>(Schaeff. : Fr.) Corner</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr"/>
+      <c r="P245" t="inlineStr">
+        <is>
+          <t>Kurravaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q245" t="n">
+        <v>722928</v>
+      </c>
+      <c r="R245" t="n">
+        <v>7544587</v>
+      </c>
+      <c r="S245" t="n">
+        <v>10</v>
+      </c>
+      <c r="T245" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U245" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V245" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W245" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y245" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA245" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD245" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE245" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF245" t="inlineStr"/>
+      <c r="AG245" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT245" t="inlineStr"/>
+      <c r="AW245" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX245" t="inlineStr">
+        <is>
+          <t>Christina Boyd, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY245" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>129015614</v>
+      </c>
+      <c r="B246" t="n">
+        <v>91809</v>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E246" t="n">
+        <v>658</v>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr"/>
+      <c r="P246" t="inlineStr">
+        <is>
+          <t>Kurravaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q246" t="n">
+        <v>722949</v>
+      </c>
+      <c r="R246" t="n">
+        <v>7544575</v>
+      </c>
+      <c r="S246" t="n">
+        <v>10</v>
+      </c>
+      <c r="T246" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U246" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V246" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W246" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y246" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA246" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD246" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE246" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG246" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT246" t="inlineStr"/>
+      <c r="AW246" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX246" t="inlineStr">
+        <is>
+          <t>per-erik mukka, Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY246" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>129015607</v>
+      </c>
+      <c r="B247" t="n">
+        <v>79115</v>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E247" t="n">
+        <v>6450</v>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>Skuggblåslav</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>Hypogymnia vittata</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr"/>
+      <c r="P247" t="inlineStr">
+        <is>
+          <t>Kurravaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q247" t="n">
+        <v>722874</v>
+      </c>
+      <c r="R247" t="n">
+        <v>7544377</v>
+      </c>
+      <c r="S247" t="n">
+        <v>10</v>
+      </c>
+      <c r="T247" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U247" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V247" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W247" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y247" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA247" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD247" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE247" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG247" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT247" t="inlineStr"/>
+      <c r="AW247" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX247" t="inlineStr">
+        <is>
+          <t>Christina Boyd, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY247" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>129015596</v>
+      </c>
+      <c r="B248" t="n">
+        <v>79648</v>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E248" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr"/>
+      <c r="P248" t="inlineStr">
+        <is>
+          <t>Kurravaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q248" t="n">
+        <v>723041</v>
+      </c>
+      <c r="R248" t="n">
+        <v>7544565</v>
+      </c>
+      <c r="S248" t="n">
+        <v>10</v>
+      </c>
+      <c r="T248" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U248" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V248" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W248" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y248" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA248" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD248" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE248" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG248" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT248" t="inlineStr"/>
+      <c r="AW248" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX248" t="inlineStr">
+        <is>
+          <t>Christina Boyd, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY248" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -27151,32 +27151,32 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>129015603</v>
+        <v>129015628</v>
       </c>
       <c r="B242" t="n">
-        <v>80168</v>
+        <v>91538</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
@@ -27186,10 +27186,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>722995</v>
+        <v>723040</v>
       </c>
       <c r="R242" t="n">
-        <v>7544632</v>
+        <v>7544636</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -27248,32 +27248,32 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>129015628</v>
+        <v>129015603</v>
       </c>
       <c r="B243" t="n">
-        <v>91538</v>
+        <v>80168</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
@@ -27283,10 +27283,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>723040</v>
+        <v>722995</v>
       </c>
       <c r="R243" t="n">
-        <v>7544636</v>
+        <v>7544632</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -25286,7 +25286,7 @@
         <v>128880600</v>
       </c>
       <c r="B223" t="n">
-        <v>92163</v>
+        <v>92168</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -25387,7 +25387,7 @@
         <v>128880607</v>
       </c>
       <c r="B224" t="n">
-        <v>91516</v>
+        <v>91519</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -25484,7 +25484,7 @@
         <v>128880616</v>
       </c>
       <c r="B225" t="n">
-        <v>91781</v>
+        <v>91784</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -25585,7 +25585,7 @@
         <v>128880594</v>
       </c>
       <c r="B226" t="n">
-        <v>91975</v>
+        <v>91978</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -25683,45 +25683,48 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>128880613</v>
+        <v>128880583</v>
       </c>
       <c r="B227" t="n">
-        <v>91538</v>
+        <v>92223</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
+      <c r="J227" t="inlineStr"/>
+      <c r="K227" t="inlineStr"/>
+      <c r="N227" t="inlineStr"/>
       <c r="P227" t="inlineStr">
         <is>
           <t>Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>722995</v>
+        <v>722997</v>
       </c>
       <c r="R227" t="n">
-        <v>7544630</v>
+        <v>7544482</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25762,6 +25765,7 @@
       <c r="AE227" t="b">
         <v>0</v>
       </c>
+      <c r="AF227" t="inlineStr"/>
       <c r="AG227" t="b">
         <v>0</v>
       </c>
@@ -25780,48 +25784,45 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>128880583</v>
+        <v>128880613</v>
       </c>
       <c r="B228" t="n">
-        <v>92218</v>
+        <v>91541</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
-      <c r="J228" t="inlineStr"/>
-      <c r="K228" t="inlineStr"/>
-      <c r="N228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
           <t>Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>722997</v>
+        <v>722995</v>
       </c>
       <c r="R228" t="n">
-        <v>7544482</v>
+        <v>7544630</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25862,7 +25863,6 @@
       <c r="AE228" t="b">
         <v>0</v>
       </c>
-      <c r="AF228" t="inlineStr"/>
       <c r="AG228" t="b">
         <v>0</v>
       </c>
@@ -25884,7 +25884,7 @@
         <v>128880596</v>
       </c>
       <c r="B229" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -26087,7 +26087,7 @@
         <v>128981901</v>
       </c>
       <c r="B231" t="n">
-        <v>91534</v>
+        <v>91537</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -26184,7 +26184,7 @@
         <v>128981896</v>
       </c>
       <c r="B232" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -26281,7 +26281,7 @@
         <v>128981895</v>
       </c>
       <c r="B233" t="n">
-        <v>91975</v>
+        <v>91978</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -26378,7 +26378,7 @@
         <v>128981900</v>
       </c>
       <c r="B234" t="n">
-        <v>91516</v>
+        <v>91519</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -26475,7 +26475,7 @@
         <v>128981894</v>
       </c>
       <c r="B235" t="n">
-        <v>92218</v>
+        <v>92223</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -26669,7 +26669,7 @@
         <v>129004991</v>
       </c>
       <c r="B237" t="n">
-        <v>91442</v>
+        <v>91445</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -26957,32 +26957,32 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>129005009</v>
+        <v>129005011</v>
       </c>
       <c r="B240" t="n">
-        <v>91893</v>
+        <v>56904</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>1505</v>
+        <v>102612</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Kristallticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Skeletocutis stellae</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Pilát) Jean Keller</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
@@ -26992,10 +26992,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>723109</v>
+        <v>723208</v>
       </c>
       <c r="R240" t="n">
-        <v>7544621</v>
+        <v>7544649</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -27054,32 +27054,32 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>129005011</v>
+        <v>129005009</v>
       </c>
       <c r="B241" t="n">
-        <v>56904</v>
+        <v>91896</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>102612</v>
+        <v>1505</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kristallticka</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Skeletocutis stellae</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pilát) Jean Keller</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
@@ -27089,10 +27089,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>723208</v>
+        <v>723109</v>
       </c>
       <c r="R241" t="n">
-        <v>7544649</v>
+        <v>7544621</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -27154,7 +27154,7 @@
         <v>129015628</v>
       </c>
       <c r="B242" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -27445,7 +27445,7 @@
         <v>129016111</v>
       </c>
       <c r="B245" t="n">
-        <v>88605</v>
+        <v>88608</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -27543,7 +27543,7 @@
         <v>129015614</v>
       </c>
       <c r="B246" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -25286,7 +25286,7 @@
         <v>128880600</v>
       </c>
       <c r="B223" t="n">
-        <v>92168</v>
+        <v>92171</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -25387,7 +25387,7 @@
         <v>128880607</v>
       </c>
       <c r="B224" t="n">
-        <v>91519</v>
+        <v>91522</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -25484,7 +25484,7 @@
         <v>128880616</v>
       </c>
       <c r="B225" t="n">
-        <v>91784</v>
+        <v>91787</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -25585,7 +25585,7 @@
         <v>128880594</v>
       </c>
       <c r="B226" t="n">
-        <v>91978</v>
+        <v>91981</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -25683,48 +25683,45 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>128880583</v>
+        <v>128880613</v>
       </c>
       <c r="B227" t="n">
-        <v>92223</v>
+        <v>91544</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
-      <c r="J227" t="inlineStr"/>
-      <c r="K227" t="inlineStr"/>
-      <c r="N227" t="inlineStr"/>
       <c r="P227" t="inlineStr">
         <is>
           <t>Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>722997</v>
+        <v>722995</v>
       </c>
       <c r="R227" t="n">
-        <v>7544482</v>
+        <v>7544630</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25765,7 +25762,6 @@
       <c r="AE227" t="b">
         <v>0</v>
       </c>
-      <c r="AF227" t="inlineStr"/>
       <c r="AG227" t="b">
         <v>0</v>
       </c>
@@ -25784,45 +25780,48 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>128880613</v>
+        <v>128880583</v>
       </c>
       <c r="B228" t="n">
-        <v>91541</v>
+        <v>92226</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
+      <c r="J228" t="inlineStr"/>
+      <c r="K228" t="inlineStr"/>
+      <c r="N228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
           <t>Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>722995</v>
+        <v>722997</v>
       </c>
       <c r="R228" t="n">
-        <v>7544630</v>
+        <v>7544482</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25863,6 +25862,7 @@
       <c r="AE228" t="b">
         <v>0</v>
       </c>
+      <c r="AF228" t="inlineStr"/>
       <c r="AG228" t="b">
         <v>0</v>
       </c>
@@ -25884,7 +25884,7 @@
         <v>128880596</v>
       </c>
       <c r="B229" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -25985,7 +25985,7 @@
         <v>128880601</v>
       </c>
       <c r="B230" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -26087,7 +26087,7 @@
         <v>128981901</v>
       </c>
       <c r="B231" t="n">
-        <v>91537</v>
+        <v>91540</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -26184,7 +26184,7 @@
         <v>128981896</v>
       </c>
       <c r="B232" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -26281,7 +26281,7 @@
         <v>128981895</v>
       </c>
       <c r="B233" t="n">
-        <v>91978</v>
+        <v>91981</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -26378,7 +26378,7 @@
         <v>128981900</v>
       </c>
       <c r="B234" t="n">
-        <v>91519</v>
+        <v>91522</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -26475,7 +26475,7 @@
         <v>128981894</v>
       </c>
       <c r="B235" t="n">
-        <v>92223</v>
+        <v>92226</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -26669,7 +26669,7 @@
         <v>129004991</v>
       </c>
       <c r="B237" t="n">
-        <v>91445</v>
+        <v>91448</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -26766,7 +26766,7 @@
         <v>129005002</v>
       </c>
       <c r="B238" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -26860,32 +26860,32 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>129005003</v>
+        <v>129005009</v>
       </c>
       <c r="B239" t="n">
-        <v>80140</v>
+        <v>91899</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>2081</v>
+        <v>1505</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kristallticka</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Skeletocutis stellae</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Pilát) Jean Keller</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
@@ -26895,10 +26895,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>722853</v>
+        <v>723109</v>
       </c>
       <c r="R239" t="n">
-        <v>7544438</v>
+        <v>7544621</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -26957,10 +26957,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>129005011</v>
+        <v>129005003</v>
       </c>
       <c r="B240" t="n">
-        <v>56904</v>
+        <v>80141</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -26968,21 +26968,21 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>102612</v>
+        <v>2081</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
@@ -26992,10 +26992,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>723208</v>
+        <v>722853</v>
       </c>
       <c r="R240" t="n">
-        <v>7544649</v>
+        <v>7544438</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -27054,32 +27054,32 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>129005009</v>
+        <v>129005011</v>
       </c>
       <c r="B241" t="n">
-        <v>91896</v>
+        <v>56904</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>1505</v>
+        <v>102612</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Kristallticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Skeletocutis stellae</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Pilát) Jean Keller</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
@@ -27089,10 +27089,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>723109</v>
+        <v>723208</v>
       </c>
       <c r="R241" t="n">
-        <v>7544621</v>
+        <v>7544649</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -27154,7 +27154,7 @@
         <v>129015628</v>
       </c>
       <c r="B242" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -27251,7 +27251,7 @@
         <v>129015603</v>
       </c>
       <c r="B243" t="n">
-        <v>80168</v>
+        <v>80169</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -27348,7 +27348,7 @@
         <v>129015623</v>
       </c>
       <c r="B244" t="n">
-        <v>79113</v>
+        <v>79114</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -27445,7 +27445,7 @@
         <v>129016111</v>
       </c>
       <c r="B245" t="n">
-        <v>88608</v>
+        <v>88611</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -27543,7 +27543,7 @@
         <v>129015614</v>
       </c>
       <c r="B246" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -27640,7 +27640,7 @@
         <v>129015607</v>
       </c>
       <c r="B247" t="n">
-        <v>79120</v>
+        <v>79121</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -27737,7 +27737,7 @@
         <v>129015596</v>
       </c>
       <c r="B248" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -27931,7 +27931,7 @@
         <v>129051460</v>
       </c>
       <c r="B250" t="n">
-        <v>80043</v>
+        <v>80044</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -28028,7 +28028,7 @@
         <v>129040495</v>
       </c>
       <c r="B251" t="n">
-        <v>80093</v>
+        <v>80094</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -25683,45 +25683,48 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>128880613</v>
+        <v>128880583</v>
       </c>
       <c r="B227" t="n">
-        <v>91544</v>
+        <v>92226</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
+      <c r="J227" t="inlineStr"/>
+      <c r="K227" t="inlineStr"/>
+      <c r="N227" t="inlineStr"/>
       <c r="P227" t="inlineStr">
         <is>
           <t>Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>722995</v>
+        <v>722997</v>
       </c>
       <c r="R227" t="n">
-        <v>7544630</v>
+        <v>7544482</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25762,6 +25765,7 @@
       <c r="AE227" t="b">
         <v>0</v>
       </c>
+      <c r="AF227" t="inlineStr"/>
       <c r="AG227" t="b">
         <v>0</v>
       </c>
@@ -25780,48 +25784,45 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>128880583</v>
+        <v>128880613</v>
       </c>
       <c r="B228" t="n">
-        <v>92226</v>
+        <v>91544</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
-      <c r="J228" t="inlineStr"/>
-      <c r="K228" t="inlineStr"/>
-      <c r="N228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
           <t>Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>722997</v>
+        <v>722995</v>
       </c>
       <c r="R228" t="n">
-        <v>7544482</v>
+        <v>7544630</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25862,7 +25863,6 @@
       <c r="AE228" t="b">
         <v>0</v>
       </c>
-      <c r="AF228" t="inlineStr"/>
       <c r="AG228" t="b">
         <v>0</v>
       </c>
@@ -26860,32 +26860,32 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>129005009</v>
+        <v>129005011</v>
       </c>
       <c r="B239" t="n">
-        <v>91899</v>
+        <v>56904</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>1505</v>
+        <v>102612</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Kristallticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Skeletocutis stellae</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Pilát) Jean Keller</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
@@ -26895,10 +26895,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>723109</v>
+        <v>723208</v>
       </c>
       <c r="R239" t="n">
-        <v>7544621</v>
+        <v>7544649</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -26957,32 +26957,32 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>129005003</v>
+        <v>129005009</v>
       </c>
       <c r="B240" t="n">
-        <v>80141</v>
+        <v>91899</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>2081</v>
+        <v>1505</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kristallticka</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Skeletocutis stellae</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Pilát) Jean Keller</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
@@ -26992,10 +26992,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>722853</v>
+        <v>723109</v>
       </c>
       <c r="R240" t="n">
-        <v>7544438</v>
+        <v>7544621</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -27054,10 +27054,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>129005011</v>
+        <v>129005003</v>
       </c>
       <c r="B241" t="n">
-        <v>56904</v>
+        <v>80141</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -27065,21 +27065,21 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>102612</v>
+        <v>2081</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
@@ -27089,10 +27089,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>723208</v>
+        <v>722853</v>
       </c>
       <c r="R241" t="n">
-        <v>7544649</v>
+        <v>7544438</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -26860,10 +26860,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>129005011</v>
+        <v>129005003</v>
       </c>
       <c r="B239" t="n">
-        <v>56904</v>
+        <v>80141</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -26871,21 +26871,21 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>102612</v>
+        <v>2081</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
@@ -26895,10 +26895,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>723208</v>
+        <v>722853</v>
       </c>
       <c r="R239" t="n">
-        <v>7544649</v>
+        <v>7544438</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -27054,10 +27054,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>129005003</v>
+        <v>129005011</v>
       </c>
       <c r="B241" t="n">
-        <v>80141</v>
+        <v>56904</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -27065,21 +27065,21 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>2081</v>
+        <v>102612</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
@@ -27089,10 +27089,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>722853</v>
+        <v>723208</v>
       </c>
       <c r="R241" t="n">
-        <v>7544438</v>
+        <v>7544649</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -25286,7 +25286,7 @@
         <v>128880600</v>
       </c>
       <c r="B223" t="n">
-        <v>92171</v>
+        <v>92178</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -25387,7 +25387,7 @@
         <v>128880607</v>
       </c>
       <c r="B224" t="n">
-        <v>91522</v>
+        <v>91529</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -25484,7 +25484,7 @@
         <v>128880616</v>
       </c>
       <c r="B225" t="n">
-        <v>91787</v>
+        <v>91794</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -25585,7 +25585,7 @@
         <v>128880594</v>
       </c>
       <c r="B226" t="n">
-        <v>91981</v>
+        <v>91988</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -25683,48 +25683,45 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>128880583</v>
+        <v>128880613</v>
       </c>
       <c r="B227" t="n">
-        <v>92226</v>
+        <v>91551</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
-      <c r="J227" t="inlineStr"/>
-      <c r="K227" t="inlineStr"/>
-      <c r="N227" t="inlineStr"/>
       <c r="P227" t="inlineStr">
         <is>
           <t>Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>722997</v>
+        <v>722995</v>
       </c>
       <c r="R227" t="n">
-        <v>7544482</v>
+        <v>7544630</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25765,7 +25762,6 @@
       <c r="AE227" t="b">
         <v>0</v>
       </c>
-      <c r="AF227" t="inlineStr"/>
       <c r="AG227" t="b">
         <v>0</v>
       </c>
@@ -25784,45 +25780,48 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>128880613</v>
+        <v>128880583</v>
       </c>
       <c r="B228" t="n">
-        <v>91544</v>
+        <v>92233</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
+      <c r="J228" t="inlineStr"/>
+      <c r="K228" t="inlineStr"/>
+      <c r="N228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
           <t>Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>722995</v>
+        <v>722997</v>
       </c>
       <c r="R228" t="n">
-        <v>7544630</v>
+        <v>7544482</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25863,6 +25862,7 @@
       <c r="AE228" t="b">
         <v>0</v>
       </c>
+      <c r="AF228" t="inlineStr"/>
       <c r="AG228" t="b">
         <v>0</v>
       </c>
@@ -25884,7 +25884,7 @@
         <v>128880596</v>
       </c>
       <c r="B229" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -25985,7 +25985,7 @@
         <v>128880601</v>
       </c>
       <c r="B230" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -26087,7 +26087,7 @@
         <v>128981901</v>
       </c>
       <c r="B231" t="n">
-        <v>91540</v>
+        <v>91547</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -26184,7 +26184,7 @@
         <v>128981896</v>
       </c>
       <c r="B232" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -26281,7 +26281,7 @@
         <v>128981895</v>
       </c>
       <c r="B233" t="n">
-        <v>91981</v>
+        <v>91988</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -26378,7 +26378,7 @@
         <v>128981900</v>
       </c>
       <c r="B234" t="n">
-        <v>91522</v>
+        <v>91529</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -26475,7 +26475,7 @@
         <v>128981894</v>
       </c>
       <c r="B235" t="n">
-        <v>92226</v>
+        <v>92233</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -26572,7 +26572,7 @@
         <v>129004994</v>
       </c>
       <c r="B236" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -26669,7 +26669,7 @@
         <v>129004991</v>
       </c>
       <c r="B237" t="n">
-        <v>91448</v>
+        <v>91454</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -26766,7 +26766,7 @@
         <v>129005002</v>
       </c>
       <c r="B238" t="n">
-        <v>80141</v>
+        <v>80145</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -26860,32 +26860,32 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>129005003</v>
+        <v>129005009</v>
       </c>
       <c r="B239" t="n">
-        <v>80141</v>
+        <v>91906</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>2081</v>
+        <v>1505</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kristallticka</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Skeletocutis stellae</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Pilát) Jean Keller</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
@@ -26895,10 +26895,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>722853</v>
+        <v>723109</v>
       </c>
       <c r="R239" t="n">
-        <v>7544438</v>
+        <v>7544621</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -26957,32 +26957,32 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>129005009</v>
+        <v>129005003</v>
       </c>
       <c r="B240" t="n">
-        <v>91899</v>
+        <v>80145</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>1505</v>
+        <v>2081</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Kristallticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Skeletocutis stellae</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Pilát) Jean Keller</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
@@ -26992,10 +26992,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>723109</v>
+        <v>722853</v>
       </c>
       <c r="R240" t="n">
-        <v>7544621</v>
+        <v>7544438</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -27057,7 +27057,7 @@
         <v>129005011</v>
       </c>
       <c r="B241" t="n">
-        <v>56904</v>
+        <v>56906</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -27151,32 +27151,32 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>129015628</v>
+        <v>129015603</v>
       </c>
       <c r="B242" t="n">
-        <v>91544</v>
+        <v>80173</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
@@ -27186,10 +27186,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>723040</v>
+        <v>722995</v>
       </c>
       <c r="R242" t="n">
-        <v>7544636</v>
+        <v>7544632</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -27248,32 +27248,32 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>129015603</v>
+        <v>129015628</v>
       </c>
       <c r="B243" t="n">
-        <v>80169</v>
+        <v>91551</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
@@ -27283,10 +27283,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>722995</v>
+        <v>723040</v>
       </c>
       <c r="R243" t="n">
-        <v>7544632</v>
+        <v>7544636</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -27348,7 +27348,7 @@
         <v>129015623</v>
       </c>
       <c r="B244" t="n">
-        <v>79114</v>
+        <v>79118</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -27445,7 +27445,7 @@
         <v>129016111</v>
       </c>
       <c r="B245" t="n">
-        <v>88611</v>
+        <v>88615</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -27543,7 +27543,7 @@
         <v>129015614</v>
       </c>
       <c r="B246" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -27640,7 +27640,7 @@
         <v>129015607</v>
       </c>
       <c r="B247" t="n">
-        <v>79121</v>
+        <v>79125</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -27737,7 +27737,7 @@
         <v>129015596</v>
       </c>
       <c r="B248" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -27834,7 +27834,7 @@
         <v>129051458</v>
       </c>
       <c r="B249" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -27931,7 +27931,7 @@
         <v>129051460</v>
       </c>
       <c r="B250" t="n">
-        <v>80044</v>
+        <v>80048</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -28028,7 +28028,7 @@
         <v>129040495</v>
       </c>
       <c r="B251" t="n">
-        <v>80094</v>
+        <v>80098</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -28129,7 +28129,7 @@
         <v>129051462</v>
       </c>
       <c r="B252" t="n">
-        <v>57879</v>
+        <v>57881</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -28226,7 +28226,7 @@
         <v>129051461</v>
       </c>
       <c r="B253" t="n">
-        <v>57827</v>
+        <v>57829</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY253"/>
+  <dimension ref="A1:AY258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25286,7 +25286,7 @@
         <v>128880600</v>
       </c>
       <c r="B223" t="n">
-        <v>92178</v>
+        <v>92185</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -25387,7 +25387,7 @@
         <v>128880607</v>
       </c>
       <c r="B224" t="n">
-        <v>91529</v>
+        <v>91536</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -25484,7 +25484,7 @@
         <v>128880616</v>
       </c>
       <c r="B225" t="n">
-        <v>91794</v>
+        <v>91801</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -25585,7 +25585,7 @@
         <v>128880594</v>
       </c>
       <c r="B226" t="n">
-        <v>91988</v>
+        <v>91995</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -25686,7 +25686,7 @@
         <v>128880613</v>
       </c>
       <c r="B227" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -25783,7 +25783,7 @@
         <v>128880583</v>
       </c>
       <c r="B228" t="n">
-        <v>92233</v>
+        <v>92240</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -25884,7 +25884,7 @@
         <v>128880596</v>
       </c>
       <c r="B229" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -26087,7 +26087,7 @@
         <v>128981901</v>
       </c>
       <c r="B231" t="n">
-        <v>91547</v>
+        <v>91554</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -26184,7 +26184,7 @@
         <v>128981896</v>
       </c>
       <c r="B232" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -26281,7 +26281,7 @@
         <v>128981895</v>
       </c>
       <c r="B233" t="n">
-        <v>91988</v>
+        <v>91995</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -26378,7 +26378,7 @@
         <v>128981900</v>
       </c>
       <c r="B234" t="n">
-        <v>91529</v>
+        <v>91536</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -26475,7 +26475,7 @@
         <v>128981894</v>
       </c>
       <c r="B235" t="n">
-        <v>92233</v>
+        <v>92240</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -26669,7 +26669,7 @@
         <v>129004991</v>
       </c>
       <c r="B237" t="n">
-        <v>91454</v>
+        <v>91461</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -26860,32 +26860,32 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>129005009</v>
+        <v>129005003</v>
       </c>
       <c r="B239" t="n">
-        <v>91906</v>
+        <v>80145</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>1505</v>
+        <v>2081</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Kristallticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Skeletocutis stellae</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Pilát) Jean Keller</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
@@ -26895,10 +26895,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>723109</v>
+        <v>722853</v>
       </c>
       <c r="R239" t="n">
-        <v>7544621</v>
+        <v>7544438</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -26957,10 +26957,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>129005003</v>
+        <v>129005011</v>
       </c>
       <c r="B240" t="n">
-        <v>80145</v>
+        <v>56906</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -26968,21 +26968,21 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>2081</v>
+        <v>102612</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
@@ -26992,10 +26992,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>722853</v>
+        <v>723208</v>
       </c>
       <c r="R240" t="n">
-        <v>7544438</v>
+        <v>7544649</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -27054,32 +27054,32 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>129005011</v>
+        <v>129005009</v>
       </c>
       <c r="B241" t="n">
-        <v>56906</v>
+        <v>91913</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>102612</v>
+        <v>1505</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kristallticka</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Skeletocutis stellae</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pilát) Jean Keller</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
@@ -27089,10 +27089,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>723208</v>
+        <v>723109</v>
       </c>
       <c r="R241" t="n">
-        <v>7544649</v>
+        <v>7544621</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -27151,32 +27151,32 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>129015603</v>
+        <v>129015628</v>
       </c>
       <c r="B242" t="n">
-        <v>80173</v>
+        <v>91558</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
@@ -27186,10 +27186,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>722995</v>
+        <v>723040</v>
       </c>
       <c r="R242" t="n">
-        <v>7544632</v>
+        <v>7544636</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -27248,32 +27248,32 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>129015628</v>
+        <v>129015603</v>
       </c>
       <c r="B243" t="n">
-        <v>91551</v>
+        <v>80173</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
@@ -27283,10 +27283,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>723040</v>
+        <v>722995</v>
       </c>
       <c r="R243" t="n">
-        <v>7544636</v>
+        <v>7544632</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -27445,7 +27445,7 @@
         <v>129016111</v>
       </c>
       <c r="B245" t="n">
-        <v>88615</v>
+        <v>88622</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -27543,7 +27543,7 @@
         <v>129015614</v>
       </c>
       <c r="B246" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -28318,6 +28318,509 @@
       </c>
       <c r="AY253" t="inlineStr"/>
     </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>129309942</v>
+      </c>
+      <c r="B254" t="n">
+        <v>91995</v>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E254" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P254" t="inlineStr">
+        <is>
+          <t>Kurravaara berg, Kurravaara berg, T lm</t>
+        </is>
+      </c>
+      <c r="Q254" t="n">
+        <v>723259</v>
+      </c>
+      <c r="R254" t="n">
+        <v>7544295</v>
+      </c>
+      <c r="S254" t="n">
+        <v>1</v>
+      </c>
+      <c r="T254" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U254" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V254" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W254" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y254" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AA254" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AD254" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE254" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG254" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT254" t="inlineStr"/>
+      <c r="AW254" t="inlineStr">
+        <is>
+          <t>Anna Öhlund</t>
+        </is>
+      </c>
+      <c r="AX254" t="inlineStr">
+        <is>
+          <t>Anna Öhlund</t>
+        </is>
+      </c>
+      <c r="AY254" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>129310241</v>
+      </c>
+      <c r="B255" t="n">
+        <v>92240</v>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E255" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P255" t="inlineStr">
+        <is>
+          <t>Kurravaara berg, Kurravaara berg, T lm</t>
+        </is>
+      </c>
+      <c r="Q255" t="n">
+        <v>723050</v>
+      </c>
+      <c r="R255" t="n">
+        <v>7544229</v>
+      </c>
+      <c r="S255" t="n">
+        <v>1</v>
+      </c>
+      <c r="T255" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U255" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V255" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W255" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y255" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AA255" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AD255" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE255" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG255" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT255" t="inlineStr"/>
+      <c r="AW255" t="inlineStr">
+        <is>
+          <t>Anna Öhlund</t>
+        </is>
+      </c>
+      <c r="AX255" t="inlineStr">
+        <is>
+          <t>Anna Öhlund</t>
+        </is>
+      </c>
+      <c r="AY255" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>129310552</v>
+      </c>
+      <c r="B256" t="n">
+        <v>80144</v>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E256" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr"/>
+      <c r="P256" t="inlineStr">
+        <is>
+          <t>Kirkkojärvi, Kirkkojärvi, T lm</t>
+        </is>
+      </c>
+      <c r="Q256" t="n">
+        <v>722793</v>
+      </c>
+      <c r="R256" t="n">
+        <v>7544229</v>
+      </c>
+      <c r="S256" t="n">
+        <v>1</v>
+      </c>
+      <c r="T256" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U256" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V256" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W256" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y256" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AD256" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE256" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG256" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT256" t="inlineStr"/>
+      <c r="AW256" t="inlineStr">
+        <is>
+          <t>Anna Öhlund</t>
+        </is>
+      </c>
+      <c r="AX256" t="inlineStr">
+        <is>
+          <t>Anna Öhlund</t>
+        </is>
+      </c>
+      <c r="AY256" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>129309997</v>
+      </c>
+      <c r="B257" t="n">
+        <v>91825</v>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E257" t="n">
+        <v>658</v>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr"/>
+      <c r="P257" t="inlineStr">
+        <is>
+          <t>Kurravaara berg, Kurravaara berg, T lm</t>
+        </is>
+      </c>
+      <c r="Q257" t="n">
+        <v>723255</v>
+      </c>
+      <c r="R257" t="n">
+        <v>7544298</v>
+      </c>
+      <c r="S257" t="n">
+        <v>2</v>
+      </c>
+      <c r="T257" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U257" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V257" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W257" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y257" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AA257" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AD257" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE257" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG257" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT257" t="inlineStr"/>
+      <c r="AW257" t="inlineStr">
+        <is>
+          <t>Anna Öhlund</t>
+        </is>
+      </c>
+      <c r="AX257" t="inlineStr">
+        <is>
+          <t>Anna Öhlund</t>
+        </is>
+      </c>
+      <c r="AY257" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>129310941</v>
+      </c>
+      <c r="B258" t="n">
+        <v>80144</v>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E258" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr"/>
+      <c r="P258" t="inlineStr">
+        <is>
+          <t>Kirkkojärvi, Kirkkojärvi, T lm</t>
+        </is>
+      </c>
+      <c r="Q258" t="n">
+        <v>722696</v>
+      </c>
+      <c r="R258" t="n">
+        <v>7543922</v>
+      </c>
+      <c r="S258" t="n">
+        <v>1</v>
+      </c>
+      <c r="T258" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U258" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V258" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W258" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y258" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AA258" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AD258" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE258" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG258" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT258" t="inlineStr"/>
+      <c r="AW258" t="inlineStr">
+        <is>
+          <t>Anna Öhlund</t>
+        </is>
+      </c>
+      <c r="AX258" t="inlineStr">
+        <is>
+          <t>Anna Öhlund</t>
+        </is>
+      </c>
+      <c r="AY258" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -25286,7 +25286,7 @@
         <v>128880600</v>
       </c>
       <c r="B223" t="n">
-        <v>92185</v>
+        <v>92187</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -25387,7 +25387,7 @@
         <v>128880607</v>
       </c>
       <c r="B224" t="n">
-        <v>91536</v>
+        <v>91538</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -25484,7 +25484,7 @@
         <v>128880616</v>
       </c>
       <c r="B225" t="n">
-        <v>91801</v>
+        <v>91803</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -25585,7 +25585,7 @@
         <v>128880594</v>
       </c>
       <c r="B226" t="n">
-        <v>91995</v>
+        <v>91997</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -25683,45 +25683,48 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>128880613</v>
+        <v>128880583</v>
       </c>
       <c r="B227" t="n">
-        <v>91558</v>
+        <v>92242</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
+      <c r="J227" t="inlineStr"/>
+      <c r="K227" t="inlineStr"/>
+      <c r="N227" t="inlineStr"/>
       <c r="P227" t="inlineStr">
         <is>
           <t>Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>722995</v>
+        <v>722997</v>
       </c>
       <c r="R227" t="n">
-        <v>7544630</v>
+        <v>7544482</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25762,6 +25765,7 @@
       <c r="AE227" t="b">
         <v>0</v>
       </c>
+      <c r="AF227" t="inlineStr"/>
       <c r="AG227" t="b">
         <v>0</v>
       </c>
@@ -25780,48 +25784,45 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>128880583</v>
+        <v>128880613</v>
       </c>
       <c r="B228" t="n">
-        <v>92240</v>
+        <v>91560</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
-      <c r="J228" t="inlineStr"/>
-      <c r="K228" t="inlineStr"/>
-      <c r="N228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
           <t>Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>722997</v>
+        <v>722995</v>
       </c>
       <c r="R228" t="n">
-        <v>7544482</v>
+        <v>7544630</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25862,7 +25863,6 @@
       <c r="AE228" t="b">
         <v>0</v>
       </c>
-      <c r="AF228" t="inlineStr"/>
       <c r="AG228" t="b">
         <v>0</v>
       </c>
@@ -25884,7 +25884,7 @@
         <v>128880596</v>
       </c>
       <c r="B229" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -25985,7 +25985,7 @@
         <v>128880601</v>
       </c>
       <c r="B230" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -26087,7 +26087,7 @@
         <v>128981901</v>
       </c>
       <c r="B231" t="n">
-        <v>91554</v>
+        <v>91556</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -26184,7 +26184,7 @@
         <v>128981896</v>
       </c>
       <c r="B232" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -26281,7 +26281,7 @@
         <v>128981895</v>
       </c>
       <c r="B233" t="n">
-        <v>91995</v>
+        <v>91997</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -26378,7 +26378,7 @@
         <v>128981900</v>
       </c>
       <c r="B234" t="n">
-        <v>91536</v>
+        <v>91538</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -26475,7 +26475,7 @@
         <v>128981894</v>
       </c>
       <c r="B235" t="n">
-        <v>92240</v>
+        <v>92242</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -26572,7 +26572,7 @@
         <v>129004994</v>
       </c>
       <c r="B236" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -26669,7 +26669,7 @@
         <v>129004991</v>
       </c>
       <c r="B237" t="n">
-        <v>91461</v>
+        <v>91463</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -26766,7 +26766,7 @@
         <v>129005002</v>
       </c>
       <c r="B238" t="n">
-        <v>80145</v>
+        <v>80147</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -26863,7 +26863,7 @@
         <v>129005003</v>
       </c>
       <c r="B239" t="n">
-        <v>80145</v>
+        <v>80147</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -26957,32 +26957,32 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>129005011</v>
+        <v>129005009</v>
       </c>
       <c r="B240" t="n">
-        <v>56906</v>
+        <v>91915</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>102612</v>
+        <v>1505</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kristallticka</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Skeletocutis stellae</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pilát) Jean Keller</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
@@ -26992,10 +26992,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>723208</v>
+        <v>723109</v>
       </c>
       <c r="R240" t="n">
-        <v>7544649</v>
+        <v>7544621</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -27054,32 +27054,32 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>129005009</v>
+        <v>129005011</v>
       </c>
       <c r="B241" t="n">
-        <v>91913</v>
+        <v>56908</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>1505</v>
+        <v>102612</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Kristallticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Skeletocutis stellae</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Pilát) Jean Keller</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
@@ -27089,10 +27089,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>723109</v>
+        <v>723208</v>
       </c>
       <c r="R241" t="n">
-        <v>7544621</v>
+        <v>7544649</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -27154,7 +27154,7 @@
         <v>129015628</v>
       </c>
       <c r="B242" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -27251,7 +27251,7 @@
         <v>129015603</v>
       </c>
       <c r="B243" t="n">
-        <v>80173</v>
+        <v>80175</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -27348,7 +27348,7 @@
         <v>129015623</v>
       </c>
       <c r="B244" t="n">
-        <v>79118</v>
+        <v>79120</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -27445,7 +27445,7 @@
         <v>129016111</v>
       </c>
       <c r="B245" t="n">
-        <v>88622</v>
+        <v>88624</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -27543,7 +27543,7 @@
         <v>129015614</v>
       </c>
       <c r="B246" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -27640,7 +27640,7 @@
         <v>129015607</v>
       </c>
       <c r="B247" t="n">
-        <v>79125</v>
+        <v>79127</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -27737,7 +27737,7 @@
         <v>129015596</v>
       </c>
       <c r="B248" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -27824,7 +27824,7 @@
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka</t>
+          <t>per-erik mukka, Christina Boyd</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
@@ -27834,7 +27834,7 @@
         <v>129051458</v>
       </c>
       <c r="B249" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -27931,7 +27931,7 @@
         <v>129051460</v>
       </c>
       <c r="B250" t="n">
-        <v>80048</v>
+        <v>80050</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -28028,7 +28028,7 @@
         <v>129040495</v>
       </c>
       <c r="B251" t="n">
-        <v>80098</v>
+        <v>80100</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -28129,7 +28129,7 @@
         <v>129051462</v>
       </c>
       <c r="B252" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -28226,7 +28226,7 @@
         <v>129051461</v>
       </c>
       <c r="B253" t="n">
-        <v>57829</v>
+        <v>57831</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -28323,7 +28323,7 @@
         <v>129309942</v>
       </c>
       <c r="B254" t="n">
-        <v>91995</v>
+        <v>91997</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -28429,7 +28429,7 @@
         <v>129310241</v>
       </c>
       <c r="B255" t="n">
-        <v>92240</v>
+        <v>92242</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -28535,7 +28535,7 @@
         <v>129310552</v>
       </c>
       <c r="B256" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -28632,7 +28632,7 @@
         <v>129309997</v>
       </c>
       <c r="B257" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -28729,7 +28729,7 @@
         <v>129310941</v>
       </c>
       <c r="B258" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -26860,32 +26860,32 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>129005003</v>
+        <v>129005009</v>
       </c>
       <c r="B239" t="n">
-        <v>80147</v>
+        <v>91915</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>2081</v>
+        <v>1505</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kristallticka</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Skeletocutis stellae</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Pilát) Jean Keller</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
@@ -26895,10 +26895,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>722853</v>
+        <v>723109</v>
       </c>
       <c r="R239" t="n">
-        <v>7544438</v>
+        <v>7544621</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -26957,32 +26957,32 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>129005009</v>
+        <v>129005003</v>
       </c>
       <c r="B240" t="n">
-        <v>91915</v>
+        <v>80147</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>1505</v>
+        <v>2081</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Kristallticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Skeletocutis stellae</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Pilát) Jean Keller</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
@@ -26992,10 +26992,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>723109</v>
+        <v>722853</v>
       </c>
       <c r="R240" t="n">
-        <v>7544621</v>
+        <v>7544438</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -27824,7 +27824,7 @@
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>per-erik mukka, Christina Boyd</t>
+          <t>Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -26860,32 +26860,32 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>129005009</v>
+        <v>129005011</v>
       </c>
       <c r="B239" t="n">
-        <v>91915</v>
+        <v>56908</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>1505</v>
+        <v>102612</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Kristallticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Skeletocutis stellae</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Pilát) Jean Keller</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
@@ -26895,10 +26895,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>723109</v>
+        <v>723208</v>
       </c>
       <c r="R239" t="n">
-        <v>7544621</v>
+        <v>7544649</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -26957,32 +26957,32 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>129005003</v>
+        <v>129005009</v>
       </c>
       <c r="B240" t="n">
-        <v>80147</v>
+        <v>91915</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>2081</v>
+        <v>1505</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kristallticka</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Skeletocutis stellae</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Pilát) Jean Keller</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
@@ -26992,10 +26992,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>722853</v>
+        <v>723109</v>
       </c>
       <c r="R240" t="n">
-        <v>7544438</v>
+        <v>7544621</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -27054,10 +27054,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>129005011</v>
+        <v>129005003</v>
       </c>
       <c r="B241" t="n">
-        <v>56908</v>
+        <v>80147</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -27065,21 +27065,21 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>102612</v>
+        <v>2081</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
@@ -27089,10 +27089,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>723208</v>
+        <v>722853</v>
       </c>
       <c r="R241" t="n">
-        <v>7544649</v>
+        <v>7544438</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -25286,7 +25286,7 @@
         <v>128880600</v>
       </c>
       <c r="B223" t="n">
-        <v>92187</v>
+        <v>92202</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -25387,7 +25387,7 @@
         <v>128880607</v>
       </c>
       <c r="B224" t="n">
-        <v>91538</v>
+        <v>91536</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -25484,7 +25484,7 @@
         <v>128880616</v>
       </c>
       <c r="B225" t="n">
-        <v>91803</v>
+        <v>91812</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -25585,7 +25585,7 @@
         <v>128880594</v>
       </c>
       <c r="B226" t="n">
-        <v>91997</v>
+        <v>91992</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -25602,12 +25602,12 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -25683,48 +25683,45 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>128880583</v>
+        <v>128880613</v>
       </c>
       <c r="B227" t="n">
-        <v>92242</v>
+        <v>91558</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
-      <c r="J227" t="inlineStr"/>
-      <c r="K227" t="inlineStr"/>
-      <c r="N227" t="inlineStr"/>
       <c r="P227" t="inlineStr">
         <is>
           <t>Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>722997</v>
+        <v>722995</v>
       </c>
       <c r="R227" t="n">
-        <v>7544482</v>
+        <v>7544630</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25765,7 +25762,6 @@
       <c r="AE227" t="b">
         <v>0</v>
       </c>
-      <c r="AF227" t="inlineStr"/>
       <c r="AG227" t="b">
         <v>0</v>
       </c>
@@ -25784,45 +25780,48 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>128880613</v>
+        <v>128880583</v>
       </c>
       <c r="B228" t="n">
-        <v>91560</v>
+        <v>92257</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
+      <c r="J228" t="inlineStr"/>
+      <c r="K228" t="inlineStr"/>
+      <c r="N228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
           <t>Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>722995</v>
+        <v>722997</v>
       </c>
       <c r="R228" t="n">
-        <v>7544630</v>
+        <v>7544482</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25863,6 +25862,7 @@
       <c r="AE228" t="b">
         <v>0</v>
       </c>
+      <c r="AF228" t="inlineStr"/>
       <c r="AG228" t="b">
         <v>0</v>
       </c>
@@ -25884,7 +25884,7 @@
         <v>128880596</v>
       </c>
       <c r="B229" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -26087,7 +26087,7 @@
         <v>128981901</v>
       </c>
       <c r="B231" t="n">
-        <v>91556</v>
+        <v>91554</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -26184,7 +26184,7 @@
         <v>128981896</v>
       </c>
       <c r="B232" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -26281,7 +26281,7 @@
         <v>128981895</v>
       </c>
       <c r="B233" t="n">
-        <v>91997</v>
+        <v>91992</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -26298,12 +26298,12 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
@@ -26378,7 +26378,7 @@
         <v>128981900</v>
       </c>
       <c r="B234" t="n">
-        <v>91538</v>
+        <v>91536</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -26475,7 +26475,7 @@
         <v>128981894</v>
       </c>
       <c r="B235" t="n">
-        <v>92242</v>
+        <v>92257</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -26957,32 +26957,32 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>129005009</v>
+        <v>129005003</v>
       </c>
       <c r="B240" t="n">
-        <v>91915</v>
+        <v>80147</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>1505</v>
+        <v>2081</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Kristallticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Skeletocutis stellae</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Pilát) Jean Keller</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
@@ -26992,10 +26992,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>723109</v>
+        <v>722853</v>
       </c>
       <c r="R240" t="n">
-        <v>7544621</v>
+        <v>7544438</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -27054,32 +27054,32 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>129005003</v>
+        <v>129005009</v>
       </c>
       <c r="B241" t="n">
-        <v>80147</v>
+        <v>91924</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>2081</v>
+        <v>1505</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kristallticka</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Skeletocutis stellae</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Pilát) Jean Keller</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
@@ -27089,10 +27089,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>722853</v>
+        <v>723109</v>
       </c>
       <c r="R241" t="n">
-        <v>7544438</v>
+        <v>7544621</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -27151,32 +27151,32 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>129015628</v>
+        <v>129015603</v>
       </c>
       <c r="B242" t="n">
-        <v>91560</v>
+        <v>80175</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
@@ -27186,10 +27186,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>723040</v>
+        <v>722995</v>
       </c>
       <c r="R242" t="n">
-        <v>7544636</v>
+        <v>7544632</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -27248,32 +27248,32 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>129015603</v>
+        <v>129015628</v>
       </c>
       <c r="B243" t="n">
-        <v>80175</v>
+        <v>91558</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
@@ -27283,10 +27283,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>722995</v>
+        <v>723040</v>
       </c>
       <c r="R243" t="n">
-        <v>7544632</v>
+        <v>7544636</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -27445,7 +27445,7 @@
         <v>129016111</v>
       </c>
       <c r="B245" t="n">
-        <v>88624</v>
+        <v>88625</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -27543,7 +27543,7 @@
         <v>129015614</v>
       </c>
       <c r="B246" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -28323,7 +28323,7 @@
         <v>129309942</v>
       </c>
       <c r="B254" t="n">
-        <v>91997</v>
+        <v>91992</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -28340,12 +28340,12 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -28429,7 +28429,7 @@
         <v>129310241</v>
       </c>
       <c r="B255" t="n">
-        <v>92242</v>
+        <v>92257</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -28632,7 +28632,7 @@
         <v>129309997</v>
       </c>
       <c r="B257" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -25286,7 +25286,7 @@
         <v>128880600</v>
       </c>
       <c r="B223" t="n">
-        <v>92202</v>
+        <v>92203</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -25484,7 +25484,7 @@
         <v>128880616</v>
       </c>
       <c r="B225" t="n">
-        <v>91812</v>
+        <v>91813</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -25585,7 +25585,7 @@
         <v>128880594</v>
       </c>
       <c r="B226" t="n">
-        <v>91992</v>
+        <v>91993</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -25686,7 +25686,7 @@
         <v>128880613</v>
       </c>
       <c r="B227" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -25703,14 +25703,10 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H227" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr"/>
       <c r="I227" t="inlineStr"/>
       <c r="P227" t="inlineStr">
         <is>
@@ -25783,7 +25779,7 @@
         <v>128880583</v>
       </c>
       <c r="B228" t="n">
-        <v>92257</v>
+        <v>92258</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -25884,7 +25880,7 @@
         <v>128880596</v>
       </c>
       <c r="B229" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -26184,7 +26180,7 @@
         <v>128981896</v>
       </c>
       <c r="B232" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -26281,7 +26277,7 @@
         <v>128981895</v>
       </c>
       <c r="B233" t="n">
-        <v>91992</v>
+        <v>91993</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -26475,7 +26471,7 @@
         <v>128981894</v>
       </c>
       <c r="B235" t="n">
-        <v>92257</v>
+        <v>92258</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -26860,32 +26856,32 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>129005011</v>
+        <v>129005009</v>
       </c>
       <c r="B239" t="n">
-        <v>56908</v>
+        <v>91925</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>102612</v>
+        <v>1505</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kristallticka</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Skeletocutis stellae</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pilát) Jean Keller</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
@@ -26895,10 +26891,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>723208</v>
+        <v>723109</v>
       </c>
       <c r="R239" t="n">
-        <v>7544649</v>
+        <v>7544621</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -27054,32 +27050,32 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>129005009</v>
+        <v>129005011</v>
       </c>
       <c r="B241" t="n">
-        <v>91924</v>
+        <v>56908</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>1505</v>
+        <v>102612</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Kristallticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Skeletocutis stellae</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Pilát) Jean Keller</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
@@ -27089,10 +27085,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>723109</v>
+        <v>723208</v>
       </c>
       <c r="R241" t="n">
-        <v>7544621</v>
+        <v>7544649</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -27251,7 +27247,7 @@
         <v>129015628</v>
       </c>
       <c r="B243" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -27268,14 +27264,10 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H243" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr"/>
       <c r="I243" t="inlineStr"/>
       <c r="P243" t="inlineStr">
         <is>
@@ -27543,7 +27535,7 @@
         <v>129015614</v>
       </c>
       <c r="B246" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -28126,32 +28118,32 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>129051462</v>
+        <v>129051461</v>
       </c>
       <c r="B252" t="n">
-        <v>57883</v>
+        <v>57831</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>103022</v>
+        <v>103031</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
@@ -28161,10 +28153,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>723343</v>
+        <v>723207</v>
       </c>
       <c r="R252" t="n">
-        <v>7544271</v>
+        <v>7544292</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -28223,32 +28215,32 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>129051461</v>
+        <v>129051462</v>
       </c>
       <c r="B253" t="n">
-        <v>57831</v>
+        <v>57883</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>103031</v>
+        <v>103022</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -28258,10 +28250,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>723207</v>
+        <v>723343</v>
       </c>
       <c r="R253" t="n">
-        <v>7544292</v>
+        <v>7544271</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -28323,7 +28315,7 @@
         <v>129309942</v>
       </c>
       <c r="B254" t="n">
-        <v>91992</v>
+        <v>91993</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -28429,7 +28421,7 @@
         <v>129310241</v>
       </c>
       <c r="B255" t="n">
-        <v>92257</v>
+        <v>92258</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -28632,7 +28624,7 @@
         <v>129309997</v>
       </c>
       <c r="B257" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -25683,41 +25683,48 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>128880613</v>
+        <v>128880583</v>
       </c>
       <c r="B227" t="n">
-        <v>91560</v>
+        <v>92258</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H227" t="inlineStr"/>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
       <c r="I227" t="inlineStr"/>
+      <c r="J227" t="inlineStr"/>
+      <c r="K227" t="inlineStr"/>
+      <c r="N227" t="inlineStr"/>
       <c r="P227" t="inlineStr">
         <is>
           <t>Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>722995</v>
+        <v>722997</v>
       </c>
       <c r="R227" t="n">
-        <v>7544630</v>
+        <v>7544482</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25758,6 +25765,7 @@
       <c r="AE227" t="b">
         <v>0</v>
       </c>
+      <c r="AF227" t="inlineStr"/>
       <c r="AG227" t="b">
         <v>0</v>
       </c>
@@ -25776,48 +25784,41 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>128880583</v>
+        <v>128880613</v>
       </c>
       <c r="B228" t="n">
-        <v>92258</v>
+        <v>91560</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
-        </is>
-      </c>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr"/>
       <c r="I228" t="inlineStr"/>
-      <c r="J228" t="inlineStr"/>
-      <c r="K228" t="inlineStr"/>
-      <c r="N228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
           <t>Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>722997</v>
+        <v>722995</v>
       </c>
       <c r="R228" t="n">
-        <v>7544482</v>
+        <v>7544630</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25858,7 +25859,6 @@
       <c r="AE228" t="b">
         <v>0</v>
       </c>
-      <c r="AF228" t="inlineStr"/>
       <c r="AG228" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -25286,7 +25286,7 @@
         <v>128880600</v>
       </c>
       <c r="B223" t="n">
-        <v>92203</v>
+        <v>92206</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -25387,7 +25387,7 @@
         <v>128880607</v>
       </c>
       <c r="B224" t="n">
-        <v>91536</v>
+        <v>91539</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -25484,7 +25484,7 @@
         <v>128880616</v>
       </c>
       <c r="B225" t="n">
-        <v>91813</v>
+        <v>91816</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -25585,7 +25585,7 @@
         <v>128880594</v>
       </c>
       <c r="B226" t="n">
-        <v>91993</v>
+        <v>91996</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -25683,48 +25683,41 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>128880583</v>
+        <v>128880613</v>
       </c>
       <c r="B227" t="n">
-        <v>92258</v>
+        <v>91563</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
-        </is>
-      </c>
-      <c r="H227" t="inlineStr">
-        <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr"/>
       <c r="I227" t="inlineStr"/>
-      <c r="J227" t="inlineStr"/>
-      <c r="K227" t="inlineStr"/>
-      <c r="N227" t="inlineStr"/>
       <c r="P227" t="inlineStr">
         <is>
           <t>Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>722997</v>
+        <v>722995</v>
       </c>
       <c r="R227" t="n">
-        <v>7544482</v>
+        <v>7544630</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25765,7 +25758,6 @@
       <c r="AE227" t="b">
         <v>0</v>
       </c>
-      <c r="AF227" t="inlineStr"/>
       <c r="AG227" t="b">
         <v>0</v>
       </c>
@@ -25784,41 +25776,48 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>128880613</v>
+        <v>128880583</v>
       </c>
       <c r="B228" t="n">
-        <v>91560</v>
+        <v>92261</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H228" t="inlineStr"/>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
       <c r="I228" t="inlineStr"/>
+      <c r="J228" t="inlineStr"/>
+      <c r="K228" t="inlineStr"/>
+      <c r="N228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
           <t>Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>722995</v>
+        <v>722997</v>
       </c>
       <c r="R228" t="n">
-        <v>7544630</v>
+        <v>7544482</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25859,6 +25858,7 @@
       <c r="AE228" t="b">
         <v>0</v>
       </c>
+      <c r="AF228" t="inlineStr"/>
       <c r="AG228" t="b">
         <v>0</v>
       </c>
@@ -25880,7 +25880,7 @@
         <v>128880596</v>
       </c>
       <c r="B229" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -25981,7 +25981,7 @@
         <v>128880601</v>
       </c>
       <c r="B230" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -26083,7 +26083,7 @@
         <v>128981901</v>
       </c>
       <c r="B231" t="n">
-        <v>91554</v>
+        <v>91557</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -26180,7 +26180,7 @@
         <v>128981896</v>
       </c>
       <c r="B232" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -26277,7 +26277,7 @@
         <v>128981895</v>
       </c>
       <c r="B233" t="n">
-        <v>91993</v>
+        <v>91996</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -26374,7 +26374,7 @@
         <v>128981900</v>
       </c>
       <c r="B234" t="n">
-        <v>91536</v>
+        <v>91539</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -26471,7 +26471,7 @@
         <v>128981894</v>
       </c>
       <c r="B235" t="n">
-        <v>92258</v>
+        <v>92261</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -26665,7 +26665,7 @@
         <v>129004991</v>
       </c>
       <c r="B237" t="n">
-        <v>91463</v>
+        <v>91466</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -26762,7 +26762,7 @@
         <v>129005002</v>
       </c>
       <c r="B238" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -26859,7 +26859,7 @@
         <v>129005009</v>
       </c>
       <c r="B239" t="n">
-        <v>91925</v>
+        <v>91928</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -26956,7 +26956,7 @@
         <v>129005003</v>
       </c>
       <c r="B240" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -27147,34 +27147,30 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>129015603</v>
+        <v>129015628</v>
       </c>
       <c r="B242" t="n">
-        <v>80175</v>
+        <v>91563</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H242" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr"/>
       <c r="I242" t="inlineStr"/>
       <c r="P242" t="inlineStr">
         <is>
@@ -27182,10 +27178,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>722995</v>
+        <v>723040</v>
       </c>
       <c r="R242" t="n">
-        <v>7544632</v>
+        <v>7544636</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -27244,30 +27240,34 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>129015628</v>
+        <v>129015603</v>
       </c>
       <c r="B243" t="n">
-        <v>91560</v>
+        <v>80177</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H243" t="inlineStr"/>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
       <c r="I243" t="inlineStr"/>
       <c r="P243" t="inlineStr">
         <is>
@@ -27275,10 +27275,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>723040</v>
+        <v>722995</v>
       </c>
       <c r="R243" t="n">
-        <v>7544636</v>
+        <v>7544632</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -27340,7 +27340,7 @@
         <v>129015623</v>
       </c>
       <c r="B244" t="n">
-        <v>79120</v>
+        <v>79122</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -27437,7 +27437,7 @@
         <v>129016111</v>
       </c>
       <c r="B245" t="n">
-        <v>88625</v>
+        <v>88628</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -27535,7 +27535,7 @@
         <v>129015614</v>
       </c>
       <c r="B246" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -27632,7 +27632,7 @@
         <v>129015607</v>
       </c>
       <c r="B247" t="n">
-        <v>79127</v>
+        <v>79129</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -27729,7 +27729,7 @@
         <v>129015596</v>
       </c>
       <c r="B248" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -27923,7 +27923,7 @@
         <v>129051460</v>
       </c>
       <c r="B250" t="n">
-        <v>80050</v>
+        <v>80052</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -28020,7 +28020,7 @@
         <v>129040495</v>
       </c>
       <c r="B251" t="n">
-        <v>80100</v>
+        <v>80102</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -28118,32 +28118,32 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>129051461</v>
+        <v>129051462</v>
       </c>
       <c r="B252" t="n">
-        <v>57831</v>
+        <v>57883</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>103031</v>
+        <v>103022</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
@@ -28153,10 +28153,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>723207</v>
+        <v>723343</v>
       </c>
       <c r="R252" t="n">
-        <v>7544292</v>
+        <v>7544271</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -28215,32 +28215,32 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>129051462</v>
+        <v>129051461</v>
       </c>
       <c r="B253" t="n">
-        <v>57883</v>
+        <v>57831</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>103022</v>
+        <v>103031</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -28250,10 +28250,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>723343</v>
+        <v>723207</v>
       </c>
       <c r="R253" t="n">
-        <v>7544271</v>
+        <v>7544292</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -28315,7 +28315,7 @@
         <v>129309942</v>
       </c>
       <c r="B254" t="n">
-        <v>91993</v>
+        <v>91996</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -28421,7 +28421,7 @@
         <v>129310241</v>
       </c>
       <c r="B255" t="n">
-        <v>92258</v>
+        <v>92261</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -28527,7 +28527,7 @@
         <v>129310552</v>
       </c>
       <c r="B256" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -28624,7 +28624,7 @@
         <v>129309997</v>
       </c>
       <c r="B257" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -28721,7 +28721,7 @@
         <v>129310941</v>
       </c>
       <c r="B258" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -26953,10 +26953,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>129005003</v>
+        <v>129005011</v>
       </c>
       <c r="B240" t="n">
-        <v>80149</v>
+        <v>56908</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -26964,21 +26964,21 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>2081</v>
+        <v>102612</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
@@ -26988,10 +26988,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>722853</v>
+        <v>723208</v>
       </c>
       <c r="R240" t="n">
-        <v>7544438</v>
+        <v>7544649</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -27050,10 +27050,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>129005011</v>
+        <v>129005003</v>
       </c>
       <c r="B241" t="n">
-        <v>56908</v>
+        <v>80149</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -27061,21 +27061,21 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>102612</v>
+        <v>2081</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
@@ -27085,10 +27085,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>723208</v>
+        <v>722853</v>
       </c>
       <c r="R241" t="n">
-        <v>7544649</v>
+        <v>7544438</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -26083,7 +26083,7 @@
         <v>128981901</v>
       </c>
       <c r="B231" t="n">
-        <v>91557</v>
+        <v>91559</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -26180,7 +26180,7 @@
         <v>128981896</v>
       </c>
       <c r="B232" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -26277,7 +26277,7 @@
         <v>128981895</v>
       </c>
       <c r="B233" t="n">
-        <v>91996</v>
+        <v>91998</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -26374,7 +26374,7 @@
         <v>128981900</v>
       </c>
       <c r="B234" t="n">
-        <v>91539</v>
+        <v>91541</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -26471,7 +26471,7 @@
         <v>128981894</v>
       </c>
       <c r="B235" t="n">
-        <v>92261</v>
+        <v>92263</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -26665,7 +26665,7 @@
         <v>129004991</v>
       </c>
       <c r="B237" t="n">
-        <v>91466</v>
+        <v>91468</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -26762,7 +26762,7 @@
         <v>129005002</v>
       </c>
       <c r="B238" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -26856,32 +26856,32 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>129005009</v>
+        <v>129005011</v>
       </c>
       <c r="B239" t="n">
-        <v>91928</v>
+        <v>56908</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>1505</v>
+        <v>102612</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Kristallticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Skeletocutis stellae</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Pilát) Jean Keller</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
@@ -26891,10 +26891,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>723109</v>
+        <v>723208</v>
       </c>
       <c r="R239" t="n">
-        <v>7544621</v>
+        <v>7544649</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -26953,32 +26953,32 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>129005011</v>
+        <v>129005009</v>
       </c>
       <c r="B240" t="n">
-        <v>56908</v>
+        <v>91930</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>102612</v>
+        <v>1505</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kristallticka</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Skeletocutis stellae</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pilát) Jean Keller</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
@@ -26988,10 +26988,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>723208</v>
+        <v>723109</v>
       </c>
       <c r="R240" t="n">
-        <v>7544649</v>
+        <v>7544621</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -27053,7 +27053,7 @@
         <v>129005003</v>
       </c>
       <c r="B241" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -27147,30 +27147,34 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>129015628</v>
+        <v>129015603</v>
       </c>
       <c r="B242" t="n">
-        <v>91563</v>
+        <v>80178</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H242" t="inlineStr"/>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
       <c r="I242" t="inlineStr"/>
       <c r="P242" t="inlineStr">
         <is>
@@ -27178,10 +27182,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>723040</v>
+        <v>722995</v>
       </c>
       <c r="R242" t="n">
-        <v>7544636</v>
+        <v>7544632</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -27240,34 +27244,30 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>129015603</v>
+        <v>129015628</v>
       </c>
       <c r="B243" t="n">
-        <v>80177</v>
+        <v>91565</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H243" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr"/>
       <c r="I243" t="inlineStr"/>
       <c r="P243" t="inlineStr">
         <is>
@@ -27275,10 +27275,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>722995</v>
+        <v>723040</v>
       </c>
       <c r="R243" t="n">
-        <v>7544632</v>
+        <v>7544636</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -27340,7 +27340,7 @@
         <v>129015623</v>
       </c>
       <c r="B244" t="n">
-        <v>79122</v>
+        <v>79123</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -27437,7 +27437,7 @@
         <v>129016111</v>
       </c>
       <c r="B245" t="n">
-        <v>88628</v>
+        <v>88630</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -27535,7 +27535,7 @@
         <v>129015614</v>
       </c>
       <c r="B246" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -27632,7 +27632,7 @@
         <v>129015607</v>
       </c>
       <c r="B247" t="n">
-        <v>79129</v>
+        <v>79130</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -27729,7 +27729,7 @@
         <v>129015596</v>
       </c>
       <c r="B248" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -27923,7 +27923,7 @@
         <v>129051460</v>
       </c>
       <c r="B250" t="n">
-        <v>80052</v>
+        <v>80053</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -28020,7 +28020,7 @@
         <v>129040495</v>
       </c>
       <c r="B251" t="n">
-        <v>80102</v>
+        <v>80103</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -28118,32 +28118,32 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>129051462</v>
+        <v>129051461</v>
       </c>
       <c r="B252" t="n">
-        <v>57883</v>
+        <v>57831</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>103022</v>
+        <v>103031</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
@@ -28153,10 +28153,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>723343</v>
+        <v>723207</v>
       </c>
       <c r="R252" t="n">
-        <v>7544271</v>
+        <v>7544292</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -28215,32 +28215,32 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>129051461</v>
+        <v>129051462</v>
       </c>
       <c r="B253" t="n">
-        <v>57831</v>
+        <v>57883</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>103031</v>
+        <v>103022</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -28250,10 +28250,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>723207</v>
+        <v>723343</v>
       </c>
       <c r="R253" t="n">
-        <v>7544292</v>
+        <v>7544271</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -28315,7 +28315,7 @@
         <v>129309942</v>
       </c>
       <c r="B254" t="n">
-        <v>91996</v>
+        <v>91998</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -28421,7 +28421,7 @@
         <v>129310241</v>
       </c>
       <c r="B255" t="n">
-        <v>92261</v>
+        <v>92263</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -28527,7 +28527,7 @@
         <v>129310552</v>
       </c>
       <c r="B256" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -28624,7 +28624,7 @@
         <v>129309997</v>
       </c>
       <c r="B257" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -28721,7 +28721,7 @@
         <v>129310941</v>
       </c>
       <c r="B258" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -26083,7 +26083,7 @@
         <v>128981901</v>
       </c>
       <c r="B231" t="n">
-        <v>91559</v>
+        <v>91563</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -26180,7 +26180,7 @@
         <v>128981896</v>
       </c>
       <c r="B232" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -26277,7 +26277,7 @@
         <v>128981895</v>
       </c>
       <c r="B233" t="n">
-        <v>91998</v>
+        <v>92002</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -26374,7 +26374,7 @@
         <v>128981900</v>
       </c>
       <c r="B234" t="n">
-        <v>91541</v>
+        <v>91545</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -26471,7 +26471,7 @@
         <v>128981894</v>
       </c>
       <c r="B235" t="n">
-        <v>92263</v>
+        <v>92267</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -26665,7 +26665,7 @@
         <v>129004991</v>
       </c>
       <c r="B237" t="n">
-        <v>91468</v>
+        <v>91472</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -26956,7 +26956,7 @@
         <v>129005009</v>
       </c>
       <c r="B240" t="n">
-        <v>91930</v>
+        <v>91934</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -27147,34 +27147,30 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>129015603</v>
+        <v>129015628</v>
       </c>
       <c r="B242" t="n">
-        <v>80178</v>
+        <v>91569</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H242" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr"/>
       <c r="I242" t="inlineStr"/>
       <c r="P242" t="inlineStr">
         <is>
@@ -27182,10 +27178,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>722995</v>
+        <v>723040</v>
       </c>
       <c r="R242" t="n">
-        <v>7544632</v>
+        <v>7544636</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -27244,30 +27240,34 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>129015628</v>
+        <v>129015603</v>
       </c>
       <c r="B243" t="n">
-        <v>91565</v>
+        <v>80178</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H243" t="inlineStr"/>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
       <c r="I243" t="inlineStr"/>
       <c r="P243" t="inlineStr">
         <is>
@@ -27275,10 +27275,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>723040</v>
+        <v>722995</v>
       </c>
       <c r="R243" t="n">
-        <v>7544636</v>
+        <v>7544632</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -27437,7 +27437,7 @@
         <v>129016111</v>
       </c>
       <c r="B245" t="n">
-        <v>88630</v>
+        <v>88634</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -27535,7 +27535,7 @@
         <v>129015614</v>
       </c>
       <c r="B246" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -28118,32 +28118,32 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>129051461</v>
+        <v>129051462</v>
       </c>
       <c r="B252" t="n">
-        <v>57831</v>
+        <v>57883</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>103031</v>
+        <v>103022</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
@@ -28153,10 +28153,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>723207</v>
+        <v>723343</v>
       </c>
       <c r="R252" t="n">
-        <v>7544292</v>
+        <v>7544271</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -28215,32 +28215,32 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>129051462</v>
+        <v>129051461</v>
       </c>
       <c r="B253" t="n">
-        <v>57883</v>
+        <v>57831</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>103022</v>
+        <v>103031</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -28250,10 +28250,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>723343</v>
+        <v>723207</v>
       </c>
       <c r="R253" t="n">
-        <v>7544271</v>
+        <v>7544292</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -28315,7 +28315,7 @@
         <v>129309942</v>
       </c>
       <c r="B254" t="n">
-        <v>91998</v>
+        <v>92002</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -28421,7 +28421,7 @@
         <v>129310241</v>
       </c>
       <c r="B255" t="n">
-        <v>92263</v>
+        <v>92267</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -28624,7 +28624,7 @@
         <v>129309997</v>
       </c>
       <c r="B257" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -26083,7 +26083,7 @@
         <v>128981901</v>
       </c>
       <c r="B231" t="n">
-        <v>91563</v>
+        <v>91564</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -26180,7 +26180,7 @@
         <v>128981896</v>
       </c>
       <c r="B232" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -26277,7 +26277,7 @@
         <v>128981895</v>
       </c>
       <c r="B233" t="n">
-        <v>92002</v>
+        <v>92003</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -26374,7 +26374,7 @@
         <v>128981900</v>
       </c>
       <c r="B234" t="n">
-        <v>91545</v>
+        <v>91546</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -26471,7 +26471,7 @@
         <v>128981894</v>
       </c>
       <c r="B235" t="n">
-        <v>92267</v>
+        <v>92268</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -26665,7 +26665,7 @@
         <v>129004991</v>
       </c>
       <c r="B237" t="n">
-        <v>91472</v>
+        <v>91473</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -26856,32 +26856,32 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>129005011</v>
+        <v>129005009</v>
       </c>
       <c r="B239" t="n">
-        <v>56908</v>
+        <v>91935</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>102612</v>
+        <v>1505</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kristallticka</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Skeletocutis stellae</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pilát) Jean Keller</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
@@ -26891,10 +26891,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>723208</v>
+        <v>723109</v>
       </c>
       <c r="R239" t="n">
-        <v>7544649</v>
+        <v>7544621</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -26953,32 +26953,32 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>129005009</v>
+        <v>129005003</v>
       </c>
       <c r="B240" t="n">
-        <v>91934</v>
+        <v>80150</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>1505</v>
+        <v>2081</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Kristallticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Skeletocutis stellae</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Pilát) Jean Keller</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
@@ -26988,10 +26988,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>723109</v>
+        <v>722853</v>
       </c>
       <c r="R240" t="n">
-        <v>7544621</v>
+        <v>7544438</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -27050,10 +27050,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>129005003</v>
+        <v>129005011</v>
       </c>
       <c r="B241" t="n">
-        <v>80150</v>
+        <v>56908</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -27061,21 +27061,21 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>2081</v>
+        <v>102612</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
@@ -27085,10 +27085,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>722853</v>
+        <v>723208</v>
       </c>
       <c r="R241" t="n">
-        <v>7544438</v>
+        <v>7544649</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -27150,7 +27150,7 @@
         <v>129015628</v>
       </c>
       <c r="B242" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -27437,7 +27437,7 @@
         <v>129016111</v>
       </c>
       <c r="B245" t="n">
-        <v>88634</v>
+        <v>88635</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -27535,7 +27535,7 @@
         <v>129015614</v>
       </c>
       <c r="B246" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -28118,32 +28118,32 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>129051462</v>
+        <v>129051461</v>
       </c>
       <c r="B252" t="n">
-        <v>57883</v>
+        <v>57831</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>103022</v>
+        <v>103031</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
@@ -28153,10 +28153,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>723343</v>
+        <v>723207</v>
       </c>
       <c r="R252" t="n">
-        <v>7544271</v>
+        <v>7544292</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -28215,32 +28215,32 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>129051461</v>
+        <v>129051462</v>
       </c>
       <c r="B253" t="n">
-        <v>57831</v>
+        <v>57883</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>103031</v>
+        <v>103022</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -28250,10 +28250,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>723207</v>
+        <v>723343</v>
       </c>
       <c r="R253" t="n">
-        <v>7544292</v>
+        <v>7544271</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -28315,7 +28315,7 @@
         <v>129309942</v>
       </c>
       <c r="B254" t="n">
-        <v>92002</v>
+        <v>92003</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -28421,7 +28421,7 @@
         <v>129310241</v>
       </c>
       <c r="B255" t="n">
-        <v>92267</v>
+        <v>92268</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -28624,7 +28624,7 @@
         <v>129309997</v>
       </c>
       <c r="B257" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -26856,32 +26856,32 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>129005009</v>
+        <v>129005003</v>
       </c>
       <c r="B239" t="n">
-        <v>91935</v>
+        <v>80150</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>1505</v>
+        <v>2081</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Kristallticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Skeletocutis stellae</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Pilát) Jean Keller</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
@@ -26891,10 +26891,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>723109</v>
+        <v>722853</v>
       </c>
       <c r="R239" t="n">
-        <v>7544621</v>
+        <v>7544438</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -26953,32 +26953,32 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>129005003</v>
+        <v>129005009</v>
       </c>
       <c r="B240" t="n">
-        <v>80150</v>
+        <v>91935</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>2081</v>
+        <v>1505</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kristallticka</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Skeletocutis stellae</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Pilát) Jean Keller</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
@@ -26988,10 +26988,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>722853</v>
+        <v>723109</v>
       </c>
       <c r="R240" t="n">
-        <v>7544438</v>
+        <v>7544621</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -28118,32 +28118,32 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>129051461</v>
+        <v>129051462</v>
       </c>
       <c r="B252" t="n">
-        <v>57831</v>
+        <v>57883</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>103031</v>
+        <v>103022</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
@@ -28153,10 +28153,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>723207</v>
+        <v>723343</v>
       </c>
       <c r="R252" t="n">
-        <v>7544292</v>
+        <v>7544271</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -28215,32 +28215,32 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>129051462</v>
+        <v>129051461</v>
       </c>
       <c r="B253" t="n">
-        <v>57883</v>
+        <v>57831</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>103022</v>
+        <v>103031</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -28250,10 +28250,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>723343</v>
+        <v>723207</v>
       </c>
       <c r="R253" t="n">
-        <v>7544271</v>
+        <v>7544292</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -26665,7 +26665,7 @@
         <v>129004991</v>
       </c>
       <c r="B237" t="n">
-        <v>91473</v>
+        <v>91476</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -26856,32 +26856,32 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>129005003</v>
+        <v>129005009</v>
       </c>
       <c r="B239" t="n">
-        <v>80150</v>
+        <v>91938</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>2081</v>
+        <v>1505</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kristallticka</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Skeletocutis stellae</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Pilát) Jean Keller</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
@@ -26891,10 +26891,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>722853</v>
+        <v>723109</v>
       </c>
       <c r="R239" t="n">
-        <v>7544438</v>
+        <v>7544621</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -26953,32 +26953,32 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>129005009</v>
+        <v>129005003</v>
       </c>
       <c r="B240" t="n">
-        <v>91935</v>
+        <v>80150</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>1505</v>
+        <v>2081</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Kristallticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Skeletocutis stellae</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Pilát) Jean Keller</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
@@ -26988,10 +26988,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>723109</v>
+        <v>722853</v>
       </c>
       <c r="R240" t="n">
-        <v>7544621</v>
+        <v>7544438</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -27150,7 +27150,7 @@
         <v>129015628</v>
       </c>
       <c r="B242" t="n">
-        <v>91570</v>
+        <v>91573</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -27535,7 +27535,7 @@
         <v>129015614</v>
       </c>
       <c r="B246" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -28315,7 +28315,7 @@
         <v>129309942</v>
       </c>
       <c r="B254" t="n">
-        <v>92003</v>
+        <v>92006</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -28421,7 +28421,7 @@
         <v>129310241</v>
       </c>
       <c r="B255" t="n">
-        <v>92268</v>
+        <v>92271</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -28624,7 +28624,7 @@
         <v>129309997</v>
       </c>
       <c r="B257" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -28118,32 +28118,32 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>129051462</v>
+        <v>129051461</v>
       </c>
       <c r="B252" t="n">
-        <v>57883</v>
+        <v>57831</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>103022</v>
+        <v>103031</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
@@ -28153,10 +28153,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>723343</v>
+        <v>723207</v>
       </c>
       <c r="R252" t="n">
-        <v>7544271</v>
+        <v>7544292</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -28215,32 +28215,32 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>129051461</v>
+        <v>129051462</v>
       </c>
       <c r="B253" t="n">
-        <v>57831</v>
+        <v>57883</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>103031</v>
+        <v>103022</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -28250,10 +28250,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>723207</v>
+        <v>723343</v>
       </c>
       <c r="R253" t="n">
-        <v>7544292</v>
+        <v>7544271</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -28315,7 +28315,7 @@
         <v>129309942</v>
       </c>
       <c r="B254" t="n">
-        <v>92006</v>
+        <v>92034</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -28421,7 +28421,7 @@
         <v>129310241</v>
       </c>
       <c r="B255" t="n">
-        <v>92271</v>
+        <v>92299</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -28527,7 +28527,7 @@
         <v>129310552</v>
       </c>
       <c r="B256" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -28624,7 +28624,7 @@
         <v>129309997</v>
       </c>
       <c r="B257" t="n">
-        <v>91851</v>
+        <v>91879</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -28721,7 +28721,7 @@
         <v>129310941</v>
       </c>
       <c r="B258" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -28315,7 +28315,7 @@
         <v>129309942</v>
       </c>
       <c r="B254" t="n">
-        <v>92034</v>
+        <v>92040</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -28421,7 +28421,7 @@
         <v>129310241</v>
       </c>
       <c r="B255" t="n">
-        <v>92299</v>
+        <v>92305</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -28527,7 +28527,7 @@
         <v>129310552</v>
       </c>
       <c r="B256" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -28624,7 +28624,7 @@
         <v>129309997</v>
       </c>
       <c r="B257" t="n">
-        <v>91879</v>
+        <v>91885</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -28721,7 +28721,7 @@
         <v>129310941</v>
       </c>
       <c r="B258" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -28315,7 +28315,7 @@
         <v>129309942</v>
       </c>
       <c r="B254" t="n">
-        <v>92040</v>
+        <v>92041</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -28421,7 +28421,7 @@
         <v>129310241</v>
       </c>
       <c r="B255" t="n">
-        <v>92305</v>
+        <v>92306</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -28527,7 +28527,7 @@
         <v>129310552</v>
       </c>
       <c r="B256" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -28624,7 +28624,7 @@
         <v>129309997</v>
       </c>
       <c r="B257" t="n">
-        <v>91885</v>
+        <v>91886</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -28721,7 +28721,7 @@
         <v>129310941</v>
       </c>
       <c r="B258" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -28315,7 +28315,7 @@
         <v>129309942</v>
       </c>
       <c r="B254" t="n">
-        <v>92041</v>
+        <v>92046</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -28421,7 +28421,7 @@
         <v>129310241</v>
       </c>
       <c r="B255" t="n">
-        <v>92306</v>
+        <v>92311</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -28527,7 +28527,7 @@
         <v>129310552</v>
       </c>
       <c r="B256" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -28624,7 +28624,7 @@
         <v>129309997</v>
       </c>
       <c r="B257" t="n">
-        <v>91886</v>
+        <v>91891</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -28721,7 +28721,7 @@
         <v>129310941</v>
       </c>
       <c r="B258" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -28915,17 +28915,17 @@
       </c>
       <c r="AX259" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka, Stefan Andersson, Sara Sand</t>
+          <t>Christina Boyd, per-erik mukka, Sara Sand, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>134008031</v>
+        <v>133982087</v>
       </c>
       <c r="B260" t="n">
-        <v>80475</v>
+        <v>78762</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -28933,37 +28933,34 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>2081</v>
+        <v>6437</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
-      <c r="J260" t="inlineStr"/>
-      <c r="K260" t="inlineStr"/>
-      <c r="N260" t="inlineStr"/>
       <c r="P260" t="inlineStr">
         <is>
-          <t>Kurravaara, T lm</t>
+          <t>Kurravaara, Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>723403</v>
+        <v>723479</v>
       </c>
       <c r="R260" t="n">
-        <v>7544262</v>
+        <v>7544244</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -28995,7 +28992,7 @@
       </c>
       <c r="Z260" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA260" t="inlineStr">
@@ -29005,7 +29002,7 @@
       </c>
       <c r="AB260" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD260" t="b">
@@ -29014,29 +29011,28 @@
       <c r="AE260" t="b">
         <v>0</v>
       </c>
-      <c r="AF260" t="inlineStr"/>
       <c r="AG260" t="b">
         <v>0</v>
       </c>
       <c r="AT260" t="inlineStr"/>
       <c r="AW260" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>Sara Sand, Christina Boyd, per-erik mukka</t>
+          <t>Christina Boyd, per-erik mukka, Sara Sand, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>133982087</v>
+        <v>134008031</v>
       </c>
       <c r="B261" t="n">
-        <v>78762</v>
+        <v>80475</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -29044,34 +29040,37 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>6437</v>
+        <v>2081</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
+      <c r="J261" t="inlineStr"/>
+      <c r="K261" t="inlineStr"/>
+      <c r="N261" t="inlineStr"/>
       <c r="P261" t="inlineStr">
         <is>
-          <t>Kurravaara, Kurravaara, T lm</t>
+          <t>Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>723479</v>
+        <v>723403</v>
       </c>
       <c r="R261" t="n">
-        <v>7544244</v>
+        <v>7544262</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -29103,7 +29102,7 @@
       </c>
       <c r="Z261" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA261" t="inlineStr">
@@ -29113,7 +29112,7 @@
       </c>
       <c r="AB261" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD261" t="b">
@@ -29122,18 +29121,19 @@
       <c r="AE261" t="b">
         <v>0</v>
       </c>
+      <c r="AF261" t="inlineStr"/>
       <c r="AG261" t="b">
         <v>0</v>
       </c>
       <c r="AT261" t="inlineStr"/>
       <c r="AW261" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX261" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka, Stefan Andersson, Sara Sand</t>
+          <t>Sara Sand, Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY261" t="inlineStr"/>
@@ -29362,33 +29362,42 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>134007964</v>
+        <v>134006872</v>
       </c>
       <c r="B264" t="n">
-        <v>91980</v>
+        <v>58658</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E264" t="n">
-        <v>5432</v>
+        <v>103044</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H264" t="inlineStr"/>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I264" t="inlineStr"/>
-      <c r="J264" t="inlineStr"/>
       <c r="K264" t="inlineStr"/>
+      <c r="L264" t="inlineStr"/>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N264" t="inlineStr"/>
       <c r="P264" t="inlineStr">
         <is>
@@ -29396,13 +29405,13 @@
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>723274</v>
+        <v>723154</v>
       </c>
       <c r="R264" t="n">
-        <v>7544307</v>
+        <v>7544271</v>
       </c>
       <c r="S264" t="n">
-        <v>10</v>
+        <v>300</v>
       </c>
       <c r="T264" t="inlineStr">
         <is>
@@ -29450,7 +29459,6 @@
       <c r="AE264" t="b">
         <v>0</v>
       </c>
-      <c r="AF264" t="inlineStr"/>
       <c r="AG264" t="b">
         <v>0</v>
       </c>
@@ -29462,49 +29470,40 @@
       </c>
       <c r="AX264" t="inlineStr">
         <is>
-          <t>Sara Sand, Christina Boyd, per-erik mukka</t>
+          <t>Sara Sand, per-erik mukka, Christina Boyd</t>
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>134006872</v>
+        <v>134007964</v>
       </c>
       <c r="B265" t="n">
-        <v>58658</v>
+        <v>91980</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E265" t="n">
-        <v>103044</v>
+        <v>5432</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
-        </is>
-      </c>
-      <c r="H265" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr"/>
       <c r="I265" t="inlineStr"/>
+      <c r="J265" t="inlineStr"/>
       <c r="K265" t="inlineStr"/>
-      <c r="L265" t="inlineStr"/>
-      <c r="M265" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N265" t="inlineStr"/>
       <c r="P265" t="inlineStr">
         <is>
@@ -29512,13 +29511,13 @@
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>723154</v>
+        <v>723274</v>
       </c>
       <c r="R265" t="n">
-        <v>7544271</v>
+        <v>7544307</v>
       </c>
       <c r="S265" t="n">
-        <v>300</v>
+        <v>10</v>
       </c>
       <c r="T265" t="inlineStr">
         <is>
@@ -29566,6 +29565,7 @@
       <c r="AE265" t="b">
         <v>0</v>
       </c>
+      <c r="AF265" t="inlineStr"/>
       <c r="AG265" t="b">
         <v>0</v>
       </c>
@@ -29577,39 +29577,39 @@
       </c>
       <c r="AX265" t="inlineStr">
         <is>
-          <t>Sara Sand, per-erik mukka, Christina Boyd</t>
+          <t>Sara Sand, Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>133993902</v>
+        <v>133990618</v>
       </c>
       <c r="B266" t="n">
-        <v>79438</v>
+        <v>80418</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E266" t="n">
-        <v>864</v>
+        <v>1152</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Grynlav</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pannaria conoplea</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Bory</t>
         </is>
       </c>
       <c r="I266" t="inlineStr"/>
@@ -29619,13 +29619,13 @@
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>722903</v>
+        <v>722975</v>
       </c>
       <c r="R266" t="n">
-        <v>7544442</v>
+        <v>7544331</v>
       </c>
       <c r="S266" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T266" t="inlineStr">
         <is>
@@ -29654,7 +29654,7 @@
       </c>
       <c r="Z266" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA266" t="inlineStr">
@@ -29664,7 +29664,7 @@
       </c>
       <c r="AB266" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD266" t="b">
@@ -29691,32 +29691,32 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>133990618</v>
+        <v>133993902</v>
       </c>
       <c r="B267" t="n">
-        <v>80418</v>
+        <v>79438</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>1152</v>
+        <v>864</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Grynlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Pannaria conoplea</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>(Ach.) Bory</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
@@ -29726,13 +29726,13 @@
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>722975</v>
+        <v>722903</v>
       </c>
       <c r="R267" t="n">
-        <v>7544331</v>
+        <v>7544442</v>
       </c>
       <c r="S267" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T267" t="inlineStr">
         <is>
@@ -29761,7 +29761,7 @@
       </c>
       <c r="Z267" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA267" t="inlineStr">
@@ -29771,7 +29771,7 @@
       </c>
       <c r="AB267" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD267" t="b">
@@ -30020,48 +30020,45 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>134008220</v>
+        <v>133982984</v>
       </c>
       <c r="B270" t="n">
-        <v>80486</v>
+        <v>91956</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E270" t="n">
-        <v>6464</v>
+        <v>1108</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I270" t="inlineStr"/>
-      <c r="J270" t="inlineStr"/>
-      <c r="K270" t="inlineStr"/>
-      <c r="N270" t="inlineStr"/>
       <c r="P270" t="inlineStr">
         <is>
-          <t>Kurravaara, T lm</t>
+          <t>Kurravaara, Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>723686</v>
+        <v>723301</v>
       </c>
       <c r="R270" t="n">
-        <v>7544123</v>
+        <v>7544291</v>
       </c>
       <c r="S270" t="n">
         <v>10</v>
@@ -30093,7 +30090,7 @@
       </c>
       <c r="Z270" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA270" t="inlineStr">
@@ -30103,7 +30100,7 @@
       </c>
       <c r="AB270" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD270" t="b">
@@ -30112,64 +30109,66 @@
       <c r="AE270" t="b">
         <v>0</v>
       </c>
-      <c r="AF270" t="inlineStr"/>
       <c r="AG270" t="b">
         <v>0</v>
       </c>
       <c r="AT270" t="inlineStr"/>
       <c r="AW270" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX270" t="inlineStr">
         <is>
-          <t>Sara Sand, Christina Boyd, per-erik mukka</t>
+          <t>per-erik mukka, Sara Sand, Christina Boyd</t>
         </is>
       </c>
       <c r="AY270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>133982984</v>
+        <v>134008220</v>
       </c>
       <c r="B271" t="n">
-        <v>91956</v>
+        <v>80486</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E271" t="n">
-        <v>1108</v>
+        <v>6464</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I271" t="inlineStr"/>
+      <c r="J271" t="inlineStr"/>
+      <c r="K271" t="inlineStr"/>
+      <c r="N271" t="inlineStr"/>
       <c r="P271" t="inlineStr">
         <is>
-          <t>Kurravaara, Kurravaara, T lm</t>
+          <t>Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>723301</v>
+        <v>723686</v>
       </c>
       <c r="R271" t="n">
-        <v>7544291</v>
+        <v>7544123</v>
       </c>
       <c r="S271" t="n">
         <v>10</v>
@@ -30201,7 +30200,7 @@
       </c>
       <c r="Z271" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA271" t="inlineStr">
@@ -30211,7 +30210,7 @@
       </c>
       <c r="AB271" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD271" t="b">
@@ -30220,66 +30219,75 @@
       <c r="AE271" t="b">
         <v>0</v>
       </c>
+      <c r="AF271" t="inlineStr"/>
       <c r="AG271" t="b">
         <v>0</v>
       </c>
       <c r="AT271" t="inlineStr"/>
       <c r="AW271" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX271" t="inlineStr">
         <is>
-          <t>per-erik mukka, Christina Boyd, Sara Sand</t>
+          <t>Sara Sand, Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>133995809</v>
+        <v>134006977</v>
       </c>
       <c r="B272" t="n">
-        <v>80474</v>
+        <v>58519</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E272" t="n">
-        <v>6458</v>
+        <v>102990</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I272" t="inlineStr"/>
+      <c r="K272" t="inlineStr"/>
+      <c r="L272" t="inlineStr"/>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N272" t="inlineStr"/>
       <c r="P272" t="inlineStr">
         <is>
-          <t>kurravaara, kurravaara, T lm</t>
+          <t>Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>723358</v>
+        <v>723154</v>
       </c>
       <c r="R272" t="n">
-        <v>7544205</v>
+        <v>7544271</v>
       </c>
       <c r="S272" t="n">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="T272" t="inlineStr">
         <is>
@@ -30308,7 +30316,7 @@
       </c>
       <c r="Z272" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA272" t="inlineStr">
@@ -30318,7 +30326,7 @@
       </c>
       <c r="AB272" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD272" t="b">
@@ -30333,68 +30341,60 @@
       <c r="AT272" t="inlineStr"/>
       <c r="AW272" t="inlineStr">
         <is>
-          <t>Stefan Andersson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX272" t="inlineStr">
         <is>
-          <t>Stefan Andersson, Christina Boyd, per-erik mukka</t>
+          <t>Sara Sand, per-erik mukka, Christina Boyd</t>
         </is>
       </c>
       <c r="AY272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>134006977</v>
+        <v>133995809</v>
       </c>
       <c r="B273" t="n">
-        <v>58519</v>
+        <v>80474</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>102990</v>
+        <v>6458</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I273" t="inlineStr"/>
-      <c r="K273" t="inlineStr"/>
-      <c r="L273" t="inlineStr"/>
-      <c r="M273" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N273" t="inlineStr"/>
       <c r="P273" t="inlineStr">
         <is>
-          <t>Kurravaara, T lm</t>
+          <t>kurravaara, kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>723154</v>
+        <v>723358</v>
       </c>
       <c r="R273" t="n">
-        <v>7544271</v>
+        <v>7544205</v>
       </c>
       <c r="S273" t="n">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="T273" t="inlineStr">
         <is>
@@ -30423,7 +30423,7 @@
       </c>
       <c r="Z273" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA273" t="inlineStr">
@@ -30433,7 +30433,7 @@
       </c>
       <c r="AB273" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD273" t="b">
@@ -30448,12 +30448,12 @@
       <c r="AT273" t="inlineStr"/>
       <c r="AW273" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Stefan Andersson</t>
         </is>
       </c>
       <c r="AX273" t="inlineStr">
         <is>
-          <t>Sara Sand, per-erik mukka, Christina Boyd</t>
+          <t>Stefan Andersson, Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY273" t="inlineStr"/>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -28818,7 +28818,7 @@
         <v>133982077</v>
       </c>
       <c r="B259" t="n">
-        <v>79978</v>
+        <v>79985</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -28915,7 +28915,7 @@
       </c>
       <c r="AX259" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka, Sara Sand, Stefan Andersson</t>
+          <t>Christina Boyd, per-erik mukka, Stefan Andersson, Sara Sand</t>
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>
@@ -28925,7 +28925,7 @@
         <v>133982087</v>
       </c>
       <c r="B260" t="n">
-        <v>78762</v>
+        <v>78769</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -29022,7 +29022,7 @@
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka, Sara Sand, Stefan Andersson</t>
+          <t>Christina Boyd, per-erik mukka, Stefan Andersson, Sara Sand</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
@@ -29032,7 +29032,7 @@
         <v>134008031</v>
       </c>
       <c r="B261" t="n">
-        <v>80475</v>
+        <v>80482</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -29143,7 +29143,7 @@
         <v>134007979</v>
       </c>
       <c r="B262" t="n">
-        <v>80479</v>
+        <v>80486</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -29254,7 +29254,7 @@
         <v>134008216</v>
       </c>
       <c r="B263" t="n">
-        <v>80479</v>
+        <v>80486</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -29362,42 +29362,33 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>134006872</v>
+        <v>134007964</v>
       </c>
       <c r="B264" t="n">
-        <v>58658</v>
+        <v>91987</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E264" t="n">
-        <v>103044</v>
+        <v>5432</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
-        </is>
-      </c>
-      <c r="H264" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr"/>
       <c r="I264" t="inlineStr"/>
+      <c r="J264" t="inlineStr"/>
       <c r="K264" t="inlineStr"/>
-      <c r="L264" t="inlineStr"/>
-      <c r="M264" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N264" t="inlineStr"/>
       <c r="P264" t="inlineStr">
         <is>
@@ -29405,13 +29396,13 @@
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>723154</v>
+        <v>723274</v>
       </c>
       <c r="R264" t="n">
-        <v>7544271</v>
+        <v>7544307</v>
       </c>
       <c r="S264" t="n">
-        <v>300</v>
+        <v>10</v>
       </c>
       <c r="T264" t="inlineStr">
         <is>
@@ -29459,6 +29450,7 @@
       <c r="AE264" t="b">
         <v>0</v>
       </c>
+      <c r="AF264" t="inlineStr"/>
       <c r="AG264" t="b">
         <v>0</v>
       </c>
@@ -29470,40 +29462,49 @@
       </c>
       <c r="AX264" t="inlineStr">
         <is>
-          <t>Sara Sand, per-erik mukka, Christina Boyd</t>
+          <t>Sara Sand, Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>134007964</v>
+        <v>134006872</v>
       </c>
       <c r="B265" t="n">
-        <v>91980</v>
+        <v>58658</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E265" t="n">
-        <v>5432</v>
+        <v>103044</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H265" t="inlineStr"/>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I265" t="inlineStr"/>
-      <c r="J265" t="inlineStr"/>
       <c r="K265" t="inlineStr"/>
+      <c r="L265" t="inlineStr"/>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N265" t="inlineStr"/>
       <c r="P265" t="inlineStr">
         <is>
@@ -29511,13 +29512,13 @@
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>723274</v>
+        <v>723154</v>
       </c>
       <c r="R265" t="n">
-        <v>7544307</v>
+        <v>7544271</v>
       </c>
       <c r="S265" t="n">
-        <v>10</v>
+        <v>300</v>
       </c>
       <c r="T265" t="inlineStr">
         <is>
@@ -29565,7 +29566,6 @@
       <c r="AE265" t="b">
         <v>0</v>
       </c>
-      <c r="AF265" t="inlineStr"/>
       <c r="AG265" t="b">
         <v>0</v>
       </c>
@@ -29577,7 +29577,7 @@
       </c>
       <c r="AX265" t="inlineStr">
         <is>
-          <t>Sara Sand, Christina Boyd, per-erik mukka</t>
+          <t>Sara Sand, per-erik mukka, Christina Boyd</t>
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>
@@ -29587,7 +29587,7 @@
         <v>133990618</v>
       </c>
       <c r="B266" t="n">
-        <v>80418</v>
+        <v>80425</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -29694,7 +29694,7 @@
         <v>133993902</v>
       </c>
       <c r="B267" t="n">
-        <v>79438</v>
+        <v>79445</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -29801,7 +29801,7 @@
         <v>134007962</v>
       </c>
       <c r="B268" t="n">
-        <v>91974</v>
+        <v>91981</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -29912,7 +29912,7 @@
         <v>134008021</v>
       </c>
       <c r="B269" t="n">
-        <v>78762</v>
+        <v>78769</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -30020,45 +30020,48 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>133982984</v>
+        <v>134008220</v>
       </c>
       <c r="B270" t="n">
-        <v>91956</v>
+        <v>80493</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E270" t="n">
-        <v>1108</v>
+        <v>6464</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I270" t="inlineStr"/>
+      <c r="J270" t="inlineStr"/>
+      <c r="K270" t="inlineStr"/>
+      <c r="N270" t="inlineStr"/>
       <c r="P270" t="inlineStr">
         <is>
-          <t>Kurravaara, Kurravaara, T lm</t>
+          <t>Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>723301</v>
+        <v>723686</v>
       </c>
       <c r="R270" t="n">
-        <v>7544291</v>
+        <v>7544123</v>
       </c>
       <c r="S270" t="n">
         <v>10</v>
@@ -30090,7 +30093,7 @@
       </c>
       <c r="Z270" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA270" t="inlineStr">
@@ -30100,7 +30103,7 @@
       </c>
       <c r="AB270" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD270" t="b">
@@ -30109,66 +30112,64 @@
       <c r="AE270" t="b">
         <v>0</v>
       </c>
+      <c r="AF270" t="inlineStr"/>
       <c r="AG270" t="b">
         <v>0</v>
       </c>
       <c r="AT270" t="inlineStr"/>
       <c r="AW270" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX270" t="inlineStr">
         <is>
-          <t>per-erik mukka, Sara Sand, Christina Boyd</t>
+          <t>Sara Sand, Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>134008220</v>
+        <v>133982984</v>
       </c>
       <c r="B271" t="n">
-        <v>80486</v>
+        <v>91963</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E271" t="n">
-        <v>6464</v>
+        <v>1108</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I271" t="inlineStr"/>
-      <c r="J271" t="inlineStr"/>
-      <c r="K271" t="inlineStr"/>
-      <c r="N271" t="inlineStr"/>
       <c r="P271" t="inlineStr">
         <is>
-          <t>Kurravaara, T lm</t>
+          <t>Kurravaara, Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>723686</v>
+        <v>723301</v>
       </c>
       <c r="R271" t="n">
-        <v>7544123</v>
+        <v>7544291</v>
       </c>
       <c r="S271" t="n">
         <v>10</v>
@@ -30200,7 +30201,7 @@
       </c>
       <c r="Z271" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA271" t="inlineStr">
@@ -30210,7 +30211,7 @@
       </c>
       <c r="AB271" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD271" t="b">
@@ -30219,75 +30220,66 @@
       <c r="AE271" t="b">
         <v>0</v>
       </c>
-      <c r="AF271" t="inlineStr"/>
       <c r="AG271" t="b">
         <v>0</v>
       </c>
       <c r="AT271" t="inlineStr"/>
       <c r="AW271" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX271" t="inlineStr">
         <is>
-          <t>Sara Sand, Christina Boyd, per-erik mukka</t>
+          <t>per-erik mukka, Christina Boyd, Sara Sand</t>
         </is>
       </c>
       <c r="AY271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>134006977</v>
+        <v>133995809</v>
       </c>
       <c r="B272" t="n">
-        <v>58519</v>
+        <v>80481</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E272" t="n">
-        <v>102990</v>
+        <v>6458</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I272" t="inlineStr"/>
-      <c r="K272" t="inlineStr"/>
-      <c r="L272" t="inlineStr"/>
-      <c r="M272" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N272" t="inlineStr"/>
       <c r="P272" t="inlineStr">
         <is>
-          <t>Kurravaara, T lm</t>
+          <t>kurravaara, kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>723154</v>
+        <v>723358</v>
       </c>
       <c r="R272" t="n">
-        <v>7544271</v>
+        <v>7544205</v>
       </c>
       <c r="S272" t="n">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="T272" t="inlineStr">
         <is>
@@ -30316,7 +30308,7 @@
       </c>
       <c r="Z272" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA272" t="inlineStr">
@@ -30326,7 +30318,7 @@
       </c>
       <c r="AB272" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD272" t="b">
@@ -30341,60 +30333,68 @@
       <c r="AT272" t="inlineStr"/>
       <c r="AW272" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Stefan Andersson</t>
         </is>
       </c>
       <c r="AX272" t="inlineStr">
         <is>
-          <t>Sara Sand, per-erik mukka, Christina Boyd</t>
+          <t>Stefan Andersson, Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>133995809</v>
+        <v>134006977</v>
       </c>
       <c r="B273" t="n">
-        <v>80474</v>
+        <v>58519</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>6458</v>
+        <v>102990</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I273" t="inlineStr"/>
+      <c r="K273" t="inlineStr"/>
+      <c r="L273" t="inlineStr"/>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N273" t="inlineStr"/>
       <c r="P273" t="inlineStr">
         <is>
-          <t>kurravaara, kurravaara, T lm</t>
+          <t>Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>723358</v>
+        <v>723154</v>
       </c>
       <c r="R273" t="n">
-        <v>7544205</v>
+        <v>7544271</v>
       </c>
       <c r="S273" t="n">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="T273" t="inlineStr">
         <is>
@@ -30423,7 +30423,7 @@
       </c>
       <c r="Z273" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA273" t="inlineStr">
@@ -30433,7 +30433,7 @@
       </c>
       <c r="AB273" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD273" t="b">
@@ -30448,12 +30448,12 @@
       <c r="AT273" t="inlineStr"/>
       <c r="AW273" t="inlineStr">
         <is>
-          <t>Stefan Andersson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX273" t="inlineStr">
         <is>
-          <t>Stefan Andersson, Christina Boyd, per-erik mukka</t>
+          <t>Sara Sand, per-erik mukka, Christina Boyd</t>
         </is>
       </c>
       <c r="AY273" t="inlineStr"/>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -6018,7 +6018,7 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>per-erik mukka, Christina Boyd, Sara Sand</t>
+          <t>per-erik mukka, Sara Sand, Christina Boyd</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -6018,7 +6018,7 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>per-erik mukka, Sara Sand, Christina Boyd</t>
+          <t>per-erik mukka, Christina Boyd, Sara Sand</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY295"/>
+  <dimension ref="A1:AZ295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -772,6 +777,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67457959</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -872,6 +882,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67458198</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128880616</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124355877</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1167,6 +1192,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124355870</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1264,6 +1294,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124355654</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1361,6 +1396,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110382722</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1463,6 +1503,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6759582</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1569,6 +1614,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6759594</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1675,6 +1725,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6759596</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1777,6 +1832,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6759597</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1879,6 +1939,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6759599</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1981,6 +2046,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6759605</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2083,6 +2153,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6759850</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2180,6 +2255,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501244</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2277,6 +2357,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501245</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2374,6 +2459,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501246</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2486,6 +2576,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111494950</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2583,6 +2678,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/207973</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2683,6 +2783,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61746470</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2788,6 +2893,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67458012</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2889,6 +2999,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87501008</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2987,6 +3102,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103727916</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3084,6 +3204,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110049101</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3181,6 +3306,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501745</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3278,6 +3408,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501746</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3379,6 +3514,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128880596</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3476,6 +3616,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128981896</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3573,6 +3718,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129015614</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3670,6 +3820,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129309997</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3771,6 +3926,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87515915</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3868,6 +4028,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110382430</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3965,6 +4130,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501423</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4062,6 +4232,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501467</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4159,6 +4334,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501468</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4256,6 +4436,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501469</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4353,6 +4538,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501470</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4450,6 +4640,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501482</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4547,6 +4742,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501483</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4644,6 +4844,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501484</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4741,6 +4946,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129015623</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4848,6 +5058,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133993902</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4945,6 +5160,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501777</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5042,6 +5262,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110382709</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5139,6 +5364,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501764</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5236,6 +5466,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124355798</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5333,6 +5568,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128391313</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5430,6 +5670,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128880606</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5527,6 +5772,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128880607</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5624,6 +5874,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128981900</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5731,6 +5986,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133982984</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5832,6 +6092,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129040495</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5939,6 +6204,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133990618</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6036,6 +6306,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110049482</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6134,6 +6409,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103728009</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6231,6 +6511,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128981901</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6342,6 +6627,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134007962</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6442,6 +6732,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61746473</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6539,6 +6834,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110049107</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6636,6 +6936,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128391239</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6737,6 +7042,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128880594</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6834,6 +7144,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128981895</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6940,6 +7255,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129309942</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7037,6 +7357,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129005009</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7141,6 +7466,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67458215</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7238,6 +7568,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110382720</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7335,6 +7670,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110382721</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7432,6 +7772,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501375</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7529,6 +7874,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501376</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7626,6 +7976,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501379</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7724,6 +8079,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111473568</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7821,6 +8181,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129005002</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7918,6 +8283,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129005003</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8029,6 +8399,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134008031</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8126,6 +8501,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110382588</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8223,6 +8603,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110382597</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8320,6 +8705,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501630</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8417,6 +8807,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/964235</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8514,6 +8909,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/964236</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8611,6 +9011,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/964237</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8711,6 +9116,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61745848</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8808,6 +9218,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129004991</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8906,6 +9321,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129016111</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9006,6 +9426,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61746445</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9104,6 +9529,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111474891</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9202,6 +9632,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111475500</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9303,6 +9738,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128880583</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9400,6 +9840,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128981894</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9506,6 +9951,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129310241</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9606,6 +10056,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61744918</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9706,6 +10161,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67457912</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9803,6 +10263,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119385415</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9900,6 +10365,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128391652</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -9997,6 +10467,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110049102</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10091,6 +10566,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129004992</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10188,6 +10668,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110044450</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10285,6 +10770,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119386180</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10382,6 +10872,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501724</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10479,6 +10974,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1564049</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10576,6 +11076,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1564050</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10673,6 +11178,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1564051</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10770,6 +11280,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1564052</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10867,6 +11382,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501718</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -10967,6 +11487,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61745863</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11067,6 +11592,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67458222</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11164,6 +11694,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91838195</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11262,6 +11797,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103728018</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11359,6 +11899,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124355570</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11456,6 +12001,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1710047</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11556,6 +12106,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61745853</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11653,6 +12208,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124355905</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -11760,6 +12320,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133982087</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -11871,6 +12436,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134008021</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -11968,6 +12538,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129015607</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12065,6 +12640,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129015596</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12172,6 +12752,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133982077</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12271,6 +12856,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61744996</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12368,6 +12958,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91838191</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12465,6 +13060,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501386</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12562,6 +13162,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501387</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -12659,6 +13264,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129051460</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -12756,6 +13366,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501402</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -12864,6 +13479,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111493799</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -12966,6 +13586,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128880601</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13063,6 +13688,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129310552</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13160,6 +13790,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129310941</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13267,6 +13902,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133995809</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13364,6 +14004,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110382606</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13461,6 +14106,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501341</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -13558,6 +14208,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501342</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -13655,6 +14310,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501354</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -13752,6 +14412,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501355</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -13849,6 +14514,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501356</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -13946,6 +14616,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501357</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14043,6 +14718,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501358</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14140,6 +14820,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501359</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14237,6 +14922,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501360</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -14334,6 +15024,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501361</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -14435,6 +15130,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111594797</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -14532,6 +15232,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124355592</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -14629,6 +15334,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124355598</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -14726,6 +15436,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129015603</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -14837,6 +15552,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134007979</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -14948,6 +15668,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134008216</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -15045,6 +15770,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501527</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -15142,6 +15872,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124355873</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -15239,6 +15974,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501405</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -15336,6 +16076,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124355646</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -15447,6 +16192,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134008220</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -15549,6 +16299,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124355611</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -15664,6 +16419,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134008044</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -15761,6 +16521,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129005011</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -15867,6 +16632,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110515875</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -15982,6 +16752,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134006977</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -16091,6 +16866,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110514938</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -16197,6 +16977,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110515786</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -16303,6 +17088,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110515794</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -16412,6 +17202,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110515861</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -16518,6 +17313,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110514972</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -16624,6 +17424,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110515651</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -16733,6 +17538,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110515644</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -16839,6 +17649,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110515685</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -16950,6 +17765,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111494318</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -17047,6 +17867,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129004994</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -17144,6 +17969,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129051458</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -17241,6 +18071,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129051462</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -17338,6 +18173,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129051461</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -17453,6 +18293,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134006906</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -17559,6 +18404,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110515666</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -17665,6 +18515,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110514959</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -17774,6 +18629,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110514995</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -17883,6 +18743,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110515013</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -17989,6 +18854,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110515679</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -18098,6 +18968,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110515713</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -18204,6 +19079,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110515738</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -18313,6 +19193,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110515750</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -18422,6 +19307,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110515756</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -18531,6 +19421,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110515768</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -18637,6 +19532,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110515815</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -18743,6 +19643,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110515817</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -18852,6 +19757,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110515862</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -18958,6 +19868,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110515876</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -19064,6 +19979,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110515879</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -19179,6 +20099,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134006872</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -19291,6 +20216,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13742468</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -19391,6 +20321,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61746528</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -19492,6 +20427,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87501049</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -19593,6 +20533,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128880600</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -19690,6 +20635,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2556929</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -19801,6 +20751,11 @@
           <t>Florainventering av vita fläckar i Lappland</t>
         </is>
       </c>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87248027</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -19898,6 +20853,11 @@
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501137</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -19995,6 +20955,11 @@
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501138</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -20092,6 +21057,11 @@
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501151</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -20189,6 +21159,11 @@
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501152</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -20286,6 +21261,11 @@
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124355802</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -20383,6 +21363,11 @@
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124355806</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -20480,6 +21465,11 @@
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124355807</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -20577,6 +21567,11 @@
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2269240</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -20688,6 +21683,11 @@
           <t>Florainventering av vita fläckar i Lappland</t>
         </is>
       </c>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87248035</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -20794,6 +21794,11 @@
           <t>noteringar från Torne lappmark</t>
         </is>
       </c>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89201534</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -20891,6 +21896,11 @@
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501015</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -20988,6 +21998,11 @@
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501016</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -21085,6 +22100,11 @@
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501017</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -21182,6 +22202,11 @@
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501018</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -21279,6 +22304,11 @@
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501019</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -21376,6 +22406,11 @@
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501020</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -21473,6 +22508,11 @@
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501021</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -21570,6 +22610,11 @@
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501022</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -21680,6 +22725,11 @@
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111187621</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -21777,6 +22827,11 @@
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124355882</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -21874,6 +22929,11 @@
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3550638</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -21974,6 +23034,11 @@
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67458206</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -22071,6 +23136,11 @@
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501196</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -22168,6 +23238,11 @@
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501197</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -22265,6 +23340,11 @@
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501198</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -22362,6 +23442,11 @@
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501199</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -22459,6 +23544,11 @@
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501200</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -22556,6 +23646,11 @@
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501201</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -22653,6 +23748,11 @@
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501202</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -22750,6 +23850,11 @@
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501205</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -22847,6 +23952,11 @@
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501206</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -22944,6 +24054,11 @@
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501207</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -23041,6 +24156,11 @@
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501208</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -23138,6 +24258,11 @@
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124355666</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -23235,6 +24360,11 @@
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124355667</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -23332,6 +24462,11 @@
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124355668</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -23429,6 +24564,11 @@
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124355672</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -23540,6 +24680,11 @@
           <t>Florainventering av vita fläckar i Lappland</t>
         </is>
       </c>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87248041</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -23637,6 +24782,11 @@
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124355513</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -23734,6 +24884,11 @@
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124355515</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -23831,6 +24986,11 @@
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124355516</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -23928,6 +25088,11 @@
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124355528</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -24025,6 +25190,11 @@
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124355529</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -24122,6 +25292,11 @@
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124355530</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -24219,6 +25394,11 @@
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124355531</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -24316,6 +25496,11 @@
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124355538</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -24413,6 +25598,11 @@
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
+      <c r="AZ238" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124355539</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -24510,6 +25700,11 @@
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
+      <c r="AZ239" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124355540</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -24607,6 +25802,11 @@
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
+      <c r="AZ240" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124355541</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -24704,6 +25904,11 @@
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
+      <c r="AZ241" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124355542</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -24801,6 +26006,11 @@
         </is>
       </c>
       <c r="AY242" t="inlineStr"/>
+      <c r="AZ242" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124355543</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -24898,6 +26108,11 @@
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124355544</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -24995,6 +26210,11 @@
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124355546</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -25092,6 +26312,11 @@
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124355548</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -25189,6 +26414,11 @@
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124355551</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -25286,6 +26516,11 @@
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
+      <c r="AZ247" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124355552</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -25383,6 +26618,11 @@
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
+      <c r="AZ248" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129015591</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -25480,6 +26720,11 @@
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
+      <c r="AZ249" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501257</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -25577,6 +26822,11 @@
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
+      <c r="AZ250" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501260</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -25674,6 +26924,11 @@
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124355632</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -25774,6 +27029,11 @@
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
+      <c r="AZ252" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61744985</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -25880,6 +27140,11 @@
           <t>noteringar från Torne lappmark</t>
         </is>
       </c>
+      <c r="AZ253" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89201575</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -25977,6 +27242,11 @@
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
+      <c r="AZ254" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110382633</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -26074,6 +27344,11 @@
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
+      <c r="AZ255" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501251</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -26171,6 +27446,11 @@
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>
+      <c r="AZ256" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124355609</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -26268,6 +27548,11 @@
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
+      <c r="AZ257" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4870391</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -26365,6 +27650,11 @@
         </is>
       </c>
       <c r="AY258" t="inlineStr"/>
+      <c r="AZ258" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120543965</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -26462,6 +27752,11 @@
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>
+      <c r="AZ259" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5171824</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -26573,6 +27868,11 @@
           <t>Florainventering av vita fläckar i Lappland</t>
         </is>
       </c>
+      <c r="AZ260" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87248016</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -26670,6 +27970,11 @@
         </is>
       </c>
       <c r="AY261" t="inlineStr"/>
+      <c r="AZ261" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501113</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -26767,6 +28072,11 @@
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
+      <c r="AZ262" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501115</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -26864,6 +28174,11 @@
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>
+      <c r="AZ263" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501116</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -26961,6 +28276,11 @@
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
+      <c r="AZ264" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501117</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -27058,6 +28378,11 @@
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>
+      <c r="AZ265" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501118</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -27155,6 +28480,11 @@
         </is>
       </c>
       <c r="AY266" t="inlineStr"/>
+      <c r="AZ266" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501119</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -27252,6 +28582,11 @@
         </is>
       </c>
       <c r="AY267" t="inlineStr"/>
+      <c r="AZ267" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501120</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -27350,6 +28685,11 @@
         </is>
       </c>
       <c r="AY268" t="inlineStr"/>
+      <c r="AZ268" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111474170</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -27447,6 +28787,11 @@
         </is>
       </c>
       <c r="AY269" t="inlineStr"/>
+      <c r="AZ269" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124355850</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -27544,6 +28889,11 @@
         </is>
       </c>
       <c r="AY270" t="inlineStr"/>
+      <c r="AZ270" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124355851</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -27641,6 +28991,11 @@
         </is>
       </c>
       <c r="AY271" t="inlineStr"/>
+      <c r="AZ271" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124355855</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -27738,6 +29093,11 @@
         </is>
       </c>
       <c r="AY272" t="inlineStr"/>
+      <c r="AZ272" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124355856</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -27835,6 +29195,11 @@
         </is>
       </c>
       <c r="AY273" t="inlineStr"/>
+      <c r="AZ273" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124355857</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -27932,6 +29297,11 @@
         </is>
       </c>
       <c r="AY274" t="inlineStr"/>
+      <c r="AZ274" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501266</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -28031,6 +29401,11 @@
         </is>
       </c>
       <c r="AY275" t="inlineStr"/>
+      <c r="AZ275" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61746564</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -28130,6 +29505,11 @@
         </is>
       </c>
       <c r="AY276" t="inlineStr"/>
+      <c r="AZ276" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67458187</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -28227,6 +29607,11 @@
         </is>
       </c>
       <c r="AY277" t="inlineStr"/>
+      <c r="AZ277" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110501373</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -28324,6 +29709,11 @@
         </is>
       </c>
       <c r="AY278" t="inlineStr"/>
+      <c r="AZ278" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110382589</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -28421,6 +29811,11 @@
         </is>
       </c>
       <c r="AY279" t="inlineStr"/>
+      <c r="AZ279" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110382591</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -28518,6 +29913,11 @@
         </is>
       </c>
       <c r="AY280" t="inlineStr"/>
+      <c r="AZ280" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110382592</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -28615,6 +30015,11 @@
         </is>
       </c>
       <c r="AY281" t="inlineStr"/>
+      <c r="AZ281" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110044455</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -28712,6 +30117,11 @@
         </is>
       </c>
       <c r="AY282" t="inlineStr"/>
+      <c r="AZ282" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110044453</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -28809,6 +30219,11 @@
         </is>
       </c>
       <c r="AY283" t="inlineStr"/>
+      <c r="AZ283" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110044454</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -28917,6 +30332,11 @@
         </is>
       </c>
       <c r="AY284" t="inlineStr"/>
+      <c r="AZ284" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102907874</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -29014,6 +30434,11 @@
         </is>
       </c>
       <c r="AY285" t="inlineStr"/>
+      <c r="AZ285" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110044449</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -29126,6 +30551,11 @@
         </is>
       </c>
       <c r="AY286" t="inlineStr"/>
+      <c r="AZ286" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117357759</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -29232,6 +30662,11 @@
         </is>
       </c>
       <c r="AY287" t="inlineStr"/>
+      <c r="AZ287" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111591780</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -29342,6 +30777,11 @@
         </is>
       </c>
       <c r="AY288" t="inlineStr"/>
+      <c r="AZ288" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87676926</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -29455,6 +30895,11 @@
         </is>
       </c>
       <c r="AY289" t="inlineStr"/>
+      <c r="AZ289" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95153649</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -29568,6 +31013,11 @@
         </is>
       </c>
       <c r="AY290" t="inlineStr"/>
+      <c r="AZ290" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95153730</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -29681,6 +31131,11 @@
         </is>
       </c>
       <c r="AY291" t="inlineStr"/>
+      <c r="AZ291" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95153759</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -29790,6 +31245,11 @@
         </is>
       </c>
       <c r="AY292" t="inlineStr"/>
+      <c r="AZ292" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95153809</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -29903,6 +31363,11 @@
         </is>
       </c>
       <c r="AY293" t="inlineStr"/>
+      <c r="AZ293" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95153843</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -30016,6 +31481,11 @@
         </is>
       </c>
       <c r="AY294" t="inlineStr"/>
+      <c r="AZ294" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95153900</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -30129,8 +31599,309 @@
         </is>
       </c>
       <c r="AY295" t="inlineStr"/>
+      <c r="AZ295" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94564368</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ258" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ259" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ260" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ262" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ263" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ264" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ265" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ266" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ267" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ268" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ269" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ270" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ271" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ272" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ273" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ274" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ275" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ276" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ277" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ278" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ279" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ280" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ281" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ282" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ283" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ284" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ285" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ286" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ287" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ288" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ289" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ290" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ291" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ292" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ293" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ294" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ295" r:id="rId294"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ295"/>
+  <dimension ref="A1:AZ297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24572,52 +24572,57 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>87248041</v>
+        <v>135650446</v>
       </c>
       <c r="B229" t="n">
-        <v>106229</v>
+        <v>99242</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I229" t="inlineStr"/>
-      <c r="J229" t="inlineStr"/>
-      <c r="K229" t="inlineStr"/>
-      <c r="L229" t="inlineStr"/>
-      <c r="N229" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P229" t="inlineStr">
         <is>
-          <t>Kurravaara, södra delen av byn, T lm</t>
+          <t>Koivuvaara SV Kurravaara by, T lm</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>723794</v>
+        <v>723076</v>
       </c>
       <c r="R229" t="n">
-        <v>7544657</v>
+        <v>7545065</v>
       </c>
       <c r="S229" t="n">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="T229" t="inlineStr">
         <is>
@@ -24641,12 +24646,12 @@
       </c>
       <c r="Y229" t="inlineStr">
         <is>
-          <t>2020-07-22</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
         <is>
-          <t>2020-07-22</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -24655,81 +24660,75 @@
       <c r="AE229" t="b">
         <v>0</v>
       </c>
-      <c r="AF229" t="inlineStr"/>
       <c r="AG229" t="b">
         <v>0</v>
-      </c>
-      <c r="AI229" t="inlineStr">
-        <is>
-          <t>översilad björkskog</t>
-        </is>
       </c>
       <c r="AT229" t="inlineStr"/>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>Lars Fröberg</t>
+          <t>Anna Öhlund</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>Lars Fröberg, Rolf Enander, Patrik Engström</t>
-        </is>
-      </c>
-      <c r="AY229" t="inlineStr">
-        <is>
-          <t>Florainventering av vita fläckar i Lappland</t>
-        </is>
-      </c>
+          <t>Anna Öhlund</t>
+        </is>
+      </c>
+      <c r="AY229" t="inlineStr"/>
       <c r="AZ229" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/87248041</t>
+          <t>https://artportalen.se/Sighting/135650446</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>124355513</v>
+        <v>135651394</v>
       </c>
       <c r="B230" t="n">
-        <v>106229</v>
+        <v>99242</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I230" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P230" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Gruvberget, T lm</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>723653</v>
+        <v>723268</v>
       </c>
       <c r="R230" t="n">
-        <v>7544288</v>
+        <v>7544995</v>
       </c>
       <c r="S230" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T230" t="inlineStr">
         <is>
@@ -24753,12 +24752,12 @@
       </c>
       <c r="Y230" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA230" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD230" t="b">
@@ -24773,24 +24772,24 @@
       <c r="AT230" t="inlineStr"/>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Anna Öhlund</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Anna Öhlund</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
       <c r="AZ230" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355513</t>
+          <t>https://artportalen.se/Sighting/135651394</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>124355515</v>
+        <v>87248041</v>
       </c>
       <c r="B231" t="n">
         <v>106229</v>
@@ -24819,19 +24818,23 @@
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
+      <c r="J231" t="inlineStr"/>
+      <c r="K231" t="inlineStr"/>
+      <c r="L231" t="inlineStr"/>
+      <c r="N231" t="inlineStr"/>
       <c r="P231" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Kurravaara, södra delen av byn, T lm</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>723720</v>
+        <v>723794</v>
       </c>
       <c r="R231" t="n">
-        <v>7544240</v>
+        <v>7544657</v>
       </c>
       <c r="S231" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T231" t="inlineStr">
         <is>
@@ -24855,12 +24858,12 @@
       </c>
       <c r="Y231" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2020-07-22</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2020-07-22</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -24869,30 +24872,40 @@
       <c r="AE231" t="b">
         <v>0</v>
       </c>
+      <c r="AF231" t="inlineStr"/>
       <c r="AG231" t="b">
         <v>0</v>
+      </c>
+      <c r="AI231" t="inlineStr">
+        <is>
+          <t>översilad björkskog</t>
+        </is>
       </c>
       <c r="AT231" t="inlineStr"/>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Lars Fröberg</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
-        </is>
-      </c>
-      <c r="AY231" t="inlineStr"/>
+          <t>Lars Fröberg, Rolf Enander, Patrik Engström</t>
+        </is>
+      </c>
+      <c r="AY231" t="inlineStr">
+        <is>
+          <t>Florainventering av vita fläckar i Lappland</t>
+        </is>
+      </c>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355515</t>
+          <t>https://artportalen.se/Sighting/87248041</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>124355516</v>
+        <v>124355513</v>
       </c>
       <c r="B232" t="n">
         <v>106229</v>
@@ -24927,10 +24940,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>723694</v>
+        <v>723653</v>
       </c>
       <c r="R232" t="n">
-        <v>7544160</v>
+        <v>7544288</v>
       </c>
       <c r="S232" t="n">
         <v>5</v>
@@ -24988,13 +25001,13 @@
       <c r="AY232" t="inlineStr"/>
       <c r="AZ232" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355516</t>
+          <t>https://artportalen.se/Sighting/124355513</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>124355528</v>
+        <v>124355515</v>
       </c>
       <c r="B233" t="n">
         <v>106229</v>
@@ -25025,14 +25038,14 @@
       <c r="I233" t="inlineStr"/>
       <c r="P233" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>723593</v>
+        <v>723720</v>
       </c>
       <c r="R233" t="n">
-        <v>7545295</v>
+        <v>7544240</v>
       </c>
       <c r="S233" t="n">
         <v>5</v>
@@ -25059,12 +25072,12 @@
       </c>
       <c r="Y233" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA233" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -25090,13 +25103,13 @@
       <c r="AY233" t="inlineStr"/>
       <c r="AZ233" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355528</t>
+          <t>https://artportalen.se/Sighting/124355515</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>124355529</v>
+        <v>124355516</v>
       </c>
       <c r="B234" t="n">
         <v>106229</v>
@@ -25127,14 +25140,14 @@
       <c r="I234" t="inlineStr"/>
       <c r="P234" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>723365</v>
+        <v>723694</v>
       </c>
       <c r="R234" t="n">
-        <v>7545207</v>
+        <v>7544160</v>
       </c>
       <c r="S234" t="n">
         <v>5</v>
@@ -25161,12 +25174,12 @@
       </c>
       <c r="Y234" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA234" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD234" t="b">
@@ -25192,13 +25205,13 @@
       <c r="AY234" t="inlineStr"/>
       <c r="AZ234" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355529</t>
+          <t>https://artportalen.se/Sighting/124355516</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>124355530</v>
+        <v>124355528</v>
       </c>
       <c r="B235" t="n">
         <v>106229</v>
@@ -25233,10 +25246,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>723178</v>
+        <v>723593</v>
       </c>
       <c r="R235" t="n">
-        <v>7545219</v>
+        <v>7545295</v>
       </c>
       <c r="S235" t="n">
         <v>5</v>
@@ -25294,13 +25307,13 @@
       <c r="AY235" t="inlineStr"/>
       <c r="AZ235" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355530</t>
+          <t>https://artportalen.se/Sighting/124355528</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>124355531</v>
+        <v>124355529</v>
       </c>
       <c r="B236" t="n">
         <v>106229</v>
@@ -25335,10 +25348,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>723120</v>
+        <v>723365</v>
       </c>
       <c r="R236" t="n">
-        <v>7545233</v>
+        <v>7545207</v>
       </c>
       <c r="S236" t="n">
         <v>5</v>
@@ -25396,13 +25409,13 @@
       <c r="AY236" t="inlineStr"/>
       <c r="AZ236" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355531</t>
+          <t>https://artportalen.se/Sighting/124355529</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>124355538</v>
+        <v>124355530</v>
       </c>
       <c r="B237" t="n">
         <v>106229</v>
@@ -25437,10 +25450,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>722917</v>
+        <v>723178</v>
       </c>
       <c r="R237" t="n">
-        <v>7544575</v>
+        <v>7545219</v>
       </c>
       <c r="S237" t="n">
         <v>5</v>
@@ -25498,13 +25511,13 @@
       <c r="AY237" t="inlineStr"/>
       <c r="AZ237" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355538</t>
+          <t>https://artportalen.se/Sighting/124355530</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>124355539</v>
+        <v>124355531</v>
       </c>
       <c r="B238" t="n">
         <v>106229</v>
@@ -25539,10 +25552,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>722977</v>
+        <v>723120</v>
       </c>
       <c r="R238" t="n">
-        <v>7544571</v>
+        <v>7545233</v>
       </c>
       <c r="S238" t="n">
         <v>5</v>
@@ -25600,13 +25613,13 @@
       <c r="AY238" t="inlineStr"/>
       <c r="AZ238" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355539</t>
+          <t>https://artportalen.se/Sighting/124355531</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>124355540</v>
+        <v>124355538</v>
       </c>
       <c r="B239" t="n">
         <v>106229</v>
@@ -25641,10 +25654,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>723038</v>
+        <v>722917</v>
       </c>
       <c r="R239" t="n">
-        <v>7544552</v>
+        <v>7544575</v>
       </c>
       <c r="S239" t="n">
         <v>5</v>
@@ -25702,13 +25715,13 @@
       <c r="AY239" t="inlineStr"/>
       <c r="AZ239" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355540</t>
+          <t>https://artportalen.se/Sighting/124355538</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>124355541</v>
+        <v>124355539</v>
       </c>
       <c r="B240" t="n">
         <v>106229</v>
@@ -25743,10 +25756,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>723087</v>
+        <v>722977</v>
       </c>
       <c r="R240" t="n">
-        <v>7544566</v>
+        <v>7544571</v>
       </c>
       <c r="S240" t="n">
         <v>5</v>
@@ -25804,13 +25817,13 @@
       <c r="AY240" t="inlineStr"/>
       <c r="AZ240" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355541</t>
+          <t>https://artportalen.se/Sighting/124355539</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>124355542</v>
+        <v>124355540</v>
       </c>
       <c r="B241" t="n">
         <v>106229</v>
@@ -25845,10 +25858,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>723159</v>
+        <v>723038</v>
       </c>
       <c r="R241" t="n">
-        <v>7544605</v>
+        <v>7544552</v>
       </c>
       <c r="S241" t="n">
         <v>5</v>
@@ -25906,13 +25919,13 @@
       <c r="AY241" t="inlineStr"/>
       <c r="AZ241" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355542</t>
+          <t>https://artportalen.se/Sighting/124355540</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>124355543</v>
+        <v>124355541</v>
       </c>
       <c r="B242" t="n">
         <v>106229</v>
@@ -25947,10 +25960,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>723227</v>
+        <v>723087</v>
       </c>
       <c r="R242" t="n">
-        <v>7544640</v>
+        <v>7544566</v>
       </c>
       <c r="S242" t="n">
         <v>5</v>
@@ -26008,13 +26021,13 @@
       <c r="AY242" t="inlineStr"/>
       <c r="AZ242" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355543</t>
+          <t>https://artportalen.se/Sighting/124355541</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>124355544</v>
+        <v>124355542</v>
       </c>
       <c r="B243" t="n">
         <v>106229</v>
@@ -26049,10 +26062,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>723301</v>
+        <v>723159</v>
       </c>
       <c r="R243" t="n">
-        <v>7544640</v>
+        <v>7544605</v>
       </c>
       <c r="S243" t="n">
         <v>5</v>
@@ -26110,13 +26123,13 @@
       <c r="AY243" t="inlineStr"/>
       <c r="AZ243" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355544</t>
+          <t>https://artportalen.se/Sighting/124355542</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>124355546</v>
+        <v>124355543</v>
       </c>
       <c r="B244" t="n">
         <v>106229</v>
@@ -26151,10 +26164,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>723347</v>
+        <v>723227</v>
       </c>
       <c r="R244" t="n">
-        <v>7544617</v>
+        <v>7544640</v>
       </c>
       <c r="S244" t="n">
         <v>5</v>
@@ -26212,13 +26225,13 @@
       <c r="AY244" t="inlineStr"/>
       <c r="AZ244" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355546</t>
+          <t>https://artportalen.se/Sighting/124355543</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>124355548</v>
+        <v>124355544</v>
       </c>
       <c r="B245" t="n">
         <v>106229</v>
@@ -26253,10 +26266,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>723515</v>
+        <v>723301</v>
       </c>
       <c r="R245" t="n">
-        <v>7544632</v>
+        <v>7544640</v>
       </c>
       <c r="S245" t="n">
         <v>5</v>
@@ -26314,13 +26327,13 @@
       <c r="AY245" t="inlineStr"/>
       <c r="AZ245" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355548</t>
+          <t>https://artportalen.se/Sighting/124355544</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>124355551</v>
+        <v>124355546</v>
       </c>
       <c r="B246" t="n">
         <v>106229</v>
@@ -26355,10 +26368,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>723547</v>
+        <v>723347</v>
       </c>
       <c r="R246" t="n">
-        <v>7544600</v>
+        <v>7544617</v>
       </c>
       <c r="S246" t="n">
         <v>5</v>
@@ -26416,13 +26429,13 @@
       <c r="AY246" t="inlineStr"/>
       <c r="AZ246" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355551</t>
+          <t>https://artportalen.se/Sighting/124355546</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>124355552</v>
+        <v>124355548</v>
       </c>
       <c r="B247" t="n">
         <v>106229</v>
@@ -26457,10 +26470,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>723608</v>
+        <v>723515</v>
       </c>
       <c r="R247" t="n">
-        <v>7544580</v>
+        <v>7544632</v>
       </c>
       <c r="S247" t="n">
         <v>5</v>
@@ -26518,16 +26531,16 @@
       <c r="AY247" t="inlineStr"/>
       <c r="AZ247" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355552</t>
+          <t>https://artportalen.se/Sighting/124355548</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>129015591</v>
+        <v>124355551</v>
       </c>
       <c r="B248" t="n">
-        <v>106228</v>
+        <v>106229</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -26555,17 +26568,17 @@
       <c r="I248" t="inlineStr"/>
       <c r="P248" t="inlineStr">
         <is>
-          <t>Kurravaara, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>722800</v>
+        <v>723547</v>
       </c>
       <c r="R248" t="n">
-        <v>7544375</v>
+        <v>7544600</v>
       </c>
       <c r="S248" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T248" t="inlineStr">
         <is>
@@ -26589,12 +26602,12 @@
       </c>
       <c r="Y248" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA248" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -26609,27 +26622,27 @@
       <c r="AT248" t="inlineStr"/>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
       <c r="AZ248" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129015591</t>
+          <t>https://artportalen.se/Sighting/124355551</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>110501257</v>
+        <v>124355552</v>
       </c>
       <c r="B249" t="n">
-        <v>97989</v>
+        <v>106229</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -26637,37 +26650,37 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>221941</v>
+        <v>221725</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
       <c r="P249" t="inlineStr">
         <is>
-          <t>Per Geijerområdet, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>723085</v>
+        <v>723608</v>
       </c>
       <c r="R249" t="n">
-        <v>7544696</v>
+        <v>7544580</v>
       </c>
       <c r="S249" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T249" t="inlineStr">
         <is>
@@ -26691,12 +26704,12 @@
       </c>
       <c r="Y249" t="inlineStr">
         <is>
-          <t>2022-08-01</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA249" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD249" t="b">
@@ -26711,27 +26724,27 @@
       <c r="AT249" t="inlineStr"/>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>Mats Williamson, Billy Lindblom, Nils Ericson, Marie Riskilä</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
       <c r="AZ249" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110501257</t>
+          <t>https://artportalen.se/Sighting/124355552</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>110501260</v>
+        <v>129015591</v>
       </c>
       <c r="B250" t="n">
-        <v>97989</v>
+        <v>106228</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -26739,34 +26752,34 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>221941</v>
+        <v>221725</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
       <c r="P250" t="inlineStr">
         <is>
-          <t>Per Geijerområdet, T lm</t>
+          <t>Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>723645</v>
+        <v>722800</v>
       </c>
       <c r="R250" t="n">
-        <v>7545074</v>
+        <v>7544375</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -26793,12 +26806,12 @@
       </c>
       <c r="Y250" t="inlineStr">
         <is>
-          <t>2022-08-01</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="AA250" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="AD250" t="b">
@@ -26813,24 +26826,24 @@
       <c r="AT250" t="inlineStr"/>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>Mats Williamson, Billy Lindblom, Nils Ericson, Marie Riskilä</t>
+          <t>Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
       <c r="AZ250" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110501260</t>
+          <t>https://artportalen.se/Sighting/129015591</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>124355632</v>
+        <v>110501257</v>
       </c>
       <c r="B251" t="n">
         <v>97989</v>
@@ -26861,17 +26874,17 @@
       <c r="I251" t="inlineStr"/>
       <c r="P251" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Per Geijerområdet, T lm</t>
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>723668</v>
+        <v>723085</v>
       </c>
       <c r="R251" t="n">
-        <v>7544288</v>
+        <v>7544696</v>
       </c>
       <c r="S251" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T251" t="inlineStr">
         <is>
@@ -26895,12 +26908,12 @@
       </c>
       <c r="Y251" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2022-08-01</t>
         </is>
       </c>
       <c r="AA251" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2022-09-07</t>
         </is>
       </c>
       <c r="AD251" t="b">
@@ -26915,27 +26928,27 @@
       <c r="AT251" t="inlineStr"/>
       <c r="AW251" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Mats Williamson</t>
         </is>
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Mats Williamson, Billy Lindblom, Nils Ericson, Marie Riskilä</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
       <c r="AZ251" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355632</t>
+          <t>https://artportalen.se/Sighting/110501257</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>61744985</v>
+        <v>110501260</v>
       </c>
       <c r="B252" t="n">
-        <v>97983</v>
+        <v>97989</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -26943,16 +26956,16 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -26961,19 +26974,16 @@
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
-      <c r="J252" t="inlineStr"/>
-      <c r="K252" t="inlineStr"/>
-      <c r="L252" t="inlineStr"/>
       <c r="P252" t="inlineStr">
         <is>
-          <t>kurravaara ravinen, T lm</t>
+          <t>Per Geijerområdet, T lm</t>
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>723578</v>
+        <v>723645</v>
       </c>
       <c r="R252" t="n">
-        <v>7544434</v>
+        <v>7545074</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -27000,12 +27010,12 @@
       </c>
       <c r="Y252" t="inlineStr">
         <is>
-          <t>2016-10-13</t>
+          <t>2022-08-01</t>
         </is>
       </c>
       <c r="AA252" t="inlineStr">
         <is>
-          <t>2016-10-13</t>
+          <t>2022-09-07</t>
         </is>
       </c>
       <c r="AD252" t="b">
@@ -27020,27 +27030,27 @@
       <c r="AT252" t="inlineStr"/>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Mats Williamson</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Mats Williamson, Billy Lindblom, Nils Ericson, Marie Riskilä</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
       <c r="AZ252" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/61744985</t>
+          <t>https://artportalen.se/Sighting/110501260</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>89201575</v>
+        <v>124355632</v>
       </c>
       <c r="B253" t="n">
-        <v>97983</v>
+        <v>97989</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -27048,16 +27058,16 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -27068,17 +27078,17 @@
       <c r="I253" t="inlineStr"/>
       <c r="P253" t="inlineStr">
         <is>
-          <t>Kurravaara, Iso Mäntyvaaravan V, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>723763</v>
+        <v>723668</v>
       </c>
       <c r="R253" t="n">
-        <v>7544642</v>
+        <v>7544288</v>
       </c>
       <c r="S253" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T253" t="inlineStr">
         <is>
@@ -27102,12 +27112,12 @@
       </c>
       <c r="Y253" t="inlineStr">
         <is>
-          <t>2002-08-03</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA253" t="inlineStr">
         <is>
-          <t>2002-08-03</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD253" t="b">
@@ -27118,37 +27128,28 @@
       </c>
       <c r="AG253" t="b">
         <v>0</v>
-      </c>
-      <c r="AI253" t="inlineStr">
-        <is>
-          <t>rikkärr</t>
-        </is>
       </c>
       <c r="AT253" t="inlineStr"/>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>Peter Ståhl</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>Peter Ståhl</t>
-        </is>
-      </c>
-      <c r="AY253" t="inlineStr">
-        <is>
-          <t>noteringar från Torne lappmark</t>
-        </is>
-      </c>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY253" t="inlineStr"/>
       <c r="AZ253" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89201575</t>
+          <t>https://artportalen.se/Sighting/124355632</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>110382633</v>
+        <v>61744985</v>
       </c>
       <c r="B254" t="n">
         <v>97983</v>
@@ -27177,16 +27178,19 @@
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
+      <c r="J254" t="inlineStr"/>
+      <c r="K254" t="inlineStr"/>
+      <c r="L254" t="inlineStr"/>
       <c r="P254" t="inlineStr">
         <is>
-          <t>Per Geijerområdet, T lm</t>
+          <t>kurravaara ravinen, T lm</t>
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>723303</v>
+        <v>723578</v>
       </c>
       <c r="R254" t="n">
-        <v>7543864</v>
+        <v>7544434</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -27213,12 +27217,12 @@
       </c>
       <c r="Y254" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2016-10-13</t>
         </is>
       </c>
       <c r="AA254" t="inlineStr">
         <is>
-          <t>2021-09-17</t>
+          <t>2016-10-13</t>
         </is>
       </c>
       <c r="AD254" t="b">
@@ -27233,24 +27237,24 @@
       <c r="AT254" t="inlineStr"/>
       <c r="AW254" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>Mats Williamson, Billy Lindblom</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
       <c r="AZ254" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110382633</t>
+          <t>https://artportalen.se/Sighting/61744985</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>110501251</v>
+        <v>89201575</v>
       </c>
       <c r="B255" t="n">
         <v>97983</v>
@@ -27281,17 +27285,17 @@
       <c r="I255" t="inlineStr"/>
       <c r="P255" t="inlineStr">
         <is>
-          <t>Per Geijerområdet, T lm</t>
+          <t>Kurravaara, Iso Mäntyvaaravan V, T lm</t>
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>723816</v>
+        <v>723763</v>
       </c>
       <c r="R255" t="n">
-        <v>7544835</v>
+        <v>7544642</v>
       </c>
       <c r="S255" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T255" t="inlineStr">
         <is>
@@ -27315,12 +27319,12 @@
       </c>
       <c r="Y255" t="inlineStr">
         <is>
-          <t>2022-08-01</t>
+          <t>2002-08-03</t>
         </is>
       </c>
       <c r="AA255" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
+          <t>2002-08-03</t>
         </is>
       </c>
       <c r="AD255" t="b">
@@ -27331,31 +27335,40 @@
       </c>
       <c r="AG255" t="b">
         <v>0</v>
+      </c>
+      <c r="AI255" t="inlineStr">
+        <is>
+          <t>rikkärr</t>
+        </is>
       </c>
       <c r="AT255" t="inlineStr"/>
       <c r="AW255" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>Peter Ståhl</t>
         </is>
       </c>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>Mats Williamson, Billy Lindblom, Nils Ericson, Marie Riskilä</t>
-        </is>
-      </c>
-      <c r="AY255" t="inlineStr"/>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AY255" t="inlineStr">
+        <is>
+          <t>noteringar från Torne lappmark</t>
+        </is>
+      </c>
       <c r="AZ255" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110501251</t>
+          <t>https://artportalen.se/Sighting/89201575</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>124355609</v>
+        <v>110382633</v>
       </c>
       <c r="B256" t="n">
-        <v>99140</v>
+        <v>97983</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -27363,37 +27376,37 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
       <c r="P256" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Per Geijerområdet, T lm</t>
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>723343</v>
+        <v>723303</v>
       </c>
       <c r="R256" t="n">
-        <v>7544612</v>
+        <v>7543864</v>
       </c>
       <c r="S256" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T256" t="inlineStr">
         <is>
@@ -27417,12 +27430,12 @@
       </c>
       <c r="Y256" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="AA256" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2021-09-17</t>
         </is>
       </c>
       <c r="AD256" t="b">
@@ -27437,27 +27450,27 @@
       <c r="AT256" t="inlineStr"/>
       <c r="AW256" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Mats Williamson</t>
         </is>
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Mats Williamson, Billy Lindblom</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>
       <c r="AZ256" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355609</t>
+          <t>https://artportalen.se/Sighting/110382633</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>4870391</v>
+        <v>110501251</v>
       </c>
       <c r="B257" t="n">
-        <v>100143</v>
+        <v>97983</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -27465,37 +27478,37 @@
         </is>
       </c>
       <c r="E257" t="n">
-        <v>222467</v>
+        <v>221945</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Gräsull</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Eriophorum latifolium</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>Hoppe</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
       <c r="P257" t="inlineStr">
         <is>
-          <t>Koivuvaara, N-sluttning, myr, T lm</t>
+          <t>Per Geijerområdet, T lm</t>
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>723271</v>
+        <v>723816</v>
       </c>
       <c r="R257" t="n">
-        <v>7545161</v>
+        <v>7544835</v>
       </c>
       <c r="S257" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T257" t="inlineStr">
         <is>
@@ -27519,12 +27532,12 @@
       </c>
       <c r="Y257" t="inlineStr">
         <is>
-          <t>1981-07-02</t>
+          <t>2022-08-01</t>
         </is>
       </c>
       <c r="AA257" t="inlineStr">
         <is>
-          <t>1981-07-02</t>
+          <t>2022-09-07</t>
         </is>
       </c>
       <c r="AD257" t="b">
@@ -27539,27 +27552,27 @@
       <c r="AT257" t="inlineStr"/>
       <c r="AW257" t="inlineStr">
         <is>
-          <t>Birgitta Öster</t>
+          <t>Mats Williamson</t>
         </is>
       </c>
       <c r="AX257" t="inlineStr">
         <is>
-          <t>Birgitta Öster</t>
+          <t>Mats Williamson, Billy Lindblom, Nils Ericson, Marie Riskilä</t>
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
       <c r="AZ257" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4870391</t>
+          <t>https://artportalen.se/Sighting/110501251</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>120543965</v>
+        <v>124355609</v>
       </c>
       <c r="B258" t="n">
-        <v>100143</v>
+        <v>99140</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -27567,21 +27580,21 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>222467</v>
+        <v>221952</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Gräsull</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Eriophorum latifolium</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>Hoppe</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
@@ -27591,10 +27604,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>723813</v>
+        <v>723343</v>
       </c>
       <c r="R258" t="n">
-        <v>7544469</v>
+        <v>7544612</v>
       </c>
       <c r="S258" t="n">
         <v>5</v>
@@ -27652,16 +27665,16 @@
       <c r="AY258" t="inlineStr"/>
       <c r="AZ258" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120543965</t>
+          <t>https://artportalen.se/Sighting/124355609</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>5171824</v>
+        <v>4870391</v>
       </c>
       <c r="B259" t="n">
-        <v>98137</v>
+        <v>100143</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -27669,37 +27682,37 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>222741</v>
+        <v>222467</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Gräsull</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Eriophorum latifolium</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>Hoppe</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
       <c r="P259" t="inlineStr">
         <is>
-          <t>kurravaararavinen, T lm</t>
+          <t>Koivuvaara, N-sluttning, myr, T lm</t>
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>723525</v>
+        <v>723271</v>
       </c>
       <c r="R259" t="n">
-        <v>7544228</v>
+        <v>7545161</v>
       </c>
       <c r="S259" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T259" t="inlineStr">
         <is>
@@ -27723,12 +27736,12 @@
       </c>
       <c r="Y259" t="inlineStr">
         <is>
-          <t>2012-08-29</t>
+          <t>1981-07-02</t>
         </is>
       </c>
       <c r="AA259" t="inlineStr">
         <is>
-          <t>2012-08-29</t>
+          <t>1981-07-02</t>
         </is>
       </c>
       <c r="AD259" t="b">
@@ -27743,27 +27756,27 @@
       <c r="AT259" t="inlineStr"/>
       <c r="AW259" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Birgitta Öster</t>
         </is>
       </c>
       <c r="AX259" t="inlineStr">
         <is>
-          <t>per-erik mukka, Robert Sandberg, Frédéric Forsmark</t>
+          <t>Birgitta Öster</t>
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>
       <c r="AZ259" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/5171824</t>
+          <t>https://artportalen.se/Sighting/4870391</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>87248016</v>
+        <v>120543965</v>
       </c>
       <c r="B260" t="n">
-        <v>98137</v>
+        <v>100143</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -27771,41 +27784,37 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>222741</v>
+        <v>222467</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Gräsull</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Eriophorum latifolium</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>Hoppe</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
-      <c r="J260" t="inlineStr"/>
-      <c r="K260" t="inlineStr"/>
-      <c r="L260" t="inlineStr"/>
-      <c r="N260" t="inlineStr"/>
       <c r="P260" t="inlineStr">
         <is>
-          <t>Kurravaara, södra delen av byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>723794</v>
+        <v>723813</v>
       </c>
       <c r="R260" t="n">
-        <v>7544657</v>
+        <v>7544469</v>
       </c>
       <c r="S260" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T260" t="inlineStr">
         <is>
@@ -27829,12 +27838,12 @@
       </c>
       <c r="Y260" t="inlineStr">
         <is>
-          <t>2020-07-22</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA260" t="inlineStr">
         <is>
-          <t>2020-07-22</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD260" t="b">
@@ -27843,40 +27852,30 @@
       <c r="AE260" t="b">
         <v>0</v>
       </c>
-      <c r="AF260" t="inlineStr"/>
       <c r="AG260" t="b">
         <v>0</v>
-      </c>
-      <c r="AI260" t="inlineStr">
-        <is>
-          <t>översilad björkskog</t>
-        </is>
       </c>
       <c r="AT260" t="inlineStr"/>
       <c r="AW260" t="inlineStr">
         <is>
-          <t>Lars Fröberg</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>Lars Fröberg, Rolf Enander, Patrik Engström</t>
-        </is>
-      </c>
-      <c r="AY260" t="inlineStr">
-        <is>
-          <t>Florainventering av vita fläckar i Lappland</t>
-        </is>
-      </c>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY260" t="inlineStr"/>
       <c r="AZ260" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/87248016</t>
+          <t>https://artportalen.se/Sighting/120543965</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>110501113</v>
+        <v>5171824</v>
       </c>
       <c r="B261" t="n">
         <v>98137</v>
@@ -27907,14 +27906,14 @@
       <c r="I261" t="inlineStr"/>
       <c r="P261" t="inlineStr">
         <is>
-          <t>Per Geijerområdet, T lm</t>
+          <t>kurravaararavinen, T lm</t>
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>723419</v>
+        <v>723525</v>
       </c>
       <c r="R261" t="n">
-        <v>7544672</v>
+        <v>7544228</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -27941,12 +27940,12 @@
       </c>
       <c r="Y261" t="inlineStr">
         <is>
-          <t>2022-08-01</t>
+          <t>2012-08-29</t>
         </is>
       </c>
       <c r="AA261" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
+          <t>2012-08-29</t>
         </is>
       </c>
       <c r="AD261" t="b">
@@ -27961,24 +27960,24 @@
       <c r="AT261" t="inlineStr"/>
       <c r="AW261" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX261" t="inlineStr">
         <is>
-          <t>Mats Williamson, Billy Lindblom, Nils Ericson, Marie Riskilä</t>
+          <t>per-erik mukka, Robert Sandberg, Frédéric Forsmark</t>
         </is>
       </c>
       <c r="AY261" t="inlineStr"/>
       <c r="AZ261" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110501113</t>
+          <t>https://artportalen.se/Sighting/5171824</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>110501115</v>
+        <v>87248016</v>
       </c>
       <c r="B262" t="n">
         <v>98137</v>
@@ -28007,19 +28006,23 @@
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
+      <c r="J262" t="inlineStr"/>
+      <c r="K262" t="inlineStr"/>
+      <c r="L262" t="inlineStr"/>
+      <c r="N262" t="inlineStr"/>
       <c r="P262" t="inlineStr">
         <is>
-          <t>Per Geijerområdet, T lm</t>
+          <t>Kurravaara, södra delen av byn, T lm</t>
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>723637</v>
+        <v>723794</v>
       </c>
       <c r="R262" t="n">
-        <v>7544141</v>
+        <v>7544657</v>
       </c>
       <c r="S262" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T262" t="inlineStr">
         <is>
@@ -28043,12 +28046,12 @@
       </c>
       <c r="Y262" t="inlineStr">
         <is>
-          <t>2022-08-01</t>
+          <t>2020-07-22</t>
         </is>
       </c>
       <c r="AA262" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
+          <t>2020-07-22</t>
         </is>
       </c>
       <c r="AD262" t="b">
@@ -28057,30 +28060,40 @@
       <c r="AE262" t="b">
         <v>0</v>
       </c>
+      <c r="AF262" t="inlineStr"/>
       <c r="AG262" t="b">
         <v>0</v>
+      </c>
+      <c r="AI262" t="inlineStr">
+        <is>
+          <t>översilad björkskog</t>
+        </is>
       </c>
       <c r="AT262" t="inlineStr"/>
       <c r="AW262" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>Lars Fröberg</t>
         </is>
       </c>
       <c r="AX262" t="inlineStr">
         <is>
-          <t>Mats Williamson, Billy Lindblom, Nils Ericson, Marie Riskilä</t>
-        </is>
-      </c>
-      <c r="AY262" t="inlineStr"/>
+          <t>Lars Fröberg, Rolf Enander, Patrik Engström</t>
+        </is>
+      </c>
+      <c r="AY262" t="inlineStr">
+        <is>
+          <t>Florainventering av vita fläckar i Lappland</t>
+        </is>
+      </c>
       <c r="AZ262" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110501115</t>
+          <t>https://artportalen.se/Sighting/87248016</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>110501116</v>
+        <v>110501113</v>
       </c>
       <c r="B263" t="n">
         <v>98137</v>
@@ -28115,10 +28128,10 @@
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>723344</v>
+        <v>723419</v>
       </c>
       <c r="R263" t="n">
-        <v>7544187</v>
+        <v>7544672</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -28176,13 +28189,13 @@
       <c r="AY263" t="inlineStr"/>
       <c r="AZ263" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110501116</t>
+          <t>https://artportalen.se/Sighting/110501113</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>110501117</v>
+        <v>110501115</v>
       </c>
       <c r="B264" t="n">
         <v>98137</v>
@@ -28217,10 +28230,10 @@
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>723094</v>
+        <v>723637</v>
       </c>
       <c r="R264" t="n">
-        <v>7545148</v>
+        <v>7544141</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -28278,13 +28291,13 @@
       <c r="AY264" t="inlineStr"/>
       <c r="AZ264" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110501117</t>
+          <t>https://artportalen.se/Sighting/110501115</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>110501118</v>
+        <v>110501116</v>
       </c>
       <c r="B265" t="n">
         <v>98137</v>
@@ -28319,10 +28332,10 @@
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>723089</v>
+        <v>723344</v>
       </c>
       <c r="R265" t="n">
-        <v>7545162</v>
+        <v>7544187</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -28380,13 +28393,13 @@
       <c r="AY265" t="inlineStr"/>
       <c r="AZ265" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110501118</t>
+          <t>https://artportalen.se/Sighting/110501116</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>110501119</v>
+        <v>110501117</v>
       </c>
       <c r="B266" t="n">
         <v>98137</v>
@@ -28421,10 +28434,10 @@
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>723687</v>
+        <v>723094</v>
       </c>
       <c r="R266" t="n">
-        <v>7545096</v>
+        <v>7545148</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>
@@ -28482,13 +28495,13 @@
       <c r="AY266" t="inlineStr"/>
       <c r="AZ266" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110501119</t>
+          <t>https://artportalen.se/Sighting/110501117</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>110501120</v>
+        <v>110501118</v>
       </c>
       <c r="B267" t="n">
         <v>98137</v>
@@ -28523,10 +28536,10 @@
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>723689</v>
+        <v>723089</v>
       </c>
       <c r="R267" t="n">
-        <v>7545128</v>
+        <v>7545162</v>
       </c>
       <c r="S267" t="n">
         <v>10</v>
@@ -28584,13 +28597,13 @@
       <c r="AY267" t="inlineStr"/>
       <c r="AZ267" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110501120</t>
+          <t>https://artportalen.se/Sighting/110501118</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>111474170</v>
+        <v>110501119</v>
       </c>
       <c r="B268" t="n">
         <v>98137</v>
@@ -28619,17 +28632,16 @@
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
-      <c r="K268" t="inlineStr"/>
       <c r="P268" t="inlineStr">
         <is>
-          <t>kurra, T lm</t>
+          <t>Per Geijerområdet, T lm</t>
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>723317</v>
+        <v>723687</v>
       </c>
       <c r="R268" t="n">
-        <v>7544195</v>
+        <v>7545096</v>
       </c>
       <c r="S268" t="n">
         <v>10</v>
@@ -28656,12 +28668,12 @@
       </c>
       <c r="Y268" t="inlineStr">
         <is>
-          <t>2023-08-14</t>
+          <t>2022-08-01</t>
         </is>
       </c>
       <c r="AA268" t="inlineStr">
         <is>
-          <t>2023-08-14</t>
+          <t>2022-09-07</t>
         </is>
       </c>
       <c r="AD268" t="b">
@@ -28676,24 +28688,24 @@
       <c r="AT268" t="inlineStr"/>
       <c r="AW268" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Mats Williamson</t>
         </is>
       </c>
       <c r="AX268" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Mats Williamson, Billy Lindblom, Nils Ericson, Marie Riskilä</t>
         </is>
       </c>
       <c r="AY268" t="inlineStr"/>
       <c r="AZ268" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111474170</t>
+          <t>https://artportalen.se/Sighting/110501119</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>124355850</v>
+        <v>110501120</v>
       </c>
       <c r="B269" t="n">
         <v>98137</v>
@@ -28724,17 +28736,17 @@
       <c r="I269" t="inlineStr"/>
       <c r="P269" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Per Geijerområdet, T lm</t>
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>723616</v>
+        <v>723689</v>
       </c>
       <c r="R269" t="n">
-        <v>7544154</v>
+        <v>7545128</v>
       </c>
       <c r="S269" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T269" t="inlineStr">
         <is>
@@ -28758,12 +28770,12 @@
       </c>
       <c r="Y269" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2022-08-01</t>
         </is>
       </c>
       <c r="AA269" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2022-09-07</t>
         </is>
       </c>
       <c r="AD269" t="b">
@@ -28778,24 +28790,24 @@
       <c r="AT269" t="inlineStr"/>
       <c r="AW269" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Mats Williamson</t>
         </is>
       </c>
       <c r="AX269" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Mats Williamson, Billy Lindblom, Nils Ericson, Marie Riskilä</t>
         </is>
       </c>
       <c r="AY269" t="inlineStr"/>
       <c r="AZ269" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355850</t>
+          <t>https://artportalen.se/Sighting/110501120</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>124355851</v>
+        <v>111474170</v>
       </c>
       <c r="B270" t="n">
         <v>98137</v>
@@ -28824,19 +28836,20 @@
         </is>
       </c>
       <c r="I270" t="inlineStr"/>
+      <c r="K270" t="inlineStr"/>
       <c r="P270" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>kurra, T lm</t>
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>723705</v>
+        <v>723317</v>
       </c>
       <c r="R270" t="n">
-        <v>7544144</v>
+        <v>7544195</v>
       </c>
       <c r="S270" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T270" t="inlineStr">
         <is>
@@ -28860,12 +28873,12 @@
       </c>
       <c r="Y270" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2023-08-14</t>
         </is>
       </c>
       <c r="AA270" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2023-08-14</t>
         </is>
       </c>
       <c r="AD270" t="b">
@@ -28880,24 +28893,24 @@
       <c r="AT270" t="inlineStr"/>
       <c r="AW270" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX270" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY270" t="inlineStr"/>
       <c r="AZ270" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355851</t>
+          <t>https://artportalen.se/Sighting/111474170</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>124355855</v>
+        <v>124355850</v>
       </c>
       <c r="B271" t="n">
         <v>98137</v>
@@ -28928,14 +28941,14 @@
       <c r="I271" t="inlineStr"/>
       <c r="P271" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>722944</v>
+        <v>723616</v>
       </c>
       <c r="R271" t="n">
-        <v>7544574</v>
+        <v>7544154</v>
       </c>
       <c r="S271" t="n">
         <v>5</v>
@@ -28962,12 +28975,12 @@
       </c>
       <c r="Y271" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA271" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD271" t="b">
@@ -28993,13 +29006,13 @@
       <c r="AY271" t="inlineStr"/>
       <c r="AZ271" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355855</t>
+          <t>https://artportalen.se/Sighting/124355850</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>124355856</v>
+        <v>124355851</v>
       </c>
       <c r="B272" t="n">
         <v>98137</v>
@@ -29030,14 +29043,14 @@
       <c r="I272" t="inlineStr"/>
       <c r="P272" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>723068</v>
+        <v>723705</v>
       </c>
       <c r="R272" t="n">
-        <v>7544568</v>
+        <v>7544144</v>
       </c>
       <c r="S272" t="n">
         <v>5</v>
@@ -29064,12 +29077,12 @@
       </c>
       <c r="Y272" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA272" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD272" t="b">
@@ -29095,13 +29108,13 @@
       <c r="AY272" t="inlineStr"/>
       <c r="AZ272" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355856</t>
+          <t>https://artportalen.se/Sighting/124355851</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>124355857</v>
+        <v>124355855</v>
       </c>
       <c r="B273" t="n">
         <v>98137</v>
@@ -29136,10 +29149,10 @@
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>723343</v>
+        <v>722944</v>
       </c>
       <c r="R273" t="n">
-        <v>7544616</v>
+        <v>7544574</v>
       </c>
       <c r="S273" t="n">
         <v>5</v>
@@ -29197,16 +29210,16 @@
       <c r="AY273" t="inlineStr"/>
       <c r="AZ273" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355857</t>
+          <t>https://artportalen.se/Sighting/124355855</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>110501266</v>
+        <v>124355856</v>
       </c>
       <c r="B274" t="n">
-        <v>97984</v>
+        <v>98137</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -29214,37 +29227,37 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>224362</v>
+        <v>222741</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Nordlummer</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. alpestre</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(Hartm.) Á. Löve &amp; D. Löve</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
       <c r="P274" t="inlineStr">
         <is>
-          <t>Per Geijerområdet, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>723080</v>
+        <v>723068</v>
       </c>
       <c r="R274" t="n">
-        <v>7544690</v>
+        <v>7544568</v>
       </c>
       <c r="S274" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T274" t="inlineStr">
         <is>
@@ -29268,12 +29281,12 @@
       </c>
       <c r="Y274" t="inlineStr">
         <is>
-          <t>2022-08-01</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA274" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD274" t="b">
@@ -29288,67 +29301,65 @@
       <c r="AT274" t="inlineStr"/>
       <c r="AW274" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX274" t="inlineStr">
         <is>
-          <t>Mats Williamson, Billy Lindblom, Nils Ericson, Marie Riskilä</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AY274" t="inlineStr"/>
       <c r="AZ274" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110501266</t>
+          <t>https://artportalen.se/Sighting/124355856</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>61746564</v>
+        <v>124355857</v>
       </c>
       <c r="B275" t="n">
-        <v>79853</v>
+        <v>98137</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>229830</v>
+        <v>222741</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Späd brosklav</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Ramalina dilacerata</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
-      <c r="J275" t="inlineStr"/>
-      <c r="K275" t="inlineStr"/>
       <c r="P275" t="inlineStr">
         <is>
-          <t>kurravaara ravinen, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>723149</v>
+        <v>723343</v>
       </c>
       <c r="R275" t="n">
-        <v>7544666</v>
+        <v>7544616</v>
       </c>
       <c r="S275" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T275" t="inlineStr">
         <is>
@@ -29372,12 +29383,12 @@
       </c>
       <c r="Y275" t="inlineStr">
         <is>
-          <t>2016-10-13</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA275" t="inlineStr">
         <is>
-          <t>2016-10-13</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD275" t="b">
@@ -29392,64 +29403,62 @@
       <c r="AT275" t="inlineStr"/>
       <c r="AW275" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX275" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AY275" t="inlineStr"/>
       <c r="AZ275" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/61746564</t>
+          <t>https://artportalen.se/Sighting/124355857</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>67458187</v>
+        <v>110501266</v>
       </c>
       <c r="B276" t="n">
-        <v>79853</v>
+        <v>97984</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>229830</v>
+        <v>224362</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Späd brosklav</t>
+          <t>Nordlummer</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Ramalina dilacerata</t>
+          <t>Lycopodium annotinum subsp. alpestre</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartm.) Á. Löve &amp; D. Löve</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
-      <c r="J276" t="inlineStr"/>
-      <c r="K276" t="inlineStr"/>
       <c r="P276" t="inlineStr">
         <is>
-          <t>kurravaara ravinen, T lm</t>
+          <t>Per Geijerområdet, T lm</t>
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>723035</v>
+        <v>723080</v>
       </c>
       <c r="R276" t="n">
-        <v>7544622</v>
+        <v>7544690</v>
       </c>
       <c r="S276" t="n">
         <v>10</v>
@@ -29476,12 +29485,12 @@
       </c>
       <c r="Y276" t="inlineStr">
         <is>
-          <t>2017-09-06</t>
+          <t>2022-08-01</t>
         </is>
       </c>
       <c r="AA276" t="inlineStr">
         <is>
-          <t>2017-09-06</t>
+          <t>2022-09-07</t>
         </is>
       </c>
       <c r="AD276" t="b">
@@ -29496,24 +29505,24 @@
       <c r="AT276" t="inlineStr"/>
       <c r="AW276" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Mats Williamson</t>
         </is>
       </c>
       <c r="AX276" t="inlineStr">
         <is>
-          <t>per-erik mukka, Anton Gustafsson</t>
+          <t>Mats Williamson, Billy Lindblom, Nils Ericson, Marie Riskilä</t>
         </is>
       </c>
       <c r="AY276" t="inlineStr"/>
       <c r="AZ276" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67458187</t>
+          <t>https://artportalen.se/Sighting/110501266</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>110501373</v>
+        <v>61746564</v>
       </c>
       <c r="B277" t="n">
         <v>79853</v>
@@ -29542,16 +29551,18 @@
         </is>
       </c>
       <c r="I277" t="inlineStr"/>
+      <c r="J277" t="inlineStr"/>
+      <c r="K277" t="inlineStr"/>
       <c r="P277" t="inlineStr">
         <is>
-          <t>Per Geijerområdet, T lm</t>
+          <t>kurravaara ravinen, T lm</t>
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>723700</v>
+        <v>723149</v>
       </c>
       <c r="R277" t="n">
-        <v>7545087</v>
+        <v>7544666</v>
       </c>
       <c r="S277" t="n">
         <v>10</v>
@@ -29578,12 +29589,12 @@
       </c>
       <c r="Y277" t="inlineStr">
         <is>
-          <t>2022-08-01</t>
+          <t>2016-10-13</t>
         </is>
       </c>
       <c r="AA277" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
+          <t>2016-10-13</t>
         </is>
       </c>
       <c r="AD277" t="b">
@@ -29598,62 +29609,64 @@
       <c r="AT277" t="inlineStr"/>
       <c r="AW277" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX277" t="inlineStr">
         <is>
-          <t>Mats Williamson, Billy Lindblom, Nils Ericson, Marie Riskilä</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY277" t="inlineStr"/>
       <c r="AZ277" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110501373</t>
+          <t>https://artportalen.se/Sighting/61746564</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>110382589</v>
+        <v>67458187</v>
       </c>
       <c r="B278" t="n">
-        <v>95765</v>
+        <v>79853</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E278" t="n">
-        <v>1004672</v>
+        <v>229830</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Källmossor</t>
+          <t>Späd brosklav</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Philonotis</t>
+          <t>Ramalina dilacerata</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>Brid.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
+      <c r="J278" t="inlineStr"/>
+      <c r="K278" t="inlineStr"/>
       <c r="P278" t="inlineStr">
         <is>
-          <t>Per Geijerområdet, T lm</t>
+          <t>kurravaara ravinen, T lm</t>
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>722988</v>
+        <v>723035</v>
       </c>
       <c r="R278" t="n">
-        <v>7544586</v>
+        <v>7544622</v>
       </c>
       <c r="S278" t="n">
         <v>10</v>
@@ -29680,12 +29693,12 @@
       </c>
       <c r="Y278" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2017-09-06</t>
         </is>
       </c>
       <c r="AA278" t="inlineStr">
         <is>
-          <t>2021-09-17</t>
+          <t>2017-09-06</t>
         </is>
       </c>
       <c r="AD278" t="b">
@@ -29700,49 +29713,49 @@
       <c r="AT278" t="inlineStr"/>
       <c r="AW278" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX278" t="inlineStr">
         <is>
-          <t>Mats Williamson, Billy Lindblom</t>
+          <t>per-erik mukka, Anton Gustafsson</t>
         </is>
       </c>
       <c r="AY278" t="inlineStr"/>
       <c r="AZ278" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110382589</t>
+          <t>https://artportalen.se/Sighting/67458187</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>110382591</v>
+        <v>110501373</v>
       </c>
       <c r="B279" t="n">
-        <v>95765</v>
+        <v>79853</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E279" t="n">
-        <v>1004672</v>
+        <v>229830</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Källmossor</t>
+          <t>Späd brosklav</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Philonotis</t>
+          <t>Ramalina dilacerata</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>Brid.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I279" t="inlineStr"/>
@@ -29752,10 +29765,10 @@
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>723470</v>
+        <v>723700</v>
       </c>
       <c r="R279" t="n">
-        <v>7543932</v>
+        <v>7545087</v>
       </c>
       <c r="S279" t="n">
         <v>10</v>
@@ -29782,12 +29795,12 @@
       </c>
       <c r="Y279" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2022-08-01</t>
         </is>
       </c>
       <c r="AA279" t="inlineStr">
         <is>
-          <t>2021-09-17</t>
+          <t>2022-09-07</t>
         </is>
       </c>
       <c r="AD279" t="b">
@@ -29807,19 +29820,19 @@
       </c>
       <c r="AX279" t="inlineStr">
         <is>
-          <t>Mats Williamson, Billy Lindblom</t>
+          <t>Mats Williamson, Billy Lindblom, Nils Ericson, Marie Riskilä</t>
         </is>
       </c>
       <c r="AY279" t="inlineStr"/>
       <c r="AZ279" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110382591</t>
+          <t>https://artportalen.se/Sighting/110501373</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>110382592</v>
+        <v>110382589</v>
       </c>
       <c r="B280" t="n">
         <v>95765</v>
@@ -29854,10 +29867,10 @@
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>723244</v>
+        <v>722988</v>
       </c>
       <c r="R280" t="n">
-        <v>7544649</v>
+        <v>7544586</v>
       </c>
       <c r="S280" t="n">
         <v>10</v>
@@ -29915,51 +29928,51 @@
       <c r="AY280" t="inlineStr"/>
       <c r="AZ280" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110382592</t>
+          <t>https://artportalen.se/Sighting/110382589</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>110044455</v>
+        <v>110382591</v>
       </c>
       <c r="B281" t="n">
-        <v>79406</v>
+        <v>95765</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E281" t="n">
-        <v>864</v>
+        <v>1004672</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Källmossor</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Philonotis</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>Brid.</t>
         </is>
       </c>
       <c r="I281" t="inlineStr"/>
       <c r="P281" t="inlineStr">
         <is>
-          <t>Rautasälven-Sakkaravaara, T lm</t>
+          <t>Per Geijerområdet, T lm</t>
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>723964</v>
+        <v>723470</v>
       </c>
       <c r="R281" t="n">
-        <v>7543542</v>
+        <v>7543932</v>
       </c>
       <c r="S281" t="n">
         <v>10</v>
@@ -29986,12 +29999,12 @@
       </c>
       <c r="Y281" t="inlineStr">
         <is>
-          <t>2022-08-15</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="AA281" t="inlineStr">
         <is>
-          <t>2022-08-15</t>
+          <t>2021-09-17</t>
         </is>
       </c>
       <c r="AD281" t="b">
@@ -30006,62 +30019,62 @@
       <c r="AT281" t="inlineStr"/>
       <c r="AW281" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Mats Williamson</t>
         </is>
       </c>
       <c r="AX281" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Mats Williamson, Billy Lindblom</t>
         </is>
       </c>
       <c r="AY281" t="inlineStr"/>
       <c r="AZ281" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110044455</t>
+          <t>https://artportalen.se/Sighting/110382591</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>110044453</v>
+        <v>110382592</v>
       </c>
       <c r="B282" t="n">
-        <v>91905</v>
+        <v>95765</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E282" t="n">
-        <v>1108</v>
+        <v>1004672</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Källmossor</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Philonotis</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Brid.</t>
         </is>
       </c>
       <c r="I282" t="inlineStr"/>
       <c r="P282" t="inlineStr">
         <is>
-          <t>Rautasälven-Sakkaravaara, T lm</t>
+          <t>Per Geijerområdet, T lm</t>
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>723912</v>
+        <v>723244</v>
       </c>
       <c r="R282" t="n">
-        <v>7543588</v>
+        <v>7544649</v>
       </c>
       <c r="S282" t="n">
         <v>10</v>
@@ -30088,12 +30101,12 @@
       </c>
       <c r="Y282" t="inlineStr">
         <is>
-          <t>2022-08-15</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="AA282" t="inlineStr">
         <is>
-          <t>2022-08-15</t>
+          <t>2021-09-17</t>
         </is>
       </c>
       <c r="AD282" t="b">
@@ -30108,27 +30121,27 @@
       <c r="AT282" t="inlineStr"/>
       <c r="AW282" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Mats Williamson</t>
         </is>
       </c>
       <c r="AX282" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Mats Williamson, Billy Lindblom</t>
         </is>
       </c>
       <c r="AY282" t="inlineStr"/>
       <c r="AZ282" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110044453</t>
+          <t>https://artportalen.se/Sighting/110382592</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>110044454</v>
+        <v>110044455</v>
       </c>
       <c r="B283" t="n">
-        <v>91905</v>
+        <v>79406</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -30136,21 +30149,21 @@
         </is>
       </c>
       <c r="E283" t="n">
-        <v>1108</v>
+        <v>864</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I283" t="inlineStr"/>
@@ -30160,10 +30173,10 @@
         </is>
       </c>
       <c r="Q283" t="n">
-        <v>723973</v>
+        <v>723964</v>
       </c>
       <c r="R283" t="n">
-        <v>7543537</v>
+        <v>7543542</v>
       </c>
       <c r="S283" t="n">
         <v>10</v>
@@ -30221,16 +30234,16 @@
       <c r="AY283" t="inlineStr"/>
       <c r="AZ283" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110044454</t>
+          <t>https://artportalen.se/Sighting/110044455</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>102907874</v>
+        <v>110044453</v>
       </c>
       <c r="B284" t="n">
-        <v>89156</v>
+        <v>91905</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -30238,38 +30251,37 @@
         </is>
       </c>
       <c r="E284" t="n">
-        <v>4412</v>
+        <v>1108</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I284" t="inlineStr"/>
-      <c r="K284" t="inlineStr"/>
       <c r="P284" t="inlineStr">
         <is>
-          <t>Kurravaara vägen , T lm</t>
+          <t>Rautasälven-Sakkaravaara, T lm</t>
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>723850</v>
+        <v>723912</v>
       </c>
       <c r="R284" t="n">
-        <v>7543562</v>
+        <v>7543588</v>
       </c>
       <c r="S284" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T284" t="inlineStr">
         <is>
@@ -30296,19 +30308,9 @@
           <t>2022-08-15</t>
         </is>
       </c>
-      <c r="Z284" t="inlineStr">
-        <is>
-          <t>17:50</t>
-        </is>
-      </c>
       <c r="AA284" t="inlineStr">
         <is>
           <t>2022-08-15</t>
-        </is>
-      </c>
-      <c r="AB284" t="inlineStr">
-        <is>
-          <t>17:50</t>
         </is>
       </c>
       <c r="AD284" t="b">
@@ -30323,7 +30325,7 @@
       <c r="AT284" t="inlineStr"/>
       <c r="AW284" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AX284" t="inlineStr">
@@ -30334,16 +30336,16 @@
       <c r="AY284" t="inlineStr"/>
       <c r="AZ284" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102907874</t>
+          <t>https://artportalen.se/Sighting/110044453</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>110044449</v>
+        <v>110044454</v>
       </c>
       <c r="B285" t="n">
-        <v>89156</v>
+        <v>91905</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -30351,21 +30353,21 @@
         </is>
       </c>
       <c r="E285" t="n">
-        <v>4412</v>
+        <v>1108</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I285" t="inlineStr"/>
@@ -30375,10 +30377,10 @@
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>723831</v>
+        <v>723973</v>
       </c>
       <c r="R285" t="n">
-        <v>7543547</v>
+        <v>7543537</v>
       </c>
       <c r="S285" t="n">
         <v>10</v>
@@ -30436,16 +30438,16 @@
       <c r="AY285" t="inlineStr"/>
       <c r="AZ285" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110044449</t>
+          <t>https://artportalen.se/Sighting/110044454</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>117357759</v>
+        <v>102907874</v>
       </c>
       <c r="B286" t="n">
-        <v>58388</v>
+        <v>89156</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -30453,39 +30455,35 @@
         </is>
       </c>
       <c r="E286" t="n">
-        <v>103001</v>
+        <v>4412</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I286" t="inlineStr"/>
-      <c r="M286" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="K286" t="inlineStr"/>
       <c r="P286" t="inlineStr">
         <is>
-          <t>Kurravaaravägen, Kiruna, T lm</t>
+          <t>Kurravaara vägen , T lm</t>
         </is>
       </c>
       <c r="Q286" t="n">
-        <v>724020</v>
+        <v>723850</v>
       </c>
       <c r="R286" t="n">
-        <v>7543442</v>
+        <v>7543562</v>
       </c>
       <c r="S286" t="n">
         <v>25</v>
@@ -30512,22 +30510,22 @@
       </c>
       <c r="Y286" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2022-08-15</t>
         </is>
       </c>
       <c r="Z286" t="inlineStr">
         <is>
-          <t>19:46</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA286" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2022-08-15</t>
         </is>
       </c>
       <c r="AB286" t="inlineStr">
         <is>
-          <t>19:46</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD286" t="b">
@@ -30547,65 +30545,57 @@
       </c>
       <c r="AX286" t="inlineStr">
         <is>
-          <t>per-erik mukka, Robert Flygare</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY286" t="inlineStr"/>
       <c r="AZ286" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117357759</t>
+          <t>https://artportalen.se/Sighting/102907874</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>111591780</v>
+        <v>110044449</v>
       </c>
       <c r="B287" t="n">
-        <v>99120</v>
+        <v>89156</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E287" t="n">
-        <v>219811</v>
+        <v>4412</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I287" t="inlineStr"/>
-      <c r="J287" t="inlineStr"/>
-      <c r="K287" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L287" t="inlineStr"/>
-      <c r="N287" t="inlineStr"/>
       <c r="P287" t="inlineStr">
         <is>
-          <t>Kurravaaravägen 60, Kiruna, Kurravaaravägen 60, Kiruna, T lm</t>
+          <t>Rautasälven-Sakkaravaara, T lm</t>
         </is>
       </c>
       <c r="Q287" t="n">
-        <v>723842</v>
+        <v>723831</v>
       </c>
       <c r="R287" t="n">
-        <v>7544794</v>
+        <v>7543547</v>
       </c>
       <c r="S287" t="n">
         <v>10</v>
@@ -30632,12 +30622,12 @@
       </c>
       <c r="Y287" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2022-08-15</t>
         </is>
       </c>
       <c r="AA287" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2022-08-15</t>
         </is>
       </c>
       <c r="AD287" t="b">
@@ -30646,84 +30636,76 @@
       <c r="AE287" t="b">
         <v>0</v>
       </c>
-      <c r="AF287" t="inlineStr"/>
       <c r="AG287" t="b">
         <v>0</v>
       </c>
       <c r="AT287" t="inlineStr"/>
       <c r="AW287" t="inlineStr">
         <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX287" t="inlineStr">
+        <is>
           <t>per-erik mukka</t>
-        </is>
-      </c>
-      <c r="AX287" t="inlineStr">
-        <is>
-          <t>per-erik mukka, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY287" t="inlineStr"/>
       <c r="AZ287" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111591780</t>
+          <t>https://artportalen.se/Sighting/110044449</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>87676926</v>
+        <v>117357759</v>
       </c>
       <c r="B288" t="n">
-        <v>99118</v>
+        <v>58388</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E288" t="n">
-        <v>220787</v>
+        <v>103001</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I288" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J288" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K288" t="inlineStr"/>
-      <c r="L288" t="inlineStr"/>
-      <c r="N288" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr"/>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P288" t="inlineStr">
         <is>
-          <t>kurravaara, T lm</t>
+          <t>Kurravaaravägen, Kiruna, T lm</t>
         </is>
       </c>
       <c r="Q288" t="n">
-        <v>724031</v>
+        <v>724020</v>
       </c>
       <c r="R288" t="n">
-        <v>7543433</v>
+        <v>7543442</v>
       </c>
       <c r="S288" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T288" t="inlineStr">
         <is>
@@ -30747,12 +30729,22 @@
       </c>
       <c r="Y288" t="inlineStr">
         <is>
-          <t>2020-08-12</t>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="Z288" t="inlineStr">
+        <is>
+          <t>19:46</t>
         </is>
       </c>
       <c r="AA288" t="inlineStr">
         <is>
-          <t>2020-08-12</t>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AB288" t="inlineStr">
+        <is>
+          <t>19:46</t>
         </is>
       </c>
       <c r="AD288" t="b">
@@ -30761,51 +30753,50 @@
       <c r="AE288" t="b">
         <v>0</v>
       </c>
-      <c r="AF288" t="inlineStr"/>
       <c r="AG288" t="b">
         <v>0</v>
       </c>
       <c r="AT288" t="inlineStr"/>
       <c r="AW288" t="inlineStr">
         <is>
-          <t>Albin Belsing</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX288" t="inlineStr">
         <is>
-          <t>Albin Belsing</t>
+          <t>per-erik mukka, Robert Flygare</t>
         </is>
       </c>
       <c r="AY288" t="inlineStr"/>
       <c r="AZ288" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/87676926</t>
+          <t>https://artportalen.se/Sighting/117357759</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>95153649</v>
+        <v>111591780</v>
       </c>
       <c r="B289" t="n">
-        <v>99118</v>
+        <v>99120</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E289" t="n">
-        <v>220787</v>
+        <v>219811</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -30813,26 +30804,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I289" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K289" t="inlineStr"/>
+      <c r="I289" t="inlineStr"/>
+      <c r="J289" t="inlineStr"/>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L289" t="inlineStr"/>
+      <c r="N289" t="inlineStr"/>
       <c r="P289" t="inlineStr">
         <is>
-          <t>Kurravaaravägen, Kiruna, T lm</t>
+          <t>Kurravaaravägen 60, Kiruna, Kurravaaravägen 60, Kiruna, T lm</t>
         </is>
       </c>
       <c r="Q289" t="n">
-        <v>724068</v>
+        <v>723842</v>
       </c>
       <c r="R289" t="n">
-        <v>7543343</v>
+        <v>7544794</v>
       </c>
       <c r="S289" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T289" t="inlineStr">
         <is>
@@ -30856,22 +30849,12 @@
       </c>
       <c r="Y289" t="inlineStr">
         <is>
-          <t>2021-07-29</t>
-        </is>
-      </c>
-      <c r="Z289" t="inlineStr">
-        <is>
-          <t>14:11</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="AA289" t="inlineStr">
         <is>
-          <t>2021-07-29</t>
-        </is>
-      </c>
-      <c r="AB289" t="inlineStr">
-        <is>
-          <t>14:11</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="AD289" t="b">
@@ -30880,6 +30863,7 @@
       <c r="AE289" t="b">
         <v>0</v>
       </c>
+      <c r="AF289" t="inlineStr"/>
       <c r="AG289" t="b">
         <v>0</v>
       </c>
@@ -30891,19 +30875,19 @@
       </c>
       <c r="AX289" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>per-erik mukka, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY289" t="inlineStr"/>
       <c r="AZ289" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95153649</t>
+          <t>https://artportalen.se/Sighting/111591780</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>95153730</v>
+        <v>87676926</v>
       </c>
       <c r="B290" t="n">
         <v>99118</v>
@@ -30933,24 +30917,30 @@
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K290" t="inlineStr"/>
       <c r="L290" t="inlineStr"/>
+      <c r="N290" t="inlineStr"/>
       <c r="P290" t="inlineStr">
         <is>
-          <t>Kurravaaravägen, Kiruna, T lm</t>
+          <t>kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q290" t="n">
-        <v>724057</v>
+        <v>724031</v>
       </c>
       <c r="R290" t="n">
-        <v>7543346</v>
+        <v>7543433</v>
       </c>
       <c r="S290" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T290" t="inlineStr">
         <is>
@@ -30974,22 +30964,12 @@
       </c>
       <c r="Y290" t="inlineStr">
         <is>
-          <t>2021-07-29</t>
-        </is>
-      </c>
-      <c r="Z290" t="inlineStr">
-        <is>
-          <t>14:16</t>
+          <t>2020-08-12</t>
         </is>
       </c>
       <c r="AA290" t="inlineStr">
         <is>
-          <t>2021-07-29</t>
-        </is>
-      </c>
-      <c r="AB290" t="inlineStr">
-        <is>
-          <t>14:16</t>
+          <t>2020-08-12</t>
         </is>
       </c>
       <c r="AD290" t="b">
@@ -30998,30 +30978,31 @@
       <c r="AE290" t="b">
         <v>0</v>
       </c>
+      <c r="AF290" t="inlineStr"/>
       <c r="AG290" t="b">
         <v>0</v>
       </c>
       <c r="AT290" t="inlineStr"/>
       <c r="AW290" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Albin Belsing</t>
         </is>
       </c>
       <c r="AX290" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Albin Belsing</t>
         </is>
       </c>
       <c r="AY290" t="inlineStr"/>
       <c r="AZ290" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95153730</t>
+          <t>https://artportalen.se/Sighting/87676926</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>95153759</v>
+        <v>95153649</v>
       </c>
       <c r="B291" t="n">
         <v>99118</v>
@@ -31051,7 +31032,7 @@
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K291" t="inlineStr"/>
@@ -31062,10 +31043,10 @@
         </is>
       </c>
       <c r="Q291" t="n">
-        <v>724041</v>
+        <v>724068</v>
       </c>
       <c r="R291" t="n">
-        <v>7543391</v>
+        <v>7543343</v>
       </c>
       <c r="S291" t="n">
         <v>25</v>
@@ -31097,7 +31078,7 @@
       </c>
       <c r="Z291" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA291" t="inlineStr">
@@ -31107,7 +31088,7 @@
       </c>
       <c r="AB291" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD291" t="b">
@@ -31133,13 +31114,13 @@
       <c r="AY291" t="inlineStr"/>
       <c r="AZ291" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95153759</t>
+          <t>https://artportalen.se/Sighting/95153649</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>95153809</v>
+        <v>95153730</v>
       </c>
       <c r="B292" t="n">
         <v>99118</v>
@@ -31167,7 +31148,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I292" t="inlineStr"/>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="K292" t="inlineStr"/>
       <c r="L292" t="inlineStr"/>
       <c r="P292" t="inlineStr">
@@ -31176,10 +31161,10 @@
         </is>
       </c>
       <c r="Q292" t="n">
-        <v>724024</v>
+        <v>724057</v>
       </c>
       <c r="R292" t="n">
-        <v>7543435</v>
+        <v>7543346</v>
       </c>
       <c r="S292" t="n">
         <v>25</v>
@@ -31211,7 +31196,7 @@
       </c>
       <c r="Z292" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA292" t="inlineStr">
@@ -31221,7 +31206,7 @@
       </c>
       <c r="AB292" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD292" t="b">
@@ -31247,13 +31232,13 @@
       <c r="AY292" t="inlineStr"/>
       <c r="AZ292" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95153809</t>
+          <t>https://artportalen.se/Sighting/95153730</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>95153843</v>
+        <v>95153759</v>
       </c>
       <c r="B293" t="n">
         <v>99118</v>
@@ -31283,7 +31268,7 @@
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K293" t="inlineStr"/>
@@ -31294,10 +31279,10 @@
         </is>
       </c>
       <c r="Q293" t="n">
-        <v>724022</v>
+        <v>724041</v>
       </c>
       <c r="R293" t="n">
-        <v>7543454</v>
+        <v>7543391</v>
       </c>
       <c r="S293" t="n">
         <v>25</v>
@@ -31329,7 +31314,7 @@
       </c>
       <c r="Z293" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA293" t="inlineStr">
@@ -31339,7 +31324,7 @@
       </c>
       <c r="AB293" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD293" t="b">
@@ -31365,13 +31350,13 @@
       <c r="AY293" t="inlineStr"/>
       <c r="AZ293" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95153843</t>
+          <t>https://artportalen.se/Sighting/95153759</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>95153900</v>
+        <v>95153809</v>
       </c>
       <c r="B294" t="n">
         <v>99118</v>
@@ -31399,11 +31384,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I294" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="I294" t="inlineStr"/>
       <c r="K294" t="inlineStr"/>
       <c r="L294" t="inlineStr"/>
       <c r="P294" t="inlineStr">
@@ -31412,10 +31393,10 @@
         </is>
       </c>
       <c r="Q294" t="n">
-        <v>724016</v>
+        <v>724024</v>
       </c>
       <c r="R294" t="n">
-        <v>7543475</v>
+        <v>7543435</v>
       </c>
       <c r="S294" t="n">
         <v>25</v>
@@ -31447,7 +31428,7 @@
       </c>
       <c r="Z294" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA294" t="inlineStr">
@@ -31457,7 +31438,7 @@
       </c>
       <c r="AB294" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD294" t="b">
@@ -31483,43 +31464,43 @@
       <c r="AY294" t="inlineStr"/>
       <c r="AZ294" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95153900</t>
+          <t>https://artportalen.se/Sighting/95153809</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>94564368</v>
+        <v>95153843</v>
       </c>
       <c r="B295" t="n">
-        <v>106229</v>
+        <v>99118</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E295" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K295" t="inlineStr"/>
@@ -31530,10 +31511,10 @@
         </is>
       </c>
       <c r="Q295" t="n">
-        <v>724020</v>
+        <v>724022</v>
       </c>
       <c r="R295" t="n">
-        <v>7543442</v>
+        <v>7543454</v>
       </c>
       <c r="S295" t="n">
         <v>25</v>
@@ -31560,22 +31541,22 @@
       </c>
       <c r="Y295" t="inlineStr">
         <is>
-          <t>2021-06-29</t>
+          <t>2021-07-29</t>
         </is>
       </c>
       <c r="Z295" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA295" t="inlineStr">
         <is>
-          <t>2021-06-29</t>
+          <t>2021-07-29</t>
         </is>
       </c>
       <c r="AB295" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD295" t="b">
@@ -31600,6 +31581,242 @@
       </c>
       <c r="AY295" t="inlineStr"/>
       <c r="AZ295" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95153843</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="n">
+        <v>95153900</v>
+      </c>
+      <c r="B296" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E296" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr"/>
+      <c r="L296" t="inlineStr"/>
+      <c r="P296" t="inlineStr">
+        <is>
+          <t>Kurravaaravägen, Kiruna, T lm</t>
+        </is>
+      </c>
+      <c r="Q296" t="n">
+        <v>724016</v>
+      </c>
+      <c r="R296" t="n">
+        <v>7543475</v>
+      </c>
+      <c r="S296" t="n">
+        <v>25</v>
+      </c>
+      <c r="T296" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U296" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V296" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W296" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y296" t="inlineStr">
+        <is>
+          <t>2021-07-29</t>
+        </is>
+      </c>
+      <c r="Z296" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AA296" t="inlineStr">
+        <is>
+          <t>2021-07-29</t>
+        </is>
+      </c>
+      <c r="AB296" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AD296" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE296" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG296" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT296" t="inlineStr"/>
+      <c r="AW296" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX296" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY296" t="inlineStr"/>
+      <c r="AZ296" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95153900</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="n">
+        <v>94564368</v>
+      </c>
+      <c r="B297" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E297" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr"/>
+      <c r="L297" t="inlineStr"/>
+      <c r="P297" t="inlineStr">
+        <is>
+          <t>Kurravaaravägen, Kiruna, T lm</t>
+        </is>
+      </c>
+      <c r="Q297" t="n">
+        <v>724020</v>
+      </c>
+      <c r="R297" t="n">
+        <v>7543442</v>
+      </c>
+      <c r="S297" t="n">
+        <v>25</v>
+      </c>
+      <c r="T297" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U297" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V297" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W297" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y297" t="inlineStr">
+        <is>
+          <t>2021-06-29</t>
+        </is>
+      </c>
+      <c r="Z297" t="inlineStr">
+        <is>
+          <t>19:56</t>
+        </is>
+      </c>
+      <c r="AA297" t="inlineStr">
+        <is>
+          <t>2021-06-29</t>
+        </is>
+      </c>
+      <c r="AB297" t="inlineStr">
+        <is>
+          <t>19:56</t>
+        </is>
+      </c>
+      <c r="AD297" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE297" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG297" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT297" t="inlineStr"/>
+      <c r="AW297" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX297" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY297" t="inlineStr"/>
+      <c r="AZ297" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/94564368</t>
         </is>
@@ -31901,6 +32118,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ293" r:id="rId292"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ294" r:id="rId293"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ295" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ296" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ297" r:id="rId296"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -24575,7 +24575,7 @@
         <v>135650446</v>
       </c>
       <c r="B229" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -24686,7 +24686,7 @@
         <v>135651394</v>
       </c>
       <c r="B230" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ295"/>
+  <dimension ref="A1:AZ297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24572,52 +24572,57 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>87248041</v>
+        <v>135650446</v>
       </c>
       <c r="B229" t="n">
-        <v>106229</v>
+        <v>99274</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I229" t="inlineStr"/>
-      <c r="J229" t="inlineStr"/>
-      <c r="K229" t="inlineStr"/>
-      <c r="L229" t="inlineStr"/>
-      <c r="N229" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P229" t="inlineStr">
         <is>
-          <t>Kurravaara, södra delen av byn, T lm</t>
+          <t>Koivuvaara SV Kurravaara by, T lm</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>723794</v>
+        <v>723076</v>
       </c>
       <c r="R229" t="n">
-        <v>7544657</v>
+        <v>7545065</v>
       </c>
       <c r="S229" t="n">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="T229" t="inlineStr">
         <is>
@@ -24641,12 +24646,12 @@
       </c>
       <c r="Y229" t="inlineStr">
         <is>
-          <t>2020-07-22</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
         <is>
-          <t>2020-07-22</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -24655,81 +24660,75 @@
       <c r="AE229" t="b">
         <v>0</v>
       </c>
-      <c r="AF229" t="inlineStr"/>
       <c r="AG229" t="b">
         <v>0</v>
-      </c>
-      <c r="AI229" t="inlineStr">
-        <is>
-          <t>översilad björkskog</t>
-        </is>
       </c>
       <c r="AT229" t="inlineStr"/>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>Lars Fröberg</t>
+          <t>Anna Öhlund</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>Lars Fröberg, Rolf Enander, Patrik Engström</t>
-        </is>
-      </c>
-      <c r="AY229" t="inlineStr">
-        <is>
-          <t>Florainventering av vita fläckar i Lappland</t>
-        </is>
-      </c>
+          <t>Anna Öhlund</t>
+        </is>
+      </c>
+      <c r="AY229" t="inlineStr"/>
       <c r="AZ229" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/87248041</t>
+          <t>https://artportalen.se/Sighting/135650446</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>124355513</v>
+        <v>135651394</v>
       </c>
       <c r="B230" t="n">
-        <v>106229</v>
+        <v>99274</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I230" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P230" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Gruvberget, T lm</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>723653</v>
+        <v>723268</v>
       </c>
       <c r="R230" t="n">
-        <v>7544288</v>
+        <v>7544995</v>
       </c>
       <c r="S230" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T230" t="inlineStr">
         <is>
@@ -24753,12 +24752,12 @@
       </c>
       <c r="Y230" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA230" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD230" t="b">
@@ -24773,24 +24772,24 @@
       <c r="AT230" t="inlineStr"/>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Anna Öhlund</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Anna Öhlund</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
       <c r="AZ230" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355513</t>
+          <t>https://artportalen.se/Sighting/135651394</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>124355515</v>
+        <v>87248041</v>
       </c>
       <c r="B231" t="n">
         <v>106229</v>
@@ -24819,19 +24818,23 @@
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
+      <c r="J231" t="inlineStr"/>
+      <c r="K231" t="inlineStr"/>
+      <c r="L231" t="inlineStr"/>
+      <c r="N231" t="inlineStr"/>
       <c r="P231" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Kurravaara, södra delen av byn, T lm</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>723720</v>
+        <v>723794</v>
       </c>
       <c r="R231" t="n">
-        <v>7544240</v>
+        <v>7544657</v>
       </c>
       <c r="S231" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T231" t="inlineStr">
         <is>
@@ -24855,12 +24858,12 @@
       </c>
       <c r="Y231" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2020-07-22</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2020-07-22</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -24869,30 +24872,40 @@
       <c r="AE231" t="b">
         <v>0</v>
       </c>
+      <c r="AF231" t="inlineStr"/>
       <c r="AG231" t="b">
         <v>0</v>
+      </c>
+      <c r="AI231" t="inlineStr">
+        <is>
+          <t>översilad björkskog</t>
+        </is>
       </c>
       <c r="AT231" t="inlineStr"/>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Lars Fröberg</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
-        </is>
-      </c>
-      <c r="AY231" t="inlineStr"/>
+          <t>Lars Fröberg, Rolf Enander, Patrik Engström</t>
+        </is>
+      </c>
+      <c r="AY231" t="inlineStr">
+        <is>
+          <t>Florainventering av vita fläckar i Lappland</t>
+        </is>
+      </c>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355515</t>
+          <t>https://artportalen.se/Sighting/87248041</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>124355516</v>
+        <v>124355513</v>
       </c>
       <c r="B232" t="n">
         <v>106229</v>
@@ -24927,10 +24940,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>723694</v>
+        <v>723653</v>
       </c>
       <c r="R232" t="n">
-        <v>7544160</v>
+        <v>7544288</v>
       </c>
       <c r="S232" t="n">
         <v>5</v>
@@ -24988,13 +25001,13 @@
       <c r="AY232" t="inlineStr"/>
       <c r="AZ232" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355516</t>
+          <t>https://artportalen.se/Sighting/124355513</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>124355528</v>
+        <v>124355515</v>
       </c>
       <c r="B233" t="n">
         <v>106229</v>
@@ -25025,14 +25038,14 @@
       <c r="I233" t="inlineStr"/>
       <c r="P233" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>723593</v>
+        <v>723720</v>
       </c>
       <c r="R233" t="n">
-        <v>7545295</v>
+        <v>7544240</v>
       </c>
       <c r="S233" t="n">
         <v>5</v>
@@ -25059,12 +25072,12 @@
       </c>
       <c r="Y233" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA233" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -25090,13 +25103,13 @@
       <c r="AY233" t="inlineStr"/>
       <c r="AZ233" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355528</t>
+          <t>https://artportalen.se/Sighting/124355515</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>124355529</v>
+        <v>124355516</v>
       </c>
       <c r="B234" t="n">
         <v>106229</v>
@@ -25127,14 +25140,14 @@
       <c r="I234" t="inlineStr"/>
       <c r="P234" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>723365</v>
+        <v>723694</v>
       </c>
       <c r="R234" t="n">
-        <v>7545207</v>
+        <v>7544160</v>
       </c>
       <c r="S234" t="n">
         <v>5</v>
@@ -25161,12 +25174,12 @@
       </c>
       <c r="Y234" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA234" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD234" t="b">
@@ -25192,13 +25205,13 @@
       <c r="AY234" t="inlineStr"/>
       <c r="AZ234" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355529</t>
+          <t>https://artportalen.se/Sighting/124355516</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>124355530</v>
+        <v>124355528</v>
       </c>
       <c r="B235" t="n">
         <v>106229</v>
@@ -25233,10 +25246,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>723178</v>
+        <v>723593</v>
       </c>
       <c r="R235" t="n">
-        <v>7545219</v>
+        <v>7545295</v>
       </c>
       <c r="S235" t="n">
         <v>5</v>
@@ -25294,13 +25307,13 @@
       <c r="AY235" t="inlineStr"/>
       <c r="AZ235" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355530</t>
+          <t>https://artportalen.se/Sighting/124355528</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>124355531</v>
+        <v>124355529</v>
       </c>
       <c r="B236" t="n">
         <v>106229</v>
@@ -25335,10 +25348,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>723120</v>
+        <v>723365</v>
       </c>
       <c r="R236" t="n">
-        <v>7545233</v>
+        <v>7545207</v>
       </c>
       <c r="S236" t="n">
         <v>5</v>
@@ -25396,13 +25409,13 @@
       <c r="AY236" t="inlineStr"/>
       <c r="AZ236" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355531</t>
+          <t>https://artportalen.se/Sighting/124355529</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>124355538</v>
+        <v>124355530</v>
       </c>
       <c r="B237" t="n">
         <v>106229</v>
@@ -25437,10 +25450,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>722917</v>
+        <v>723178</v>
       </c>
       <c r="R237" t="n">
-        <v>7544575</v>
+        <v>7545219</v>
       </c>
       <c r="S237" t="n">
         <v>5</v>
@@ -25498,13 +25511,13 @@
       <c r="AY237" t="inlineStr"/>
       <c r="AZ237" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355538</t>
+          <t>https://artportalen.se/Sighting/124355530</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>124355539</v>
+        <v>124355531</v>
       </c>
       <c r="B238" t="n">
         <v>106229</v>
@@ -25539,10 +25552,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>722977</v>
+        <v>723120</v>
       </c>
       <c r="R238" t="n">
-        <v>7544571</v>
+        <v>7545233</v>
       </c>
       <c r="S238" t="n">
         <v>5</v>
@@ -25600,13 +25613,13 @@
       <c r="AY238" t="inlineStr"/>
       <c r="AZ238" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355539</t>
+          <t>https://artportalen.se/Sighting/124355531</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>124355540</v>
+        <v>124355538</v>
       </c>
       <c r="B239" t="n">
         <v>106229</v>
@@ -25641,10 +25654,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>723038</v>
+        <v>722917</v>
       </c>
       <c r="R239" t="n">
-        <v>7544552</v>
+        <v>7544575</v>
       </c>
       <c r="S239" t="n">
         <v>5</v>
@@ -25702,13 +25715,13 @@
       <c r="AY239" t="inlineStr"/>
       <c r="AZ239" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355540</t>
+          <t>https://artportalen.se/Sighting/124355538</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>124355541</v>
+        <v>124355539</v>
       </c>
       <c r="B240" t="n">
         <v>106229</v>
@@ -25743,10 +25756,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>723087</v>
+        <v>722977</v>
       </c>
       <c r="R240" t="n">
-        <v>7544566</v>
+        <v>7544571</v>
       </c>
       <c r="S240" t="n">
         <v>5</v>
@@ -25804,13 +25817,13 @@
       <c r="AY240" t="inlineStr"/>
       <c r="AZ240" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355541</t>
+          <t>https://artportalen.se/Sighting/124355539</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>124355542</v>
+        <v>124355540</v>
       </c>
       <c r="B241" t="n">
         <v>106229</v>
@@ -25845,10 +25858,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>723159</v>
+        <v>723038</v>
       </c>
       <c r="R241" t="n">
-        <v>7544605</v>
+        <v>7544552</v>
       </c>
       <c r="S241" t="n">
         <v>5</v>
@@ -25906,13 +25919,13 @@
       <c r="AY241" t="inlineStr"/>
       <c r="AZ241" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355542</t>
+          <t>https://artportalen.se/Sighting/124355540</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>124355543</v>
+        <v>124355541</v>
       </c>
       <c r="B242" t="n">
         <v>106229</v>
@@ -25947,10 +25960,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>723227</v>
+        <v>723087</v>
       </c>
       <c r="R242" t="n">
-        <v>7544640</v>
+        <v>7544566</v>
       </c>
       <c r="S242" t="n">
         <v>5</v>
@@ -26008,13 +26021,13 @@
       <c r="AY242" t="inlineStr"/>
       <c r="AZ242" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355543</t>
+          <t>https://artportalen.se/Sighting/124355541</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>124355544</v>
+        <v>124355542</v>
       </c>
       <c r="B243" t="n">
         <v>106229</v>
@@ -26049,10 +26062,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>723301</v>
+        <v>723159</v>
       </c>
       <c r="R243" t="n">
-        <v>7544640</v>
+        <v>7544605</v>
       </c>
       <c r="S243" t="n">
         <v>5</v>
@@ -26110,13 +26123,13 @@
       <c r="AY243" t="inlineStr"/>
       <c r="AZ243" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355544</t>
+          <t>https://artportalen.se/Sighting/124355542</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>124355546</v>
+        <v>124355543</v>
       </c>
       <c r="B244" t="n">
         <v>106229</v>
@@ -26151,10 +26164,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>723347</v>
+        <v>723227</v>
       </c>
       <c r="R244" t="n">
-        <v>7544617</v>
+        <v>7544640</v>
       </c>
       <c r="S244" t="n">
         <v>5</v>
@@ -26212,13 +26225,13 @@
       <c r="AY244" t="inlineStr"/>
       <c r="AZ244" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355546</t>
+          <t>https://artportalen.se/Sighting/124355543</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>124355548</v>
+        <v>124355544</v>
       </c>
       <c r="B245" t="n">
         <v>106229</v>
@@ -26253,10 +26266,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>723515</v>
+        <v>723301</v>
       </c>
       <c r="R245" t="n">
-        <v>7544632</v>
+        <v>7544640</v>
       </c>
       <c r="S245" t="n">
         <v>5</v>
@@ -26314,13 +26327,13 @@
       <c r="AY245" t="inlineStr"/>
       <c r="AZ245" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355548</t>
+          <t>https://artportalen.se/Sighting/124355544</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>124355551</v>
+        <v>124355546</v>
       </c>
       <c r="B246" t="n">
         <v>106229</v>
@@ -26355,10 +26368,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>723547</v>
+        <v>723347</v>
       </c>
       <c r="R246" t="n">
-        <v>7544600</v>
+        <v>7544617</v>
       </c>
       <c r="S246" t="n">
         <v>5</v>
@@ -26416,13 +26429,13 @@
       <c r="AY246" t="inlineStr"/>
       <c r="AZ246" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355551</t>
+          <t>https://artportalen.se/Sighting/124355546</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>124355552</v>
+        <v>124355548</v>
       </c>
       <c r="B247" t="n">
         <v>106229</v>
@@ -26457,10 +26470,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>723608</v>
+        <v>723515</v>
       </c>
       <c r="R247" t="n">
-        <v>7544580</v>
+        <v>7544632</v>
       </c>
       <c r="S247" t="n">
         <v>5</v>
@@ -26518,16 +26531,16 @@
       <c r="AY247" t="inlineStr"/>
       <c r="AZ247" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355552</t>
+          <t>https://artportalen.se/Sighting/124355548</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>129015591</v>
+        <v>124355551</v>
       </c>
       <c r="B248" t="n">
-        <v>106228</v>
+        <v>106229</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -26555,17 +26568,17 @@
       <c r="I248" t="inlineStr"/>
       <c r="P248" t="inlineStr">
         <is>
-          <t>Kurravaara, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>722800</v>
+        <v>723547</v>
       </c>
       <c r="R248" t="n">
-        <v>7544375</v>
+        <v>7544600</v>
       </c>
       <c r="S248" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T248" t="inlineStr">
         <is>
@@ -26589,12 +26602,12 @@
       </c>
       <c r="Y248" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA248" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -26609,27 +26622,27 @@
       <c r="AT248" t="inlineStr"/>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
       <c r="AZ248" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129015591</t>
+          <t>https://artportalen.se/Sighting/124355551</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>110501257</v>
+        <v>124355552</v>
       </c>
       <c r="B249" t="n">
-        <v>97989</v>
+        <v>106229</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -26637,37 +26650,37 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>221941</v>
+        <v>221725</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
       <c r="P249" t="inlineStr">
         <is>
-          <t>Per Geijerområdet, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>723085</v>
+        <v>723608</v>
       </c>
       <c r="R249" t="n">
-        <v>7544696</v>
+        <v>7544580</v>
       </c>
       <c r="S249" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T249" t="inlineStr">
         <is>
@@ -26691,12 +26704,12 @@
       </c>
       <c r="Y249" t="inlineStr">
         <is>
-          <t>2022-08-01</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA249" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD249" t="b">
@@ -26711,27 +26724,27 @@
       <c r="AT249" t="inlineStr"/>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>Mats Williamson, Billy Lindblom, Nils Ericson, Marie Riskilä</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
       <c r="AZ249" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110501257</t>
+          <t>https://artportalen.se/Sighting/124355552</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>110501260</v>
+        <v>129015591</v>
       </c>
       <c r="B250" t="n">
-        <v>97989</v>
+        <v>106228</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -26739,34 +26752,34 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>221941</v>
+        <v>221725</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
       <c r="P250" t="inlineStr">
         <is>
-          <t>Per Geijerområdet, T lm</t>
+          <t>Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>723645</v>
+        <v>722800</v>
       </c>
       <c r="R250" t="n">
-        <v>7545074</v>
+        <v>7544375</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -26793,12 +26806,12 @@
       </c>
       <c r="Y250" t="inlineStr">
         <is>
-          <t>2022-08-01</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="AA250" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="AD250" t="b">
@@ -26813,24 +26826,24 @@
       <c r="AT250" t="inlineStr"/>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>Mats Williamson, Billy Lindblom, Nils Ericson, Marie Riskilä</t>
+          <t>Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
       <c r="AZ250" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110501260</t>
+          <t>https://artportalen.se/Sighting/129015591</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>124355632</v>
+        <v>110501257</v>
       </c>
       <c r="B251" t="n">
         <v>97989</v>
@@ -26861,17 +26874,17 @@
       <c r="I251" t="inlineStr"/>
       <c r="P251" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Per Geijerområdet, T lm</t>
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>723668</v>
+        <v>723085</v>
       </c>
       <c r="R251" t="n">
-        <v>7544288</v>
+        <v>7544696</v>
       </c>
       <c r="S251" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T251" t="inlineStr">
         <is>
@@ -26895,12 +26908,12 @@
       </c>
       <c r="Y251" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2022-08-01</t>
         </is>
       </c>
       <c r="AA251" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2022-09-07</t>
         </is>
       </c>
       <c r="AD251" t="b">
@@ -26915,27 +26928,27 @@
       <c r="AT251" t="inlineStr"/>
       <c r="AW251" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Mats Williamson</t>
         </is>
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Mats Williamson, Billy Lindblom, Nils Ericson, Marie Riskilä</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
       <c r="AZ251" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355632</t>
+          <t>https://artportalen.se/Sighting/110501257</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>61744985</v>
+        <v>110501260</v>
       </c>
       <c r="B252" t="n">
-        <v>97983</v>
+        <v>97989</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -26943,16 +26956,16 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -26961,19 +26974,16 @@
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
-      <c r="J252" t="inlineStr"/>
-      <c r="K252" t="inlineStr"/>
-      <c r="L252" t="inlineStr"/>
       <c r="P252" t="inlineStr">
         <is>
-          <t>kurravaara ravinen, T lm</t>
+          <t>Per Geijerområdet, T lm</t>
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>723578</v>
+        <v>723645</v>
       </c>
       <c r="R252" t="n">
-        <v>7544434</v>
+        <v>7545074</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -27000,12 +27010,12 @@
       </c>
       <c r="Y252" t="inlineStr">
         <is>
-          <t>2016-10-13</t>
+          <t>2022-08-01</t>
         </is>
       </c>
       <c r="AA252" t="inlineStr">
         <is>
-          <t>2016-10-13</t>
+          <t>2022-09-07</t>
         </is>
       </c>
       <c r="AD252" t="b">
@@ -27020,27 +27030,27 @@
       <c r="AT252" t="inlineStr"/>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Mats Williamson</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Mats Williamson, Billy Lindblom, Nils Ericson, Marie Riskilä</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
       <c r="AZ252" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/61744985</t>
+          <t>https://artportalen.se/Sighting/110501260</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>89201575</v>
+        <v>124355632</v>
       </c>
       <c r="B253" t="n">
-        <v>97983</v>
+        <v>97989</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -27048,16 +27058,16 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -27068,17 +27078,17 @@
       <c r="I253" t="inlineStr"/>
       <c r="P253" t="inlineStr">
         <is>
-          <t>Kurravaara, Iso Mäntyvaaravan V, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>723763</v>
+        <v>723668</v>
       </c>
       <c r="R253" t="n">
-        <v>7544642</v>
+        <v>7544288</v>
       </c>
       <c r="S253" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T253" t="inlineStr">
         <is>
@@ -27102,12 +27112,12 @@
       </c>
       <c r="Y253" t="inlineStr">
         <is>
-          <t>2002-08-03</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA253" t="inlineStr">
         <is>
-          <t>2002-08-03</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD253" t="b">
@@ -27118,37 +27128,28 @@
       </c>
       <c r="AG253" t="b">
         <v>0</v>
-      </c>
-      <c r="AI253" t="inlineStr">
-        <is>
-          <t>rikkärr</t>
-        </is>
       </c>
       <c r="AT253" t="inlineStr"/>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>Peter Ståhl</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>Peter Ståhl</t>
-        </is>
-      </c>
-      <c r="AY253" t="inlineStr">
-        <is>
-          <t>noteringar från Torne lappmark</t>
-        </is>
-      </c>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY253" t="inlineStr"/>
       <c r="AZ253" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89201575</t>
+          <t>https://artportalen.se/Sighting/124355632</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>110382633</v>
+        <v>61744985</v>
       </c>
       <c r="B254" t="n">
         <v>97983</v>
@@ -27177,16 +27178,19 @@
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
+      <c r="J254" t="inlineStr"/>
+      <c r="K254" t="inlineStr"/>
+      <c r="L254" t="inlineStr"/>
       <c r="P254" t="inlineStr">
         <is>
-          <t>Per Geijerområdet, T lm</t>
+          <t>kurravaara ravinen, T lm</t>
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>723303</v>
+        <v>723578</v>
       </c>
       <c r="R254" t="n">
-        <v>7543864</v>
+        <v>7544434</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -27213,12 +27217,12 @@
       </c>
       <c r="Y254" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2016-10-13</t>
         </is>
       </c>
       <c r="AA254" t="inlineStr">
         <is>
-          <t>2021-09-17</t>
+          <t>2016-10-13</t>
         </is>
       </c>
       <c r="AD254" t="b">
@@ -27233,24 +27237,24 @@
       <c r="AT254" t="inlineStr"/>
       <c r="AW254" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>Mats Williamson, Billy Lindblom</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
       <c r="AZ254" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110382633</t>
+          <t>https://artportalen.se/Sighting/61744985</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>110501251</v>
+        <v>89201575</v>
       </c>
       <c r="B255" t="n">
         <v>97983</v>
@@ -27281,17 +27285,17 @@
       <c r="I255" t="inlineStr"/>
       <c r="P255" t="inlineStr">
         <is>
-          <t>Per Geijerområdet, T lm</t>
+          <t>Kurravaara, Iso Mäntyvaaravan V, T lm</t>
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>723816</v>
+        <v>723763</v>
       </c>
       <c r="R255" t="n">
-        <v>7544835</v>
+        <v>7544642</v>
       </c>
       <c r="S255" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T255" t="inlineStr">
         <is>
@@ -27315,12 +27319,12 @@
       </c>
       <c r="Y255" t="inlineStr">
         <is>
-          <t>2022-08-01</t>
+          <t>2002-08-03</t>
         </is>
       </c>
       <c r="AA255" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
+          <t>2002-08-03</t>
         </is>
       </c>
       <c r="AD255" t="b">
@@ -27331,31 +27335,40 @@
       </c>
       <c r="AG255" t="b">
         <v>0</v>
+      </c>
+      <c r="AI255" t="inlineStr">
+        <is>
+          <t>rikkärr</t>
+        </is>
       </c>
       <c r="AT255" t="inlineStr"/>
       <c r="AW255" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>Peter Ståhl</t>
         </is>
       </c>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>Mats Williamson, Billy Lindblom, Nils Ericson, Marie Riskilä</t>
-        </is>
-      </c>
-      <c r="AY255" t="inlineStr"/>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AY255" t="inlineStr">
+        <is>
+          <t>noteringar från Torne lappmark</t>
+        </is>
+      </c>
       <c r="AZ255" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110501251</t>
+          <t>https://artportalen.se/Sighting/89201575</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>124355609</v>
+        <v>110382633</v>
       </c>
       <c r="B256" t="n">
-        <v>99140</v>
+        <v>97983</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -27363,37 +27376,37 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
       <c r="P256" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Per Geijerområdet, T lm</t>
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>723343</v>
+        <v>723303</v>
       </c>
       <c r="R256" t="n">
-        <v>7544612</v>
+        <v>7543864</v>
       </c>
       <c r="S256" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T256" t="inlineStr">
         <is>
@@ -27417,12 +27430,12 @@
       </c>
       <c r="Y256" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="AA256" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2021-09-17</t>
         </is>
       </c>
       <c r="AD256" t="b">
@@ -27437,27 +27450,27 @@
       <c r="AT256" t="inlineStr"/>
       <c r="AW256" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Mats Williamson</t>
         </is>
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Mats Williamson, Billy Lindblom</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>
       <c r="AZ256" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355609</t>
+          <t>https://artportalen.se/Sighting/110382633</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>4870391</v>
+        <v>110501251</v>
       </c>
       <c r="B257" t="n">
-        <v>100143</v>
+        <v>97983</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -27465,37 +27478,37 @@
         </is>
       </c>
       <c r="E257" t="n">
-        <v>222467</v>
+        <v>221945</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Gräsull</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Eriophorum latifolium</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>Hoppe</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
       <c r="P257" t="inlineStr">
         <is>
-          <t>Koivuvaara, N-sluttning, myr, T lm</t>
+          <t>Per Geijerområdet, T lm</t>
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>723271</v>
+        <v>723816</v>
       </c>
       <c r="R257" t="n">
-        <v>7545161</v>
+        <v>7544835</v>
       </c>
       <c r="S257" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T257" t="inlineStr">
         <is>
@@ -27519,12 +27532,12 @@
       </c>
       <c r="Y257" t="inlineStr">
         <is>
-          <t>1981-07-02</t>
+          <t>2022-08-01</t>
         </is>
       </c>
       <c r="AA257" t="inlineStr">
         <is>
-          <t>1981-07-02</t>
+          <t>2022-09-07</t>
         </is>
       </c>
       <c r="AD257" t="b">
@@ -27539,27 +27552,27 @@
       <c r="AT257" t="inlineStr"/>
       <c r="AW257" t="inlineStr">
         <is>
-          <t>Birgitta Öster</t>
+          <t>Mats Williamson</t>
         </is>
       </c>
       <c r="AX257" t="inlineStr">
         <is>
-          <t>Birgitta Öster</t>
+          <t>Mats Williamson, Billy Lindblom, Nils Ericson, Marie Riskilä</t>
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
       <c r="AZ257" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4870391</t>
+          <t>https://artportalen.se/Sighting/110501251</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>120543965</v>
+        <v>124355609</v>
       </c>
       <c r="B258" t="n">
-        <v>100143</v>
+        <v>99140</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -27567,21 +27580,21 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>222467</v>
+        <v>221952</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Gräsull</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Eriophorum latifolium</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>Hoppe</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
@@ -27591,10 +27604,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>723813</v>
+        <v>723343</v>
       </c>
       <c r="R258" t="n">
-        <v>7544469</v>
+        <v>7544612</v>
       </c>
       <c r="S258" t="n">
         <v>5</v>
@@ -27652,16 +27665,16 @@
       <c r="AY258" t="inlineStr"/>
       <c r="AZ258" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120543965</t>
+          <t>https://artportalen.se/Sighting/124355609</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>5171824</v>
+        <v>4870391</v>
       </c>
       <c r="B259" t="n">
-        <v>98137</v>
+        <v>100143</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -27669,37 +27682,37 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>222741</v>
+        <v>222467</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Gräsull</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Eriophorum latifolium</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>Hoppe</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
       <c r="P259" t="inlineStr">
         <is>
-          <t>kurravaararavinen, T lm</t>
+          <t>Koivuvaara, N-sluttning, myr, T lm</t>
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>723525</v>
+        <v>723271</v>
       </c>
       <c r="R259" t="n">
-        <v>7544228</v>
+        <v>7545161</v>
       </c>
       <c r="S259" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T259" t="inlineStr">
         <is>
@@ -27723,12 +27736,12 @@
       </c>
       <c r="Y259" t="inlineStr">
         <is>
-          <t>2012-08-29</t>
+          <t>1981-07-02</t>
         </is>
       </c>
       <c r="AA259" t="inlineStr">
         <is>
-          <t>2012-08-29</t>
+          <t>1981-07-02</t>
         </is>
       </c>
       <c r="AD259" t="b">
@@ -27743,27 +27756,27 @@
       <c r="AT259" t="inlineStr"/>
       <c r="AW259" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Birgitta Öster</t>
         </is>
       </c>
       <c r="AX259" t="inlineStr">
         <is>
-          <t>per-erik mukka, Robert Sandberg, Frédéric Forsmark</t>
+          <t>Birgitta Öster</t>
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>
       <c r="AZ259" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/5171824</t>
+          <t>https://artportalen.se/Sighting/4870391</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>87248016</v>
+        <v>120543965</v>
       </c>
       <c r="B260" t="n">
-        <v>98137</v>
+        <v>100143</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -27771,41 +27784,37 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>222741</v>
+        <v>222467</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Gräsull</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Eriophorum latifolium</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>Hoppe</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
-      <c r="J260" t="inlineStr"/>
-      <c r="K260" t="inlineStr"/>
-      <c r="L260" t="inlineStr"/>
-      <c r="N260" t="inlineStr"/>
       <c r="P260" t="inlineStr">
         <is>
-          <t>Kurravaara, södra delen av byn, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>723794</v>
+        <v>723813</v>
       </c>
       <c r="R260" t="n">
-        <v>7544657</v>
+        <v>7544469</v>
       </c>
       <c r="S260" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T260" t="inlineStr">
         <is>
@@ -27829,12 +27838,12 @@
       </c>
       <c r="Y260" t="inlineStr">
         <is>
-          <t>2020-07-22</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA260" t="inlineStr">
         <is>
-          <t>2020-07-22</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD260" t="b">
@@ -27843,40 +27852,30 @@
       <c r="AE260" t="b">
         <v>0</v>
       </c>
-      <c r="AF260" t="inlineStr"/>
       <c r="AG260" t="b">
         <v>0</v>
-      </c>
-      <c r="AI260" t="inlineStr">
-        <is>
-          <t>översilad björkskog</t>
-        </is>
       </c>
       <c r="AT260" t="inlineStr"/>
       <c r="AW260" t="inlineStr">
         <is>
-          <t>Lars Fröberg</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>Lars Fröberg, Rolf Enander, Patrik Engström</t>
-        </is>
-      </c>
-      <c r="AY260" t="inlineStr">
-        <is>
-          <t>Florainventering av vita fläckar i Lappland</t>
-        </is>
-      </c>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY260" t="inlineStr"/>
       <c r="AZ260" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/87248016</t>
+          <t>https://artportalen.se/Sighting/120543965</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>110501113</v>
+        <v>5171824</v>
       </c>
       <c r="B261" t="n">
         <v>98137</v>
@@ -27907,14 +27906,14 @@
       <c r="I261" t="inlineStr"/>
       <c r="P261" t="inlineStr">
         <is>
-          <t>Per Geijerområdet, T lm</t>
+          <t>kurravaararavinen, T lm</t>
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>723419</v>
+        <v>723525</v>
       </c>
       <c r="R261" t="n">
-        <v>7544672</v>
+        <v>7544228</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -27941,12 +27940,12 @@
       </c>
       <c r="Y261" t="inlineStr">
         <is>
-          <t>2022-08-01</t>
+          <t>2012-08-29</t>
         </is>
       </c>
       <c r="AA261" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
+          <t>2012-08-29</t>
         </is>
       </c>
       <c r="AD261" t="b">
@@ -27961,24 +27960,24 @@
       <c r="AT261" t="inlineStr"/>
       <c r="AW261" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX261" t="inlineStr">
         <is>
-          <t>Mats Williamson, Billy Lindblom, Nils Ericson, Marie Riskilä</t>
+          <t>per-erik mukka, Robert Sandberg, Frédéric Forsmark</t>
         </is>
       </c>
       <c r="AY261" t="inlineStr"/>
       <c r="AZ261" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110501113</t>
+          <t>https://artportalen.se/Sighting/5171824</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>110501115</v>
+        <v>87248016</v>
       </c>
       <c r="B262" t="n">
         <v>98137</v>
@@ -28007,19 +28006,23 @@
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
+      <c r="J262" t="inlineStr"/>
+      <c r="K262" t="inlineStr"/>
+      <c r="L262" t="inlineStr"/>
+      <c r="N262" t="inlineStr"/>
       <c r="P262" t="inlineStr">
         <is>
-          <t>Per Geijerområdet, T lm</t>
+          <t>Kurravaara, södra delen av byn, T lm</t>
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>723637</v>
+        <v>723794</v>
       </c>
       <c r="R262" t="n">
-        <v>7544141</v>
+        <v>7544657</v>
       </c>
       <c r="S262" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T262" t="inlineStr">
         <is>
@@ -28043,12 +28046,12 @@
       </c>
       <c r="Y262" t="inlineStr">
         <is>
-          <t>2022-08-01</t>
+          <t>2020-07-22</t>
         </is>
       </c>
       <c r="AA262" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
+          <t>2020-07-22</t>
         </is>
       </c>
       <c r="AD262" t="b">
@@ -28057,30 +28060,40 @@
       <c r="AE262" t="b">
         <v>0</v>
       </c>
+      <c r="AF262" t="inlineStr"/>
       <c r="AG262" t="b">
         <v>0</v>
+      </c>
+      <c r="AI262" t="inlineStr">
+        <is>
+          <t>översilad björkskog</t>
+        </is>
       </c>
       <c r="AT262" t="inlineStr"/>
       <c r="AW262" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>Lars Fröberg</t>
         </is>
       </c>
       <c r="AX262" t="inlineStr">
         <is>
-          <t>Mats Williamson, Billy Lindblom, Nils Ericson, Marie Riskilä</t>
-        </is>
-      </c>
-      <c r="AY262" t="inlineStr"/>
+          <t>Lars Fröberg, Rolf Enander, Patrik Engström</t>
+        </is>
+      </c>
+      <c r="AY262" t="inlineStr">
+        <is>
+          <t>Florainventering av vita fläckar i Lappland</t>
+        </is>
+      </c>
       <c r="AZ262" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110501115</t>
+          <t>https://artportalen.se/Sighting/87248016</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>110501116</v>
+        <v>110501113</v>
       </c>
       <c r="B263" t="n">
         <v>98137</v>
@@ -28115,10 +28128,10 @@
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>723344</v>
+        <v>723419</v>
       </c>
       <c r="R263" t="n">
-        <v>7544187</v>
+        <v>7544672</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -28176,13 +28189,13 @@
       <c r="AY263" t="inlineStr"/>
       <c r="AZ263" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110501116</t>
+          <t>https://artportalen.se/Sighting/110501113</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>110501117</v>
+        <v>110501115</v>
       </c>
       <c r="B264" t="n">
         <v>98137</v>
@@ -28217,10 +28230,10 @@
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>723094</v>
+        <v>723637</v>
       </c>
       <c r="R264" t="n">
-        <v>7545148</v>
+        <v>7544141</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -28278,13 +28291,13 @@
       <c r="AY264" t="inlineStr"/>
       <c r="AZ264" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110501117</t>
+          <t>https://artportalen.se/Sighting/110501115</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>110501118</v>
+        <v>110501116</v>
       </c>
       <c r="B265" t="n">
         <v>98137</v>
@@ -28319,10 +28332,10 @@
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>723089</v>
+        <v>723344</v>
       </c>
       <c r="R265" t="n">
-        <v>7545162</v>
+        <v>7544187</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -28380,13 +28393,13 @@
       <c r="AY265" t="inlineStr"/>
       <c r="AZ265" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110501118</t>
+          <t>https://artportalen.se/Sighting/110501116</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>110501119</v>
+        <v>110501117</v>
       </c>
       <c r="B266" t="n">
         <v>98137</v>
@@ -28421,10 +28434,10 @@
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>723687</v>
+        <v>723094</v>
       </c>
       <c r="R266" t="n">
-        <v>7545096</v>
+        <v>7545148</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>
@@ -28482,13 +28495,13 @@
       <c r="AY266" t="inlineStr"/>
       <c r="AZ266" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110501119</t>
+          <t>https://artportalen.se/Sighting/110501117</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>110501120</v>
+        <v>110501118</v>
       </c>
       <c r="B267" t="n">
         <v>98137</v>
@@ -28523,10 +28536,10 @@
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>723689</v>
+        <v>723089</v>
       </c>
       <c r="R267" t="n">
-        <v>7545128</v>
+        <v>7545162</v>
       </c>
       <c r="S267" t="n">
         <v>10</v>
@@ -28584,13 +28597,13 @@
       <c r="AY267" t="inlineStr"/>
       <c r="AZ267" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110501120</t>
+          <t>https://artportalen.se/Sighting/110501118</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>111474170</v>
+        <v>110501119</v>
       </c>
       <c r="B268" t="n">
         <v>98137</v>
@@ -28619,17 +28632,16 @@
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
-      <c r="K268" t="inlineStr"/>
       <c r="P268" t="inlineStr">
         <is>
-          <t>kurra, T lm</t>
+          <t>Per Geijerområdet, T lm</t>
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>723317</v>
+        <v>723687</v>
       </c>
       <c r="R268" t="n">
-        <v>7544195</v>
+        <v>7545096</v>
       </c>
       <c r="S268" t="n">
         <v>10</v>
@@ -28656,12 +28668,12 @@
       </c>
       <c r="Y268" t="inlineStr">
         <is>
-          <t>2023-08-14</t>
+          <t>2022-08-01</t>
         </is>
       </c>
       <c r="AA268" t="inlineStr">
         <is>
-          <t>2023-08-14</t>
+          <t>2022-09-07</t>
         </is>
       </c>
       <c r="AD268" t="b">
@@ -28676,24 +28688,24 @@
       <c r="AT268" t="inlineStr"/>
       <c r="AW268" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Mats Williamson</t>
         </is>
       </c>
       <c r="AX268" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Mats Williamson, Billy Lindblom, Nils Ericson, Marie Riskilä</t>
         </is>
       </c>
       <c r="AY268" t="inlineStr"/>
       <c r="AZ268" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111474170</t>
+          <t>https://artportalen.se/Sighting/110501119</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>124355850</v>
+        <v>110501120</v>
       </c>
       <c r="B269" t="n">
         <v>98137</v>
@@ -28724,17 +28736,17 @@
       <c r="I269" t="inlineStr"/>
       <c r="P269" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>Per Geijerområdet, T lm</t>
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>723616</v>
+        <v>723689</v>
       </c>
       <c r="R269" t="n">
-        <v>7544154</v>
+        <v>7545128</v>
       </c>
       <c r="S269" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T269" t="inlineStr">
         <is>
@@ -28758,12 +28770,12 @@
       </c>
       <c r="Y269" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2022-08-01</t>
         </is>
       </c>
       <c r="AA269" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2022-09-07</t>
         </is>
       </c>
       <c r="AD269" t="b">
@@ -28778,24 +28790,24 @@
       <c r="AT269" t="inlineStr"/>
       <c r="AW269" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Mats Williamson</t>
         </is>
       </c>
       <c r="AX269" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Mats Williamson, Billy Lindblom, Nils Ericson, Marie Riskilä</t>
         </is>
       </c>
       <c r="AY269" t="inlineStr"/>
       <c r="AZ269" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355850</t>
+          <t>https://artportalen.se/Sighting/110501120</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>124355851</v>
+        <v>111474170</v>
       </c>
       <c r="B270" t="n">
         <v>98137</v>
@@ -28824,19 +28836,20 @@
         </is>
       </c>
       <c r="I270" t="inlineStr"/>
+      <c r="K270" t="inlineStr"/>
       <c r="P270" t="inlineStr">
         <is>
-          <t>Kurravaaravägen söder om byn, T lm</t>
+          <t>kurra, T lm</t>
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>723705</v>
+        <v>723317</v>
       </c>
       <c r="R270" t="n">
-        <v>7544144</v>
+        <v>7544195</v>
       </c>
       <c r="S270" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T270" t="inlineStr">
         <is>
@@ -28860,12 +28873,12 @@
       </c>
       <c r="Y270" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2023-08-14</t>
         </is>
       </c>
       <c r="AA270" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2023-08-14</t>
         </is>
       </c>
       <c r="AD270" t="b">
@@ -28880,24 +28893,24 @@
       <c r="AT270" t="inlineStr"/>
       <c r="AW270" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX270" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY270" t="inlineStr"/>
       <c r="AZ270" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355851</t>
+          <t>https://artportalen.se/Sighting/111474170</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>124355855</v>
+        <v>124355850</v>
       </c>
       <c r="B271" t="n">
         <v>98137</v>
@@ -28928,14 +28941,14 @@
       <c r="I271" t="inlineStr"/>
       <c r="P271" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>722944</v>
+        <v>723616</v>
       </c>
       <c r="R271" t="n">
-        <v>7544574</v>
+        <v>7544154</v>
       </c>
       <c r="S271" t="n">
         <v>5</v>
@@ -28962,12 +28975,12 @@
       </c>
       <c r="Y271" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA271" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD271" t="b">
@@ -28993,13 +29006,13 @@
       <c r="AY271" t="inlineStr"/>
       <c r="AZ271" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355855</t>
+          <t>https://artportalen.se/Sighting/124355850</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>124355856</v>
+        <v>124355851</v>
       </c>
       <c r="B272" t="n">
         <v>98137</v>
@@ -29030,14 +29043,14 @@
       <c r="I272" t="inlineStr"/>
       <c r="P272" t="inlineStr">
         <is>
-          <t>Vid Gruvberget Kurravaara, T lm</t>
+          <t>Kurravaaravägen söder om byn, T lm</t>
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>723068</v>
+        <v>723705</v>
       </c>
       <c r="R272" t="n">
-        <v>7544568</v>
+        <v>7544144</v>
       </c>
       <c r="S272" t="n">
         <v>5</v>
@@ -29064,12 +29077,12 @@
       </c>
       <c r="Y272" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA272" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD272" t="b">
@@ -29095,13 +29108,13 @@
       <c r="AY272" t="inlineStr"/>
       <c r="AZ272" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355856</t>
+          <t>https://artportalen.se/Sighting/124355851</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>124355857</v>
+        <v>124355855</v>
       </c>
       <c r="B273" t="n">
         <v>98137</v>
@@ -29136,10 +29149,10 @@
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>723343</v>
+        <v>722944</v>
       </c>
       <c r="R273" t="n">
-        <v>7544616</v>
+        <v>7544574</v>
       </c>
       <c r="S273" t="n">
         <v>5</v>
@@ -29197,16 +29210,16 @@
       <c r="AY273" t="inlineStr"/>
       <c r="AZ273" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124355857</t>
+          <t>https://artportalen.se/Sighting/124355855</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>110501266</v>
+        <v>124355856</v>
       </c>
       <c r="B274" t="n">
-        <v>97984</v>
+        <v>98137</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -29214,37 +29227,37 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>224362</v>
+        <v>222741</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Nordlummer</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. alpestre</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(Hartm.) Á. Löve &amp; D. Löve</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
       <c r="P274" t="inlineStr">
         <is>
-          <t>Per Geijerområdet, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>723080</v>
+        <v>723068</v>
       </c>
       <c r="R274" t="n">
-        <v>7544690</v>
+        <v>7544568</v>
       </c>
       <c r="S274" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T274" t="inlineStr">
         <is>
@@ -29268,12 +29281,12 @@
       </c>
       <c r="Y274" t="inlineStr">
         <is>
-          <t>2022-08-01</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA274" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD274" t="b">
@@ -29288,67 +29301,65 @@
       <c r="AT274" t="inlineStr"/>
       <c r="AW274" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX274" t="inlineStr">
         <is>
-          <t>Mats Williamson, Billy Lindblom, Nils Ericson, Marie Riskilä</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AY274" t="inlineStr"/>
       <c r="AZ274" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110501266</t>
+          <t>https://artportalen.se/Sighting/124355856</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>61746564</v>
+        <v>124355857</v>
       </c>
       <c r="B275" t="n">
-        <v>79853</v>
+        <v>98137</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>229830</v>
+        <v>222741</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Späd brosklav</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Ramalina dilacerata</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
-      <c r="J275" t="inlineStr"/>
-      <c r="K275" t="inlineStr"/>
       <c r="P275" t="inlineStr">
         <is>
-          <t>kurravaara ravinen, T lm</t>
+          <t>Vid Gruvberget Kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>723149</v>
+        <v>723343</v>
       </c>
       <c r="R275" t="n">
-        <v>7544666</v>
+        <v>7544616</v>
       </c>
       <c r="S275" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T275" t="inlineStr">
         <is>
@@ -29372,12 +29383,12 @@
       </c>
       <c r="Y275" t="inlineStr">
         <is>
-          <t>2016-10-13</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA275" t="inlineStr">
         <is>
-          <t>2016-10-13</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD275" t="b">
@@ -29392,64 +29403,62 @@
       <c r="AT275" t="inlineStr"/>
       <c r="AW275" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX275" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AY275" t="inlineStr"/>
       <c r="AZ275" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/61746564</t>
+          <t>https://artportalen.se/Sighting/124355857</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>67458187</v>
+        <v>110501266</v>
       </c>
       <c r="B276" t="n">
-        <v>79853</v>
+        <v>97984</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>229830</v>
+        <v>224362</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Späd brosklav</t>
+          <t>Nordlummer</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Ramalina dilacerata</t>
+          <t>Lycopodium annotinum subsp. alpestre</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartm.) Á. Löve &amp; D. Löve</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
-      <c r="J276" t="inlineStr"/>
-      <c r="K276" t="inlineStr"/>
       <c r="P276" t="inlineStr">
         <is>
-          <t>kurravaara ravinen, T lm</t>
+          <t>Per Geijerområdet, T lm</t>
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>723035</v>
+        <v>723080</v>
       </c>
       <c r="R276" t="n">
-        <v>7544622</v>
+        <v>7544690</v>
       </c>
       <c r="S276" t="n">
         <v>10</v>
@@ -29476,12 +29485,12 @@
       </c>
       <c r="Y276" t="inlineStr">
         <is>
-          <t>2017-09-06</t>
+          <t>2022-08-01</t>
         </is>
       </c>
       <c r="AA276" t="inlineStr">
         <is>
-          <t>2017-09-06</t>
+          <t>2022-09-07</t>
         </is>
       </c>
       <c r="AD276" t="b">
@@ -29496,24 +29505,24 @@
       <c r="AT276" t="inlineStr"/>
       <c r="AW276" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Mats Williamson</t>
         </is>
       </c>
       <c r="AX276" t="inlineStr">
         <is>
-          <t>per-erik mukka, Anton Gustafsson</t>
+          <t>Mats Williamson, Billy Lindblom, Nils Ericson, Marie Riskilä</t>
         </is>
       </c>
       <c r="AY276" t="inlineStr"/>
       <c r="AZ276" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67458187</t>
+          <t>https://artportalen.se/Sighting/110501266</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>110501373</v>
+        <v>61746564</v>
       </c>
       <c r="B277" t="n">
         <v>79853</v>
@@ -29542,16 +29551,18 @@
         </is>
       </c>
       <c r="I277" t="inlineStr"/>
+      <c r="J277" t="inlineStr"/>
+      <c r="K277" t="inlineStr"/>
       <c r="P277" t="inlineStr">
         <is>
-          <t>Per Geijerområdet, T lm</t>
+          <t>kurravaara ravinen, T lm</t>
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>723700</v>
+        <v>723149</v>
       </c>
       <c r="R277" t="n">
-        <v>7545087</v>
+        <v>7544666</v>
       </c>
       <c r="S277" t="n">
         <v>10</v>
@@ -29578,12 +29589,12 @@
       </c>
       <c r="Y277" t="inlineStr">
         <is>
-          <t>2022-08-01</t>
+          <t>2016-10-13</t>
         </is>
       </c>
       <c r="AA277" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
+          <t>2016-10-13</t>
         </is>
       </c>
       <c r="AD277" t="b">
@@ -29598,62 +29609,64 @@
       <c r="AT277" t="inlineStr"/>
       <c r="AW277" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX277" t="inlineStr">
         <is>
-          <t>Mats Williamson, Billy Lindblom, Nils Ericson, Marie Riskilä</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY277" t="inlineStr"/>
       <c r="AZ277" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110501373</t>
+          <t>https://artportalen.se/Sighting/61746564</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>110382589</v>
+        <v>67458187</v>
       </c>
       <c r="B278" t="n">
-        <v>95765</v>
+        <v>79853</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E278" t="n">
-        <v>1004672</v>
+        <v>229830</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Källmossor</t>
+          <t>Späd brosklav</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Philonotis</t>
+          <t>Ramalina dilacerata</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>Brid.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
+      <c r="J278" t="inlineStr"/>
+      <c r="K278" t="inlineStr"/>
       <c r="P278" t="inlineStr">
         <is>
-          <t>Per Geijerområdet, T lm</t>
+          <t>kurravaara ravinen, T lm</t>
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>722988</v>
+        <v>723035</v>
       </c>
       <c r="R278" t="n">
-        <v>7544586</v>
+        <v>7544622</v>
       </c>
       <c r="S278" t="n">
         <v>10</v>
@@ -29680,12 +29693,12 @@
       </c>
       <c r="Y278" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2017-09-06</t>
         </is>
       </c>
       <c r="AA278" t="inlineStr">
         <is>
-          <t>2021-09-17</t>
+          <t>2017-09-06</t>
         </is>
       </c>
       <c r="AD278" t="b">
@@ -29700,49 +29713,49 @@
       <c r="AT278" t="inlineStr"/>
       <c r="AW278" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX278" t="inlineStr">
         <is>
-          <t>Mats Williamson, Billy Lindblom</t>
+          <t>per-erik mukka, Anton Gustafsson</t>
         </is>
       </c>
       <c r="AY278" t="inlineStr"/>
       <c r="AZ278" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110382589</t>
+          <t>https://artportalen.se/Sighting/67458187</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>110382591</v>
+        <v>110501373</v>
       </c>
       <c r="B279" t="n">
-        <v>95765</v>
+        <v>79853</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E279" t="n">
-        <v>1004672</v>
+        <v>229830</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Källmossor</t>
+          <t>Späd brosklav</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Philonotis</t>
+          <t>Ramalina dilacerata</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>Brid.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I279" t="inlineStr"/>
@@ -29752,10 +29765,10 @@
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>723470</v>
+        <v>723700</v>
       </c>
       <c r="R279" t="n">
-        <v>7543932</v>
+        <v>7545087</v>
       </c>
       <c r="S279" t="n">
         <v>10</v>
@@ -29782,12 +29795,12 @@
       </c>
       <c r="Y279" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2022-08-01</t>
         </is>
       </c>
       <c r="AA279" t="inlineStr">
         <is>
-          <t>2021-09-17</t>
+          <t>2022-09-07</t>
         </is>
       </c>
       <c r="AD279" t="b">
@@ -29807,19 +29820,19 @@
       </c>
       <c r="AX279" t="inlineStr">
         <is>
-          <t>Mats Williamson, Billy Lindblom</t>
+          <t>Mats Williamson, Billy Lindblom, Nils Ericson, Marie Riskilä</t>
         </is>
       </c>
       <c r="AY279" t="inlineStr"/>
       <c r="AZ279" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110382591</t>
+          <t>https://artportalen.se/Sighting/110501373</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>110382592</v>
+        <v>110382589</v>
       </c>
       <c r="B280" t="n">
         <v>95765</v>
@@ -29854,10 +29867,10 @@
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>723244</v>
+        <v>722988</v>
       </c>
       <c r="R280" t="n">
-        <v>7544649</v>
+        <v>7544586</v>
       </c>
       <c r="S280" t="n">
         <v>10</v>
@@ -29915,51 +29928,51 @@
       <c r="AY280" t="inlineStr"/>
       <c r="AZ280" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110382592</t>
+          <t>https://artportalen.se/Sighting/110382589</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>110044455</v>
+        <v>110382591</v>
       </c>
       <c r="B281" t="n">
-        <v>79406</v>
+        <v>95765</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E281" t="n">
-        <v>864</v>
+        <v>1004672</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Källmossor</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Philonotis</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>Brid.</t>
         </is>
       </c>
       <c r="I281" t="inlineStr"/>
       <c r="P281" t="inlineStr">
         <is>
-          <t>Rautasälven-Sakkaravaara, T lm</t>
+          <t>Per Geijerområdet, T lm</t>
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>723964</v>
+        <v>723470</v>
       </c>
       <c r="R281" t="n">
-        <v>7543542</v>
+        <v>7543932</v>
       </c>
       <c r="S281" t="n">
         <v>10</v>
@@ -29986,12 +29999,12 @@
       </c>
       <c r="Y281" t="inlineStr">
         <is>
-          <t>2022-08-15</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="AA281" t="inlineStr">
         <is>
-          <t>2022-08-15</t>
+          <t>2021-09-17</t>
         </is>
       </c>
       <c r="AD281" t="b">
@@ -30006,62 +30019,62 @@
       <c r="AT281" t="inlineStr"/>
       <c r="AW281" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Mats Williamson</t>
         </is>
       </c>
       <c r="AX281" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Mats Williamson, Billy Lindblom</t>
         </is>
       </c>
       <c r="AY281" t="inlineStr"/>
       <c r="AZ281" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110044455</t>
+          <t>https://artportalen.se/Sighting/110382591</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>110044453</v>
+        <v>110382592</v>
       </c>
       <c r="B282" t="n">
-        <v>91905</v>
+        <v>95765</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E282" t="n">
-        <v>1108</v>
+        <v>1004672</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Källmossor</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Philonotis</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Brid.</t>
         </is>
       </c>
       <c r="I282" t="inlineStr"/>
       <c r="P282" t="inlineStr">
         <is>
-          <t>Rautasälven-Sakkaravaara, T lm</t>
+          <t>Per Geijerområdet, T lm</t>
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>723912</v>
+        <v>723244</v>
       </c>
       <c r="R282" t="n">
-        <v>7543588</v>
+        <v>7544649</v>
       </c>
       <c r="S282" t="n">
         <v>10</v>
@@ -30088,12 +30101,12 @@
       </c>
       <c r="Y282" t="inlineStr">
         <is>
-          <t>2022-08-15</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="AA282" t="inlineStr">
         <is>
-          <t>2022-08-15</t>
+          <t>2021-09-17</t>
         </is>
       </c>
       <c r="AD282" t="b">
@@ -30108,27 +30121,27 @@
       <c r="AT282" t="inlineStr"/>
       <c r="AW282" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Mats Williamson</t>
         </is>
       </c>
       <c r="AX282" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Mats Williamson, Billy Lindblom</t>
         </is>
       </c>
       <c r="AY282" t="inlineStr"/>
       <c r="AZ282" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110044453</t>
+          <t>https://artportalen.se/Sighting/110382592</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>110044454</v>
+        <v>110044455</v>
       </c>
       <c r="B283" t="n">
-        <v>91905</v>
+        <v>79406</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -30136,21 +30149,21 @@
         </is>
       </c>
       <c r="E283" t="n">
-        <v>1108</v>
+        <v>864</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I283" t="inlineStr"/>
@@ -30160,10 +30173,10 @@
         </is>
       </c>
       <c r="Q283" t="n">
-        <v>723973</v>
+        <v>723964</v>
       </c>
       <c r="R283" t="n">
-        <v>7543537</v>
+        <v>7543542</v>
       </c>
       <c r="S283" t="n">
         <v>10</v>
@@ -30221,16 +30234,16 @@
       <c r="AY283" t="inlineStr"/>
       <c r="AZ283" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110044454</t>
+          <t>https://artportalen.se/Sighting/110044455</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>102907874</v>
+        <v>110044453</v>
       </c>
       <c r="B284" t="n">
-        <v>89156</v>
+        <v>91905</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -30238,38 +30251,37 @@
         </is>
       </c>
       <c r="E284" t="n">
-        <v>4412</v>
+        <v>1108</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I284" t="inlineStr"/>
-      <c r="K284" t="inlineStr"/>
       <c r="P284" t="inlineStr">
         <is>
-          <t>Kurravaara vägen , T lm</t>
+          <t>Rautasälven-Sakkaravaara, T lm</t>
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>723850</v>
+        <v>723912</v>
       </c>
       <c r="R284" t="n">
-        <v>7543562</v>
+        <v>7543588</v>
       </c>
       <c r="S284" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T284" t="inlineStr">
         <is>
@@ -30296,19 +30308,9 @@
           <t>2022-08-15</t>
         </is>
       </c>
-      <c r="Z284" t="inlineStr">
-        <is>
-          <t>17:50</t>
-        </is>
-      </c>
       <c r="AA284" t="inlineStr">
         <is>
           <t>2022-08-15</t>
-        </is>
-      </c>
-      <c r="AB284" t="inlineStr">
-        <is>
-          <t>17:50</t>
         </is>
       </c>
       <c r="AD284" t="b">
@@ -30323,7 +30325,7 @@
       <c r="AT284" t="inlineStr"/>
       <c r="AW284" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AX284" t="inlineStr">
@@ -30334,16 +30336,16 @@
       <c r="AY284" t="inlineStr"/>
       <c r="AZ284" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102907874</t>
+          <t>https://artportalen.se/Sighting/110044453</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>110044449</v>
+        <v>110044454</v>
       </c>
       <c r="B285" t="n">
-        <v>89156</v>
+        <v>91905</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -30351,21 +30353,21 @@
         </is>
       </c>
       <c r="E285" t="n">
-        <v>4412</v>
+        <v>1108</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I285" t="inlineStr"/>
@@ -30375,10 +30377,10 @@
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>723831</v>
+        <v>723973</v>
       </c>
       <c r="R285" t="n">
-        <v>7543547</v>
+        <v>7543537</v>
       </c>
       <c r="S285" t="n">
         <v>10</v>
@@ -30436,16 +30438,16 @@
       <c r="AY285" t="inlineStr"/>
       <c r="AZ285" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110044449</t>
+          <t>https://artportalen.se/Sighting/110044454</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>117357759</v>
+        <v>102907874</v>
       </c>
       <c r="B286" t="n">
-        <v>58388</v>
+        <v>89156</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -30453,39 +30455,35 @@
         </is>
       </c>
       <c r="E286" t="n">
-        <v>103001</v>
+        <v>4412</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I286" t="inlineStr"/>
-      <c r="M286" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="K286" t="inlineStr"/>
       <c r="P286" t="inlineStr">
         <is>
-          <t>Kurravaaravägen, Kiruna, T lm</t>
+          <t>Kurravaara vägen , T lm</t>
         </is>
       </c>
       <c r="Q286" t="n">
-        <v>724020</v>
+        <v>723850</v>
       </c>
       <c r="R286" t="n">
-        <v>7543442</v>
+        <v>7543562</v>
       </c>
       <c r="S286" t="n">
         <v>25</v>
@@ -30512,22 +30510,22 @@
       </c>
       <c r="Y286" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2022-08-15</t>
         </is>
       </c>
       <c r="Z286" t="inlineStr">
         <is>
-          <t>19:46</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA286" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2022-08-15</t>
         </is>
       </c>
       <c r="AB286" t="inlineStr">
         <is>
-          <t>19:46</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD286" t="b">
@@ -30547,65 +30545,57 @@
       </c>
       <c r="AX286" t="inlineStr">
         <is>
-          <t>per-erik mukka, Robert Flygare</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY286" t="inlineStr"/>
       <c r="AZ286" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117357759</t>
+          <t>https://artportalen.se/Sighting/102907874</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>111591780</v>
+        <v>110044449</v>
       </c>
       <c r="B287" t="n">
-        <v>99120</v>
+        <v>89156</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E287" t="n">
-        <v>219811</v>
+        <v>4412</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I287" t="inlineStr"/>
-      <c r="J287" t="inlineStr"/>
-      <c r="K287" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L287" t="inlineStr"/>
-      <c r="N287" t="inlineStr"/>
       <c r="P287" t="inlineStr">
         <is>
-          <t>Kurravaaravägen 60, Kiruna, Kurravaaravägen 60, Kiruna, T lm</t>
+          <t>Rautasälven-Sakkaravaara, T lm</t>
         </is>
       </c>
       <c r="Q287" t="n">
-        <v>723842</v>
+        <v>723831</v>
       </c>
       <c r="R287" t="n">
-        <v>7544794</v>
+        <v>7543547</v>
       </c>
       <c r="S287" t="n">
         <v>10</v>
@@ -30632,12 +30622,12 @@
       </c>
       <c r="Y287" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2022-08-15</t>
         </is>
       </c>
       <c r="AA287" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2022-08-15</t>
         </is>
       </c>
       <c r="AD287" t="b">
@@ -30646,84 +30636,76 @@
       <c r="AE287" t="b">
         <v>0</v>
       </c>
-      <c r="AF287" t="inlineStr"/>
       <c r="AG287" t="b">
         <v>0</v>
       </c>
       <c r="AT287" t="inlineStr"/>
       <c r="AW287" t="inlineStr">
         <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX287" t="inlineStr">
+        <is>
           <t>per-erik mukka</t>
-        </is>
-      </c>
-      <c r="AX287" t="inlineStr">
-        <is>
-          <t>per-erik mukka, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY287" t="inlineStr"/>
       <c r="AZ287" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111591780</t>
+          <t>https://artportalen.se/Sighting/110044449</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>87676926</v>
+        <v>117357759</v>
       </c>
       <c r="B288" t="n">
-        <v>99118</v>
+        <v>58388</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E288" t="n">
-        <v>220787</v>
+        <v>103001</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I288" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J288" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K288" t="inlineStr"/>
-      <c r="L288" t="inlineStr"/>
-      <c r="N288" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr"/>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P288" t="inlineStr">
         <is>
-          <t>kurravaara, T lm</t>
+          <t>Kurravaaravägen, Kiruna, T lm</t>
         </is>
       </c>
       <c r="Q288" t="n">
-        <v>724031</v>
+        <v>724020</v>
       </c>
       <c r="R288" t="n">
-        <v>7543433</v>
+        <v>7543442</v>
       </c>
       <c r="S288" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T288" t="inlineStr">
         <is>
@@ -30747,12 +30729,22 @@
       </c>
       <c r="Y288" t="inlineStr">
         <is>
-          <t>2020-08-12</t>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="Z288" t="inlineStr">
+        <is>
+          <t>19:46</t>
         </is>
       </c>
       <c r="AA288" t="inlineStr">
         <is>
-          <t>2020-08-12</t>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AB288" t="inlineStr">
+        <is>
+          <t>19:46</t>
         </is>
       </c>
       <c r="AD288" t="b">
@@ -30761,51 +30753,50 @@
       <c r="AE288" t="b">
         <v>0</v>
       </c>
-      <c r="AF288" t="inlineStr"/>
       <c r="AG288" t="b">
         <v>0</v>
       </c>
       <c r="AT288" t="inlineStr"/>
       <c r="AW288" t="inlineStr">
         <is>
-          <t>Albin Belsing</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX288" t="inlineStr">
         <is>
-          <t>Albin Belsing</t>
+          <t>per-erik mukka, Robert Flygare</t>
         </is>
       </c>
       <c r="AY288" t="inlineStr"/>
       <c r="AZ288" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/87676926</t>
+          <t>https://artportalen.se/Sighting/117357759</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>95153649</v>
+        <v>111591780</v>
       </c>
       <c r="B289" t="n">
-        <v>99118</v>
+        <v>99120</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E289" t="n">
-        <v>220787</v>
+        <v>219811</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -30813,26 +30804,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I289" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K289" t="inlineStr"/>
+      <c r="I289" t="inlineStr"/>
+      <c r="J289" t="inlineStr"/>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L289" t="inlineStr"/>
+      <c r="N289" t="inlineStr"/>
       <c r="P289" t="inlineStr">
         <is>
-          <t>Kurravaaravägen, Kiruna, T lm</t>
+          <t>Kurravaaravägen 60, Kiruna, Kurravaaravägen 60, Kiruna, T lm</t>
         </is>
       </c>
       <c r="Q289" t="n">
-        <v>724068</v>
+        <v>723842</v>
       </c>
       <c r="R289" t="n">
-        <v>7543343</v>
+        <v>7544794</v>
       </c>
       <c r="S289" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T289" t="inlineStr">
         <is>
@@ -30856,22 +30849,12 @@
       </c>
       <c r="Y289" t="inlineStr">
         <is>
-          <t>2021-07-29</t>
-        </is>
-      </c>
-      <c r="Z289" t="inlineStr">
-        <is>
-          <t>14:11</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="AA289" t="inlineStr">
         <is>
-          <t>2021-07-29</t>
-        </is>
-      </c>
-      <c r="AB289" t="inlineStr">
-        <is>
-          <t>14:11</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="AD289" t="b">
@@ -30880,6 +30863,7 @@
       <c r="AE289" t="b">
         <v>0</v>
       </c>
+      <c r="AF289" t="inlineStr"/>
       <c r="AG289" t="b">
         <v>0</v>
       </c>
@@ -30891,19 +30875,19 @@
       </c>
       <c r="AX289" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>per-erik mukka, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY289" t="inlineStr"/>
       <c r="AZ289" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95153649</t>
+          <t>https://artportalen.se/Sighting/111591780</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>95153730</v>
+        <v>87676926</v>
       </c>
       <c r="B290" t="n">
         <v>99118</v>
@@ -30933,24 +30917,30 @@
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K290" t="inlineStr"/>
       <c r="L290" t="inlineStr"/>
+      <c r="N290" t="inlineStr"/>
       <c r="P290" t="inlineStr">
         <is>
-          <t>Kurravaaravägen, Kiruna, T lm</t>
+          <t>kurravaara, T lm</t>
         </is>
       </c>
       <c r="Q290" t="n">
-        <v>724057</v>
+        <v>724031</v>
       </c>
       <c r="R290" t="n">
-        <v>7543346</v>
+        <v>7543433</v>
       </c>
       <c r="S290" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T290" t="inlineStr">
         <is>
@@ -30974,22 +30964,12 @@
       </c>
       <c r="Y290" t="inlineStr">
         <is>
-          <t>2021-07-29</t>
-        </is>
-      </c>
-      <c r="Z290" t="inlineStr">
-        <is>
-          <t>14:16</t>
+          <t>2020-08-12</t>
         </is>
       </c>
       <c r="AA290" t="inlineStr">
         <is>
-          <t>2021-07-29</t>
-        </is>
-      </c>
-      <c r="AB290" t="inlineStr">
-        <is>
-          <t>14:16</t>
+          <t>2020-08-12</t>
         </is>
       </c>
       <c r="AD290" t="b">
@@ -30998,30 +30978,31 @@
       <c r="AE290" t="b">
         <v>0</v>
       </c>
+      <c r="AF290" t="inlineStr"/>
       <c r="AG290" t="b">
         <v>0</v>
       </c>
       <c r="AT290" t="inlineStr"/>
       <c r="AW290" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Albin Belsing</t>
         </is>
       </c>
       <c r="AX290" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Albin Belsing</t>
         </is>
       </c>
       <c r="AY290" t="inlineStr"/>
       <c r="AZ290" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95153730</t>
+          <t>https://artportalen.se/Sighting/87676926</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>95153759</v>
+        <v>95153649</v>
       </c>
       <c r="B291" t="n">
         <v>99118</v>
@@ -31051,7 +31032,7 @@
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K291" t="inlineStr"/>
@@ -31062,10 +31043,10 @@
         </is>
       </c>
       <c r="Q291" t="n">
-        <v>724041</v>
+        <v>724068</v>
       </c>
       <c r="R291" t="n">
-        <v>7543391</v>
+        <v>7543343</v>
       </c>
       <c r="S291" t="n">
         <v>25</v>
@@ -31097,7 +31078,7 @@
       </c>
       <c r="Z291" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA291" t="inlineStr">
@@ -31107,7 +31088,7 @@
       </c>
       <c r="AB291" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD291" t="b">
@@ -31133,13 +31114,13 @@
       <c r="AY291" t="inlineStr"/>
       <c r="AZ291" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95153759</t>
+          <t>https://artportalen.se/Sighting/95153649</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>95153809</v>
+        <v>95153730</v>
       </c>
       <c r="B292" t="n">
         <v>99118</v>
@@ -31167,7 +31148,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I292" t="inlineStr"/>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="K292" t="inlineStr"/>
       <c r="L292" t="inlineStr"/>
       <c r="P292" t="inlineStr">
@@ -31176,10 +31161,10 @@
         </is>
       </c>
       <c r="Q292" t="n">
-        <v>724024</v>
+        <v>724057</v>
       </c>
       <c r="R292" t="n">
-        <v>7543435</v>
+        <v>7543346</v>
       </c>
       <c r="S292" t="n">
         <v>25</v>
@@ -31211,7 +31196,7 @@
       </c>
       <c r="Z292" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA292" t="inlineStr">
@@ -31221,7 +31206,7 @@
       </c>
       <c r="AB292" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD292" t="b">
@@ -31247,13 +31232,13 @@
       <c r="AY292" t="inlineStr"/>
       <c r="AZ292" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95153809</t>
+          <t>https://artportalen.se/Sighting/95153730</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>95153843</v>
+        <v>95153759</v>
       </c>
       <c r="B293" t="n">
         <v>99118</v>
@@ -31283,7 +31268,7 @@
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K293" t="inlineStr"/>
@@ -31294,10 +31279,10 @@
         </is>
       </c>
       <c r="Q293" t="n">
-        <v>724022</v>
+        <v>724041</v>
       </c>
       <c r="R293" t="n">
-        <v>7543454</v>
+        <v>7543391</v>
       </c>
       <c r="S293" t="n">
         <v>25</v>
@@ -31329,7 +31314,7 @@
       </c>
       <c r="Z293" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA293" t="inlineStr">
@@ -31339,7 +31324,7 @@
       </c>
       <c r="AB293" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD293" t="b">
@@ -31365,13 +31350,13 @@
       <c r="AY293" t="inlineStr"/>
       <c r="AZ293" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95153843</t>
+          <t>https://artportalen.se/Sighting/95153759</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>95153900</v>
+        <v>95153809</v>
       </c>
       <c r="B294" t="n">
         <v>99118</v>
@@ -31399,11 +31384,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I294" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="I294" t="inlineStr"/>
       <c r="K294" t="inlineStr"/>
       <c r="L294" t="inlineStr"/>
       <c r="P294" t="inlineStr">
@@ -31412,10 +31393,10 @@
         </is>
       </c>
       <c r="Q294" t="n">
-        <v>724016</v>
+        <v>724024</v>
       </c>
       <c r="R294" t="n">
-        <v>7543475</v>
+        <v>7543435</v>
       </c>
       <c r="S294" t="n">
         <v>25</v>
@@ -31447,7 +31428,7 @@
       </c>
       <c r="Z294" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA294" t="inlineStr">
@@ -31457,7 +31438,7 @@
       </c>
       <c r="AB294" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD294" t="b">
@@ -31483,43 +31464,43 @@
       <c r="AY294" t="inlineStr"/>
       <c r="AZ294" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95153900</t>
+          <t>https://artportalen.se/Sighting/95153809</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>94564368</v>
+        <v>95153843</v>
       </c>
       <c r="B295" t="n">
-        <v>106229</v>
+        <v>99118</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E295" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K295" t="inlineStr"/>
@@ -31530,10 +31511,10 @@
         </is>
       </c>
       <c r="Q295" t="n">
-        <v>724020</v>
+        <v>724022</v>
       </c>
       <c r="R295" t="n">
-        <v>7543442</v>
+        <v>7543454</v>
       </c>
       <c r="S295" t="n">
         <v>25</v>
@@ -31560,22 +31541,22 @@
       </c>
       <c r="Y295" t="inlineStr">
         <is>
-          <t>2021-06-29</t>
+          <t>2021-07-29</t>
         </is>
       </c>
       <c r="Z295" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA295" t="inlineStr">
         <is>
-          <t>2021-06-29</t>
+          <t>2021-07-29</t>
         </is>
       </c>
       <c r="AB295" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD295" t="b">
@@ -31600,6 +31581,242 @@
       </c>
       <c r="AY295" t="inlineStr"/>
       <c r="AZ295" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95153843</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="n">
+        <v>95153900</v>
+      </c>
+      <c r="B296" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E296" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr"/>
+      <c r="L296" t="inlineStr"/>
+      <c r="P296" t="inlineStr">
+        <is>
+          <t>Kurravaaravägen, Kiruna, T lm</t>
+        </is>
+      </c>
+      <c r="Q296" t="n">
+        <v>724016</v>
+      </c>
+      <c r="R296" t="n">
+        <v>7543475</v>
+      </c>
+      <c r="S296" t="n">
+        <v>25</v>
+      </c>
+      <c r="T296" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U296" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V296" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W296" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y296" t="inlineStr">
+        <is>
+          <t>2021-07-29</t>
+        </is>
+      </c>
+      <c r="Z296" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AA296" t="inlineStr">
+        <is>
+          <t>2021-07-29</t>
+        </is>
+      </c>
+      <c r="AB296" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AD296" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE296" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG296" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT296" t="inlineStr"/>
+      <c r="AW296" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX296" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY296" t="inlineStr"/>
+      <c r="AZ296" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95153900</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="n">
+        <v>94564368</v>
+      </c>
+      <c r="B297" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E297" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr"/>
+      <c r="L297" t="inlineStr"/>
+      <c r="P297" t="inlineStr">
+        <is>
+          <t>Kurravaaravägen, Kiruna, T lm</t>
+        </is>
+      </c>
+      <c r="Q297" t="n">
+        <v>724020</v>
+      </c>
+      <c r="R297" t="n">
+        <v>7543442</v>
+      </c>
+      <c r="S297" t="n">
+        <v>25</v>
+      </c>
+      <c r="T297" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U297" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V297" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W297" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y297" t="inlineStr">
+        <is>
+          <t>2021-06-29</t>
+        </is>
+      </c>
+      <c r="Z297" t="inlineStr">
+        <is>
+          <t>19:56</t>
+        </is>
+      </c>
+      <c r="AA297" t="inlineStr">
+        <is>
+          <t>2021-06-29</t>
+        </is>
+      </c>
+      <c r="AB297" t="inlineStr">
+        <is>
+          <t>19:56</t>
+        </is>
+      </c>
+      <c r="AD297" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE297" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG297" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT297" t="inlineStr"/>
+      <c r="AW297" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX297" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY297" t="inlineStr"/>
+      <c r="AZ297" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/94564368</t>
         </is>
@@ -31901,6 +32118,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ293" r:id="rId292"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ294" r:id="rId293"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ295" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ296" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ297" r:id="rId296"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -24575,7 +24575,7 @@
         <v>135650446</v>
       </c>
       <c r="B229" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -24686,7 +24686,7 @@
         <v>135651394</v>
       </c>
       <c r="B230" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -24575,7 +24575,7 @@
         <v>135650446</v>
       </c>
       <c r="B229" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -24686,7 +24686,7 @@
         <v>135651394</v>
       </c>
       <c r="B230" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -24575,7 +24575,7 @@
         <v>135650446</v>
       </c>
       <c r="B229" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -24686,7 +24686,7 @@
         <v>135651394</v>
       </c>
       <c r="B230" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -24575,7 +24575,7 @@
         <v>135650446</v>
       </c>
       <c r="B229" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -24686,7 +24686,7 @@
         <v>135651394</v>
       </c>
       <c r="B230" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -24575,7 +24575,7 @@
         <v>135650446</v>
       </c>
       <c r="B229" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -24686,7 +24686,7 @@
         <v>135651394</v>
       </c>
       <c r="B230" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>

--- a/artfynd/A 10563-2022 artfynd.xlsx
+++ b/artfynd/A 10563-2022 artfynd.xlsx
@@ -24575,7 +24575,7 @@
         <v>135650446</v>
       </c>
       <c r="B229" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -24686,7 +24686,7 @@
         <v>135651394</v>
       </c>
       <c r="B230" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
